--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A715BF21-69AF-436F-A41F-07B3675F17B3}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E0A3D03-F6B8-4274-AC69-C078CD732997}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -515,7 +515,23 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -794,8 +810,8 @@
   <dimension ref="A1:R63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="8" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -814,13 +830,13 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -870,19 +886,19 @@
       <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -923,19 +939,19 @@
       <c r="E3" t="s">
         <v>31</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" t="s">
         <v>33</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -976,19 +992,19 @@
       <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" t="s">
         <v>33</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K4" s="1" t="s">
@@ -1032,19 +1048,19 @@
       <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>6</v>
       </c>
       <c r="I5" t="s">
         <v>33</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -1088,19 +1104,19 @@
       <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>7</v>
       </c>
       <c r="I6" t="s">
         <v>33</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -1144,19 +1160,19 @@
       <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>8</v>
       </c>
       <c r="I7" t="s">
         <v>33</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -1200,19 +1216,19 @@
       <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>33</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -1256,19 +1272,19 @@
       <c r="E9" t="s">
         <v>31</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>15</v>
       </c>
       <c r="I9" t="s">
         <v>33</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -1312,19 +1328,19 @@
       <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10">
         <v>15</v>
       </c>
       <c r="I10" t="s">
         <v>33</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -1368,19 +1384,19 @@
       <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>16</v>
       </c>
       <c r="I11" t="s">
         <v>33</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -1424,19 +1440,19 @@
       <c r="E12" t="s">
         <v>31</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>20</v>
       </c>
       <c r="I12" t="s">
         <v>33</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -1480,19 +1496,19 @@
       <c r="E13" t="s">
         <v>31</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>21</v>
       </c>
       <c r="I13" t="s">
         <v>33</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -1536,19 +1552,19 @@
       <c r="E14" t="s">
         <v>31</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14">
         <v>22</v>
       </c>
       <c r="I14" t="s">
         <v>33</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -1592,19 +1608,19 @@
       <c r="E15" t="s">
         <v>31</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" t="s">
         <v>33</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -1648,19 +1664,19 @@
       <c r="E16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16">
         <v>28</v>
       </c>
       <c r="I16" t="s">
         <v>33</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1704,19 +1720,19 @@
       <c r="E17" t="s">
         <v>31</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17">
         <v>28</v>
       </c>
       <c r="I17" t="s">
         <v>33</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -1760,19 +1776,19 @@
       <c r="E18" t="s">
         <v>31</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18">
         <v>28</v>
       </c>
       <c r="I18" t="s">
         <v>33</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K18" s="1" t="s">
@@ -1816,19 +1832,19 @@
       <c r="E19" t="s">
         <v>31</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19">
         <v>3</v>
       </c>
       <c r="I19" t="s">
         <v>24</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -1872,19 +1888,19 @@
       <c r="E20" t="s">
         <v>31</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20">
         <v>4</v>
       </c>
       <c r="I20" t="s">
         <v>24</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -1928,19 +1944,19 @@
       <c r="E21" t="s">
         <v>31</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21">
         <v>5</v>
       </c>
       <c r="I21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -1984,19 +2000,19 @@
       <c r="E22" t="s">
         <v>31</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22">
         <v>6</v>
       </c>
       <c r="I22" t="s">
         <v>24</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K22" s="1" t="s">
@@ -2040,19 +2056,19 @@
       <c r="E23" t="s">
         <v>31</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23">
         <v>7</v>
       </c>
       <c r="I23" t="s">
         <v>24</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K23" s="1" t="s">
@@ -2096,19 +2112,19 @@
       <c r="E24" t="s">
         <v>31</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24">
         <v>7</v>
       </c>
       <c r="I24" t="s">
         <v>24</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K24" s="1" t="s">
@@ -2152,19 +2168,19 @@
       <c r="E25" t="s">
         <v>31</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25">
         <v>10</v>
       </c>
       <c r="I25" t="s">
         <v>24</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K25" s="1" t="s">
@@ -2208,19 +2224,19 @@
       <c r="E26" t="s">
         <v>21</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26">
         <v>11</v>
       </c>
       <c r="I26" t="s">
         <v>24</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K26" s="1" t="s">
@@ -2264,19 +2280,19 @@
       <c r="E27" t="s">
         <v>31</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27">
         <v>11</v>
       </c>
       <c r="I27" t="s">
         <v>24</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K27" s="1" t="s">
@@ -2320,19 +2336,19 @@
       <c r="E28" t="s">
         <v>93</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28">
         <v>13</v>
       </c>
       <c r="I28" t="s">
         <v>24</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K28" s="1" t="s">
@@ -2376,19 +2392,19 @@
       <c r="E29" t="s">
         <v>31</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29">
         <v>13</v>
       </c>
       <c r="I29" t="s">
         <v>24</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K29" s="1" t="s">
@@ -2432,19 +2448,19 @@
       <c r="E30" t="s">
         <v>93</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30">
         <v>14</v>
       </c>
       <c r="I30" t="s">
         <v>24</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K30" s="1" t="s">
@@ -2488,19 +2504,19 @@
       <c r="E31" t="s">
         <v>31</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31">
         <v>17</v>
       </c>
       <c r="I31" t="s">
         <v>24</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K31" s="1" t="s">
@@ -2544,19 +2560,19 @@
       <c r="E32" t="s">
         <v>31</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32">
         <v>18</v>
       </c>
       <c r="I32" t="s">
         <v>24</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K32" s="1" t="s">
@@ -2600,19 +2616,19 @@
       <c r="E33" t="s">
         <v>93</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33">
         <v>19</v>
       </c>
       <c r="I33" t="s">
         <v>24</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K33" s="1" t="s">
@@ -2656,19 +2672,19 @@
       <c r="E34" t="s">
         <v>31</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34">
         <v>19</v>
       </c>
       <c r="I34" t="s">
         <v>24</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K34" s="1" t="s">
@@ -2712,19 +2728,19 @@
       <c r="E35" t="s">
         <v>93</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35">
         <v>20</v>
       </c>
       <c r="I35" t="s">
         <v>24</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K35" s="1" t="s">
@@ -2768,19 +2784,19 @@
       <c r="E36" t="s">
         <v>93</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36">
         <v>21</v>
       </c>
       <c r="I36" t="s">
         <v>24</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K36" s="1" t="s">
@@ -2824,19 +2840,19 @@
       <c r="E37" t="s">
         <v>93</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37">
         <v>21</v>
       </c>
       <c r="I37" t="s">
         <v>24</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K37" s="1" t="s">
@@ -2880,19 +2896,19 @@
       <c r="E38" t="s">
         <v>93</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38">
         <v>21</v>
       </c>
       <c r="I38" t="s">
         <v>24</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K38" s="1" t="s">
@@ -2936,19 +2952,19 @@
       <c r="E39" t="s">
         <v>93</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39">
         <v>21</v>
       </c>
       <c r="I39" t="s">
         <v>24</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K39" s="1" t="s">
@@ -2992,19 +3008,19 @@
       <c r="E40" t="s">
         <v>93</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40">
         <v>21</v>
       </c>
       <c r="I40" t="s">
         <v>24</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K40" s="1" t="s">
@@ -3048,19 +3064,19 @@
       <c r="E41" t="s">
         <v>93</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41">
         <v>21</v>
       </c>
       <c r="I41" t="s">
         <v>24</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K41" s="1" t="s">
@@ -3104,19 +3120,19 @@
       <c r="E42" t="s">
         <v>31</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42">
         <v>21</v>
       </c>
       <c r="I42" t="s">
         <v>24</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K42" s="1" t="s">
@@ -3160,19 +3176,19 @@
       <c r="E43" t="s">
         <v>31</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43">
         <v>24</v>
       </c>
       <c r="I43" t="s">
         <v>24</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K43" s="1" t="s">
@@ -3216,19 +3232,19 @@
       <c r="E44" t="s">
         <v>21</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="1">
+      <c r="H44">
         <v>25</v>
       </c>
       <c r="I44" t="s">
         <v>24</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K44" s="1" t="s">
@@ -3272,19 +3288,19 @@
       <c r="E45" t="s">
         <v>21</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="1">
+      <c r="H45">
         <v>25</v>
       </c>
       <c r="I45" t="s">
         <v>24</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K45" s="1" t="s">
@@ -3328,19 +3344,19 @@
       <c r="E46" t="s">
         <v>31</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H46" s="1">
+      <c r="H46">
         <v>25</v>
       </c>
       <c r="I46" t="s">
         <v>24</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K46" s="1" t="s">
@@ -3384,19 +3400,19 @@
       <c r="E47" t="s">
         <v>31</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H47" s="1">
+      <c r="H47">
         <v>25</v>
       </c>
       <c r="I47" t="s">
         <v>24</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K47" s="1" t="s">
@@ -3440,19 +3456,19 @@
       <c r="E48" t="s">
         <v>93</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H48">
         <v>27</v>
       </c>
       <c r="I48" t="s">
         <v>24</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K48" s="1" t="s">
@@ -3496,19 +3512,19 @@
       <c r="E49" t="s">
         <v>31</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H49">
         <v>27</v>
       </c>
       <c r="I49" t="s">
         <v>24</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K49" s="1" t="s">
@@ -3552,19 +3568,19 @@
       <c r="E50" t="s">
         <v>93</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H50">
         <v>28</v>
       </c>
       <c r="I50" t="s">
         <v>24</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K50" s="1" t="s">
@@ -3608,19 +3624,19 @@
       <c r="E51" t="s">
         <v>31</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
         <v>123</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K51" s="1" t="s">
@@ -3664,19 +3680,19 @@
       <c r="E52" t="s">
         <v>93</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H52">
         <v>3</v>
       </c>
       <c r="I52" t="s">
         <v>123</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K52" s="1" t="s">
@@ -3720,19 +3736,19 @@
       <c r="E53" t="s">
         <v>31</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H53">
         <v>3</v>
       </c>
       <c r="I53" t="s">
         <v>123</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K53" s="1" t="s">
@@ -3776,19 +3792,19 @@
       <c r="E54" t="s">
         <v>31</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H54">
         <v>4</v>
       </c>
       <c r="I54" t="s">
         <v>123</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K54" s="1" t="s">
@@ -3832,19 +3848,19 @@
       <c r="E55" t="s">
         <v>31</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H55">
         <v>4</v>
       </c>
       <c r="I55" t="s">
         <v>123</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K55" s="1" t="s">
@@ -3888,19 +3904,19 @@
       <c r="E56" t="s">
         <v>31</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H56">
         <v>4</v>
       </c>
       <c r="I56" t="s">
         <v>123</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K56" s="1" t="s">
@@ -3944,19 +3960,19 @@
       <c r="E57" t="s">
         <v>93</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H57">
         <v>8</v>
       </c>
       <c r="I57" t="s">
         <v>123</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K57" s="1" t="s">
@@ -4000,19 +4016,19 @@
       <c r="E58" t="s">
         <v>31</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58">
         <v>8</v>
       </c>
       <c r="I58" t="s">
         <v>123</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K58" s="1" t="s">
@@ -4056,19 +4072,19 @@
       <c r="E59" t="s">
         <v>93</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59">
         <v>9</v>
       </c>
       <c r="I59" t="s">
         <v>123</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K59" s="1" t="s">
@@ -4112,19 +4128,19 @@
       <c r="E60" t="s">
         <v>31</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H60" s="1">
+      <c r="H60">
         <v>9</v>
       </c>
       <c r="I60" t="s">
         <v>123</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K60" s="1" t="s">
@@ -4168,19 +4184,19 @@
       <c r="E61" t="s">
         <v>31</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H61">
         <v>10</v>
       </c>
       <c r="I61" t="s">
         <v>123</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K61" s="1" t="s">
@@ -4224,13 +4240,13 @@
       <c r="E62" t="s">
         <v>21</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="1">
+      <c r="H62">
         <v>11</v>
       </c>
       <c r="I62" t="s">
@@ -4239,7 +4255,7 @@
       <c r="J62" t="s">
         <v>25</v>
       </c>
-      <c r="K62" t="s">
+      <c r="K62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L62" s="1">
@@ -4280,13 +4296,13 @@
       <c r="E63" t="s">
         <v>31</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H63" s="1">
+      <c r="H63">
         <v>11</v>
       </c>
       <c r="I63" t="s">
@@ -4295,7 +4311,7 @@
       <c r="J63" t="s">
         <v>25</v>
       </c>
-      <c r="K63" t="s">
+      <c r="K63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L63" s="1">
@@ -4321,7 +4337,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5030,31 +5046,31 @@
         <v>29</v>
       </c>
       <c r="D19">
-        <v>115.85599999999999</v>
+        <v>144.655</v>
       </c>
       <c r="E19">
-        <v>69.57874000000001</v>
+        <v>91.65552000000001</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G19">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H19">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I19">
-        <v>0.46666666666666667</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="J19">
-        <v>0.9555555555555556</v>
+        <v>0.98333333333333328</v>
       </c>
       <c r="K19">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L19">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -5071,28 +5087,28 @@
         <v>84</v>
       </c>
       <c r="E20">
-        <v>54.136720000000004</v>
+        <v>64.229770000000002</v>
       </c>
       <c r="F20">
+        <v>40</v>
+      </c>
+      <c r="G20">
+        <v>60</v>
+      </c>
+      <c r="H20">
         <v>30</v>
       </c>
-      <c r="G20">
-        <v>45</v>
-      </c>
-      <c r="H20">
-        <v>24</v>
-      </c>
       <c r="I20">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J20">
-        <v>0.75555555555555554</v>
+        <v>0.71666666666666667</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L20">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -5109,28 +5125,28 @@
         <v>84</v>
       </c>
       <c r="E21">
-        <v>120.63414</v>
+        <v>141.77701999999999</v>
       </c>
       <c r="F21">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G21">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>0.21052631578947367</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="J21">
-        <v>0.97777777777777775</v>
+        <v>0.98333333333333328</v>
       </c>
       <c r="K21">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L21">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -5258,15 +5274,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -5527,6 +5534,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5539,14 +5555,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5565,6 +5573,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E0A3D03-F6B8-4274-AC69-C078CD732997}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0C5CB48-C00C-4E73-BF13-F7C4D8CE25B7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$E$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="145">
   <si>
     <t>Usuário</t>
   </si>
@@ -467,6 +467,15 @@
   </si>
   <si>
     <t>VICENTE JOAQUIM DOS SANTOS</t>
+  </si>
+  <si>
+    <t>MARIA TEREZA FREIRE BRAGA</t>
+  </si>
+  <si>
+    <t>Danilo de Lima Santos</t>
+  </si>
+  <si>
+    <t>FLAVIO DA SILVA RIBEIRO</t>
   </si>
 </sst>
 </file>
@@ -515,23 +524,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2" tint="-0.24994659260841701"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -807,11 +800,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -827,13 +820,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -883,19 +876,19 @@
       <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>54</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -936,19 +929,19 @@
       <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>54</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -989,19 +982,19 @@
       <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>43</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1045,19 +1038,19 @@
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>32</v>
       </c>
       <c r="H5">
         <v>6</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -1069,17 +1062,17 @@
       <c r="L5" s="1">
         <v>46209</v>
       </c>
-      <c r="M5">
-        <v>587363</v>
+      <c r="M5" t="s">
+        <v>139</v>
       </c>
       <c r="N5" t="s">
-        <v>138</v>
-      </c>
-      <c r="O5">
-        <v>7.85</v>
+        <v>139</v>
+      </c>
+      <c r="O5" t="s">
+        <v>139</v>
       </c>
       <c r="P5" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="s">
         <v>28</v>
@@ -1101,19 +1094,19 @@
       <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>32</v>
       </c>
       <c r="H6">
         <v>7</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1157,19 +1150,19 @@
       <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
       <c r="H7">
         <v>8</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1213,19 +1206,19 @@
       <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>32</v>
       </c>
       <c r="H8">
         <v>10</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -1269,19 +1262,19 @@
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>40</v>
       </c>
       <c r="H9">
         <v>15</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -1325,19 +1318,19 @@
       <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>32</v>
       </c>
       <c r="H10">
         <v>15</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -1381,19 +1374,19 @@
       <c r="D11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>32</v>
       </c>
       <c r="H11">
         <v>16</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -1437,19 +1430,19 @@
       <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>43</v>
       </c>
       <c r="H12">
         <v>20</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -1493,19 +1486,19 @@
       <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>32</v>
       </c>
       <c r="H13">
         <v>21</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -1549,19 +1542,19 @@
       <c r="D14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>32</v>
       </c>
       <c r="H14">
         <v>22</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -1583,7 +1576,7 @@
         <v>11.66</v>
       </c>
       <c r="P14" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q14" t="s">
         <v>28</v>
@@ -1605,19 +1598,19 @@
       <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>32</v>
       </c>
       <c r="H15">
         <v>24</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -1661,19 +1654,19 @@
       <c r="D16" t="s">
         <v>20</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>32</v>
       </c>
       <c r="H16">
         <v>28</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -1717,19 +1710,19 @@
       <c r="D17" t="s">
         <v>20</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>43</v>
       </c>
       <c r="H17">
         <v>28</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -1773,19 +1766,19 @@
       <c r="D18" t="s">
         <v>20</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>23</v>
       </c>
       <c r="H18">
         <v>28</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -1829,19 +1822,19 @@
       <c r="D19" t="s">
         <v>20</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>43</v>
       </c>
       <c r="H19">
         <v>3</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J19" s="1" t="s">
@@ -1885,19 +1878,19 @@
       <c r="D20" t="s">
         <v>20</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>32</v>
       </c>
       <c r="H20">
         <v>4</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J20" s="1" t="s">
@@ -1941,19 +1934,19 @@
       <c r="D21" t="s">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>43</v>
       </c>
       <c r="H21">
         <v>5</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
@@ -1997,19 +1990,19 @@
       <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>32</v>
       </c>
       <c r="H22">
         <v>6</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
@@ -2053,19 +2046,19 @@
       <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>32</v>
       </c>
       <c r="H23">
         <v>7</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2109,19 +2102,19 @@
       <c r="D24" t="s">
         <v>20</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>43</v>
       </c>
       <c r="H24">
         <v>7</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -2165,19 +2158,19 @@
       <c r="D25" t="s">
         <v>20</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>32</v>
       </c>
       <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
@@ -2221,19 +2214,19 @@
       <c r="D26" t="s">
         <v>20</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" t="s">
         <v>23</v>
       </c>
       <c r="H26">
         <v>11</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
@@ -2277,19 +2270,19 @@
       <c r="D27" t="s">
         <v>20</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" t="s">
         <v>32</v>
       </c>
       <c r="H27">
         <v>11</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J27" s="1" t="s">
@@ -2333,19 +2326,19 @@
       <c r="D28" t="s">
         <v>20</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" t="s">
         <v>95</v>
       </c>
       <c r="H28">
         <v>13</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J28" s="1" t="s">
@@ -2369,8 +2362,8 @@
       <c r="P28" t="s">
         <v>35</v>
       </c>
-      <c r="Q28" t="s">
-        <v>28</v>
+      <c r="Q28" t="e">
+        <v>#REF!</v>
       </c>
       <c r="R28" t="s">
         <v>26</v>
@@ -2389,19 +2382,19 @@
       <c r="D29" t="s">
         <v>20</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" t="s">
         <v>43</v>
       </c>
       <c r="H29">
         <v>13</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J29" s="1" t="s">
@@ -2423,7 +2416,7 @@
         <v>91.5</v>
       </c>
       <c r="P29" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q29" t="s">
         <v>28</v>
@@ -2445,19 +2438,19 @@
       <c r="D30" t="s">
         <v>20</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" t="s">
         <v>95</v>
       </c>
       <c r="H30">
         <v>14</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J30" s="1" t="s">
@@ -2501,19 +2494,19 @@
       <c r="D31" t="s">
         <v>20</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" t="s">
         <v>32</v>
       </c>
       <c r="H31">
         <v>17</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J31" s="1" t="s">
@@ -2557,19 +2550,19 @@
       <c r="D32" t="s">
         <v>20</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" t="s">
         <v>32</v>
       </c>
       <c r="H32">
         <v>18</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2613,19 +2606,19 @@
       <c r="D33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" t="s">
         <v>95</v>
       </c>
       <c r="H33">
         <v>19</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J33" s="1" t="s">
@@ -2669,19 +2662,19 @@
       <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" t="s">
         <v>43</v>
       </c>
       <c r="H34">
         <v>19</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J34" s="1" t="s">
@@ -2725,19 +2718,19 @@
       <c r="D35" t="s">
         <v>20</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" t="s">
         <v>95</v>
       </c>
       <c r="H35">
         <v>20</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J35" s="1" t="s">
@@ -2781,19 +2774,19 @@
       <c r="D36" t="s">
         <v>20</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" t="s">
         <v>95</v>
       </c>
       <c r="H36">
         <v>21</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J36" s="1" t="s">
@@ -2837,19 +2830,19 @@
       <c r="D37" t="s">
         <v>20</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" t="s">
         <v>95</v>
       </c>
       <c r="H37">
         <v>21</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J37" s="1" t="s">
@@ -2893,19 +2886,19 @@
       <c r="D38" t="s">
         <v>20</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" t="s">
         <v>95</v>
       </c>
       <c r="H38">
         <v>21</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J38" s="1" t="s">
@@ -2949,19 +2942,19 @@
       <c r="D39" t="s">
         <v>20</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" t="s">
         <v>108</v>
       </c>
       <c r="H39">
         <v>21</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J39" s="1" t="s">
@@ -3005,19 +2998,19 @@
       <c r="D40" t="s">
         <v>20</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" t="s">
         <v>95</v>
       </c>
       <c r="H40">
         <v>21</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J40" s="1" t="s">
@@ -3061,19 +3054,19 @@
       <c r="D41" t="s">
         <v>20</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" t="s">
         <v>95</v>
       </c>
       <c r="H41">
         <v>21</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J41" s="1" t="s">
@@ -3117,19 +3110,19 @@
       <c r="D42" t="s">
         <v>20</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" t="s">
         <v>32</v>
       </c>
       <c r="H42">
         <v>21</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J42" s="1" t="s">
@@ -3173,19 +3166,19 @@
       <c r="D43" t="s">
         <v>20</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" t="s">
         <v>32</v>
       </c>
       <c r="H43">
         <v>24</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J43" s="1" t="s">
@@ -3229,19 +3222,19 @@
       <c r="D44" t="s">
         <v>20</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" t="s">
         <v>23</v>
       </c>
       <c r="H44">
         <v>25</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J44" s="1" t="s">
@@ -3285,19 +3278,19 @@
       <c r="D45" t="s">
         <v>20</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" t="s">
         <v>23</v>
       </c>
       <c r="H45">
         <v>25</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J45" s="1" t="s">
@@ -3341,19 +3334,19 @@
       <c r="D46" t="s">
         <v>20</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" t="s">
         <v>43</v>
       </c>
       <c r="H46">
         <v>25</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J46" s="1" t="s">
@@ -3397,19 +3390,19 @@
       <c r="D47" t="s">
         <v>20</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" t="s">
         <v>32</v>
       </c>
       <c r="H47">
         <v>25</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J47" s="1" t="s">
@@ -3453,19 +3446,19 @@
       <c r="D48" t="s">
         <v>20</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" t="s">
         <v>95</v>
       </c>
       <c r="H48">
         <v>27</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J48" s="1" t="s">
@@ -3509,19 +3502,19 @@
       <c r="D49" t="s">
         <v>20</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" t="s">
         <v>32</v>
       </c>
       <c r="H49">
         <v>27</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J49" s="1" t="s">
@@ -3565,19 +3558,19 @@
       <c r="D50" t="s">
         <v>20</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" t="s">
         <v>95</v>
       </c>
       <c r="H50">
         <v>28</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="J50" s="1" t="s">
@@ -3621,19 +3614,19 @@
       <c r="D51" t="s">
         <v>20</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" t="s">
         <v>32</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J51" s="1" t="s">
@@ -3677,19 +3670,19 @@
       <c r="D52" t="s">
         <v>20</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" t="s">
         <v>95</v>
       </c>
       <c r="H52">
         <v>3</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J52" s="1" t="s">
@@ -3733,19 +3726,19 @@
       <c r="D53" t="s">
         <v>20</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" t="s">
         <v>32</v>
       </c>
       <c r="H53">
         <v>3</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J53" s="1" t="s">
@@ -3789,19 +3782,19 @@
       <c r="D54" t="s">
         <v>20</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" t="s">
         <v>32</v>
       </c>
       <c r="H54">
         <v>4</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J54" s="1" t="s">
@@ -3845,19 +3838,19 @@
       <c r="D55" t="s">
         <v>20</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" t="s">
         <v>32</v>
       </c>
       <c r="H55">
         <v>4</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J55" s="1" t="s">
@@ -3901,19 +3894,19 @@
       <c r="D56" t="s">
         <v>20</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" t="s">
         <v>32</v>
       </c>
       <c r="H56">
         <v>4</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J56" s="1" t="s">
@@ -3957,19 +3950,19 @@
       <c r="D57" t="s">
         <v>20</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" t="s">
         <v>131</v>
       </c>
       <c r="H57">
         <v>8</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J57" s="1" t="s">
@@ -4013,19 +4006,19 @@
       <c r="D58" t="s">
         <v>20</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" t="s">
         <v>32</v>
       </c>
       <c r="H58">
         <v>8</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J58" s="1" t="s">
@@ -4069,19 +4062,19 @@
       <c r="D59" t="s">
         <v>20</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" t="s">
         <v>95</v>
       </c>
       <c r="H59">
         <v>9</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J59" s="1" t="s">
@@ -4125,19 +4118,19 @@
       <c r="D60" t="s">
         <v>20</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" t="s">
         <v>32</v>
       </c>
       <c r="H60">
         <v>9</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J60" s="1" t="s">
@@ -4181,19 +4174,19 @@
       <c r="D61" t="s">
         <v>20</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G61" t="s">
         <v>43</v>
       </c>
       <c r="H61">
         <v>10</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J61" s="1" t="s">
@@ -4237,13 +4230,13 @@
       <c r="D62" t="s">
         <v>20</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G62" t="s">
         <v>43</v>
       </c>
       <c r="H62">
@@ -4252,7 +4245,7 @@
       <c r="I62" t="s">
         <v>123</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K62" s="1" t="s">
@@ -4293,13 +4286,13 @@
       <c r="D63" t="s">
         <v>20</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G63" t="s">
         <v>32</v>
       </c>
       <c r="H63">
@@ -4308,7 +4301,7 @@
       <c r="I63" t="s">
         <v>123</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K63" s="1" t="s">
@@ -4336,8 +4329,120 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G64" t="s">
+        <v>95</v>
+      </c>
+      <c r="H64">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
+        <v>123</v>
+      </c>
+      <c r="J64" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="1">
+        <v>46279</v>
+      </c>
+      <c r="M64">
+        <v>619855</v>
+      </c>
+      <c r="N64" t="s">
+        <v>138</v>
+      </c>
+      <c r="O64">
+        <v>4.68</v>
+      </c>
+      <c r="P64" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>28</v>
+      </c>
+      <c r="R64" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>29</v>
+      </c>
+      <c r="B65" t="s">
+        <v>144</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
+        <v>123</v>
+      </c>
+      <c r="J65" t="s">
+        <v>25</v>
+      </c>
+      <c r="K65" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="1">
+        <v>46279</v>
+      </c>
+      <c r="M65">
+        <v>619980</v>
+      </c>
+      <c r="N65" t="s">
+        <v>138</v>
+      </c>
+      <c r="O65">
+        <v>8.5399999999999991</v>
+      </c>
+      <c r="P65" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>28</v>
+      </c>
+      <c r="R65" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5274,6 +5379,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -5534,27 +5659,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5571,23 +5695,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0C5CB48-C00C-4E73-BF13-F7C4D8CE25B7}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00BA7B5-7F1A-49B9-B06E-B5D5DFB96D59}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="155">
   <si>
     <t>Usuário</t>
   </si>
@@ -460,9 +460,6 @@
     <t>Em andamento</t>
   </si>
   <si>
-    <t>Não encontrado</t>
-  </si>
-  <si>
     <t>LAERCIO GOMES PINTO</t>
   </si>
   <si>
@@ -476,6 +473,39 @@
   </si>
   <si>
     <t>FLAVIO DA SILVA RIBEIRO</t>
+  </si>
+  <si>
+    <t>INELEGÍVEL - BAIXO CONSUMO</t>
+  </si>
+  <si>
+    <t>INELEGÍVEL CONCORRÊNCIA RETORNO 180 DIAS</t>
+  </si>
+  <si>
+    <t>RESTRIÇÕES DE CRÉDITO RECUSA DE GARANTIA</t>
+  </si>
+  <si>
+    <t>DECLINE MASSIVO – INATIVAÇÃO VENDEDOR</t>
+  </si>
+  <si>
+    <t>CNPJ BAIXADO OU INATIVO NA RF</t>
+  </si>
+  <si>
+    <t>RESTRIÇÕES DE CRÉDITO</t>
+  </si>
+  <si>
+    <t>INELEGÍVEL CONCORRÊNCIA RETORNO 90 DIAS</t>
+  </si>
+  <si>
+    <t>JUNIOR FARIA MOTA</t>
+  </si>
+  <si>
+    <t>ANA CLAUDIA COSTA RAMOS</t>
+  </si>
+  <si>
+    <t>Ana Paula Bandeira</t>
+  </si>
+  <si>
+    <t>semana2</t>
   </si>
 </sst>
 </file>
@@ -800,11 +830,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -817,13 +847,13 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -873,19 +903,19 @@
       <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
       <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -911,6 +941,9 @@
       </c>
       <c r="P2" t="s">
         <v>28</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>144</v>
       </c>
       <c r="R2" t="s">
         <v>26</v>
@@ -926,19 +959,19 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3" t="s">
         <v>54</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -964,6 +997,9 @@
       </c>
       <c r="P3" t="s">
         <v>28</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>145</v>
       </c>
       <c r="R3" t="s">
         <v>26</v>
@@ -979,19 +1015,19 @@
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
       <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -1016,9 +1052,6 @@
         <v>30.92</v>
       </c>
       <c r="P4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" t="s">
         <v>28</v>
       </c>
       <c r="R4" t="s">
@@ -1035,19 +1068,19 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>22</v>
       </c>
       <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>6</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -1062,19 +1095,16 @@
       <c r="L5" s="1">
         <v>46209</v>
       </c>
-      <c r="M5" t="s">
-        <v>139</v>
+      <c r="M5">
+        <v>587363</v>
       </c>
       <c r="N5" t="s">
-        <v>139</v>
-      </c>
-      <c r="O5" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O5">
+        <v>7.85</v>
       </c>
       <c r="P5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" t="s">
         <v>28</v>
       </c>
       <c r="R5" t="s">
@@ -1091,19 +1121,19 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>7</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1129,9 +1159,6 @@
       </c>
       <c r="P6" t="s">
         <v>35</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>28</v>
       </c>
       <c r="R6" t="s">
         <v>26</v>
@@ -1147,19 +1174,19 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1185,9 +1212,6 @@
       </c>
       <c r="P7" t="s">
         <v>35</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>28</v>
       </c>
       <c r="R7" t="s">
         <v>26</v>
@@ -1203,19 +1227,19 @@
       <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>22</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1241,9 +1265,6 @@
       </c>
       <c r="P8" t="s">
         <v>35</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>28</v>
       </c>
       <c r="R8" t="s">
         <v>26</v>
@@ -1259,19 +1280,19 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" t="s">
         <v>40</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>15</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1297,9 +1318,6 @@
       </c>
       <c r="P9" t="s">
         <v>35</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>28</v>
       </c>
       <c r="R9" t="s">
         <v>26</v>
@@ -1315,19 +1333,19 @@
       <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10" t="s">
         <v>32</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1353,9 +1371,6 @@
       </c>
       <c r="P10" t="s">
         <v>35</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>28</v>
       </c>
       <c r="R10" t="s">
         <v>26</v>
@@ -1371,19 +1386,19 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>22</v>
       </c>
       <c r="G11" t="s">
         <v>32</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1409,9 +1424,6 @@
       </c>
       <c r="P11" t="s">
         <v>35</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>28</v>
       </c>
       <c r="R11" t="s">
         <v>26</v>
@@ -1427,19 +1439,19 @@
       <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>22</v>
       </c>
       <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1454,19 +1466,16 @@
       <c r="L12" s="1">
         <v>46223</v>
       </c>
-      <c r="M12" t="s">
-        <v>139</v>
+      <c r="M12">
+        <v>594209</v>
       </c>
       <c r="N12" t="s">
-        <v>139</v>
-      </c>
-      <c r="O12" t="s">
-        <v>139</v>
+        <v>59</v>
+      </c>
+      <c r="O12">
+        <v>41.35</v>
       </c>
       <c r="P12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q12" t="s">
         <v>28</v>
       </c>
       <c r="R12" t="s">
@@ -1483,19 +1492,19 @@
       <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>21</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1510,19 +1519,16 @@
       <c r="L13" s="1">
         <v>46224</v>
       </c>
-      <c r="M13" t="s">
-        <v>139</v>
+      <c r="M13">
+        <v>593210</v>
       </c>
       <c r="N13" t="s">
-        <v>139</v>
-      </c>
-      <c r="O13" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O13">
+        <v>3.5</v>
       </c>
       <c r="P13" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" t="s">
         <v>28</v>
       </c>
       <c r="R13" t="s">
@@ -1539,19 +1545,19 @@
       <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>32</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>22</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1577,9 +1583,6 @@
       </c>
       <c r="P14" t="s">
         <v>35</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>28</v>
       </c>
       <c r="R14" t="s">
         <v>26</v>
@@ -1595,19 +1598,19 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>22</v>
       </c>
       <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -1622,19 +1625,16 @@
       <c r="L15" s="1">
         <v>46227</v>
       </c>
-      <c r="M15" t="s">
-        <v>139</v>
+      <c r="M15">
+        <v>582148</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
-      </c>
-      <c r="O15" t="s">
-        <v>139</v>
+        <v>59</v>
+      </c>
+      <c r="O15">
+        <v>7.87</v>
       </c>
       <c r="P15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q15" t="s">
         <v>28</v>
       </c>
       <c r="R15" t="s">
@@ -1651,19 +1651,19 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>22</v>
       </c>
       <c r="G16" t="s">
         <v>32</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>28</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1689,9 +1689,6 @@
       </c>
       <c r="P16" t="s">
         <v>55</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>28</v>
       </c>
       <c r="R16" t="s">
         <v>26</v>
@@ -1707,19 +1704,19 @@
       <c r="C17" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>22</v>
       </c>
       <c r="G17" t="s">
         <v>43</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -1734,19 +1731,16 @@
       <c r="L17" s="1">
         <v>46231</v>
       </c>
-      <c r="M17" t="s">
-        <v>139</v>
+      <c r="M17">
+        <v>598334</v>
       </c>
       <c r="N17" t="s">
-        <v>139</v>
-      </c>
-      <c r="O17" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O17">
+        <v>9.7899999999999991</v>
       </c>
       <c r="P17" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" t="s">
         <v>28</v>
       </c>
       <c r="R17" t="s">
@@ -1763,19 +1757,19 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
         <v>23</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -1801,9 +1795,6 @@
       </c>
       <c r="P18" t="s">
         <v>35</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>28</v>
       </c>
       <c r="R18" t="s">
         <v>26</v>
@@ -1819,19 +1810,19 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>22</v>
       </c>
       <c r="G19" t="s">
         <v>43</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -1850,16 +1841,16 @@
         <v>601583</v>
       </c>
       <c r="N19" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -1875,19 +1866,19 @@
       <c r="C20" t="s">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>22</v>
       </c>
       <c r="G20" t="s">
         <v>32</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -1931,19 +1922,19 @@
       <c r="C21" t="s">
         <v>19</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>22</v>
       </c>
       <c r="G21" t="s">
         <v>43</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>5</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -1987,19 +1978,19 @@
       <c r="C22" t="s">
         <v>19</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>22</v>
       </c>
       <c r="G22" t="s">
         <v>32</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>6</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -2043,19 +2034,19 @@
       <c r="C23" t="s">
         <v>19</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>22</v>
       </c>
       <c r="G23" t="s">
         <v>32</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>7</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -2074,16 +2065,16 @@
         <v>603017</v>
       </c>
       <c r="N23" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="O23">
         <v>1.89</v>
       </c>
       <c r="P23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q23" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="R23" t="s">
         <v>26</v>
@@ -2099,19 +2090,19 @@
       <c r="C24" t="s">
         <v>19</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>22</v>
       </c>
       <c r="G24" t="s">
         <v>43</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>7</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2155,19 +2146,19 @@
       <c r="C25" t="s">
         <v>19</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>22</v>
       </c>
       <c r="G25" t="s">
         <v>32</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -2211,19 +2202,19 @@
       <c r="C26" t="s">
         <v>19</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>22</v>
       </c>
       <c r="G26" t="s">
         <v>23</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>11</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -2267,19 +2258,19 @@
       <c r="C27" t="s">
         <v>19</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>22</v>
       </c>
       <c r="G27" t="s">
         <v>32</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>11</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2307,7 +2298,7 @@
         <v>35</v>
       </c>
       <c r="Q27" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="R27" t="s">
         <v>26</v>
@@ -2323,19 +2314,19 @@
       <c r="C28" t="s">
         <v>19</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>94</v>
       </c>
       <c r="G28" t="s">
         <v>95</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>13</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2362,8 +2353,8 @@
       <c r="P28" t="s">
         <v>35</v>
       </c>
-      <c r="Q28" t="e">
-        <v>#REF!</v>
+      <c r="Q28" t="s">
+        <v>28</v>
       </c>
       <c r="R28" t="s">
         <v>26</v>
@@ -2379,19 +2370,19 @@
       <c r="C29" t="s">
         <v>19</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>22</v>
       </c>
       <c r="G29" t="s">
         <v>43</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>13</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2435,19 +2426,19 @@
       <c r="C30" t="s">
         <v>19</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>94</v>
       </c>
       <c r="G30" t="s">
         <v>95</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>14</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2462,14 +2453,14 @@
       <c r="L30" s="1">
         <v>46248</v>
       </c>
-      <c r="M30" t="s">
-        <v>139</v>
+      <c r="M30">
+        <v>606392</v>
       </c>
       <c r="N30" t="s">
-        <v>139</v>
-      </c>
-      <c r="O30" t="s">
-        <v>139</v>
+        <v>59</v>
+      </c>
+      <c r="O30">
+        <v>5.13</v>
       </c>
       <c r="P30" t="s">
         <v>28</v>
@@ -2491,19 +2482,19 @@
       <c r="C31" t="s">
         <v>19</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>22</v>
       </c>
       <c r="G31" t="s">
         <v>32</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2547,19 +2538,19 @@
       <c r="C32" t="s">
         <v>19</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>22</v>
       </c>
       <c r="G32" t="s">
         <v>32</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -2603,19 +2594,19 @@
       <c r="C33" t="s">
         <v>19</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" t="s">
         <v>94</v>
       </c>
       <c r="G33" t="s">
         <v>95</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>19</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -2630,20 +2621,20 @@
       <c r="L33" s="1">
         <v>46253</v>
       </c>
-      <c r="M33" t="s">
-        <v>139</v>
+      <c r="M33">
+        <v>608180</v>
       </c>
       <c r="N33" t="s">
-        <v>139</v>
-      </c>
-      <c r="O33" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O33">
+        <v>3.73</v>
       </c>
       <c r="P33" t="s">
         <v>28</v>
       </c>
       <c r="Q33" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="R33" t="s">
         <v>26</v>
@@ -2659,19 +2650,19 @@
       <c r="C34" t="s">
         <v>19</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" t="s">
         <v>22</v>
       </c>
       <c r="G34" t="s">
         <v>43</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>19</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -2715,19 +2706,19 @@
       <c r="C35" t="s">
         <v>19</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" t="s">
         <v>94</v>
       </c>
       <c r="G35" t="s">
         <v>95</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>20</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -2742,14 +2733,14 @@
       <c r="L35" s="1">
         <v>46254</v>
       </c>
-      <c r="M35" t="s">
-        <v>139</v>
+      <c r="M35">
+        <v>608550</v>
       </c>
       <c r="N35" t="s">
-        <v>139</v>
-      </c>
-      <c r="O35" t="s">
-        <v>139</v>
+        <v>59</v>
+      </c>
+      <c r="O35">
+        <v>20.25</v>
       </c>
       <c r="P35" t="s">
         <v>28</v>
@@ -2771,19 +2762,19 @@
       <c r="C36" t="s">
         <v>19</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" t="s">
         <v>94</v>
       </c>
       <c r="G36" t="s">
         <v>95</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
         <v>21</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -2798,20 +2789,20 @@
       <c r="L36" s="1">
         <v>46255</v>
       </c>
-      <c r="M36" t="s">
-        <v>139</v>
+      <c r="M36">
+        <v>605205</v>
       </c>
       <c r="N36" t="s">
-        <v>139</v>
-      </c>
-      <c r="O36" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O36">
+        <v>6.23</v>
       </c>
       <c r="P36" t="s">
         <v>28</v>
       </c>
       <c r="Q36" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="R36" t="s">
         <v>26</v>
@@ -2827,19 +2818,19 @@
       <c r="C37" t="s">
         <v>19</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" t="s">
         <v>94</v>
       </c>
       <c r="G37" t="s">
         <v>95</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
         <v>21</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -2854,20 +2845,20 @@
       <c r="L37" s="1">
         <v>46255</v>
       </c>
-      <c r="M37" t="s">
-        <v>139</v>
+      <c r="M37">
+        <v>557624</v>
       </c>
       <c r="N37" t="s">
-        <v>139</v>
-      </c>
-      <c r="O37" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
       </c>
       <c r="P37" t="s">
         <v>28</v>
       </c>
       <c r="Q37" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="R37" t="s">
         <v>26</v>
@@ -2883,19 +2874,19 @@
       <c r="C38" t="s">
         <v>19</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" t="s">
         <v>94</v>
       </c>
       <c r="G38" t="s">
         <v>95</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
         <v>21</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -2939,19 +2930,19 @@
       <c r="C39" t="s">
         <v>19</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" t="s">
         <v>94</v>
       </c>
       <c r="G39" t="s">
         <v>108</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
         <v>21</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -2995,19 +2986,19 @@
       <c r="C40" t="s">
         <v>19</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" t="s">
         <v>94</v>
       </c>
       <c r="G40" t="s">
         <v>95</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
         <v>21</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -3051,19 +3042,19 @@
       <c r="C41" t="s">
         <v>19</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" t="s">
         <v>94</v>
       </c>
       <c r="G41" t="s">
         <v>95</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="1">
         <v>21</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -3078,20 +3069,20 @@
       <c r="L41" s="1">
         <v>46255</v>
       </c>
-      <c r="M41" t="s">
-        <v>139</v>
+      <c r="M41">
+        <v>605070</v>
       </c>
       <c r="N41" t="s">
-        <v>139</v>
-      </c>
-      <c r="O41" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O41">
+        <v>3.19</v>
       </c>
       <c r="P41" t="s">
         <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="R41" t="s">
         <v>26</v>
@@ -3107,19 +3098,19 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" t="s">
         <v>22</v>
       </c>
       <c r="G42" t="s">
         <v>32</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
         <v>21</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -3163,19 +3154,19 @@
       <c r="C43" t="s">
         <v>19</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" t="s">
         <v>22</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
         <v>24</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -3219,19 +3210,19 @@
       <c r="C44" t="s">
         <v>19</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" t="s">
         <v>22</v>
       </c>
       <c r="G44" t="s">
         <v>23</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
         <v>25</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -3246,20 +3237,20 @@
       <c r="L44" s="1">
         <v>46259</v>
       </c>
-      <c r="M44" t="s">
-        <v>139</v>
+      <c r="M44">
+        <v>610626</v>
       </c>
       <c r="N44" t="s">
-        <v>139</v>
-      </c>
-      <c r="O44" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O44">
+        <v>4.63</v>
       </c>
       <c r="P44" t="s">
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="R44" t="e">
         <v>#N/A</v>
@@ -3275,19 +3266,19 @@
       <c r="C45" t="s">
         <v>19</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" t="s">
         <v>22</v>
       </c>
       <c r="G45" t="s">
         <v>23</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
         <v>25</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -3331,19 +3322,19 @@
       <c r="C46" t="s">
         <v>19</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" t="s">
         <v>22</v>
       </c>
       <c r="G46" t="s">
         <v>43</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
         <v>25</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -3358,20 +3349,20 @@
       <c r="L46" s="1">
         <v>46259</v>
       </c>
-      <c r="M46" t="s">
-        <v>139</v>
+      <c r="M46">
+        <v>610910</v>
       </c>
       <c r="N46" t="s">
-        <v>139</v>
-      </c>
-      <c r="O46" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O46">
+        <v>8.44</v>
       </c>
       <c r="P46" t="s">
         <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="R46" t="s">
         <v>26</v>
@@ -3387,19 +3378,19 @@
       <c r="C47" t="s">
         <v>19</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" t="s">
         <v>22</v>
       </c>
       <c r="G47" t="s">
         <v>32</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
         <v>25</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -3443,19 +3434,19 @@
       <c r="C48" t="s">
         <v>19</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" t="s">
         <v>94</v>
       </c>
       <c r="G48" t="s">
         <v>95</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
         <v>27</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -3470,20 +3461,20 @@
       <c r="L48" s="1">
         <v>46261</v>
       </c>
-      <c r="M48" t="s">
-        <v>139</v>
+      <c r="M48">
+        <v>611732</v>
       </c>
       <c r="N48" t="s">
-        <v>139</v>
-      </c>
-      <c r="O48" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O48">
+        <v>10.1</v>
       </c>
       <c r="P48" t="s">
         <v>28</v>
       </c>
       <c r="Q48" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="R48" t="s">
         <v>26</v>
@@ -3499,19 +3490,19 @@
       <c r="C49" t="s">
         <v>19</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" t="s">
         <v>22</v>
       </c>
       <c r="G49" t="s">
         <v>32</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="1">
         <v>27</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -3555,19 +3546,19 @@
       <c r="C50" t="s">
         <v>19</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" t="s">
         <v>94</v>
       </c>
       <c r="G50" t="s">
         <v>95</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="1">
         <v>28</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -3582,20 +3573,20 @@
       <c r="L50" s="1">
         <v>46262</v>
       </c>
-      <c r="M50" t="s">
-        <v>139</v>
+      <c r="M50">
+        <v>612663</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
-      </c>
-      <c r="O50" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O50">
+        <v>2.89</v>
       </c>
       <c r="P50" t="s">
         <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="R50" t="s">
         <v>26</v>
@@ -3611,19 +3602,19 @@
       <c r="C51" t="s">
         <v>19</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" t="s">
         <v>22</v>
       </c>
       <c r="G51" t="s">
         <v>32</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -3667,19 +3658,19 @@
       <c r="C52" t="s">
         <v>19</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" t="s">
         <v>94</v>
       </c>
       <c r="G52" t="s">
         <v>95</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="1">
         <v>3</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -3694,20 +3685,20 @@
       <c r="L52" s="1">
         <v>46268</v>
       </c>
-      <c r="M52" t="s">
-        <v>139</v>
+      <c r="M52">
+        <v>615019</v>
       </c>
       <c r="N52" t="s">
-        <v>139</v>
-      </c>
-      <c r="O52" t="s">
-        <v>139</v>
+        <v>44</v>
+      </c>
+      <c r="O52">
+        <v>7.95</v>
       </c>
       <c r="P52" t="s">
         <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="R52" t="s">
         <v>26</v>
@@ -3723,19 +3714,19 @@
       <c r="C53" t="s">
         <v>19</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" t="s">
         <v>22</v>
       </c>
       <c r="G53" t="s">
         <v>32</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="1">
         <v>3</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -3779,19 +3770,19 @@
       <c r="C54" t="s">
         <v>19</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" t="s">
         <v>22</v>
       </c>
       <c r="G54" t="s">
         <v>32</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="1">
         <v>4</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -3835,19 +3826,19 @@
       <c r="C55" t="s">
         <v>19</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" t="s">
         <v>22</v>
       </c>
       <c r="G55" t="s">
         <v>32</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="1">
         <v>4</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -3891,19 +3882,19 @@
       <c r="C56" t="s">
         <v>19</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" t="s">
         <v>22</v>
       </c>
       <c r="G56" t="s">
         <v>32</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="1">
         <v>4</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -3947,19 +3938,19 @@
       <c r="C57" t="s">
         <v>19</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" t="s">
         <v>94</v>
       </c>
       <c r="G57" t="s">
         <v>131</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="1">
         <v>8</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -4003,19 +3994,19 @@
       <c r="C58" t="s">
         <v>19</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" t="s">
         <v>22</v>
       </c>
       <c r="G58" t="s">
         <v>32</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="1">
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -4059,19 +4050,19 @@
       <c r="C59" t="s">
         <v>19</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" t="s">
         <v>94</v>
       </c>
       <c r="G59" t="s">
         <v>95</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="1">
         <v>9</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -4115,19 +4106,19 @@
       <c r="C60" t="s">
         <v>19</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" t="s">
         <v>22</v>
       </c>
       <c r="G60" t="s">
         <v>32</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="1">
         <v>9</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -4152,13 +4143,13 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="P60" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q60" t="s">
         <v>28</v>
       </c>
-      <c r="R60" t="e">
-        <v>#N/A</v>
+      <c r="R60" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
@@ -4171,19 +4162,19 @@
       <c r="C61" t="s">
         <v>19</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" t="s">
         <v>22</v>
       </c>
       <c r="G61" t="s">
         <v>43</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="1">
         <v>10</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -4208,13 +4199,13 @@
         <v>8.4600000000000009</v>
       </c>
       <c r="P61" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q61" t="s">
         <v>28</v>
       </c>
-      <c r="R61" t="e">
-        <v>#N/A</v>
+      <c r="R61" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
@@ -4222,18 +4213,18 @@
         <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C62" t="s">
         <v>19</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" t="s">
         <v>22</v>
       </c>
       <c r="G62" t="s">
@@ -4242,7 +4233,7 @@
       <c r="H62">
         <v>11</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I62" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J62" s="1" t="s">
@@ -4278,18 +4269,18 @@
         <v>29</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C63" t="s">
         <v>19</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
       <c r="G63" t="s">
@@ -4298,7 +4289,7 @@
       <c r="H63">
         <v>11</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" s="1" t="s">
         <v>123</v>
       </c>
       <c r="J63" s="1" t="s">
@@ -4334,18 +4325,18 @@
         <v>72</v>
       </c>
       <c r="B64" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C64" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" t="s">
         <v>94</v>
       </c>
       <c r="G64" t="s">
@@ -4360,7 +4351,7 @@
       <c r="J64" t="s">
         <v>25</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K64" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L64" s="1">
@@ -4376,7 +4367,7 @@
         <v>4.68</v>
       </c>
       <c r="P64" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q64" t="s">
         <v>28</v>
@@ -4390,18 +4381,18 @@
         <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C65" t="s">
         <v>19</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" t="s">
         <v>22</v>
       </c>
       <c r="G65" t="s">
@@ -4416,7 +4407,7 @@
       <c r="J65" t="s">
         <v>25</v>
       </c>
-      <c r="K65" t="s">
+      <c r="K65" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L65" s="1">
@@ -4441,15 +4432,127 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66">
+        <v>15</v>
+      </c>
+      <c r="I66" t="s">
+        <v>123</v>
+      </c>
+      <c r="J66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K66" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" s="1">
+        <v>46280</v>
+      </c>
+      <c r="M66">
+        <v>617205</v>
+      </c>
+      <c r="N66" t="s">
+        <v>138</v>
+      </c>
+      <c r="O66">
+        <v>14.62</v>
+      </c>
+      <c r="P66" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>28</v>
+      </c>
+      <c r="R66" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F67" t="s">
+        <v>94</v>
+      </c>
+      <c r="G67" t="s">
+        <v>95</v>
+      </c>
+      <c r="H67">
+        <v>15</v>
+      </c>
+      <c r="I67" t="s">
+        <v>123</v>
+      </c>
+      <c r="J67" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="1">
+        <v>46280</v>
+      </c>
+      <c r="M67">
+        <v>620157</v>
+      </c>
+      <c r="N67" t="s">
+        <v>138</v>
+      </c>
+      <c r="O67">
+        <v>6.46</v>
+      </c>
+      <c r="P67" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>28</v>
+      </c>
+      <c r="R67" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:D43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -5255,7 +5358,118 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22">
+        <v>34.295999999999999</v>
+      </c>
+      <c r="E22">
+        <v>14.61999</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>15</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1.2</v>
+      </c>
+      <c r="K22">
+        <v>8</v>
+      </c>
+      <c r="L22">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23">
+        <v>7.9204399999999993</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>15</v>
+      </c>
+      <c r="H23">
+        <v>10</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B24" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24">
+        <v>6.7674200000000004</v>
+      </c>
+      <c r="F24">
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>15</v>
+      </c>
+      <c r="H24">
+        <v>8</v>
+      </c>
+      <c r="I24">
+        <v>0.8</v>
+      </c>
+      <c r="J24">
+        <v>1.2</v>
+      </c>
+      <c r="K24">
+        <v>10</v>
+      </c>
+      <c r="L24">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5379,26 +5593,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -5659,26 +5853,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5695,4 +5890,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C00BA7B5-7F1A-49B9-B06E-B5D5DFB96D59}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48B27E61-1261-44CB-A5EF-7719F56BD99A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$D$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$C$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="160">
   <si>
     <t>Usuário</t>
   </si>
@@ -379,9 +379,6 @@
     <t>NELIO LANA DA SILVA</t>
   </si>
   <si>
-    <t>NEGOCIAÇÃO QUENTE</t>
-  </si>
-  <si>
     <t>GENI NATALIA DA SILVA</t>
   </si>
   <si>
@@ -506,6 +503,24 @@
   </si>
   <si>
     <t>semana2</t>
+  </si>
+  <si>
+    <t>NÃO CONCORDOU COM MINUTA CONTRATUAL</t>
+  </si>
+  <si>
+    <t>FALTA DE CONTATO - DECISOR NÃO ENCONTRAD</t>
+  </si>
+  <si>
+    <t>POSSUI USINA PROPRIA</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO DE INFORMAÇÕES CADASTRAIS</t>
+  </si>
+  <si>
+    <t>VILMAR DE OLIVEIRA COSTA</t>
+  </si>
+  <si>
+    <t>CICERO PARENTE DA CUNHA</t>
   </si>
 </sst>
 </file>
@@ -830,11 +845,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="5" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -844,13 +859,13 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -900,19 +915,19 @@
       <c r="B2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>31</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>54</v>
       </c>
       <c r="H2" s="1">
@@ -943,7 +958,7 @@
         <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R2" t="s">
         <v>26</v>
@@ -956,19 +971,19 @@
       <c r="B3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>31</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>54</v>
       </c>
       <c r="H3" s="1">
@@ -999,7 +1014,7 @@
         <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R3" t="s">
         <v>26</v>
@@ -1012,19 +1027,19 @@
       <c r="B4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H4" s="1">
@@ -1065,19 +1080,19 @@
       <c r="B5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H5" s="1">
@@ -1106,6 +1121,9 @@
       </c>
       <c r="P5" t="s">
         <v>28</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>154</v>
       </c>
       <c r="R5" t="s">
         <v>26</v>
@@ -1118,19 +1136,19 @@
       <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H6" s="1">
@@ -1152,7 +1170,7 @@
         <v>588146</v>
       </c>
       <c r="N6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O6">
         <v>67.37</v>
@@ -1171,19 +1189,19 @@
       <c r="B7" t="s">
         <v>63</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H7" s="1">
@@ -1205,7 +1223,7 @@
         <v>588663</v>
       </c>
       <c r="N7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O7">
         <v>35.78</v>
@@ -1224,19 +1242,19 @@
       <c r="B8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>31</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H8" s="1">
@@ -1258,7 +1276,7 @@
         <v>589870</v>
       </c>
       <c r="N8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O8">
         <v>27.46</v>
@@ -1277,19 +1295,19 @@
       <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>31</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="H9" s="1">
@@ -1311,7 +1329,7 @@
         <v>591481</v>
       </c>
       <c r="N9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1330,19 +1348,19 @@
       <c r="B10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>31</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H10" s="1">
@@ -1364,7 +1382,7 @@
         <v>591629</v>
       </c>
       <c r="N10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O10">
         <v>10.44</v>
@@ -1383,19 +1401,19 @@
       <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>31</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H11" s="1">
@@ -1417,7 +1435,7 @@
         <v>594789</v>
       </c>
       <c r="N11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O11">
         <v>10.75</v>
@@ -1436,19 +1454,19 @@
       <c r="B12" t="s">
         <v>51</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>31</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H12" s="1">
@@ -1489,19 +1507,19 @@
       <c r="B13" t="s">
         <v>61</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>31</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H13" s="1">
@@ -1530,6 +1548,9 @@
       </c>
       <c r="P13" t="s">
         <v>28</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>155</v>
       </c>
       <c r="R13" t="s">
         <v>26</v>
@@ -1542,19 +1563,19 @@
       <c r="B14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H14" s="1">
@@ -1576,7 +1597,7 @@
         <v>595396</v>
       </c>
       <c r="N14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O14">
         <v>11.66</v>
@@ -1595,19 +1616,19 @@
       <c r="B15" t="s">
         <v>65</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" t="s">
         <v>31</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H15" s="1">
@@ -1648,19 +1669,19 @@
       <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>31</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H16" s="1">
@@ -1682,7 +1703,7 @@
         <v>593213</v>
       </c>
       <c r="N16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O16">
         <v>3.66</v>
@@ -1701,19 +1722,19 @@
       <c r="B17" t="s">
         <v>50</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>31</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H17" s="1">
@@ -1742,6 +1763,9 @@
       </c>
       <c r="P17" t="s">
         <v>28</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>156</v>
       </c>
       <c r="R17" t="s">
         <v>26</v>
@@ -1754,19 +1778,19 @@
       <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>31</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="1">
@@ -1788,7 +1812,7 @@
         <v>598353</v>
       </c>
       <c r="N18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O18">
         <v>6.9</v>
@@ -1807,19 +1831,19 @@
       <c r="B19" t="s">
         <v>42</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>31</v>
       </c>
       <c r="F19" t="s">
         <v>22</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H19" s="1">
@@ -1838,19 +1862,19 @@
         <v>46237</v>
       </c>
       <c r="M19">
-        <v>601583</v>
+        <v>600697</v>
       </c>
       <c r="N19" t="s">
         <v>44</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>102.72</v>
       </c>
       <c r="P19" t="s">
         <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -1863,19 +1887,19 @@
       <c r="B20" t="s">
         <v>41</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>31</v>
       </c>
       <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H20" s="1">
@@ -1897,7 +1921,7 @@
         <v>601025</v>
       </c>
       <c r="N20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O20">
         <v>41.62</v>
@@ -1919,19 +1943,19 @@
       <c r="B21" t="s">
         <v>62</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>31</v>
       </c>
       <c r="F21" t="s">
         <v>22</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H21" s="1">
@@ -1953,7 +1977,7 @@
         <v>601537</v>
       </c>
       <c r="N21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O21">
         <v>4.63</v>
@@ -1975,19 +1999,19 @@
       <c r="B22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>31</v>
       </c>
       <c r="F22" t="s">
         <v>22</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H22" s="1">
@@ -2009,7 +2033,7 @@
         <v>601944</v>
       </c>
       <c r="N22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O22">
         <v>1.96</v>
@@ -2031,19 +2055,19 @@
       <c r="B23" t="s">
         <v>37</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" t="s">
         <v>31</v>
       </c>
       <c r="F23" t="s">
         <v>22</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H23" s="1">
@@ -2074,7 +2098,7 @@
         <v>28</v>
       </c>
       <c r="Q23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R23" t="s">
         <v>26</v>
@@ -2087,19 +2111,19 @@
       <c r="B24" t="s">
         <v>60</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" t="s">
         <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>22</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H24" s="1">
@@ -2121,7 +2145,7 @@
         <v>602969</v>
       </c>
       <c r="N24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O24">
         <v>6.12</v>
@@ -2143,19 +2167,19 @@
       <c r="B25" t="s">
         <v>46</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>22</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H25" s="1">
@@ -2177,7 +2201,7 @@
         <v>603608</v>
       </c>
       <c r="N25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O25">
         <v>8.77</v>
@@ -2199,19 +2223,19 @@
       <c r="B26" t="s">
         <v>18</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" t="s">
         <v>21</v>
       </c>
       <c r="F26" t="s">
         <v>22</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="1">
@@ -2233,7 +2257,7 @@
         <v>604128</v>
       </c>
       <c r="N26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O26">
         <v>8.3699999999999992</v>
@@ -2255,19 +2279,19 @@
       <c r="B27" t="s">
         <v>47</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" t="s">
         <v>31</v>
       </c>
       <c r="F27" t="s">
         <v>22</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H27" s="1">
@@ -2289,16 +2313,16 @@
         <v>604194</v>
       </c>
       <c r="N27" t="s">
-        <v>138</v>
+        <v>44</v>
       </c>
       <c r="O27">
         <v>2.98</v>
       </c>
       <c r="P27" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R27" t="s">
         <v>26</v>
@@ -2311,19 +2335,19 @@
       <c r="B28" t="s">
         <v>92</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" t="s">
         <v>93</v>
       </c>
       <c r="F28" t="s">
         <v>94</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G28" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H28" s="1">
@@ -2345,7 +2369,7 @@
         <v>605287</v>
       </c>
       <c r="N28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O28">
         <v>61.58</v>
@@ -2367,19 +2391,19 @@
       <c r="B29" t="s">
         <v>96</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" t="s">
         <v>31</v>
       </c>
       <c r="F29" t="s">
         <v>22</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H29" s="1">
@@ -2401,7 +2425,7 @@
         <v>605244</v>
       </c>
       <c r="N29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O29">
         <v>91.5</v>
@@ -2423,19 +2447,19 @@
       <c r="B30" t="s">
         <v>97</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" t="s">
         <v>93</v>
       </c>
       <c r="F30" t="s">
         <v>94</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H30" s="1">
@@ -2479,19 +2503,19 @@
       <c r="B31" t="s">
         <v>98</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" t="s">
         <v>31</v>
       </c>
       <c r="F31" t="s">
         <v>22</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="1">
@@ -2513,7 +2537,7 @@
         <v>606908</v>
       </c>
       <c r="N31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O31">
         <v>37.299999999999997</v>
@@ -2535,19 +2559,19 @@
       <c r="B32" t="s">
         <v>99</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" t="s">
         <v>31</v>
       </c>
       <c r="F32" t="s">
         <v>22</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H32" s="1">
@@ -2569,7 +2593,7 @@
         <v>581722</v>
       </c>
       <c r="N32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O32">
         <v>21.24</v>
@@ -2591,19 +2615,19 @@
       <c r="B33" t="s">
         <v>102</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" t="s">
         <v>93</v>
       </c>
       <c r="F33" t="s">
         <v>94</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H33" s="1">
@@ -2634,7 +2658,7 @@
         <v>28</v>
       </c>
       <c r="Q33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R33" t="s">
         <v>26</v>
@@ -2647,19 +2671,19 @@
       <c r="B34" t="s">
         <v>101</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" t="s">
         <v>31</v>
       </c>
       <c r="F34" t="s">
         <v>22</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H34" s="1">
@@ -2681,7 +2705,7 @@
         <v>608150</v>
       </c>
       <c r="N34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O34">
         <v>4.54</v>
@@ -2703,19 +2727,19 @@
       <c r="B35" t="s">
         <v>103</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" t="s">
         <v>93</v>
       </c>
       <c r="F35" t="s">
         <v>94</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H35" s="1">
@@ -2759,19 +2783,19 @@
       <c r="B36" t="s">
         <v>104</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" t="s">
         <v>93</v>
       </c>
       <c r="F36" t="s">
         <v>94</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G36" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H36" s="1">
@@ -2802,7 +2826,7 @@
         <v>28</v>
       </c>
       <c r="Q36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R36" t="s">
         <v>26</v>
@@ -2815,19 +2839,19 @@
       <c r="B37" t="s">
         <v>105</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" t="s">
         <v>93</v>
       </c>
       <c r="F37" t="s">
         <v>94</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G37" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H37" s="1">
@@ -2858,7 +2882,7 @@
         <v>28</v>
       </c>
       <c r="Q37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R37" t="s">
         <v>26</v>
@@ -2871,19 +2895,19 @@
       <c r="B38" t="s">
         <v>106</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" t="s">
         <v>93</v>
       </c>
       <c r="F38" t="s">
         <v>94</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H38" s="1">
@@ -2905,13 +2929,13 @@
         <v>609384</v>
       </c>
       <c r="N38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O38">
         <v>3.39</v>
       </c>
       <c r="P38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q38" t="s">
         <v>28</v>
@@ -2927,19 +2951,19 @@
       <c r="B39" t="s">
         <v>107</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" t="s">
         <v>93</v>
       </c>
       <c r="F39" t="s">
         <v>94</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="1" t="s">
         <v>108</v>
       </c>
       <c r="H39" s="1">
@@ -2961,13 +2985,13 @@
         <v>609414</v>
       </c>
       <c r="N39" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="O39">
         <v>10.9</v>
       </c>
       <c r="P39" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="Q39" t="s">
         <v>28</v>
@@ -2983,19 +3007,19 @@
       <c r="B40" t="s">
         <v>109</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" t="s">
         <v>93</v>
       </c>
       <c r="F40" t="s">
         <v>94</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H40" s="1">
@@ -3017,13 +3041,13 @@
         <v>604864</v>
       </c>
       <c r="N40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O40">
         <v>19.47</v>
       </c>
       <c r="P40" t="s">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="Q40" t="s">
         <v>28</v>
@@ -3039,19 +3063,19 @@
       <c r="B41" t="s">
         <v>110</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" t="s">
         <v>93</v>
       </c>
       <c r="F41" t="s">
         <v>94</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H41" s="1">
@@ -3082,7 +3106,7 @@
         <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R41" t="s">
         <v>26</v>
@@ -3095,19 +3119,19 @@
       <c r="B42" t="s">
         <v>111</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" t="s">
         <v>31</v>
       </c>
       <c r="F42" t="s">
         <v>22</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H42" s="1">
@@ -3129,7 +3153,7 @@
         <v>609512</v>
       </c>
       <c r="N42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O42">
         <v>7.15</v>
@@ -3149,21 +3173,21 @@
         <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" t="s">
         <v>31</v>
       </c>
       <c r="F43" t="s">
         <v>22</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H43" s="1">
@@ -3185,7 +3209,7 @@
         <v>610104</v>
       </c>
       <c r="N43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O43">
         <v>9.2200000000000006</v>
@@ -3205,21 +3229,21 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" t="s">
         <v>21</v>
       </c>
       <c r="F44" t="s">
         <v>22</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="1">
@@ -3250,7 +3274,7 @@
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R44" t="e">
         <v>#N/A</v>
@@ -3261,21 +3285,21 @@
         <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" t="s">
         <v>21</v>
       </c>
       <c r="F45" t="s">
         <v>22</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="1">
@@ -3297,7 +3321,7 @@
         <v>614542</v>
       </c>
       <c r="N45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O45">
         <v>20.53</v>
@@ -3317,21 +3341,21 @@
         <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" t="s">
         <v>31</v>
       </c>
       <c r="F46" t="s">
         <v>22</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H46" s="1">
@@ -3362,7 +3386,7 @@
         <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R46" t="s">
         <v>26</v>
@@ -3373,21 +3397,21 @@
         <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
-      </c>
-      <c r="C47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" t="s">
         <v>31</v>
       </c>
       <c r="F47" t="s">
         <v>22</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H47" s="1">
@@ -3409,7 +3433,7 @@
         <v>610596</v>
       </c>
       <c r="N47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O47">
         <v>4.17</v>
@@ -3429,21 +3453,21 @@
         <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" t="s">
         <v>93</v>
       </c>
       <c r="F48" t="s">
         <v>94</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H48" s="1">
@@ -3474,7 +3498,7 @@
         <v>28</v>
       </c>
       <c r="Q48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R48" t="s">
         <v>26</v>
@@ -3485,21 +3509,21 @@
         <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>119</v>
-      </c>
-      <c r="C49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" t="s">
         <v>31</v>
       </c>
       <c r="F49" t="s">
         <v>22</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H49" s="1">
@@ -3521,7 +3545,7 @@
         <v>611797</v>
       </c>
       <c r="N49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O49">
         <v>9.85</v>
@@ -3541,21 +3565,21 @@
         <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
-      </c>
-      <c r="C50" t="s">
+        <v>120</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" t="s">
         <v>93</v>
       </c>
       <c r="F50" t="s">
         <v>94</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H50" s="1">
@@ -3586,7 +3610,7 @@
         <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R50" t="s">
         <v>26</v>
@@ -3597,28 +3621,28 @@
         <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>122</v>
-      </c>
-      <c r="C51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" t="s">
         <v>31</v>
       </c>
       <c r="F51" t="s">
         <v>22</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H51" s="1">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>25</v>
@@ -3633,7 +3657,7 @@
         <v>614020</v>
       </c>
       <c r="N51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O51">
         <v>2.33</v>
@@ -3653,28 +3677,28 @@
         <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
-      </c>
-      <c r="C52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" t="s">
         <v>93</v>
       </c>
       <c r="F52" t="s">
         <v>94</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G52" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H52" s="1">
         <v>3</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>25</v>
@@ -3698,7 +3722,7 @@
         <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R52" t="s">
         <v>26</v>
@@ -3709,28 +3733,28 @@
         <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" t="s">
         <v>31</v>
       </c>
       <c r="F53" t="s">
         <v>22</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G53" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H53" s="1">
         <v>3</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>25</v>
@@ -3745,7 +3769,7 @@
         <v>614995</v>
       </c>
       <c r="N53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O53">
         <v>1.91</v>
@@ -3765,28 +3789,28 @@
         <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>126</v>
-      </c>
-      <c r="C54" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" t="s">
         <v>31</v>
       </c>
       <c r="F54" t="s">
         <v>22</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G54" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H54" s="1">
         <v>4</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>25</v>
@@ -3801,7 +3825,7 @@
         <v>615314</v>
       </c>
       <c r="N54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O54">
         <v>12.23</v>
@@ -3821,28 +3845,28 @@
         <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
-      </c>
-      <c r="C55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" t="s">
         <v>31</v>
       </c>
       <c r="F55" t="s">
         <v>22</v>
       </c>
-      <c r="G55" t="s">
+      <c r="G55" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H55" s="1">
         <v>4</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>25</v>
@@ -3857,7 +3881,7 @@
         <v>615322</v>
       </c>
       <c r="N55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O55">
         <v>16.34</v>
@@ -3877,28 +3901,28 @@
         <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>129</v>
-      </c>
-      <c r="C56" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" t="s">
         <v>31</v>
       </c>
       <c r="F56" t="s">
         <v>22</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G56" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H56" s="1">
         <v>4</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>25</v>
@@ -3913,7 +3937,7 @@
         <v>615654</v>
       </c>
       <c r="N56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O56">
         <v>11.93</v>
@@ -3924,8 +3948,8 @@
       <c r="Q56" t="s">
         <v>28</v>
       </c>
-      <c r="R56" t="e">
-        <v>#N/A</v>
+      <c r="R56" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
@@ -3933,28 +3957,28 @@
         <v>72</v>
       </c>
       <c r="B57" t="s">
-        <v>130</v>
-      </c>
-      <c r="C57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" t="s">
         <v>93</v>
       </c>
       <c r="F57" t="s">
         <v>94</v>
       </c>
-      <c r="G57" t="s">
-        <v>131</v>
+      <c r="G57" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="H57" s="1">
         <v>8</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>25</v>
@@ -3969,7 +3993,7 @@
         <v>616899</v>
       </c>
       <c r="N57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O57">
         <v>6.36</v>
@@ -3989,28 +4013,28 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" t="s">
         <v>31</v>
       </c>
       <c r="F58" t="s">
         <v>22</v>
       </c>
-      <c r="G58" t="s">
+      <c r="G58" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H58" s="1">
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>25</v>
@@ -4025,19 +4049,19 @@
         <v>616788</v>
       </c>
       <c r="N58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O58">
         <v>32.82</v>
       </c>
       <c r="P58" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q58" t="s">
         <v>28</v>
       </c>
-      <c r="R58" t="e">
-        <v>#N/A</v>
+      <c r="R58" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
@@ -4045,28 +4069,28 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
-      </c>
-      <c r="C59" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" t="s">
         <v>93</v>
       </c>
       <c r="F59" t="s">
         <v>94</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H59" s="1">
         <v>9</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>25</v>
@@ -4081,7 +4105,7 @@
         <v>617206</v>
       </c>
       <c r="N59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O59">
         <v>21.23</v>
@@ -4101,28 +4125,28 @@
         <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
-      </c>
-      <c r="C60" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" t="s">
         <v>31</v>
       </c>
       <c r="F60" t="s">
         <v>22</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G60" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H60" s="1">
         <v>9</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>25</v>
@@ -4137,7 +4161,7 @@
         <v>617229</v>
       </c>
       <c r="N60" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O60">
         <v>2.2200000000000002</v>
@@ -4157,28 +4181,28 @@
         <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>137</v>
-      </c>
-      <c r="C61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" t="s">
         <v>31</v>
       </c>
       <c r="F61" t="s">
         <v>22</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G61" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H61" s="1">
         <v>10</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>25</v>
@@ -4193,7 +4217,7 @@
         <v>617914</v>
       </c>
       <c r="N61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O61">
         <v>8.4600000000000009</v>
@@ -4213,15 +4237,15 @@
         <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>139</v>
-      </c>
-      <c r="C62" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" t="s">
         <v>21</v>
       </c>
       <c r="F62" t="s">
@@ -4230,11 +4254,11 @@
       <c r="G62" t="s">
         <v>43</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="1">
         <v>11</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>25</v>
@@ -4249,7 +4273,7 @@
         <v>615347</v>
       </c>
       <c r="N62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O62">
         <v>2.76</v>
@@ -4269,15 +4293,15 @@
         <v>29</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
-      </c>
-      <c r="C63" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" t="s">
         <v>31</v>
       </c>
       <c r="F63" t="s">
@@ -4286,11 +4310,11 @@
       <c r="G63" t="s">
         <v>32</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="1">
         <v>11</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>25</v>
@@ -4305,7 +4329,7 @@
         <v>618930</v>
       </c>
       <c r="N63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O63">
         <v>17.97</v>
@@ -4325,16 +4349,16 @@
         <v>72</v>
       </c>
       <c r="B64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
         <v>141</v>
-      </c>
-      <c r="C64" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="F64" t="s">
         <v>94</v>
@@ -4346,9 +4370,9 @@
         <v>14</v>
       </c>
       <c r="I64" t="s">
-        <v>123</v>
-      </c>
-      <c r="J64" t="s">
+        <v>122</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K64" s="1" t="s">
@@ -4361,7 +4385,7 @@
         <v>619855</v>
       </c>
       <c r="N64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O64">
         <v>4.68</v>
@@ -4381,15 +4405,15 @@
         <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
-      </c>
-      <c r="C65" t="s">
+        <v>142</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" t="s">
         <v>31</v>
       </c>
       <c r="F65" t="s">
@@ -4402,9 +4426,9 @@
         <v>14</v>
       </c>
       <c r="I65" t="s">
-        <v>123</v>
-      </c>
-      <c r="J65" t="s">
+        <v>122</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K65" s="1" t="s">
@@ -4417,7 +4441,7 @@
         <v>619980</v>
       </c>
       <c r="N65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O65">
         <v>8.5399999999999991</v>
@@ -4437,15 +4461,15 @@
         <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
-      </c>
-      <c r="C66" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" t="s">
         <v>21</v>
       </c>
       <c r="F66" t="s">
@@ -4458,12 +4482,12 @@
         <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J66" t="s">
         <v>25</v>
       </c>
-      <c r="K66" t="s">
+      <c r="K66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L66" s="1">
@@ -4473,13 +4497,13 @@
         <v>617205</v>
       </c>
       <c r="N66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O66">
         <v>14.62</v>
       </c>
       <c r="P66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q66" t="s">
         <v>28</v>
@@ -4493,16 +4517,16 @@
         <v>72</v>
       </c>
       <c r="B67" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" t="s">
         <v>152</v>
-      </c>
-      <c r="C67" t="s">
-        <v>19</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="F67" t="s">
         <v>94</v>
@@ -4514,12 +4538,12 @@
         <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J67" t="s">
         <v>25</v>
       </c>
-      <c r="K67" t="s">
+      <c r="K67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L67" s="1">
@@ -4529,7 +4553,7 @@
         <v>620157</v>
       </c>
       <c r="N67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O67">
         <v>6.46</v>
@@ -4540,12 +4564,124 @@
       <c r="Q67" t="s">
         <v>28</v>
       </c>
-      <c r="R67" t="e">
+      <c r="R67" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>29</v>
+      </c>
+      <c r="B68" t="s">
+        <v>158</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68">
+        <v>15</v>
+      </c>
+      <c r="I68" t="s">
+        <v>122</v>
+      </c>
+      <c r="J68" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="1">
+        <v>46280</v>
+      </c>
+      <c r="M68">
+        <v>620523</v>
+      </c>
+      <c r="N68" t="s">
+        <v>137</v>
+      </c>
+      <c r="O68">
+        <v>8.57</v>
+      </c>
+      <c r="P68" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>28</v>
+      </c>
+      <c r="R68" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" t="s">
+        <v>152</v>
+      </c>
+      <c r="F69" t="s">
+        <v>94</v>
+      </c>
+      <c r="G69" t="s">
+        <v>95</v>
+      </c>
+      <c r="H69">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s">
+        <v>122</v>
+      </c>
+      <c r="J69" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="1">
+        <v>46281</v>
+      </c>
+      <c r="M69">
+        <v>620676</v>
+      </c>
+      <c r="N69" t="s">
+        <v>137</v>
+      </c>
+      <c r="O69">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="P69" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>28</v>
+      </c>
+      <c r="R69" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5020,7 +5156,7 @@
         <v>46235</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
@@ -5058,7 +5194,7 @@
         <v>46235</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
         <v>83</v>
@@ -5096,7 +5232,7 @@
         <v>46235</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
         <v>85</v>
@@ -5134,7 +5270,7 @@
         <v>46235</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C16" t="s">
         <v>29</v>
@@ -5172,7 +5308,7 @@
         <v>46235</v>
       </c>
       <c r="B17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
         <v>83</v>
@@ -5210,7 +5346,7 @@
         <v>46235</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
         <v>85</v>
@@ -5248,7 +5384,7 @@
         <v>46266</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
@@ -5286,7 +5422,7 @@
         <v>46266</v>
       </c>
       <c r="B20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
@@ -5324,7 +5460,7 @@
         <v>46266</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
         <v>85</v>
@@ -5362,37 +5498,37 @@
         <v>46266</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
       </c>
       <c r="D22">
-        <v>34.295999999999999</v>
+        <v>71.228000000000009</v>
       </c>
       <c r="E22">
-        <v>14.61999</v>
+        <v>48.579410000000003</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G22">
+        <v>30</v>
+      </c>
+      <c r="H22">
+        <v>17</v>
+      </c>
+      <c r="I22">
+        <v>0.85</v>
+      </c>
+      <c r="J22">
+        <v>1.0666666666666667</v>
+      </c>
+      <c r="K22">
         <v>15</v>
       </c>
-      <c r="H22">
-        <v>10</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>1.2</v>
-      </c>
-      <c r="K22">
-        <v>8</v>
-      </c>
       <c r="L22">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -5400,7 +5536,7 @@
         <v>46266</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
@@ -5409,28 +5545,28 @@
         <v>84</v>
       </c>
       <c r="E23">
-        <v>7.9204399999999993</v>
+        <v>13.872209999999999</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G23">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H23">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I23">
+        <v>0.9</v>
+      </c>
+      <c r="J23">
         <v>1</v>
       </c>
-      <c r="J23">
-        <v>0.93333333333333335</v>
-      </c>
       <c r="K23">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L23">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -5438,7 +5574,7 @@
         <v>46266</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
         <v>85</v>
@@ -5447,28 +5583,28 @@
         <v>84</v>
       </c>
       <c r="E24">
-        <v>6.7674200000000004</v>
+        <v>19.840589999999999</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G24">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H24">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I24">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J24">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L24">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -5593,6 +5729,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -5853,15 +5998,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5874,6 +6010,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5892,14 +6036,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48B27E61-1261-44CB-A5EF-7719F56BD99A}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2402B025-E6EF-4C2E-8476-827D96040E71}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$C$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="165">
   <si>
     <t>Usuário</t>
   </si>
@@ -521,6 +521,21 @@
   </si>
   <si>
     <t>CICERO PARENTE DA CUNHA</t>
+  </si>
+  <si>
+    <t>Não encontrado</t>
+  </si>
+  <si>
+    <t>SIMONE GOMES DE OLIVEIRA SOUZA</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO ICARAI DE AMONTADA ENERGIA SOLAR</t>
+  </si>
+  <si>
+    <t>MATHEUS FELIPE TEODORIO DE SOUZA AMARAL</t>
+  </si>
+  <si>
+    <t>MERCEARIA PADARIA SOMAR</t>
   </si>
 </sst>
 </file>
@@ -845,24 +860,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -912,19 +927,19 @@
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -968,19 +983,19 @@
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>20</v>
       </c>
       <c r="E3" t="s">
         <v>31</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1024,19 +1039,19 @@
       <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1077,19 +1092,19 @@
       <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1133,19 +1148,19 @@
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1186,19 +1201,19 @@
       <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1239,19 +1254,19 @@
       <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1276,13 +1291,13 @@
         <v>589870</v>
       </c>
       <c r="N8" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="O8">
         <v>27.46</v>
       </c>
       <c r="P8" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R8" t="s">
         <v>26</v>
@@ -1292,19 +1307,19 @@
       <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
         <v>31</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1345,19 +1360,19 @@
       <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>20</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1398,19 +1413,19 @@
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>20</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1451,19 +1466,19 @@
       <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>20</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1504,19 +1519,19 @@
       <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1560,19 +1575,19 @@
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>20</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1593,17 +1608,17 @@
       <c r="L14" s="1">
         <v>46225</v>
       </c>
-      <c r="M14">
-        <v>595396</v>
+      <c r="M14" t="s">
+        <v>160</v>
       </c>
       <c r="N14" t="s">
-        <v>137</v>
-      </c>
-      <c r="O14">
-        <v>11.66</v>
+        <v>160</v>
+      </c>
+      <c r="O14" t="s">
+        <v>160</v>
       </c>
       <c r="P14" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R14" t="s">
         <v>26</v>
@@ -1613,19 +1628,19 @@
       <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>20</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1666,19 +1681,19 @@
       <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>20</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1719,19 +1734,19 @@
       <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>20</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1775,19 +1790,19 @@
       <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>20</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1828,19 +1843,19 @@
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>20</v>
       </c>
       <c r="E19" t="s">
         <v>31</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1884,19 +1899,19 @@
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>20</v>
       </c>
       <c r="E20" t="s">
         <v>31</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1940,19 +1955,19 @@
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>20</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -1996,19 +2011,19 @@
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>20</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -2052,19 +2067,19 @@
       <c r="A23" t="s">
         <v>29</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>20</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -2108,19 +2123,19 @@
       <c r="A24" t="s">
         <v>29</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>20</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -2164,19 +2179,19 @@
       <c r="A25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>20</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2220,19 +2235,19 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" t="s">
         <v>20</v>
       </c>
       <c r="E26" t="s">
         <v>21</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -2276,19 +2291,19 @@
       <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" t="s">
         <v>20</v>
       </c>
       <c r="E27" t="s">
         <v>31</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -2332,19 +2347,19 @@
       <c r="A28" t="s">
         <v>72</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>20</v>
       </c>
       <c r="E28" t="s">
         <v>93</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2388,19 +2403,19 @@
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" t="s">
         <v>20</v>
       </c>
       <c r="E29" t="s">
         <v>31</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2444,19 +2459,19 @@
       <c r="A30" t="s">
         <v>72</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" t="s">
         <v>20</v>
       </c>
       <c r="E30" t="s">
         <v>93</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2500,19 +2515,19 @@
       <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>20</v>
       </c>
       <c r="E31" t="s">
         <v>31</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -2556,19 +2571,19 @@
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>20</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -2612,19 +2627,19 @@
       <c r="A33" t="s">
         <v>72</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" t="s">
         <v>20</v>
       </c>
       <c r="E33" t="s">
         <v>93</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -2668,19 +2683,19 @@
       <c r="A34" t="s">
         <v>29</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" t="s">
         <v>20</v>
       </c>
       <c r="E34" t="s">
         <v>31</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -2705,16 +2720,16 @@
         <v>608150</v>
       </c>
       <c r="N34" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="O34">
         <v>4.54</v>
       </c>
       <c r="P34" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q34" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="R34" t="s">
         <v>26</v>
@@ -2724,19 +2739,19 @@
       <c r="A35" t="s">
         <v>72</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" t="s">
         <v>20</v>
       </c>
       <c r="E35" t="s">
         <v>93</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -2780,19 +2795,19 @@
       <c r="A36" t="s">
         <v>72</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" t="s">
         <v>20</v>
       </c>
       <c r="E36" t="s">
         <v>93</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -2836,19 +2851,19 @@
       <c r="A37" t="s">
         <v>72</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" t="s">
         <v>20</v>
       </c>
       <c r="E37" t="s">
         <v>93</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -2892,19 +2907,19 @@
       <c r="A38" t="s">
         <v>72</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>20</v>
       </c>
       <c r="E38" t="s">
         <v>93</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -2948,19 +2963,19 @@
       <c r="A39" t="s">
         <v>72</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s">
         <v>20</v>
       </c>
       <c r="E39" t="s">
         <v>93</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -3004,19 +3019,19 @@
       <c r="A40" t="s">
         <v>72</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" t="s">
         <v>20</v>
       </c>
       <c r="E40" t="s">
         <v>93</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -3060,19 +3075,19 @@
       <c r="A41" t="s">
         <v>72</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>20</v>
       </c>
       <c r="E41" t="s">
         <v>93</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -3116,19 +3131,19 @@
       <c r="A42" t="s">
         <v>29</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" t="s">
         <v>20</v>
       </c>
       <c r="E42" t="s">
         <v>31</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -3172,19 +3187,19 @@
       <c r="A43" t="s">
         <v>29</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" t="s">
         <v>20</v>
       </c>
       <c r="E43" t="s">
         <v>31</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -3228,19 +3243,19 @@
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" t="s">
         <v>20</v>
       </c>
       <c r="E44" t="s">
         <v>21</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -3284,19 +3299,19 @@
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" t="s">
         <v>20</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -3340,19 +3355,19 @@
       <c r="A46" t="s">
         <v>29</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" t="s">
         <v>20</v>
       </c>
       <c r="E46" t="s">
         <v>31</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -3396,19 +3411,19 @@
       <c r="A47" t="s">
         <v>29</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" t="s">
         <v>20</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -3452,19 +3467,19 @@
       <c r="A48" t="s">
         <v>72</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" t="s">
         <v>20</v>
       </c>
       <c r="E48" t="s">
         <v>93</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -3508,19 +3523,19 @@
       <c r="A49" t="s">
         <v>29</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" t="s">
         <v>20</v>
       </c>
       <c r="E49" t="s">
         <v>31</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -3564,19 +3579,19 @@
       <c r="A50" t="s">
         <v>72</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" t="s">
         <v>20</v>
       </c>
       <c r="E50" t="s">
         <v>93</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -3620,19 +3635,19 @@
       <c r="A51" t="s">
         <v>29</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" t="s">
         <v>20</v>
       </c>
       <c r="E51" t="s">
         <v>31</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -3654,41 +3669,41 @@
         <v>46266</v>
       </c>
       <c r="M51">
-        <v>614020</v>
+        <v>615019</v>
       </c>
       <c r="N51" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="O51">
-        <v>2.33</v>
+        <v>7.95</v>
       </c>
       <c r="P51" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q51" t="s">
-        <v>28</v>
-      </c>
-      <c r="R51" t="s">
-        <v>26</v>
+        <v>146</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>72</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" t="s">
         <v>20</v>
       </c>
       <c r="E52" t="s">
         <v>93</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -3724,27 +3739,27 @@
       <c r="Q52" t="s">
         <v>146</v>
       </c>
-      <c r="R52" t="s">
-        <v>26</v>
+      <c r="R52">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>29</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" t="s">
         <v>20</v>
       </c>
       <c r="E53" t="s">
         <v>31</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -3780,27 +3795,27 @@
       <c r="Q53" t="s">
         <v>28</v>
       </c>
-      <c r="R53" t="s">
-        <v>26</v>
+      <c r="R53">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>29</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" t="s">
         <v>20</v>
       </c>
       <c r="E54" t="s">
         <v>31</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -3836,27 +3851,27 @@
       <c r="Q54" t="s">
         <v>28</v>
       </c>
-      <c r="R54" t="s">
-        <v>26</v>
+      <c r="R54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>29</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" t="s">
         <v>20</v>
       </c>
       <c r="E55" t="s">
         <v>31</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -3892,27 +3907,27 @@
       <c r="Q55" t="s">
         <v>28</v>
       </c>
-      <c r="R55" t="s">
-        <v>26</v>
+      <c r="R55">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>29</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" t="s">
         <v>20</v>
       </c>
       <c r="E56" t="s">
         <v>31</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -3948,27 +3963,27 @@
       <c r="Q56" t="s">
         <v>28</v>
       </c>
-      <c r="R56" t="s">
-        <v>26</v>
+      <c r="R56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>72</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" t="s">
         <v>20</v>
       </c>
       <c r="E57" t="s">
         <v>93</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -4012,19 +4027,19 @@
       <c r="A58" t="s">
         <v>29</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" t="s">
         <v>20</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -4060,27 +4075,27 @@
       <c r="Q58" t="s">
         <v>28</v>
       </c>
-      <c r="R58" t="s">
-        <v>26</v>
+      <c r="R58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>72</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" t="s">
         <v>20</v>
       </c>
       <c r="E59" t="s">
         <v>93</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G59" s="1" t="s">
@@ -4124,19 +4139,19 @@
       <c r="A60" t="s">
         <v>29</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" t="s">
         <v>20</v>
       </c>
       <c r="E60" t="s">
         <v>31</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G60" s="1" t="s">
@@ -4172,27 +4187,27 @@
       <c r="Q60" t="s">
         <v>28</v>
       </c>
-      <c r="R60" t="s">
-        <v>26</v>
+      <c r="R60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>29</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" t="s">
         <v>20</v>
       </c>
       <c r="E61" t="s">
         <v>31</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -4228,21 +4243,21 @@
       <c r="Q61" t="s">
         <v>28</v>
       </c>
-      <c r="R61" t="s">
-        <v>26</v>
+      <c r="R61">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>17</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" t="s">
         <v>20</v>
       </c>
       <c r="E62" t="s">
@@ -4251,7 +4266,7 @@
       <c r="F62" t="s">
         <v>22</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="1" t="s">
         <v>43</v>
       </c>
       <c r="H62" s="1">
@@ -4273,32 +4288,32 @@
         <v>615347</v>
       </c>
       <c r="N62" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="O62">
         <v>2.76</v>
       </c>
       <c r="P62" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q62" t="s">
-        <v>28</v>
-      </c>
-      <c r="R62" t="e">
-        <v>#N/A</v>
+        <v>148</v>
+      </c>
+      <c r="R62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>29</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" t="s">
         <v>20</v>
       </c>
       <c r="E63" t="s">
@@ -4307,7 +4322,7 @@
       <c r="F63" t="s">
         <v>22</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G63" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H63" s="1">
@@ -4348,13 +4363,13 @@
       <c r="A64" t="s">
         <v>72</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" t="s">
         <v>20</v>
       </c>
       <c r="E64" t="s">
@@ -4369,7 +4384,7 @@
       <c r="H64">
         <v>14</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J64" s="1" t="s">
@@ -4404,13 +4419,13 @@
       <c r="A65" t="s">
         <v>29</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" t="s">
         <v>20</v>
       </c>
       <c r="E65" t="s">
@@ -4425,7 +4440,7 @@
       <c r="H65">
         <v>14</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J65" s="1" t="s">
@@ -4460,13 +4475,13 @@
       <c r="A66" t="s">
         <v>17</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" t="s">
         <v>20</v>
       </c>
       <c r="E66" t="s">
@@ -4484,7 +4499,7 @@
       <c r="I66" t="s">
         <v>122</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K66" s="1" t="s">
@@ -4508,21 +4523,21 @@
       <c r="Q66" t="s">
         <v>28</v>
       </c>
-      <c r="R66" t="e">
-        <v>#N/A</v>
+      <c r="R66">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>72</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>151</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" t="s">
         <v>20</v>
       </c>
       <c r="E67" t="s">
@@ -4540,7 +4555,7 @@
       <c r="I67" t="s">
         <v>122</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K67" s="1" t="s">
@@ -4564,21 +4579,21 @@
       <c r="Q67" t="s">
         <v>28</v>
       </c>
-      <c r="R67" t="s">
-        <v>26</v>
+      <c r="R67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>29</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>158</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" t="s">
         <v>20</v>
       </c>
       <c r="E68" t="s">
@@ -4599,7 +4614,7 @@
       <c r="J68" t="s">
         <v>25</v>
       </c>
-      <c r="K68" t="s">
+      <c r="K68" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L68" s="1">
@@ -4628,13 +4643,13 @@
       <c r="A69" t="s">
         <v>72</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" t="s">
         <v>20</v>
       </c>
       <c r="E69" t="s">
@@ -4655,7 +4670,7 @@
       <c r="J69" t="s">
         <v>25</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L69" s="1">
@@ -4680,8 +4695,232 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" t="s">
+        <v>43</v>
+      </c>
+      <c r="H70">
+        <v>17</v>
+      </c>
+      <c r="I70" t="s">
+        <v>122</v>
+      </c>
+      <c r="J70" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" t="s">
+        <v>26</v>
+      </c>
+      <c r="L70" s="1">
+        <v>46282</v>
+      </c>
+      <c r="M70">
+        <v>620938</v>
+      </c>
+      <c r="N70" t="s">
+        <v>137</v>
+      </c>
+      <c r="O70">
+        <v>11.75</v>
+      </c>
+      <c r="P70" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>28</v>
+      </c>
+      <c r="R70" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" t="s">
+        <v>152</v>
+      </c>
+      <c r="F71" t="s">
+        <v>94</v>
+      </c>
+      <c r="G71" t="s">
+        <v>130</v>
+      </c>
+      <c r="H71">
+        <v>17</v>
+      </c>
+      <c r="I71" t="s">
+        <v>122</v>
+      </c>
+      <c r="J71" t="s">
+        <v>25</v>
+      </c>
+      <c r="K71" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="1">
+        <v>46282</v>
+      </c>
+      <c r="M71">
+        <v>621205</v>
+      </c>
+      <c r="N71" t="s">
+        <v>137</v>
+      </c>
+      <c r="O71">
+        <v>5.95</v>
+      </c>
+      <c r="P71" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>28</v>
+      </c>
+      <c r="R71" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" t="s">
+        <v>31</v>
+      </c>
+      <c r="F72" t="s">
+        <v>22</v>
+      </c>
+      <c r="G72" t="s">
+        <v>32</v>
+      </c>
+      <c r="H72">
+        <v>17</v>
+      </c>
+      <c r="I72" t="s">
+        <v>122</v>
+      </c>
+      <c r="J72" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="1">
+        <v>46282</v>
+      </c>
+      <c r="M72">
+        <v>621574</v>
+      </c>
+      <c r="N72" t="s">
+        <v>137</v>
+      </c>
+      <c r="O72">
+        <v>3.78</v>
+      </c>
+      <c r="P72" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>28</v>
+      </c>
+      <c r="R72" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
+        <v>31</v>
+      </c>
+      <c r="F73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73">
+        <v>17</v>
+      </c>
+      <c r="I73" t="s">
+        <v>122</v>
+      </c>
+      <c r="J73" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="1">
+        <v>46282</v>
+      </c>
+      <c r="M73">
+        <v>621242</v>
+      </c>
+      <c r="N73" t="s">
+        <v>137</v>
+      </c>
+      <c r="O73">
+        <v>5.46</v>
+      </c>
+      <c r="P73" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>28</v>
+      </c>
+      <c r="R73" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5504,31 +5743,31 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>71.228000000000009</v>
+        <v>135.60599999999999</v>
       </c>
       <c r="E22">
-        <v>48.579410000000003</v>
+        <v>75.700130000000001</v>
       </c>
       <c r="F22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G22">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H22">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I22">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="J22">
-        <v>1.0666666666666667</v>
+        <v>1.0888888888888888</v>
       </c>
       <c r="K22">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L22">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -5545,28 +5784,28 @@
         <v>84</v>
       </c>
       <c r="E23">
-        <v>13.872209999999999</v>
+        <v>33.459470000000003</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G23">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H23">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I23">
-        <v>0.9</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L23">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -5583,28 +5822,28 @@
         <v>84</v>
       </c>
       <c r="E24">
-        <v>19.840589999999999</v>
+        <v>32.393349999999998</v>
       </c>
       <c r="F24">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G24">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H24">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I24">
-        <v>0.6</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="L24">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -5729,12 +5968,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5999,20 +6240,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6037,12 +6279,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2402B025-E6EF-4C2E-8476-827D96040E71}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A24EFE9-E33D-4923-AD0A-6D35B17C2B29}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Metas" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$B$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$A$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="166">
   <si>
     <t>Usuário</t>
   </si>
@@ -536,6 +536,9 @@
   </si>
   <si>
     <t>MERCEARIA PADARIA SOMAR</t>
+  </si>
+  <si>
+    <t>GERALDO DE SOUZA OLIVEIRA</t>
   </si>
 </sst>
 </file>
@@ -860,11 +863,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -874,7 +877,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -930,13 +933,13 @@
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -986,13 +989,13 @@
       <c r="B3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1042,13 +1045,13 @@
       <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1095,13 +1098,13 @@
       <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1151,13 +1154,13 @@
       <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -1204,13 +1207,13 @@
       <c r="B7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -1257,13 +1260,13 @@
       <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1310,13 +1313,13 @@
       <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -1363,13 +1366,13 @@
       <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1416,13 +1419,13 @@
       <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11" t="s">
         <v>20</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1446,17 +1449,17 @@
       <c r="L11" s="1">
         <v>46219</v>
       </c>
-      <c r="M11">
-        <v>594789</v>
+      <c r="M11" t="s">
+        <v>160</v>
       </c>
       <c r="N11" t="s">
-        <v>137</v>
-      </c>
-      <c r="O11">
-        <v>10.75</v>
+        <v>160</v>
+      </c>
+      <c r="O11" t="s">
+        <v>160</v>
       </c>
       <c r="P11" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R11" t="s">
         <v>26</v>
@@ -1469,13 +1472,13 @@
       <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1522,13 +1525,13 @@
       <c r="B13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1578,13 +1581,13 @@
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1631,13 +1634,13 @@
       <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1684,13 +1687,13 @@
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1724,7 +1727,7 @@
         <v>3.66</v>
       </c>
       <c r="P16" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="R16" t="s">
         <v>26</v>
@@ -1737,13 +1740,13 @@
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>19</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -1793,13 +1796,13 @@
       <c r="B18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>19</v>
       </c>
       <c r="D18" t="s">
         <v>20</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -1846,13 +1849,13 @@
       <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>19</v>
       </c>
       <c r="D19" t="s">
         <v>20</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -1902,13 +1905,13 @@
       <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>19</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -1958,13 +1961,13 @@
       <c r="B21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>19</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -2014,13 +2017,13 @@
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -2070,13 +2073,13 @@
       <c r="B23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>19</v>
       </c>
       <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -2126,13 +2129,13 @@
       <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>19</v>
       </c>
       <c r="D24" t="s">
         <v>20</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -2182,13 +2185,13 @@
       <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>19</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -2238,13 +2241,13 @@
       <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>19</v>
       </c>
       <c r="D26" t="s">
         <v>20</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -2294,13 +2297,13 @@
       <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>19</v>
       </c>
       <c r="D27" t="s">
         <v>20</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -2350,13 +2353,13 @@
       <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>19</v>
       </c>
       <c r="D28" t="s">
         <v>20</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -2406,13 +2409,13 @@
       <c r="B29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>19</v>
       </c>
       <c r="D29" t="s">
         <v>20</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -2462,13 +2465,13 @@
       <c r="B30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>19</v>
       </c>
       <c r="D30" t="s">
         <v>20</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -2518,13 +2521,13 @@
       <c r="B31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31" t="s">
         <v>20</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -2574,13 +2577,13 @@
       <c r="B32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>19</v>
       </c>
       <c r="D32" t="s">
         <v>20</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -2630,13 +2633,13 @@
       <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>19</v>
       </c>
       <c r="D33" t="s">
         <v>20</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -2686,13 +2689,13 @@
       <c r="B34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>19</v>
       </c>
       <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -2742,13 +2745,13 @@
       <c r="B35" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>19</v>
       </c>
       <c r="D35" t="s">
         <v>20</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -2798,13 +2801,13 @@
       <c r="B36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>19</v>
       </c>
       <c r="D36" t="s">
         <v>20</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -2854,13 +2857,13 @@
       <c r="B37" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" t="s">
         <v>20</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -2910,13 +2913,13 @@
       <c r="B38" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
         <v>20</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -2966,13 +2969,13 @@
       <c r="B39" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>19</v>
       </c>
       <c r="D39" t="s">
         <v>20</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -3022,13 +3025,13 @@
       <c r="B40" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>19</v>
       </c>
       <c r="D40" t="s">
         <v>20</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -3078,13 +3081,13 @@
       <c r="B41" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>19</v>
       </c>
       <c r="D41" t="s">
         <v>20</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F41" s="1" t="s">
@@ -3134,13 +3137,13 @@
       <c r="B42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>19</v>
       </c>
       <c r="D42" t="s">
         <v>20</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -3168,16 +3171,16 @@
         <v>609512</v>
       </c>
       <c r="N42" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="O42">
         <v>7.15</v>
       </c>
       <c r="P42" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q42" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="R42" t="s">
         <v>26</v>
@@ -3190,13 +3193,13 @@
       <c r="B43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>19</v>
       </c>
       <c r="D43" t="s">
         <v>20</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -3246,13 +3249,13 @@
       <c r="B44" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>19</v>
       </c>
       <c r="D44" t="s">
         <v>20</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F44" s="1" t="s">
@@ -3302,13 +3305,13 @@
       <c r="B45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>19</v>
       </c>
       <c r="D45" t="s">
         <v>20</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -3358,13 +3361,13 @@
       <c r="B46" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>19</v>
       </c>
       <c r="D46" t="s">
         <v>20</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -3414,13 +3417,13 @@
       <c r="B47" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>19</v>
       </c>
       <c r="D47" t="s">
         <v>20</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -3470,13 +3473,13 @@
       <c r="B48" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>19</v>
       </c>
       <c r="D48" t="s">
         <v>20</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -3526,13 +3529,13 @@
       <c r="B49" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>19</v>
       </c>
       <c r="D49" t="s">
         <v>20</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -3582,13 +3585,13 @@
       <c r="B50" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>19</v>
       </c>
       <c r="D50" t="s">
         <v>20</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -3638,13 +3641,13 @@
       <c r="B51" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>19</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -3683,8 +3686,8 @@
       <c r="Q51" t="s">
         <v>146</v>
       </c>
-      <c r="R51">
-        <v>1</v>
+      <c r="R51" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -3694,13 +3697,13 @@
       <c r="B52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>19</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -3739,8 +3742,8 @@
       <c r="Q52" t="s">
         <v>146</v>
       </c>
-      <c r="R52">
-        <v>1</v>
+      <c r="R52" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -3750,13 +3753,13 @@
       <c r="B53" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>19</v>
       </c>
       <c r="D53" t="s">
         <v>20</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -3795,8 +3798,8 @@
       <c r="Q53" t="s">
         <v>28</v>
       </c>
-      <c r="R53">
-        <v>1</v>
+      <c r="R53" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -3806,13 +3809,13 @@
       <c r="B54" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>19</v>
       </c>
       <c r="D54" t="s">
         <v>20</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -3851,8 +3854,8 @@
       <c r="Q54" t="s">
         <v>28</v>
       </c>
-      <c r="R54">
-        <v>1</v>
+      <c r="R54" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
@@ -3862,13 +3865,13 @@
       <c r="B55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>19</v>
       </c>
       <c r="D55" t="s">
         <v>20</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -3907,8 +3910,8 @@
       <c r="Q55" t="s">
         <v>28</v>
       </c>
-      <c r="R55">
-        <v>1</v>
+      <c r="R55" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -3918,13 +3921,13 @@
       <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>19</v>
       </c>
       <c r="D56" t="s">
         <v>20</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -3963,8 +3966,8 @@
       <c r="Q56" t="s">
         <v>28</v>
       </c>
-      <c r="R56">
-        <v>1</v>
+      <c r="R56" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
@@ -3974,13 +3977,13 @@
       <c r="B57" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>19</v>
       </c>
       <c r="D57" t="s">
         <v>20</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F57" s="1" t="s">
@@ -4014,7 +4017,7 @@
         <v>6.36</v>
       </c>
       <c r="P57" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q57" t="s">
         <v>28</v>
@@ -4030,13 +4033,13 @@
       <c r="B58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>19</v>
       </c>
       <c r="D58" t="s">
         <v>20</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -4075,8 +4078,8 @@
       <c r="Q58" t="s">
         <v>28</v>
       </c>
-      <c r="R58">
-        <v>1</v>
+      <c r="R58" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
@@ -4086,13 +4089,13 @@
       <c r="B59" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" t="s">
         <v>19</v>
       </c>
       <c r="D59" t="s">
         <v>20</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>93</v>
       </c>
       <c r="F59" s="1" t="s">
@@ -4142,13 +4145,13 @@
       <c r="B60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" t="s">
         <v>19</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -4187,8 +4190,8 @@
       <c r="Q60" t="s">
         <v>28</v>
       </c>
-      <c r="R60">
-        <v>1</v>
+      <c r="R60" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
@@ -4198,13 +4201,13 @@
       <c r="B61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" t="s">
         <v>19</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -4243,8 +4246,8 @@
       <c r="Q61" t="s">
         <v>28</v>
       </c>
-      <c r="R61">
-        <v>1</v>
+      <c r="R61" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
@@ -4254,7 +4257,7 @@
       <c r="B62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" t="s">
         <v>19</v>
       </c>
       <c r="D62" t="s">
@@ -4263,7 +4266,7 @@
       <c r="E62" t="s">
         <v>21</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -4299,8 +4302,8 @@
       <c r="Q62" t="s">
         <v>148</v>
       </c>
-      <c r="R62">
-        <v>1</v>
+      <c r="R62" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -4310,7 +4313,7 @@
       <c r="B63" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" t="s">
         <v>19</v>
       </c>
       <c r="D63" t="s">
@@ -4319,7 +4322,7 @@
       <c r="E63" t="s">
         <v>31</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -4350,13 +4353,13 @@
         <v>17.97</v>
       </c>
       <c r="P63" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q63" t="s">
         <v>28</v>
       </c>
-      <c r="R63" t="e">
-        <v>#N/A</v>
+      <c r="R63" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -4366,7 +4369,7 @@
       <c r="B64" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" t="s">
         <v>19</v>
       </c>
       <c r="D64" t="s">
@@ -4381,7 +4384,7 @@
       <c r="G64" t="s">
         <v>95</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="1">
         <v>14</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -4422,7 +4425,7 @@
       <c r="B65" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" t="s">
         <v>19</v>
       </c>
       <c r="D65" t="s">
@@ -4437,7 +4440,7 @@
       <c r="G65" t="s">
         <v>32</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="1">
         <v>14</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -4462,13 +4465,13 @@
         <v>8.5399999999999991</v>
       </c>
       <c r="P65" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q65" t="s">
         <v>28</v>
       </c>
-      <c r="R65" t="e">
-        <v>#N/A</v>
+      <c r="R65" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
@@ -4478,7 +4481,7 @@
       <c r="B66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" t="s">
         <v>19</v>
       </c>
       <c r="D66" t="s">
@@ -4496,7 +4499,7 @@
       <c r="H66">
         <v>15</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J66" s="1" t="s">
@@ -4523,8 +4526,8 @@
       <c r="Q66" t="s">
         <v>28</v>
       </c>
-      <c r="R66">
-        <v>1</v>
+      <c r="R66" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
@@ -4534,7 +4537,7 @@
       <c r="B67" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" t="s">
         <v>19</v>
       </c>
       <c r="D67" t="s">
@@ -4552,7 +4555,7 @@
       <c r="H67">
         <v>15</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J67" s="1" t="s">
@@ -4579,8 +4582,8 @@
       <c r="Q67" t="s">
         <v>28</v>
       </c>
-      <c r="R67">
-        <v>1</v>
+      <c r="R67" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
@@ -4590,7 +4593,7 @@
       <c r="B68" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" t="s">
         <v>19</v>
       </c>
       <c r="D68" t="s">
@@ -4611,7 +4614,7 @@
       <c r="I68" t="s">
         <v>122</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K68" s="1" t="s">
@@ -4630,13 +4633,13 @@
         <v>8.57</v>
       </c>
       <c r="P68" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q68" t="s">
         <v>28</v>
       </c>
-      <c r="R68" t="e">
-        <v>#N/A</v>
+      <c r="R68" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -4646,7 +4649,7 @@
       <c r="B69" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" t="s">
         <v>19</v>
       </c>
       <c r="D69" t="s">
@@ -4667,7 +4670,7 @@
       <c r="I69" t="s">
         <v>122</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K69" s="1" t="s">
@@ -4691,8 +4694,8 @@
       <c r="Q69" t="s">
         <v>28</v>
       </c>
-      <c r="R69" t="e">
-        <v>#N/A</v>
+      <c r="R69" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -4702,7 +4705,7 @@
       <c r="B70" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" t="s">
         <v>19</v>
       </c>
       <c r="D70" t="s">
@@ -4726,7 +4729,7 @@
       <c r="J70" t="s">
         <v>25</v>
       </c>
-      <c r="K70" t="s">
+      <c r="K70" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L70" s="1">
@@ -4758,7 +4761,7 @@
       <c r="B71" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" t="s">
         <v>19</v>
       </c>
       <c r="D71" t="s">
@@ -4782,7 +4785,7 @@
       <c r="J71" t="s">
         <v>25</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K71" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L71" s="1">
@@ -4814,7 +4817,7 @@
       <c r="B72" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" t="s">
         <v>19</v>
       </c>
       <c r="D72" t="s">
@@ -4838,7 +4841,7 @@
       <c r="J72" t="s">
         <v>25</v>
       </c>
-      <c r="K72" t="s">
+      <c r="K72" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L72" s="1">
@@ -4870,7 +4873,7 @@
       <c r="B73" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" t="s">
         <v>19</v>
       </c>
       <c r="D73" t="s">
@@ -4894,7 +4897,7 @@
       <c r="J73" t="s">
         <v>25</v>
       </c>
-      <c r="K73" t="s">
+      <c r="K73" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L73" s="1">
@@ -4910,17 +4913,73 @@
         <v>5.46</v>
       </c>
       <c r="P73" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>28</v>
+      </c>
+      <c r="R73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>29</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
+        <v>31</v>
+      </c>
+      <c r="F74" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74">
+        <v>18</v>
+      </c>
+      <c r="I74" t="s">
+        <v>122</v>
+      </c>
+      <c r="J74" t="s">
+        <v>25</v>
+      </c>
+      <c r="K74" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="1">
+        <v>46283</v>
+      </c>
+      <c r="M74">
+        <v>622716</v>
+      </c>
+      <c r="N74" t="s">
+        <v>137</v>
+      </c>
+      <c r="O74">
+        <v>5.33</v>
+      </c>
+      <c r="P74" t="s">
         <v>27</v>
       </c>
-      <c r="Q73" t="s">
-        <v>28</v>
-      </c>
-      <c r="R73" t="e">
+      <c r="Q74" t="s">
+        <v>28</v>
+      </c>
+      <c r="R74" t="e">
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:A43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5743,31 +5802,31 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>135.60599999999999</v>
+        <v>163.934</v>
       </c>
       <c r="E22">
-        <v>75.700130000000001</v>
+        <v>92.051410000000004</v>
       </c>
       <c r="F22">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G22">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H22">
         <v>27</v>
       </c>
       <c r="I22">
-        <v>0.9</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="J22">
-        <v>1.0888888888888888</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="K22">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="L22">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -5784,28 +5843,28 @@
         <v>84</v>
       </c>
       <c r="E23">
-        <v>33.459470000000003</v>
+        <v>40.2303</v>
       </c>
       <c r="F23">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G23">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H23">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="I23">
-        <v>0.93333333333333335</v>
+        <v>0.95</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>1.0166666666666666</v>
       </c>
       <c r="K23">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L23">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -5822,28 +5881,28 @@
         <v>84</v>
       </c>
       <c r="E24">
-        <v>32.393349999999998</v>
+        <v>43.190839999999994</v>
       </c>
       <c r="F24">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G24">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H24">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I24">
-        <v>0.53333333333333333</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>0.98333333333333328</v>
       </c>
       <c r="K24">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L24">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5968,17 +6027,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -6239,6 +6287,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6249,17 +6308,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6278,6 +6326,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A24EFE9-E33D-4923-AD0A-6D35B17C2B29}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFDB72B8-660C-4072-A6EC-A68400A86436}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -866,15 +866,14 @@
   <dimension ref="A1:R74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -930,13 +929,13 @@
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -986,13 +985,13 @@
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1042,13 +1041,13 @@
       <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1095,13 +1094,13 @@
       <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1151,13 +1150,13 @@
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1204,13 +1203,13 @@
       <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>63</v>
       </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1257,13 +1256,13 @@
       <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1310,13 +1309,13 @@
       <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1363,13 +1362,13 @@
       <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1416,13 +1415,13 @@
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1469,13 +1468,13 @@
       <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>51</v>
       </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1522,13 +1521,13 @@
       <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>61</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1578,13 +1577,13 @@
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>34</v>
       </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1631,13 +1630,13 @@
       <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>65</v>
       </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1684,13 +1683,13 @@
       <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1737,13 +1736,13 @@
       <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>50</v>
       </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1793,13 +1792,13 @@
       <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1846,13 +1845,13 @@
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>42</v>
       </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1902,13 +1901,13 @@
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>41</v>
       </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1958,13 +1957,13 @@
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>62</v>
       </c>
-      <c r="C21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -2014,13 +2013,13 @@
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -2070,13 +2069,13 @@
       <c r="A23" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>37</v>
       </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2126,13 +2125,13 @@
       <c r="A24" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>60</v>
       </c>
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -2182,13 +2181,13 @@
       <c r="A25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>46</v>
       </c>
-      <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -2238,13 +2237,13 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>18</v>
       </c>
-      <c r="C26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -2294,13 +2293,13 @@
       <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>47</v>
       </c>
-      <c r="C27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2350,13 +2349,13 @@
       <c r="A28" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>92</v>
       </c>
-      <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -2406,13 +2405,13 @@
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>96</v>
       </c>
-      <c r="C29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -2462,13 +2461,13 @@
       <c r="A30" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>97</v>
       </c>
-      <c r="C30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -2518,13 +2517,13 @@
       <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>98</v>
       </c>
-      <c r="C31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -2574,13 +2573,13 @@
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>99</v>
       </c>
-      <c r="C32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -2630,13 +2629,13 @@
       <c r="A33" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>102</v>
       </c>
-      <c r="C33" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2686,13 +2685,13 @@
       <c r="A34" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>101</v>
       </c>
-      <c r="C34" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2742,13 +2741,13 @@
       <c r="A35" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>103</v>
       </c>
-      <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -2798,13 +2797,13 @@
       <c r="A36" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>104</v>
       </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -2854,13 +2853,13 @@
       <c r="A37" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>105</v>
       </c>
-      <c r="C37" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -2910,13 +2909,13 @@
       <c r="A38" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>106</v>
       </c>
-      <c r="C38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -2966,13 +2965,13 @@
       <c r="A39" t="s">
         <v>72</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>107</v>
       </c>
-      <c r="C39" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -3022,13 +3021,13 @@
       <c r="A40" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>109</v>
       </c>
-      <c r="C40" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -3078,13 +3077,13 @@
       <c r="A41" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>110</v>
       </c>
-      <c r="C41" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -3134,13 +3133,13 @@
       <c r="A42" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>111</v>
       </c>
-      <c r="C42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -3190,13 +3189,13 @@
       <c r="A43" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>112</v>
       </c>
-      <c r="C43" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -3246,13 +3245,13 @@
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>113</v>
       </c>
-      <c r="C44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -3302,13 +3301,13 @@
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>114</v>
       </c>
-      <c r="C45" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -3358,13 +3357,13 @@
       <c r="A46" t="s">
         <v>29</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>115</v>
       </c>
-      <c r="C46" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
@@ -3414,13 +3413,13 @@
       <c r="A47" t="s">
         <v>29</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>116</v>
       </c>
-      <c r="C47" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -3470,13 +3469,13 @@
       <c r="A48" t="s">
         <v>72</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>117</v>
       </c>
-      <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -3526,13 +3525,13 @@
       <c r="A49" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>118</v>
       </c>
-      <c r="C49" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -3582,13 +3581,13 @@
       <c r="A50" t="s">
         <v>72</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>120</v>
       </c>
-      <c r="C50" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -3638,13 +3637,13 @@
       <c r="A51" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>121</v>
       </c>
-      <c r="C51" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -3672,19 +3671,19 @@
         <v>46266</v>
       </c>
       <c r="M51">
-        <v>615019</v>
+        <v>614020</v>
       </c>
       <c r="N51" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="O51">
-        <v>7.95</v>
+        <v>2.33</v>
       </c>
       <c r="P51" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q51" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="R51" t="s">
         <v>26</v>
@@ -3692,25 +3691,25 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>72</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="H52" s="1">
         <v>3</v>
@@ -3728,19 +3727,19 @@
         <v>46268</v>
       </c>
       <c r="M52">
-        <v>615019</v>
+        <v>614995</v>
       </c>
       <c r="N52" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="O52">
-        <v>7.95</v>
+        <v>1.91</v>
       </c>
       <c r="P52" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q52" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="R52" t="s">
         <v>26</v>
@@ -3748,25 +3747,25 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="H53" s="1">
         <v>3</v>
@@ -3784,19 +3783,19 @@
         <v>46268</v>
       </c>
       <c r="M53">
-        <v>614995</v>
+        <v>615019</v>
       </c>
       <c r="N53" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="O53">
-        <v>1.91</v>
+        <v>7.95</v>
       </c>
       <c r="P53" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q53" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="R53" t="s">
         <v>26</v>
@@ -3806,13 +3805,13 @@
       <c r="A54" t="s">
         <v>29</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
         <v>125</v>
       </c>
-      <c r="C54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -3862,13 +3861,13 @@
       <c r="A55" t="s">
         <v>29</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>126</v>
       </c>
-      <c r="C55" t="s">
-        <v>19</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -3918,13 +3917,13 @@
       <c r="A56" t="s">
         <v>29</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>128</v>
       </c>
-      <c r="C56" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -3974,13 +3973,13 @@
       <c r="A57" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>129</v>
       </c>
-      <c r="C57" t="s">
-        <v>19</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -4030,13 +4029,13 @@
       <c r="A58" t="s">
         <v>29</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" t="s">
         <v>131</v>
       </c>
-      <c r="C58" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -4084,25 +4083,25 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>72</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="H59" s="1">
         <v>9</v>
@@ -4120,13 +4119,13 @@
         <v>46274</v>
       </c>
       <c r="M59">
-        <v>617206</v>
+        <v>617229</v>
       </c>
       <c r="N59" t="s">
         <v>137</v>
       </c>
       <c r="O59">
-        <v>21.23</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="P59" t="s">
         <v>35</v>
@@ -4134,31 +4133,31 @@
       <c r="Q59" t="s">
         <v>28</v>
       </c>
-      <c r="R59" t="e">
-        <v>#N/A</v>
+      <c r="R59" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>29</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C60" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="H60" s="1">
         <v>9</v>
@@ -4176,13 +4175,13 @@
         <v>46274</v>
       </c>
       <c r="M60">
-        <v>617229</v>
+        <v>617206</v>
       </c>
       <c r="N60" t="s">
         <v>137</v>
       </c>
       <c r="O60">
-        <v>2.2200000000000002</v>
+        <v>21.23</v>
       </c>
       <c r="P60" t="s">
         <v>35</v>
@@ -4190,21 +4189,21 @@
       <c r="Q60" t="s">
         <v>28</v>
       </c>
-      <c r="R60" t="s">
-        <v>26</v>
+      <c r="R60" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>29</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
         <v>136</v>
       </c>
-      <c r="C61" t="s">
-        <v>19</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -4254,16 +4253,16 @@
       <c r="A62" t="s">
         <v>17</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>138</v>
       </c>
       <c r="C62" t="s">
         <v>19</v>
       </c>
-      <c r="D62" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="D62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -4310,16 +4309,16 @@
       <c r="A63" t="s">
         <v>29</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" t="s">
         <v>139</v>
       </c>
       <c r="C63" t="s">
         <v>19</v>
       </c>
-      <c r="D63" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="D63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F63" s="1" t="s">
@@ -4364,10 +4363,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>72</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>140</v>
+        <v>29</v>
+      </c>
+      <c r="B64" t="s">
+        <v>142</v>
       </c>
       <c r="C64" t="s">
         <v>19</v>
@@ -4376,13 +4375,13 @@
         <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>141</v>
-      </c>
-      <c r="F64" t="s">
-        <v>94</v>
-      </c>
-      <c r="G64" t="s">
-        <v>95</v>
+        <v>31</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="H64" s="1">
         <v>14</v>
@@ -4400,13 +4399,13 @@
         <v>46279</v>
       </c>
       <c r="M64">
-        <v>619855</v>
+        <v>619980</v>
       </c>
       <c r="N64" t="s">
         <v>137</v>
       </c>
       <c r="O64">
-        <v>4.68</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="P64" t="s">
         <v>35</v>
@@ -4414,16 +4413,16 @@
       <c r="Q64" t="s">
         <v>28</v>
       </c>
-      <c r="R64" t="e">
-        <v>#N/A</v>
+      <c r="R64" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>29</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>142</v>
+        <v>72</v>
+      </c>
+      <c r="B65" t="s">
+        <v>140</v>
       </c>
       <c r="C65" t="s">
         <v>19</v>
@@ -4432,13 +4431,13 @@
         <v>20</v>
       </c>
       <c r="E65" t="s">
-        <v>31</v>
-      </c>
-      <c r="F65" t="s">
-        <v>22</v>
-      </c>
-      <c r="G65" t="s">
-        <v>32</v>
+        <v>141</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H65" s="1">
         <v>14</v>
@@ -4456,13 +4455,13 @@
         <v>46279</v>
       </c>
       <c r="M65">
-        <v>619980</v>
+        <v>619855</v>
       </c>
       <c r="N65" t="s">
         <v>137</v>
       </c>
       <c r="O65">
-        <v>8.5399999999999991</v>
+        <v>4.68</v>
       </c>
       <c r="P65" t="s">
         <v>35</v>
@@ -4470,16 +4469,16 @@
       <c r="Q65" t="s">
         <v>28</v>
       </c>
-      <c r="R65" t="s">
-        <v>26</v>
+      <c r="R65" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>17</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>150</v>
+        <v>72</v>
+      </c>
+      <c r="B66" t="s">
+        <v>151</v>
       </c>
       <c r="C66" t="s">
         <v>19</v>
@@ -4488,15 +4487,15 @@
         <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
-      </c>
-      <c r="G66" t="s">
-        <v>23</v>
-      </c>
-      <c r="H66">
+        <v>94</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H66" s="1">
         <v>15</v>
       </c>
       <c r="I66" s="1" t="s">
@@ -4512,16 +4511,16 @@
         <v>46280</v>
       </c>
       <c r="M66">
-        <v>617205</v>
+        <v>620157</v>
       </c>
       <c r="N66" t="s">
         <v>137</v>
       </c>
       <c r="O66">
-        <v>14.62</v>
+        <v>6.46</v>
       </c>
       <c r="P66" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="Q66" t="s">
         <v>28</v>
@@ -4532,10 +4531,10 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>72</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>17</v>
+      </c>
+      <c r="B67" t="s">
+        <v>150</v>
       </c>
       <c r="C67" t="s">
         <v>19</v>
@@ -4544,15 +4543,15 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>94</v>
-      </c>
-      <c r="G67" t="s">
-        <v>95</v>
-      </c>
-      <c r="H67">
+        <v>22</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="1">
         <v>15</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -4568,16 +4567,16 @@
         <v>46280</v>
       </c>
       <c r="M67">
-        <v>620157</v>
+        <v>617205</v>
       </c>
       <c r="N67" t="s">
         <v>137</v>
       </c>
       <c r="O67">
-        <v>6.46</v>
+        <v>14.62</v>
       </c>
       <c r="P67" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="Q67" t="s">
         <v>28</v>
@@ -4590,7 +4589,7 @@
       <c r="A68" t="s">
         <v>29</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
         <v>158</v>
       </c>
       <c r="C68" t="s">
@@ -4608,10 +4607,10 @@
       <c r="G68" t="s">
         <v>32</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="1">
         <v>15</v>
       </c>
-      <c r="I68" t="s">
+      <c r="I68" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J68" s="1" t="s">
@@ -4646,7 +4645,7 @@
       <c r="A69" t="s">
         <v>72</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" t="s">
         <v>159</v>
       </c>
       <c r="C69" t="s">
@@ -4664,10 +4663,10 @@
       <c r="G69" t="s">
         <v>95</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="1">
         <v>16</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J69" s="1" t="s">
@@ -4700,10 +4699,10 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>17</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>161</v>
+        <v>72</v>
+      </c>
+      <c r="B70" t="s">
+        <v>162</v>
       </c>
       <c r="C70" t="s">
         <v>19</v>
@@ -4712,21 +4711,21 @@
         <v>20</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="F70" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="G70" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="H70">
         <v>17</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K70" s="1" t="s">
@@ -4736,16 +4735,16 @@
         <v>46282</v>
       </c>
       <c r="M70">
-        <v>620938</v>
+        <v>621205</v>
       </c>
       <c r="N70" t="s">
         <v>137</v>
       </c>
       <c r="O70">
-        <v>11.75</v>
+        <v>5.95</v>
       </c>
       <c r="P70" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="Q70" t="s">
         <v>28</v>
@@ -4756,10 +4755,10 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>72</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>162</v>
+        <v>29</v>
+      </c>
+      <c r="B71" t="s">
+        <v>163</v>
       </c>
       <c r="C71" t="s">
         <v>19</v>
@@ -4768,21 +4767,21 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="F71" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="G71" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="H71">
         <v>17</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K71" s="1" t="s">
@@ -4792,13 +4791,13 @@
         <v>46282</v>
       </c>
       <c r="M71">
-        <v>621205</v>
+        <v>621574</v>
       </c>
       <c r="N71" t="s">
         <v>137</v>
       </c>
       <c r="O71">
-        <v>5.95</v>
+        <v>3.78</v>
       </c>
       <c r="P71" t="s">
         <v>27</v>
@@ -4814,8 +4813,8 @@
       <c r="A72" t="s">
         <v>29</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>163</v>
+      <c r="B72" t="s">
+        <v>164</v>
       </c>
       <c r="C72" t="s">
         <v>19</v>
@@ -4835,10 +4834,10 @@
       <c r="H72">
         <v>17</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I72" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J72" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K72" s="1" t="s">
@@ -4848,30 +4847,30 @@
         <v>46282</v>
       </c>
       <c r="M72">
-        <v>621574</v>
+        <v>621242</v>
       </c>
       <c r="N72" t="s">
         <v>137</v>
       </c>
       <c r="O72">
-        <v>3.78</v>
+        <v>5.46</v>
       </c>
       <c r="P72" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q72" t="s">
         <v>28</v>
       </c>
-      <c r="R72" t="e">
-        <v>#N/A</v>
+      <c r="R72" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>29</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>164</v>
+        <v>17</v>
+      </c>
+      <c r="B73" t="s">
+        <v>161</v>
       </c>
       <c r="C73" t="s">
         <v>19</v>
@@ -4880,21 +4879,21 @@
         <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F73" t="s">
         <v>22</v>
       </c>
       <c r="G73" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H73">
         <v>17</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I73" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J73" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K73" s="1" t="s">
@@ -4904,13 +4903,13 @@
         <v>46282</v>
       </c>
       <c r="M73">
-        <v>621242</v>
+        <v>620938</v>
       </c>
       <c r="N73" t="s">
         <v>137</v>
       </c>
       <c r="O73">
-        <v>5.46</v>
+        <v>11.75</v>
       </c>
       <c r="P73" t="s">
         <v>35</v>
@@ -4918,15 +4917,15 @@
       <c r="Q73" t="s">
         <v>28</v>
       </c>
-      <c r="R73" t="s">
-        <v>26</v>
+      <c r="R73" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" t="s">
         <v>165</v>
       </c>
       <c r="C74" t="s">
@@ -4950,10 +4949,10 @@
       <c r="I74" t="s">
         <v>122</v>
       </c>
-      <c r="J74" t="s">
-        <v>25</v>
-      </c>
-      <c r="K74" t="s">
+      <c r="J74" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L74" s="1">
@@ -5802,31 +5801,31 @@
         <v>29</v>
       </c>
       <c r="D22">
-        <v>163.934</v>
+        <v>179.82400000000001</v>
       </c>
       <c r="E22">
-        <v>92.051410000000004</v>
+        <v>107.06861000000001</v>
       </c>
       <c r="F22">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G22">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H22">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I22">
-        <v>0.67500000000000004</v>
+        <v>0.72</v>
       </c>
       <c r="J22">
-        <v>1.0666666666666667</v>
+        <v>1.0533333333333332</v>
       </c>
       <c r="K22">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L22">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -5843,28 +5842,28 @@
         <v>84</v>
       </c>
       <c r="E23">
-        <v>40.2303</v>
+        <v>54.846879999999999</v>
       </c>
       <c r="F23">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G23">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H23">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I23">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="J23">
-        <v>1.0166666666666666</v>
+        <v>1.0533333333333332</v>
       </c>
       <c r="K23">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="L23">
-        <v>61</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -5881,28 +5880,28 @@
         <v>84</v>
       </c>
       <c r="E24">
-        <v>43.190839999999994</v>
+        <v>52.09149</v>
       </c>
       <c r="F24">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G24">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="H24">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I24">
-        <v>0.52500000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="J24">
-        <v>0.98333333333333328</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="L24">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFDB72B8-660C-4072-A6EC-A68400A86436}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A77949AB-5086-44D6-B235-7C226F00EE13}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="169">
   <si>
     <t>Usuário</t>
   </si>
@@ -448,9 +448,6 @@
     <t>FABIO DUARTE ROSA</t>
   </si>
   <si>
-    <t>Semana1</t>
-  </si>
-  <si>
     <t>IZABELA IZARIAS</t>
   </si>
   <si>
@@ -502,9 +499,6 @@
     <t>Ana Paula Bandeira</t>
   </si>
   <si>
-    <t>semana2</t>
-  </si>
-  <si>
     <t>NÃO CONCORDOU COM MINUTA CONTRATUAL</t>
   </si>
   <si>
@@ -539,6 +533,21 @@
   </si>
   <si>
     <t>GERALDO DE SOUZA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>NEGOCIAÇÃO QUENTE</t>
+  </si>
+  <si>
+    <t>LEANDRO FERREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>RONY APARECIDA FEDOSI</t>
+  </si>
+  <si>
+    <t>semana 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana 3 </t>
   </si>
 </sst>
 </file>
@@ -580,9 +589,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -863,10 +873,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R74"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -929,7 +940,7 @@
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -941,7 +952,7 @@
       <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -956,7 +967,7 @@
       <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
       <c r="L2" s="1">
@@ -975,7 +986,7 @@
         <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R2" t="s">
         <v>26</v>
@@ -985,7 +996,7 @@
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -997,7 +1008,7 @@
       <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1012,7 +1023,7 @@
       <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="1">
@@ -1031,7 +1042,7 @@
         <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R3" t="s">
         <v>26</v>
@@ -1041,7 +1052,7 @@
       <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1053,7 +1064,7 @@
       <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1068,7 +1079,7 @@
       <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="1">
@@ -1094,7 +1105,7 @@
       <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1106,7 +1117,7 @@
       <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1121,7 +1132,7 @@
       <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="1">
@@ -1140,7 +1151,7 @@
         <v>28</v>
       </c>
       <c r="Q5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R5" t="s">
         <v>26</v>
@@ -1150,7 +1161,7 @@
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1162,7 +1173,7 @@
       <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1177,7 +1188,7 @@
       <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" t="s">
         <v>26</v>
       </c>
       <c r="L6" s="1">
@@ -1187,7 +1198,7 @@
         <v>588146</v>
       </c>
       <c r="N6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O6">
         <v>67.37</v>
@@ -1203,7 +1214,7 @@
       <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1215,7 +1226,7 @@
       <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1230,7 +1241,7 @@
       <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="K7" t="s">
         <v>26</v>
       </c>
       <c r="L7" s="1">
@@ -1240,7 +1251,7 @@
         <v>588663</v>
       </c>
       <c r="N7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O7">
         <v>35.78</v>
@@ -1256,7 +1267,7 @@
       <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1268,7 +1279,7 @@
       <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1283,7 +1294,7 @@
       <c r="J8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="K8" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="1">
@@ -1309,7 +1320,7 @@
       <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1321,7 +1332,7 @@
       <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1336,7 +1347,7 @@
       <c r="J9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="K9" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="1">
@@ -1346,7 +1357,7 @@
         <v>591481</v>
       </c>
       <c r="N9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1362,7 +1373,7 @@
       <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1374,7 +1385,7 @@
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1389,23 +1400,23 @@
       <c r="J10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" t="s">
         <v>26</v>
       </c>
       <c r="L10" s="1">
         <v>46218</v>
       </c>
-      <c r="M10">
-        <v>591629</v>
+      <c r="M10" t="s">
+        <v>158</v>
       </c>
       <c r="N10" t="s">
-        <v>137</v>
-      </c>
-      <c r="O10">
-        <v>10.44</v>
+        <v>158</v>
+      </c>
+      <c r="O10" t="s">
+        <v>158</v>
       </c>
       <c r="P10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R10" t="s">
         <v>26</v>
@@ -1415,7 +1426,7 @@
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1427,7 +1438,7 @@
       <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1442,20 +1453,20 @@
       <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K11" t="s">
         <v>26</v>
       </c>
       <c r="L11" s="1">
         <v>46219</v>
       </c>
       <c r="M11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P11" t="s">
         <v>28</v>
@@ -1468,7 +1479,7 @@
       <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1480,7 +1491,7 @@
       <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1495,7 +1506,7 @@
       <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="1">
@@ -1521,7 +1532,7 @@
       <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1533,7 +1544,7 @@
       <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1548,7 +1559,7 @@
       <c r="J13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" t="s">
         <v>26</v>
       </c>
       <c r="L13" s="1">
@@ -1567,7 +1578,7 @@
         <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R13" t="s">
         <v>26</v>
@@ -1577,7 +1588,7 @@
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1589,7 +1600,7 @@
       <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1604,20 +1615,20 @@
       <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="K14" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="1">
         <v>46225</v>
       </c>
       <c r="M14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P14" t="s">
         <v>28</v>
@@ -1630,7 +1641,7 @@
       <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1642,7 +1653,7 @@
       <c r="E15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1657,7 +1668,7 @@
       <c r="J15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" t="s">
         <v>26</v>
       </c>
       <c r="L15" s="1">
@@ -1683,7 +1694,7 @@
       <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1695,7 +1706,7 @@
       <c r="E16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1710,7 +1721,7 @@
       <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" t="s">
         <v>26</v>
       </c>
       <c r="L16" s="1">
@@ -1720,7 +1731,7 @@
         <v>593213</v>
       </c>
       <c r="N16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O16">
         <v>3.66</v>
@@ -1736,7 +1747,7 @@
       <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -1748,7 +1759,7 @@
       <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1763,7 +1774,7 @@
       <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="K17" t="s">
         <v>26</v>
       </c>
       <c r="L17" s="1">
@@ -1782,7 +1793,7 @@
         <v>28</v>
       </c>
       <c r="Q17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R17" t="s">
         <v>26</v>
@@ -1792,7 +1803,7 @@
       <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -1804,7 +1815,7 @@
       <c r="E18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1819,7 +1830,7 @@
       <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="K18" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="1">
@@ -1829,7 +1840,7 @@
         <v>598353</v>
       </c>
       <c r="N18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O18">
         <v>6.9</v>
@@ -1845,7 +1856,7 @@
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1857,7 +1868,7 @@
       <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1872,7 +1883,7 @@
       <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="1">
@@ -1891,7 +1902,7 @@
         <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R19" t="s">
         <v>26</v>
@@ -1901,7 +1912,7 @@
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -1913,7 +1924,7 @@
       <c r="E20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1928,7 +1939,7 @@
       <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K20" t="s">
         <v>26</v>
       </c>
       <c r="L20" s="1">
@@ -1938,7 +1949,7 @@
         <v>601025</v>
       </c>
       <c r="N20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O20">
         <v>41.62</v>
@@ -1957,7 +1968,7 @@
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -1969,7 +1980,7 @@
       <c r="E21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -1984,7 +1995,7 @@
       <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K21" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="1">
@@ -1994,7 +2005,7 @@
         <v>601537</v>
       </c>
       <c r="N21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O21">
         <v>4.63</v>
@@ -2013,7 +2024,7 @@
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -2025,7 +2036,7 @@
       <c r="E22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -2040,7 +2051,7 @@
       <c r="J22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K22" t="s">
         <v>26</v>
       </c>
       <c r="L22" s="1">
@@ -2050,7 +2061,7 @@
         <v>601944</v>
       </c>
       <c r="N22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O22">
         <v>1.96</v>
@@ -2069,7 +2080,7 @@
       <c r="A23" t="s">
         <v>29</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -2081,7 +2092,7 @@
       <c r="E23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -2096,7 +2107,7 @@
       <c r="J23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="K23" t="s">
         <v>26</v>
       </c>
       <c r="L23" s="1">
@@ -2115,7 +2126,7 @@
         <v>28</v>
       </c>
       <c r="Q23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R23" t="s">
         <v>26</v>
@@ -2125,7 +2136,7 @@
       <c r="A24" t="s">
         <v>29</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -2137,7 +2148,7 @@
       <c r="E24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -2152,7 +2163,7 @@
       <c r="J24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="1">
@@ -2162,7 +2173,7 @@
         <v>602969</v>
       </c>
       <c r="N24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O24">
         <v>6.12</v>
@@ -2181,7 +2192,7 @@
       <c r="A25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -2193,7 +2204,7 @@
       <c r="E25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2208,7 +2219,7 @@
       <c r="J25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" t="s">
         <v>26</v>
       </c>
       <c r="L25" s="1">
@@ -2218,7 +2229,7 @@
         <v>603608</v>
       </c>
       <c r="N25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O25">
         <v>8.77</v>
@@ -2237,7 +2248,7 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -2249,7 +2260,7 @@
       <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -2264,7 +2275,7 @@
       <c r="J26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K26" t="s">
         <v>26</v>
       </c>
       <c r="L26" s="1">
@@ -2274,7 +2285,7 @@
         <v>604128</v>
       </c>
       <c r="N26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O26">
         <v>8.3699999999999992</v>
@@ -2293,7 +2304,7 @@
       <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -2305,7 +2316,7 @@
       <c r="E27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -2320,7 +2331,7 @@
       <c r="J27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="K27" t="s">
         <v>26</v>
       </c>
       <c r="L27" s="1">
@@ -2339,7 +2350,7 @@
         <v>28</v>
       </c>
       <c r="Q27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R27" t="s">
         <v>26</v>
@@ -2349,7 +2360,7 @@
       <c r="A28" t="s">
         <v>72</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -2361,7 +2372,7 @@
       <c r="E28" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2376,7 +2387,7 @@
       <c r="J28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="K28" t="s">
         <v>26</v>
       </c>
       <c r="L28" s="1">
@@ -2386,7 +2397,7 @@
         <v>605287</v>
       </c>
       <c r="N28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O28">
         <v>61.58</v>
@@ -2405,7 +2416,7 @@
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -2417,7 +2428,7 @@
       <c r="E29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2432,7 +2443,7 @@
       <c r="J29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K29" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="1">
@@ -2442,7 +2453,7 @@
         <v>605244</v>
       </c>
       <c r="N29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O29">
         <v>91.5</v>
@@ -2461,7 +2472,7 @@
       <c r="A30" t="s">
         <v>72</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -2473,7 +2484,7 @@
       <c r="E30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2488,7 +2499,7 @@
       <c r="J30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="K30" t="s">
         <v>26</v>
       </c>
       <c r="L30" s="1">
@@ -2517,7 +2528,7 @@
       <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -2529,7 +2540,7 @@
       <c r="E31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -2544,7 +2555,7 @@
       <c r="J31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="K31" t="s">
         <v>26</v>
       </c>
       <c r="L31" s="1">
@@ -2554,7 +2565,7 @@
         <v>606908</v>
       </c>
       <c r="N31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O31">
         <v>37.299999999999997</v>
@@ -2573,7 +2584,7 @@
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -2585,7 +2596,7 @@
       <c r="E32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -2600,7 +2611,7 @@
       <c r="J32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" t="s">
         <v>26</v>
       </c>
       <c r="L32" s="1">
@@ -2610,7 +2621,7 @@
         <v>581722</v>
       </c>
       <c r="N32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O32">
         <v>21.24</v>
@@ -2629,7 +2640,7 @@
       <c r="A33" t="s">
         <v>72</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -2641,7 +2652,7 @@
       <c r="E33" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -2656,7 +2667,7 @@
       <c r="J33" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="K33" t="s">
         <v>26</v>
       </c>
       <c r="L33" s="1">
@@ -2675,7 +2686,7 @@
         <v>28</v>
       </c>
       <c r="Q33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R33" t="s">
         <v>26</v>
@@ -2685,7 +2696,7 @@
       <c r="A34" t="s">
         <v>29</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2697,7 +2708,7 @@
       <c r="E34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -2712,7 +2723,7 @@
       <c r="J34" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="1">
@@ -2731,7 +2742,7 @@
         <v>28</v>
       </c>
       <c r="Q34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R34" t="s">
         <v>26</v>
@@ -2741,7 +2752,7 @@
       <c r="A35" t="s">
         <v>72</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2753,7 +2764,7 @@
       <c r="E35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -2768,7 +2779,7 @@
       <c r="J35" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="K35" t="s">
         <v>26</v>
       </c>
       <c r="L35" s="1">
@@ -2797,7 +2808,7 @@
       <c r="A36" t="s">
         <v>72</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -2809,7 +2820,7 @@
       <c r="E36" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -2824,7 +2835,7 @@
       <c r="J36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K36" t="s">
         <v>26</v>
       </c>
       <c r="L36" s="1">
@@ -2843,7 +2854,7 @@
         <v>28</v>
       </c>
       <c r="Q36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R36" t="s">
         <v>26</v>
@@ -2853,7 +2864,7 @@
       <c r="A37" t="s">
         <v>72</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -2865,7 +2876,7 @@
       <c r="E37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -2880,7 +2891,7 @@
       <c r="J37" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K37" t="s">
         <v>26</v>
       </c>
       <c r="L37" s="1">
@@ -2899,7 +2910,7 @@
         <v>28</v>
       </c>
       <c r="Q37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R37" t="s">
         <v>26</v>
@@ -2909,7 +2920,7 @@
       <c r="A38" t="s">
         <v>72</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -2921,7 +2932,7 @@
       <c r="E38" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -2936,7 +2947,7 @@
       <c r="J38" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="K38" t="s">
         <v>26</v>
       </c>
       <c r="L38" s="1">
@@ -2946,7 +2957,7 @@
         <v>609384</v>
       </c>
       <c r="N38" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O38">
         <v>3.39</v>
@@ -2965,7 +2976,7 @@
       <c r="A39" t="s">
         <v>72</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -2977,7 +2988,7 @@
       <c r="E39" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -2992,7 +3003,7 @@
       <c r="J39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="K39" t="s">
         <v>26</v>
       </c>
       <c r="L39" s="1">
@@ -3021,7 +3032,7 @@
       <c r="A40" t="s">
         <v>72</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -3033,7 +3044,7 @@
       <c r="E40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -3048,7 +3059,7 @@
       <c r="J40" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K40" t="s">
         <v>26</v>
       </c>
       <c r="L40" s="1">
@@ -3058,7 +3069,7 @@
         <v>604864</v>
       </c>
       <c r="N40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O40">
         <v>19.47</v>
@@ -3077,7 +3088,7 @@
       <c r="A41" t="s">
         <v>72</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -3089,7 +3100,7 @@
       <c r="E41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -3104,7 +3115,7 @@
       <c r="J41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="K41" t="s">
         <v>26</v>
       </c>
       <c r="L41" s="1">
@@ -3123,7 +3134,7 @@
         <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R41" t="s">
         <v>26</v>
@@ -3133,7 +3144,7 @@
       <c r="A42" t="s">
         <v>29</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -3145,7 +3156,7 @@
       <c r="E42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -3160,7 +3171,7 @@
       <c r="J42" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="K42" t="s">
         <v>26</v>
       </c>
       <c r="L42" s="1">
@@ -3179,7 +3190,7 @@
         <v>28</v>
       </c>
       <c r="Q42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R42" t="s">
         <v>26</v>
@@ -3189,7 +3200,7 @@
       <c r="A43" t="s">
         <v>29</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -3201,7 +3212,7 @@
       <c r="E43" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -3216,7 +3227,7 @@
       <c r="J43" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="K43" t="s">
         <v>26</v>
       </c>
       <c r="L43" s="1">
@@ -3226,7 +3237,7 @@
         <v>610104</v>
       </c>
       <c r="N43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O43">
         <v>9.2200000000000006</v>
@@ -3245,7 +3256,7 @@
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -3257,7 +3268,7 @@
       <c r="E44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -3272,7 +3283,7 @@
       <c r="J44" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="K44" t="s">
         <v>26</v>
       </c>
       <c r="L44" s="1">
@@ -3291,7 +3302,7 @@
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R44" t="e">
         <v>#N/A</v>
@@ -3301,7 +3312,7 @@
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -3313,7 +3324,7 @@
       <c r="E45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -3328,7 +3339,7 @@
       <c r="J45" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="K45" t="s">
         <v>26</v>
       </c>
       <c r="L45" s="1">
@@ -3338,7 +3349,7 @@
         <v>614542</v>
       </c>
       <c r="N45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O45">
         <v>20.53</v>
@@ -3357,7 +3368,7 @@
       <c r="A46" t="s">
         <v>29</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -3369,7 +3380,7 @@
       <c r="E46" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -3384,7 +3395,7 @@
       <c r="J46" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="K46" t="s">
         <v>26</v>
       </c>
       <c r="L46" s="1">
@@ -3403,7 +3414,7 @@
         <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R46" t="s">
         <v>26</v>
@@ -3413,7 +3424,7 @@
       <c r="A47" t="s">
         <v>29</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -3425,7 +3436,7 @@
       <c r="E47" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -3440,7 +3451,7 @@
       <c r="J47" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="K47" t="s">
         <v>26</v>
       </c>
       <c r="L47" s="1">
@@ -3450,7 +3461,7 @@
         <v>610596</v>
       </c>
       <c r="N47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O47">
         <v>4.17</v>
@@ -3469,7 +3480,7 @@
       <c r="A48" t="s">
         <v>72</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -3481,7 +3492,7 @@
       <c r="E48" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -3496,7 +3507,7 @@
       <c r="J48" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K48" t="s">
         <v>26</v>
       </c>
       <c r="L48" s="1">
@@ -3515,7 +3526,7 @@
         <v>28</v>
       </c>
       <c r="Q48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R48" t="s">
         <v>26</v>
@@ -3525,7 +3536,7 @@
       <c r="A49" t="s">
         <v>29</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -3537,7 +3548,7 @@
       <c r="E49" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -3552,7 +3563,7 @@
       <c r="J49" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K49" t="s">
         <v>26</v>
       </c>
       <c r="L49" s="1">
@@ -3562,7 +3573,7 @@
         <v>611797</v>
       </c>
       <c r="N49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O49">
         <v>9.85</v>
@@ -3581,7 +3592,7 @@
       <c r="A50" t="s">
         <v>72</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -3593,7 +3604,7 @@
       <c r="E50" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -3608,7 +3619,7 @@
       <c r="J50" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="K50" t="s">
         <v>26</v>
       </c>
       <c r="L50" s="1">
@@ -3627,7 +3638,7 @@
         <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R50" t="s">
         <v>26</v>
@@ -3637,7 +3648,7 @@
       <c r="A51" t="s">
         <v>29</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -3649,7 +3660,7 @@
       <c r="E51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -3664,7 +3675,7 @@
       <c r="J51" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="K51" t="s">
         <v>26</v>
       </c>
       <c r="L51" s="1">
@@ -3674,16 +3685,16 @@
         <v>614020</v>
       </c>
       <c r="N51" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="O51">
         <v>2.33</v>
       </c>
       <c r="P51" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q51" t="s">
-        <v>28</v>
+        <v>147</v>
       </c>
       <c r="R51" t="s">
         <v>26</v>
@@ -3691,10 +3702,10 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B52" t="s">
-        <v>124</v>
+        <v>72</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>19</v>
@@ -3703,13 +3714,13 @@
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>22</v>
+        <v>93</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="H52" s="1">
         <v>3</v>
@@ -3720,26 +3731,26 @@
       <c r="J52" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="K52" t="s">
         <v>26</v>
       </c>
       <c r="L52" s="1">
         <v>46268</v>
       </c>
       <c r="M52">
-        <v>614995</v>
+        <v>615019</v>
       </c>
       <c r="N52" t="s">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="O52">
-        <v>1.91</v>
+        <v>7.95</v>
       </c>
       <c r="P52" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="R52" t="s">
         <v>26</v>
@@ -3747,10 +3758,10 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>72</v>
-      </c>
-      <c r="B53" t="s">
-        <v>123</v>
+        <v>29</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>19</v>
@@ -3759,13 +3770,13 @@
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>94</v>
+        <v>31</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="H53" s="1">
         <v>3</v>
@@ -3776,26 +3787,26 @@
       <c r="J53" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="K53" t="s">
         <v>26</v>
       </c>
       <c r="L53" s="1">
         <v>46268</v>
       </c>
       <c r="M53">
-        <v>615019</v>
+        <v>614995</v>
       </c>
       <c r="N53" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="O53">
-        <v>7.95</v>
+        <v>1.91</v>
       </c>
       <c r="P53" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q53" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="R53" t="s">
         <v>26</v>
@@ -3805,7 +3816,7 @@
       <c r="A54" t="s">
         <v>29</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -3817,7 +3828,7 @@
       <c r="E54" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -3832,7 +3843,7 @@
       <c r="J54" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="K54" t="s">
         <v>26</v>
       </c>
       <c r="L54" s="1">
@@ -3842,7 +3853,7 @@
         <v>615314</v>
       </c>
       <c r="N54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O54">
         <v>12.23</v>
@@ -3861,7 +3872,7 @@
       <c r="A55" t="s">
         <v>29</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -3873,7 +3884,7 @@
       <c r="E55" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -3888,7 +3899,7 @@
       <c r="J55" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="K55" t="s">
         <v>26</v>
       </c>
       <c r="L55" s="1">
@@ -3898,7 +3909,7 @@
         <v>615322</v>
       </c>
       <c r="N55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O55">
         <v>16.34</v>
@@ -3917,7 +3928,7 @@
       <c r="A56" t="s">
         <v>29</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -3929,7 +3940,7 @@
       <c r="E56" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -3944,7 +3955,7 @@
       <c r="J56" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="K56" t="s">
         <v>26</v>
       </c>
       <c r="L56" s="1">
@@ -3954,7 +3965,7 @@
         <v>615654</v>
       </c>
       <c r="N56" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O56">
         <v>11.93</v>
@@ -3973,7 +3984,7 @@
       <c r="A57" t="s">
         <v>72</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -3985,7 +3996,7 @@
       <c r="E57" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="2" t="s">
         <v>94</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -4000,7 +4011,7 @@
       <c r="J57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="K57" t="s">
         <v>26</v>
       </c>
       <c r="L57" s="1">
@@ -4010,7 +4021,7 @@
         <v>616899</v>
       </c>
       <c r="N57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O57">
         <v>6.36</v>
@@ -4029,7 +4040,7 @@
       <c r="A58" t="s">
         <v>29</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>131</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -4041,7 +4052,7 @@
       <c r="E58" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -4056,7 +4067,7 @@
       <c r="J58" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="K58" t="s">
         <v>26</v>
       </c>
       <c r="L58" s="1">
@@ -4066,7 +4077,7 @@
         <v>616788</v>
       </c>
       <c r="N58" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O58">
         <v>32.82</v>
@@ -4083,10 +4094,10 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
-      </c>
-      <c r="B59" t="s">
-        <v>134</v>
+        <v>72</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>19</v>
@@ -4095,13 +4106,13 @@
         <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>22</v>
+        <v>93</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="H59" s="1">
         <v>9</v>
@@ -4112,20 +4123,20 @@
       <c r="J59" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="K59" t="s">
         <v>26</v>
       </c>
       <c r="L59" s="1">
         <v>46274</v>
       </c>
       <c r="M59">
-        <v>617229</v>
+        <v>617206</v>
       </c>
       <c r="N59" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O59">
-        <v>2.2200000000000002</v>
+        <v>21.23</v>
       </c>
       <c r="P59" t="s">
         <v>35</v>
@@ -4139,10 +4150,10 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>72</v>
-      </c>
-      <c r="B60" t="s">
-        <v>133</v>
+        <v>29</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>19</v>
@@ -4151,13 +4162,13 @@
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>94</v>
+        <v>31</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="H60" s="1">
         <v>9</v>
@@ -4168,20 +4179,20 @@
       <c r="J60" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="K60" t="s">
         <v>26</v>
       </c>
       <c r="L60" s="1">
         <v>46274</v>
       </c>
       <c r="M60">
-        <v>617206</v>
+        <v>617229</v>
       </c>
       <c r="N60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O60">
-        <v>21.23</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="P60" t="s">
         <v>35</v>
@@ -4189,16 +4200,16 @@
       <c r="Q60" t="s">
         <v>28</v>
       </c>
-      <c r="R60" t="e">
-        <v>#N/A</v>
+      <c r="R60" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>29</v>
       </c>
-      <c r="B61" t="s">
-        <v>136</v>
+      <c r="B61" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>19</v>
@@ -4209,7 +4220,7 @@
       <c r="E61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -4224,7 +4235,7 @@
       <c r="J61" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="K61" t="s">
         <v>26</v>
       </c>
       <c r="L61" s="1">
@@ -4234,7 +4245,7 @@
         <v>617914</v>
       </c>
       <c r="N61" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O61">
         <v>8.4600000000000009</v>
@@ -4253,10 +4264,10 @@
       <c r="A62" t="s">
         <v>17</v>
       </c>
-      <c r="B62" t="s">
-        <v>138</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="B62" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -4265,7 +4276,7 @@
       <c r="E62" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -4280,7 +4291,7 @@
       <c r="J62" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="K62" t="s">
         <v>26</v>
       </c>
       <c r="L62" s="1">
@@ -4299,7 +4310,7 @@
         <v>28</v>
       </c>
       <c r="Q62" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R62" t="s">
         <v>26</v>
@@ -4309,10 +4320,10 @@
       <c r="A63" t="s">
         <v>29</v>
       </c>
-      <c r="B63" t="s">
-        <v>139</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="B63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -4321,7 +4332,7 @@
       <c r="E63" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -4336,7 +4347,7 @@
       <c r="J63" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="K63" t="s">
         <v>26</v>
       </c>
       <c r="L63" s="1">
@@ -4346,7 +4357,7 @@
         <v>618930</v>
       </c>
       <c r="N63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O63">
         <v>17.97</v>
@@ -4363,25 +4374,25 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C64" t="s">
         <v>19</v>
       </c>
-      <c r="D64" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" t="s">
-        <v>31</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>22</v>
+      <c r="D64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="H64" s="1">
         <v>14</v>
@@ -4392,20 +4403,20 @@
       <c r="J64" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="K64" t="s">
         <v>26</v>
       </c>
       <c r="L64" s="1">
         <v>46279</v>
       </c>
       <c r="M64">
-        <v>619980</v>
+        <v>619855</v>
       </c>
       <c r="N64" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O64">
-        <v>8.5399999999999991</v>
+        <v>4.68</v>
       </c>
       <c r="P64" t="s">
         <v>35</v>
@@ -4413,31 +4424,31 @@
       <c r="Q64" t="s">
         <v>28</v>
       </c>
-      <c r="R64" t="s">
-        <v>26</v>
+      <c r="R64" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
         <v>19</v>
       </c>
-      <c r="D65" t="s">
-        <v>20</v>
-      </c>
-      <c r="E65" t="s">
-        <v>141</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>94</v>
+      <c r="D65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="H65" s="1">
         <v>14</v>
@@ -4448,20 +4459,20 @@
       <c r="J65" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K65" t="s">
         <v>26</v>
       </c>
       <c r="L65" s="1">
         <v>46279</v>
       </c>
       <c r="M65">
-        <v>619855</v>
+        <v>619980</v>
       </c>
       <c r="N65" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O65">
-        <v>4.68</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="P65" t="s">
         <v>35</v>
@@ -4469,16 +4480,16 @@
       <c r="Q65" t="s">
         <v>28</v>
       </c>
-      <c r="R65" t="e">
-        <v>#N/A</v>
+      <c r="R65" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C66" t="s">
         <v>19</v>
@@ -4486,14 +4497,14 @@
       <c r="D66" t="s">
         <v>20</v>
       </c>
-      <c r="E66" t="s">
-        <v>152</v>
-      </c>
-      <c r="F66" t="s">
-        <v>94</v>
+      <c r="E66" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="H66" s="1">
         <v>15</v>
@@ -4504,23 +4515,23 @@
       <c r="J66" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="K66" t="s">
         <v>26</v>
       </c>
       <c r="L66" s="1">
         <v>46280</v>
       </c>
       <c r="M66">
-        <v>620157</v>
+        <v>617205</v>
       </c>
       <c r="N66" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O66">
-        <v>6.46</v>
+        <v>14.62</v>
       </c>
       <c r="P66" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="Q66" t="s">
         <v>28</v>
@@ -4531,7 +4542,7 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
         <v>150</v>
@@ -4542,14 +4553,14 @@
       <c r="D67" t="s">
         <v>20</v>
       </c>
-      <c r="E67" t="s">
-        <v>21</v>
-      </c>
-      <c r="F67" t="s">
-        <v>22</v>
+      <c r="E67" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="H67" s="1">
         <v>15</v>
@@ -4560,23 +4571,23 @@
       <c r="J67" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="K67" t="s">
         <v>26</v>
       </c>
       <c r="L67" s="1">
         <v>46280</v>
       </c>
       <c r="M67">
-        <v>617205</v>
+        <v>620157</v>
       </c>
       <c r="N67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O67">
-        <v>14.62</v>
+        <v>6.46</v>
       </c>
       <c r="P67" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="Q67" t="s">
         <v>28</v>
@@ -4590,7 +4601,7 @@
         <v>29</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C68" t="s">
         <v>19</v>
@@ -4601,10 +4612,10 @@
       <c r="E68" t="s">
         <v>31</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G68" t="s">
+      <c r="G68" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H68" s="1">
@@ -4616,7 +4627,7 @@
       <c r="J68" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="K68" t="s">
         <v>26</v>
       </c>
       <c r="L68" s="1">
@@ -4626,7 +4637,7 @@
         <v>620523</v>
       </c>
       <c r="N68" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O68">
         <v>8.57</v>
@@ -4646,7 +4657,7 @@
         <v>72</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C69" t="s">
         <v>19</v>
@@ -4655,12 +4666,12 @@
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>152</v>
-      </c>
-      <c r="F69" t="s">
+        <v>151</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="1" t="s">
         <v>95</v>
       </c>
       <c r="H69" s="1">
@@ -4672,7 +4683,7 @@
       <c r="J69" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="K69" t="s">
         <v>26</v>
       </c>
       <c r="L69" s="1">
@@ -4682,7 +4693,7 @@
         <v>620676</v>
       </c>
       <c r="N69" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O69">
         <v>8.9600000000000009</v>
@@ -4699,10 +4710,10 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
         <v>19</v>
@@ -4711,15 +4722,15 @@
         <v>20</v>
       </c>
       <c r="E70" t="s">
-        <v>152</v>
-      </c>
-      <c r="F70" t="s">
-        <v>94</v>
-      </c>
-      <c r="G70" t="s">
-        <v>130</v>
-      </c>
-      <c r="H70">
+        <v>21</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H70" s="1">
         <v>17</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -4728,23 +4739,23 @@
       <c r="J70" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="K70" t="s">
         <v>26</v>
       </c>
       <c r="L70" s="1">
         <v>46282</v>
       </c>
       <c r="M70">
-        <v>621205</v>
+        <v>620938</v>
       </c>
       <c r="N70" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O70">
-        <v>5.95</v>
+        <v>11.75</v>
       </c>
       <c r="P70" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q70" t="s">
         <v>28</v>
@@ -4755,10 +4766,10 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C71" t="s">
         <v>19</v>
@@ -4767,15 +4778,15 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>31</v>
-      </c>
-      <c r="F71" t="s">
-        <v>22</v>
-      </c>
-      <c r="G71" t="s">
-        <v>32</v>
-      </c>
-      <c r="H71">
+        <v>151</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H71" s="1">
         <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
@@ -4784,20 +4795,20 @@
       <c r="J71" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="K71" t="s">
         <v>26</v>
       </c>
       <c r="L71" s="1">
         <v>46282</v>
       </c>
       <c r="M71">
-        <v>621574</v>
+        <v>621205</v>
       </c>
       <c r="N71" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O71">
-        <v>3.78</v>
+        <v>5.95</v>
       </c>
       <c r="P71" t="s">
         <v>27</v>
@@ -4805,8 +4816,8 @@
       <c r="Q71" t="s">
         <v>28</v>
       </c>
-      <c r="R71" t="e">
-        <v>#N/A</v>
+      <c r="R71" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -4814,7 +4825,7 @@
         <v>29</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C72" t="s">
         <v>19</v>
@@ -4825,13 +4836,13 @@
       <c r="E72" t="s">
         <v>31</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G72" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="1">
         <v>17</v>
       </c>
       <c r="I72" s="1" t="s">
@@ -4840,20 +4851,20 @@
       <c r="J72" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="K72" t="s">
         <v>26</v>
       </c>
       <c r="L72" s="1">
         <v>46282</v>
       </c>
       <c r="M72">
-        <v>621242</v>
+        <v>621574</v>
       </c>
       <c r="N72" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O72">
-        <v>5.46</v>
+        <v>3.78</v>
       </c>
       <c r="P72" t="s">
         <v>35</v>
@@ -4867,10 +4878,10 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B73" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
         <v>19</v>
@@ -4879,15 +4890,15 @@
         <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
-      </c>
-      <c r="F73" t="s">
+        <v>31</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G73" t="s">
-        <v>43</v>
-      </c>
-      <c r="H73">
+      <c r="G73" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73" s="1">
         <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
@@ -4896,20 +4907,20 @@
       <c r="J73" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="K73" t="s">
         <v>26</v>
       </c>
       <c r="L73" s="1">
         <v>46282</v>
       </c>
       <c r="M73">
-        <v>620938</v>
+        <v>621242</v>
       </c>
       <c r="N73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O73">
-        <v>11.75</v>
+        <v>5.46</v>
       </c>
       <c r="P73" t="s">
         <v>35</v>
@@ -4917,8 +4928,8 @@
       <c r="Q73" t="s">
         <v>28</v>
       </c>
-      <c r="R73" t="e">
-        <v>#N/A</v>
+      <c r="R73" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -4926,7 +4937,7 @@
         <v>29</v>
       </c>
       <c r="B74" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C74" t="s">
         <v>19</v>
@@ -4937,22 +4948,22 @@
       <c r="E74" t="s">
         <v>31</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G74" t="s">
+      <c r="G74" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="1">
         <v>18</v>
       </c>
-      <c r="I74" t="s">
+      <c r="I74" s="1" t="s">
         <v>122</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="K74" t="s">
         <v>26</v>
       </c>
       <c r="L74" s="1">
@@ -4962,18 +4973,130 @@
         <v>622716</v>
       </c>
       <c r="N74" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O74">
         <v>5.33</v>
       </c>
       <c r="P74" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>28</v>
+      </c>
+      <c r="R74" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>29</v>
+      </c>
+      <c r="B75" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
+        <v>31</v>
+      </c>
+      <c r="F75" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H75" s="1">
+        <v>22</v>
+      </c>
+      <c r="I75" t="s">
+        <v>122</v>
+      </c>
+      <c r="J75" t="s">
+        <v>25</v>
+      </c>
+      <c r="K75" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="1">
+        <v>46287</v>
+      </c>
+      <c r="M75">
+        <v>624178</v>
+      </c>
+      <c r="N75" t="s">
+        <v>136</v>
+      </c>
+      <c r="O75">
+        <v>12.79</v>
+      </c>
+      <c r="P75" t="s">
         <v>27</v>
       </c>
-      <c r="Q74" t="s">
-        <v>28</v>
-      </c>
-      <c r="R74" t="e">
+      <c r="Q75" t="s">
+        <v>28</v>
+      </c>
+      <c r="R75" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>29</v>
+      </c>
+      <c r="B76" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H76" s="1">
+        <v>22</v>
+      </c>
+      <c r="I76" t="s">
+        <v>122</v>
+      </c>
+      <c r="J76" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" s="1">
+        <v>46287</v>
+      </c>
+      <c r="M76">
+        <v>624196</v>
+      </c>
+      <c r="N76" t="s">
+        <v>136</v>
+      </c>
+      <c r="O76">
+        <v>3.73</v>
+      </c>
+      <c r="P76" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>28</v>
+      </c>
+      <c r="R76" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -4985,7 +5108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -5681,7 +5804,7 @@
         <v>46266</v>
       </c>
       <c r="B19" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
@@ -5719,7 +5842,7 @@
         <v>46266</v>
       </c>
       <c r="B20" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
@@ -5757,7 +5880,7 @@
         <v>46266</v>
       </c>
       <c r="B21" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
         <v>85</v>
@@ -5795,7 +5918,7 @@
         <v>46266</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -5833,7 +5956,7 @@
         <v>46266</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
@@ -5871,7 +5994,7 @@
         <v>46266</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
         <v>85</v>
@@ -5902,6 +6025,120 @@
       </c>
       <c r="L24">
         <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25">
+        <v>15.247999999999999</v>
+      </c>
+      <c r="E25">
+        <v>9.0090000000000003</v>
+      </c>
+      <c r="F25">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>15</v>
+      </c>
+      <c r="H25">
+        <v>9</v>
+      </c>
+      <c r="I25">
+        <v>0.9</v>
+      </c>
+      <c r="J25">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="K25">
+        <v>5</v>
+      </c>
+      <c r="L25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26">
+        <v>29.870720000000002</v>
+      </c>
+      <c r="F26">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27">
+        <v>12.771660000000001</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>15</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6287,6 +6524,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
@@ -6295,15 +6541,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6326,6 +6563,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -6334,12 +6579,4 @@
     <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A77949AB-5086-44D6-B235-7C226F00EE13}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AEF0940-32B7-4A40-9838-77C05526AE48}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="170">
   <si>
     <t>Usuário</t>
   </si>
@@ -535,19 +535,22 @@
     <t>GERALDO DE SOUZA OLIVEIRA</t>
   </si>
   <si>
-    <t>NEGOCIAÇÃO QUENTE</t>
-  </si>
-  <si>
     <t>LEANDRO FERREIRA DA SILVA</t>
   </si>
   <si>
     <t>RONY APARECIDA FEDOSI</t>
   </si>
   <si>
-    <t>semana 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Semana 3 </t>
+  </si>
+  <si>
+    <t>DANTAS E DANTAS COMERCIO DE ALIMENTACAO LTDA</t>
+  </si>
+  <si>
+    <t>FRANCISCO FRANCILIO DE OLIVEIRA GONCALVES</t>
+  </si>
+  <si>
+    <t>WILLAME NOGUEIRA DE OLIVEIRA</t>
   </si>
 </sst>
 </file>
@@ -589,10 +592,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -873,11 +877,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -902,7 +908,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -914,7 +920,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -946,22 +952,22 @@
       <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="3">
         <v>2</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>33</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -1002,22 +1008,22 @@
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="3">
         <v>2</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>33</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1058,22 +1064,22 @@
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="3">
         <v>2</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>33</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1111,22 +1117,22 @@
       <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="3">
         <v>6</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>33</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -1167,22 +1173,22 @@
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="3">
         <v>7</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1220,22 +1226,22 @@
       <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="3">
         <v>8</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>33</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1273,22 +1279,22 @@
       <c r="C8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="3">
         <v>10</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>33</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -1326,22 +1332,22 @@
       <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="3">
         <v>15</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>33</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -1379,22 +1385,22 @@
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="3">
         <v>15</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>33</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -1432,22 +1438,22 @@
       <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="3">
         <v>16</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>33</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -1485,22 +1491,22 @@
       <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="1">
-        <v>20</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="H12" s="3">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s">
         <v>33</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -1538,22 +1544,22 @@
       <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="3">
         <v>21</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>33</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -1594,22 +1600,22 @@
       <c r="C14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="3">
         <v>22</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>33</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -1647,22 +1653,22 @@
       <c r="C15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="3">
         <v>24</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -1700,22 +1706,22 @@
       <c r="C16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="1">
-        <v>28</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="H16" s="3">
+        <v>28</v>
+      </c>
+      <c r="I16" t="s">
         <v>33</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -1753,22 +1759,22 @@
       <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="1">
-        <v>28</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="H17" s="3">
+        <v>28</v>
+      </c>
+      <c r="I17" t="s">
         <v>33</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -1809,22 +1815,22 @@
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="1">
-        <v>28</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="3">
+        <v>28</v>
+      </c>
+      <c r="I18" t="s">
         <v>33</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -1862,22 +1868,22 @@
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="3">
         <v>3</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" t="s">
         <v>24</v>
       </c>
       <c r="J19" s="1" t="s">
@@ -1918,22 +1924,22 @@
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="3">
         <v>4</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" t="s">
         <v>24</v>
       </c>
       <c r="J20" s="1" t="s">
@@ -1974,22 +1980,22 @@
       <c r="C21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="3">
         <v>5</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="1" t="s">
@@ -2030,22 +2036,22 @@
       <c r="C22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="3">
         <v>6</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" t="s">
         <v>24</v>
       </c>
       <c r="J22" s="1" t="s">
@@ -2086,22 +2092,22 @@
       <c r="C23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="3">
         <v>7</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" t="s">
         <v>24</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -2142,22 +2148,22 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="3">
         <v>7</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" t="s">
         <v>24</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -2198,22 +2204,22 @@
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="3">
         <v>10</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" t="s">
         <v>24</v>
       </c>
       <c r="J25" s="1" t="s">
@@ -2254,22 +2260,22 @@
       <c r="C26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="3">
         <v>11</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" t="s">
         <v>24</v>
       </c>
       <c r="J26" s="1" t="s">
@@ -2310,22 +2316,22 @@
       <c r="C27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="3">
         <v>11</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" t="s">
         <v>24</v>
       </c>
       <c r="J27" s="1" t="s">
@@ -2366,22 +2372,22 @@
       <c r="C28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="3">
         <v>13</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" t="s">
         <v>24</v>
       </c>
       <c r="J28" s="1" t="s">
@@ -2422,22 +2428,22 @@
       <c r="C29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="3">
         <v>13</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" t="s">
         <v>24</v>
       </c>
       <c r="J29" s="1" t="s">
@@ -2478,22 +2484,22 @@
       <c r="C30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="3">
         <v>14</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" t="s">
         <v>24</v>
       </c>
       <c r="J30" s="1" t="s">
@@ -2534,22 +2540,22 @@
       <c r="C31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="3">
         <v>17</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" t="s">
         <v>24</v>
       </c>
       <c r="J31" s="1" t="s">
@@ -2590,22 +2596,22 @@
       <c r="C32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="3">
         <v>18</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" t="s">
         <v>24</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -2646,22 +2652,22 @@
       <c r="C33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H33" s="1">
-        <v>19</v>
-      </c>
-      <c r="I33" s="1" t="s">
+      <c r="H33" s="3">
+        <v>19</v>
+      </c>
+      <c r="I33" t="s">
         <v>24</v>
       </c>
       <c r="J33" s="1" t="s">
@@ -2702,22 +2708,22 @@
       <c r="C34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H34" s="1">
-        <v>19</v>
-      </c>
-      <c r="I34" s="1" t="s">
+      <c r="H34" s="3">
+        <v>19</v>
+      </c>
+      <c r="I34" t="s">
         <v>24</v>
       </c>
       <c r="J34" s="1" t="s">
@@ -2758,22 +2764,22 @@
       <c r="C35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H35" s="1">
-        <v>20</v>
-      </c>
-      <c r="I35" s="1" t="s">
+      <c r="H35" s="3">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
         <v>24</v>
       </c>
       <c r="J35" s="1" t="s">
@@ -2814,22 +2820,22 @@
       <c r="C36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="3">
         <v>21</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" t="s">
         <v>24</v>
       </c>
       <c r="J36" s="1" t="s">
@@ -2870,22 +2876,22 @@
       <c r="C37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="3">
         <v>21</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" t="s">
         <v>24</v>
       </c>
       <c r="J37" s="1" t="s">
@@ -2926,22 +2932,22 @@
       <c r="C38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="3">
         <v>21</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" t="s">
         <v>24</v>
       </c>
       <c r="J38" s="1" t="s">
@@ -2982,22 +2988,22 @@
       <c r="C39" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="3">
         <v>21</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" t="s">
         <v>24</v>
       </c>
       <c r="J39" s="1" t="s">
@@ -3038,22 +3044,22 @@
       <c r="C40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="3">
         <v>21</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" t="s">
         <v>24</v>
       </c>
       <c r="J40" s="1" t="s">
@@ -3094,22 +3100,22 @@
       <c r="C41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="3">
         <v>21</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" t="s">
         <v>24</v>
       </c>
       <c r="J41" s="1" t="s">
@@ -3150,22 +3156,22 @@
       <c r="C42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="3">
         <v>21</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" t="s">
         <v>24</v>
       </c>
       <c r="J42" s="1" t="s">
@@ -3206,22 +3212,22 @@
       <c r="C43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="3">
         <v>24</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" t="s">
         <v>24</v>
       </c>
       <c r="J43" s="1" t="s">
@@ -3262,22 +3268,22 @@
       <c r="C44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="1">
-        <v>25</v>
-      </c>
-      <c r="I44" s="1" t="s">
+      <c r="H44" s="3">
+        <v>25</v>
+      </c>
+      <c r="I44" t="s">
         <v>24</v>
       </c>
       <c r="J44" s="1" t="s">
@@ -3318,22 +3324,22 @@
       <c r="C45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="1">
-        <v>25</v>
-      </c>
-      <c r="I45" s="1" t="s">
+      <c r="H45" s="3">
+        <v>25</v>
+      </c>
+      <c r="I45" t="s">
         <v>24</v>
       </c>
       <c r="J45" s="1" t="s">
@@ -3374,22 +3380,22 @@
       <c r="C46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H46" s="1">
-        <v>25</v>
-      </c>
-      <c r="I46" s="1" t="s">
+      <c r="H46" s="3">
+        <v>25</v>
+      </c>
+      <c r="I46" t="s">
         <v>24</v>
       </c>
       <c r="J46" s="1" t="s">
@@ -3430,22 +3436,22 @@
       <c r="C47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H47" s="1">
-        <v>25</v>
-      </c>
-      <c r="I47" s="1" t="s">
+      <c r="H47" s="3">
+        <v>25</v>
+      </c>
+      <c r="I47" t="s">
         <v>24</v>
       </c>
       <c r="J47" s="1" t="s">
@@ -3486,22 +3492,22 @@
       <c r="C48" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H48" s="1">
+      <c r="H48" s="3">
         <v>27</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" t="s">
         <v>24</v>
       </c>
       <c r="J48" s="1" t="s">
@@ -3542,22 +3548,22 @@
       <c r="C49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H49" s="3">
         <v>27</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" t="s">
         <v>24</v>
       </c>
       <c r="J49" s="1" t="s">
@@ -3598,22 +3604,22 @@
       <c r="C50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H50" s="1">
-        <v>28</v>
-      </c>
-      <c r="I50" s="1" t="s">
+      <c r="H50" s="3">
+        <v>28</v>
+      </c>
+      <c r="I50" t="s">
         <v>24</v>
       </c>
       <c r="J50" s="1" t="s">
@@ -3654,22 +3660,22 @@
       <c r="C51" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51" s="3">
         <v>1</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" t="s">
         <v>122</v>
       </c>
       <c r="J51" s="1" t="s">
@@ -3696,8 +3702,8 @@
       <c r="Q51" t="s">
         <v>147</v>
       </c>
-      <c r="R51" t="s">
-        <v>26</v>
+      <c r="R51">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -3710,22 +3716,22 @@
       <c r="C52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H52" s="1">
+      <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" t="s">
         <v>122</v>
       </c>
       <c r="J52" s="1" t="s">
@@ -3752,8 +3758,8 @@
       <c r="Q52" t="s">
         <v>145</v>
       </c>
-      <c r="R52" t="s">
-        <v>26</v>
+      <c r="R52">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -3766,22 +3772,22 @@
       <c r="C53" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H53" s="1">
+      <c r="H53" s="3">
         <v>3</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" t="s">
         <v>122</v>
       </c>
       <c r="J53" s="1" t="s">
@@ -3808,8 +3814,8 @@
       <c r="Q53" t="s">
         <v>28</v>
       </c>
-      <c r="R53" t="s">
-        <v>26</v>
+      <c r="R53">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -3822,22 +3828,22 @@
       <c r="C54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H54" s="1">
+      <c r="H54" s="3">
         <v>4</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" t="s">
         <v>122</v>
       </c>
       <c r="J54" s="1" t="s">
@@ -3864,8 +3870,8 @@
       <c r="Q54" t="s">
         <v>28</v>
       </c>
-      <c r="R54" t="s">
-        <v>26</v>
+      <c r="R54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
@@ -3878,22 +3884,22 @@
       <c r="C55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H55" s="1">
+      <c r="H55" s="3">
         <v>4</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" t="s">
         <v>122</v>
       </c>
       <c r="J55" s="1" t="s">
@@ -3920,8 +3926,8 @@
       <c r="Q55" t="s">
         <v>28</v>
       </c>
-      <c r="R55" t="s">
-        <v>26</v>
+      <c r="R55">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -3934,22 +3940,22 @@
       <c r="C56" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H56" s="3">
         <v>4</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" t="s">
         <v>122</v>
       </c>
       <c r="J56" s="1" t="s">
@@ -3976,8 +3982,8 @@
       <c r="Q56" t="s">
         <v>28</v>
       </c>
-      <c r="R56" t="s">
-        <v>26</v>
+      <c r="R56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
@@ -3990,22 +3996,22 @@
       <c r="C57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H57" s="1">
+      <c r="H57" s="3">
         <v>8</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" t="s">
         <v>122</v>
       </c>
       <c r="J57" s="1" t="s">
@@ -4046,22 +4052,22 @@
       <c r="C58" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H58" s="1">
+      <c r="H58" s="3">
         <v>8</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" t="s">
         <v>122</v>
       </c>
       <c r="J58" s="1" t="s">
@@ -4088,8 +4094,8 @@
       <c r="Q58" t="s">
         <v>28</v>
       </c>
-      <c r="R58" t="s">
-        <v>26</v>
+      <c r="R58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
@@ -4102,22 +4108,22 @@
       <c r="C59" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H59" s="1">
+      <c r="H59" s="3">
         <v>9</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" t="s">
         <v>122</v>
       </c>
       <c r="J59" s="1" t="s">
@@ -4144,8 +4150,8 @@
       <c r="Q59" t="s">
         <v>28</v>
       </c>
-      <c r="R59" t="s">
-        <v>26</v>
+      <c r="R59">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
@@ -4158,22 +4164,22 @@
       <c r="C60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H60" s="1">
+      <c r="H60" s="3">
         <v>9</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" t="s">
         <v>122</v>
       </c>
       <c r="J60" s="1" t="s">
@@ -4200,8 +4206,8 @@
       <c r="Q60" t="s">
         <v>28</v>
       </c>
-      <c r="R60" t="s">
-        <v>26</v>
+      <c r="R60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
@@ -4214,22 +4220,22 @@
       <c r="C61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H61" s="1">
+      <c r="H61" s="3">
         <v>10</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" t="s">
         <v>122</v>
       </c>
       <c r="J61" s="1" t="s">
@@ -4256,8 +4262,8 @@
       <c r="Q61" t="s">
         <v>28</v>
       </c>
-      <c r="R61" t="s">
-        <v>26</v>
+      <c r="R61">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
@@ -4270,22 +4276,22 @@
       <c r="C62" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="1">
+      <c r="H62" s="3">
         <v>11</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I62" t="s">
         <v>122</v>
       </c>
       <c r="J62" s="1" t="s">
@@ -4312,8 +4318,8 @@
       <c r="Q62" t="s">
         <v>147</v>
       </c>
-      <c r="R62" t="s">
-        <v>26</v>
+      <c r="R62">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -4326,22 +4332,22 @@
       <c r="C63" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G63" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H63" s="1">
+      <c r="H63" s="3">
         <v>11</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="I63" t="s">
         <v>122</v>
       </c>
       <c r="J63" s="1" t="s">
@@ -4368,36 +4374,36 @@
       <c r="Q63" t="s">
         <v>28</v>
       </c>
-      <c r="R63" t="s">
-        <v>26</v>
+      <c r="R63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C64" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="C64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="F64" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H64" s="1">
+      <c r="H64" s="3">
         <v>14</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="I64" t="s">
         <v>122</v>
       </c>
       <c r="J64" s="1" t="s">
@@ -4432,28 +4438,28 @@
       <c r="A65" t="s">
         <v>29</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C65" t="s">
-        <v>19</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="F65" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H65" s="1">
+      <c r="H65" s="3">
         <v>14</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="I65" t="s">
         <v>122</v>
       </c>
       <c r="J65" s="1" t="s">
@@ -4480,8 +4486,8 @@
       <c r="Q65" t="s">
         <v>28</v>
       </c>
-      <c r="R65" t="s">
-        <v>26</v>
+      <c r="R65">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
@@ -4491,25 +4497,25 @@
       <c r="B66" t="s">
         <v>149</v>
       </c>
-      <c r="C66" t="s">
-        <v>19</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="C66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H66" s="1">
+      <c r="H66" s="3">
         <v>15</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="I66" t="s">
         <v>122</v>
       </c>
       <c r="J66" s="1" t="s">
@@ -4525,19 +4531,19 @@
         <v>617205</v>
       </c>
       <c r="N66" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="O66">
         <v>14.62</v>
       </c>
       <c r="P66" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="Q66" t="s">
         <v>28</v>
       </c>
-      <c r="R66" t="s">
-        <v>26</v>
+      <c r="R66">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
@@ -4547,25 +4553,25 @@
       <c r="B67" t="s">
         <v>150</v>
       </c>
-      <c r="C67" t="s">
-        <v>19</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="C67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F67" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H67" s="1">
+      <c r="H67" s="3">
         <v>15</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I67" t="s">
         <v>122</v>
       </c>
       <c r="J67" s="1" t="s">
@@ -4592,8 +4598,8 @@
       <c r="Q67" t="s">
         <v>28</v>
       </c>
-      <c r="R67" t="s">
-        <v>26</v>
+      <c r="R67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
@@ -4606,22 +4612,22 @@
       <c r="C68" t="s">
         <v>19</v>
       </c>
-      <c r="D68" t="s">
-        <v>20</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="D68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H68" s="1">
+      <c r="H68" s="3">
         <v>15</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" t="s">
         <v>122</v>
       </c>
       <c r="J68" s="1" t="s">
@@ -4648,8 +4654,8 @@
       <c r="Q68" t="s">
         <v>28</v>
       </c>
-      <c r="R68" t="s">
-        <v>26</v>
+      <c r="R68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -4662,22 +4668,22 @@
       <c r="C69" t="s">
         <v>19</v>
       </c>
-      <c r="D69" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="D69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F69" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="G69" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H69" s="3">
         <v>16</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="I69" t="s">
         <v>122</v>
       </c>
       <c r="J69" s="1" t="s">
@@ -4704,8 +4710,8 @@
       <c r="Q69" t="s">
         <v>28</v>
       </c>
-      <c r="R69" t="s">
-        <v>26</v>
+      <c r="R69">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -4718,22 +4724,22 @@
       <c r="C70" t="s">
         <v>19</v>
       </c>
-      <c r="D70" t="s">
-        <v>20</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="D70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F70" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G70" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H70" s="1">
+      <c r="H70" s="3">
         <v>17</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="I70" t="s">
         <v>122</v>
       </c>
       <c r="J70" s="1" t="s">
@@ -4774,22 +4780,22 @@
       <c r="C71" t="s">
         <v>19</v>
       </c>
-      <c r="D71" t="s">
-        <v>20</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="D71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="F71" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H71" s="3">
         <v>17</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="I71" t="s">
         <v>122</v>
       </c>
       <c r="J71" s="1" t="s">
@@ -4816,8 +4822,8 @@
       <c r="Q71" t="s">
         <v>28</v>
       </c>
-      <c r="R71" t="s">
-        <v>26</v>
+      <c r="R71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -4830,22 +4836,22 @@
       <c r="C72" t="s">
         <v>19</v>
       </c>
-      <c r="D72" t="s">
-        <v>20</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="D72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F72" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G72" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H72" s="1">
+      <c r="H72" s="3">
         <v>17</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="I72" t="s">
         <v>122</v>
       </c>
       <c r="J72" s="1" t="s">
@@ -4872,8 +4878,8 @@
       <c r="Q72" t="s">
         <v>28</v>
       </c>
-      <c r="R72" t="s">
-        <v>26</v>
+      <c r="R72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -4886,22 +4892,22 @@
       <c r="C73" t="s">
         <v>19</v>
       </c>
-      <c r="D73" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="D73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="F73" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G73" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="1">
+      <c r="H73" s="3">
         <v>17</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I73" t="s">
         <v>122</v>
       </c>
       <c r="J73" s="1" t="s">
@@ -4928,8 +4934,8 @@
       <c r="Q73" t="s">
         <v>28</v>
       </c>
-      <c r="R73" t="s">
-        <v>26</v>
+      <c r="R73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -4942,22 +4948,22 @@
       <c r="C74" t="s">
         <v>19</v>
       </c>
-      <c r="D74" t="s">
-        <v>20</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="D74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="F74" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="G74" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H74" s="1">
+      <c r="H74" s="3">
         <v>18</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I74" t="s">
         <v>122</v>
       </c>
       <c r="J74" s="1" t="s">
@@ -4990,10 +4996,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="B75" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
         <v>19</v>
@@ -5001,22 +5007,22 @@
       <c r="D75" t="s">
         <v>20</v>
       </c>
-      <c r="E75" t="s">
-        <v>31</v>
-      </c>
-      <c r="F75" t="s">
-        <v>22</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H75" s="1">
+      <c r="E75" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H75" s="3">
         <v>22</v>
       </c>
       <c r="I75" t="s">
         <v>122</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J75" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K75" t="s">
@@ -5026,13 +5032,13 @@
         <v>46287</v>
       </c>
       <c r="M75">
-        <v>624178</v>
+        <v>624450</v>
       </c>
       <c r="N75" t="s">
         <v>136</v>
       </c>
       <c r="O75">
-        <v>12.79</v>
+        <v>5.46</v>
       </c>
       <c r="P75" t="s">
         <v>27</v>
@@ -5046,10 +5052,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C76" t="s">
         <v>19</v>
@@ -5057,22 +5063,22 @@
       <c r="D76" t="s">
         <v>20</v>
       </c>
-      <c r="E76" t="s">
-        <v>31</v>
-      </c>
-      <c r="F76" t="s">
-        <v>22</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H76" s="1">
+      <c r="E76" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H76" s="3">
         <v>22</v>
       </c>
       <c r="I76" t="s">
         <v>122</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J76" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K76" t="s">
@@ -5082,13 +5088,13 @@
         <v>46287</v>
       </c>
       <c r="M76">
-        <v>624196</v>
+        <v>624470</v>
       </c>
       <c r="N76" t="s">
         <v>136</v>
       </c>
       <c r="O76">
-        <v>3.73</v>
+        <v>8.34</v>
       </c>
       <c r="P76" t="s">
         <v>27</v>
@@ -5097,6 +5103,174 @@
         <v>28</v>
       </c>
       <c r="R76" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" t="s">
+        <v>31</v>
+      </c>
+      <c r="F77" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" s="3">
+        <v>22</v>
+      </c>
+      <c r="I77" t="s">
+        <v>122</v>
+      </c>
+      <c r="J77" t="s">
+        <v>25</v>
+      </c>
+      <c r="K77" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="1">
+        <v>46287</v>
+      </c>
+      <c r="M77">
+        <v>624178</v>
+      </c>
+      <c r="N77" t="s">
+        <v>136</v>
+      </c>
+      <c r="O77">
+        <v>12.79</v>
+      </c>
+      <c r="P77" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>28</v>
+      </c>
+      <c r="R77" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" t="s">
+        <v>165</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H78" s="3">
+        <v>22</v>
+      </c>
+      <c r="I78" t="s">
+        <v>122</v>
+      </c>
+      <c r="J78" t="s">
+        <v>25</v>
+      </c>
+      <c r="K78" t="s">
+        <v>26</v>
+      </c>
+      <c r="L78" s="1">
+        <v>46287</v>
+      </c>
+      <c r="M78">
+        <v>624196</v>
+      </c>
+      <c r="N78" t="s">
+        <v>136</v>
+      </c>
+      <c r="O78">
+        <v>3.73</v>
+      </c>
+      <c r="P78" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>28</v>
+      </c>
+      <c r="R78" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>72</v>
+      </c>
+      <c r="B79" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>140</v>
+      </c>
+      <c r="F79" t="s">
+        <v>94</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H79" s="3">
+        <v>23</v>
+      </c>
+      <c r="I79" t="s">
+        <v>122</v>
+      </c>
+      <c r="J79" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="1">
+        <v>46288</v>
+      </c>
+      <c r="M79">
+        <v>624882</v>
+      </c>
+      <c r="N79" t="s">
+        <v>136</v>
+      </c>
+      <c r="O79">
+        <v>22.65</v>
+      </c>
+      <c r="P79" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>28</v>
+      </c>
+      <c r="R79" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5918,7 +6092,7 @@
         <v>46266</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -5956,7 +6130,7 @@
         <v>46266</v>
       </c>
       <c r="B23" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
@@ -5994,7 +6168,7 @@
         <v>46266</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
         <v>85</v>
@@ -6032,7 +6206,7 @@
         <v>46266</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>29</v>
@@ -6070,7 +6244,7 @@
         <v>46266</v>
       </c>
       <c r="B26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
         <v>83</v>
@@ -6108,7 +6282,7 @@
         <v>46266</v>
       </c>
       <c r="B27" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C27" t="s">
         <v>85</v>
@@ -6263,6 +6437,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -6523,27 +6717,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6560,23 +6753,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AEF0940-32B7-4A40-9838-77C05526AE48}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1EEB364-71C0-4931-8CBA-A9375AA00135}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="172">
   <si>
     <t>Usuário</t>
   </si>
@@ -551,6 +551,12 @@
   </si>
   <si>
     <t>WILLAME NOGUEIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>RONY ALVES DAMASCENO</t>
+  </si>
+  <si>
+    <t>ACREMICE MARIA DE MELO BARROS</t>
   </si>
 </sst>
 </file>
@@ -592,11 +598,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -877,13 +882,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R79"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -908,7 +912,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -917,7 +921,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -949,31 +953,31 @@
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L2" s="1">
@@ -1005,31 +1009,31 @@
       <c r="B3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="1">
@@ -1061,31 +1065,31 @@
       <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L4" s="1">
@@ -1114,31 +1118,31 @@
       <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>6</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="1">
@@ -1170,31 +1174,31 @@
       <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <v>7</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L6" s="1">
@@ -1223,31 +1227,31 @@
       <c r="B7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <v>8</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L7" s="1">
@@ -1276,31 +1280,31 @@
       <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <v>10</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L8" s="1">
@@ -1329,31 +1333,31 @@
       <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <v>15</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L9" s="1">
@@ -1382,31 +1386,31 @@
       <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10">
         <v>15</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="J10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L10" s="1">
@@ -1435,31 +1439,31 @@
       <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11">
         <v>16</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="J11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L11" s="1">
@@ -1488,31 +1492,31 @@
       <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="3">
-        <v>20</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="H12">
+        <v>20</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="1">
@@ -1541,31 +1545,31 @@
       <c r="B13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13">
         <v>21</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="J13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L13" s="1">
@@ -1597,31 +1601,31 @@
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14">
         <v>22</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="J14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="1">
@@ -1650,31 +1654,31 @@
       <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15">
         <v>24</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="J15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L15" s="1">
@@ -1703,31 +1707,31 @@
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="3">
-        <v>28</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="H16">
+        <v>28</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L16" s="1">
@@ -1756,31 +1760,31 @@
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="3">
-        <v>28</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="H17">
+        <v>28</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="J17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L17" s="1">
@@ -1812,31 +1816,31 @@
       <c r="B18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="3">
-        <v>28</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="H18">
+        <v>28</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="J18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L18" s="1">
@@ -1865,31 +1869,31 @@
       <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19">
         <v>3</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="J19" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L19" s="1">
@@ -1921,31 +1925,31 @@
       <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20">
         <v>4</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="J20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L20" s="1">
@@ -1977,31 +1981,31 @@
       <c r="B21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21">
         <v>5</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="J21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="1">
@@ -2033,31 +2037,31 @@
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22">
         <v>6</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="J22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L22" s="1">
@@ -2089,31 +2093,31 @@
       <c r="B23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23">
         <v>7</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="J23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L23" s="1">
@@ -2145,31 +2149,31 @@
       <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="C24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24">
         <v>7</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" t="s">
+      <c r="J24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L24" s="1">
@@ -2201,31 +2205,31 @@
       <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25">
         <v>10</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" t="s">
+      <c r="J25" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L25" s="1">
@@ -2238,7 +2242,7 @@
         <v>136</v>
       </c>
       <c r="O25">
-        <v>8.77</v>
+        <v>10.5</v>
       </c>
       <c r="P25" t="s">
         <v>35</v>
@@ -2257,31 +2261,31 @@
       <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26">
         <v>11</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" t="s">
+      <c r="J26" t="s">
+        <v>25</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L26" s="1">
@@ -2313,31 +2317,31 @@
       <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="C27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27">
         <v>11</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="J27" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L27" s="1">
@@ -2369,31 +2373,31 @@
       <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28">
         <v>13</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" t="s">
+      <c r="J28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L28" s="1">
@@ -2425,31 +2429,31 @@
       <c r="B29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29">
         <v>13</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K29" t="s">
+      <c r="J29" t="s">
+        <v>25</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L29" s="1">
@@ -2481,31 +2485,31 @@
       <c r="B30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" t="s">
         <v>94</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30">
         <v>14</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="J30" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L30" s="1">
@@ -2537,31 +2541,31 @@
       <c r="B31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="C31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" t="s">
         <v>22</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31">
         <v>17</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K31" t="s">
+      <c r="J31" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L31" s="1">
@@ -2593,31 +2597,31 @@
       <c r="B32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="C32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" t="s">
         <v>22</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32">
         <v>18</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="J32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L32" s="1">
@@ -2649,31 +2653,31 @@
       <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="C33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" t="s">
         <v>94</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" t="s">
         <v>95</v>
       </c>
-      <c r="H33" s="3">
-        <v>19</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="H33">
+        <v>19</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" t="s">
+      <c r="J33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L33" s="1">
@@ -2705,31 +2709,31 @@
       <c r="B34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" t="s">
         <v>43</v>
       </c>
-      <c r="H34" s="3">
-        <v>19</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="H34">
+        <v>19</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K34" t="s">
+      <c r="J34" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L34" s="1">
@@ -2761,31 +2765,31 @@
       <c r="B35" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="C35" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" t="s">
         <v>94</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" t="s">
         <v>95</v>
       </c>
-      <c r="H35" s="3">
-        <v>20</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="H35">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" t="s">
+      <c r="J35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L35" s="1">
@@ -2817,31 +2821,31 @@
       <c r="B36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="C36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" t="s">
         <v>94</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" t="s">
         <v>95</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36">
         <v>21</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K36" t="s">
+      <c r="J36" t="s">
+        <v>25</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L36" s="1">
@@ -2873,31 +2877,31 @@
       <c r="B37" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="C37" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" t="s">
         <v>94</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37">
         <v>21</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" t="s">
+      <c r="J37" t="s">
+        <v>25</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L37" s="1">
@@ -2929,31 +2933,31 @@
       <c r="B38" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" t="s">
         <v>94</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" t="s">
         <v>95</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38">
         <v>21</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" t="s">
+      <c r="J38" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L38" s="1">
@@ -2985,31 +2989,31 @@
       <c r="B39" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" t="s">
         <v>108</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39">
         <v>21</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" t="s">
+      <c r="J39" t="s">
+        <v>25</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L39" s="1">
@@ -3041,31 +3045,31 @@
       <c r="B40" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="C40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" t="s">
         <v>94</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" t="s">
         <v>95</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40">
         <v>21</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="J40" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L40" s="1">
@@ -3097,31 +3101,31 @@
       <c r="B41" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="C41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" t="s">
         <v>94</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" t="s">
         <v>95</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41">
         <v>21</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="J41" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L41" s="1">
@@ -3153,31 +3157,31 @@
       <c r="B42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="C42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" t="s">
         <v>22</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" t="s">
         <v>32</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42">
         <v>21</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K42" t="s">
+      <c r="J42" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L42" s="1">
@@ -3209,31 +3213,31 @@
       <c r="B43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="C43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" t="s">
         <v>22</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43">
         <v>24</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K43" t="s">
+      <c r="J43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L43" s="1">
@@ -3265,31 +3269,31 @@
       <c r="B44" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="C44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" t="s">
         <v>22</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="3">
-        <v>25</v>
-      </c>
-      <c r="I44" t="s">
+      <c r="H44">
+        <v>25</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" t="s">
+      <c r="J44" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L44" s="1">
@@ -3321,31 +3325,31 @@
       <c r="B45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="C45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="3">
-        <v>25</v>
-      </c>
-      <c r="I45" t="s">
+      <c r="H45">
+        <v>25</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K45" t="s">
+      <c r="J45" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L45" s="1">
@@ -3377,31 +3381,31 @@
       <c r="B46" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="C46" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" t="s">
         <v>22</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" t="s">
         <v>43</v>
       </c>
-      <c r="H46" s="3">
-        <v>25</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="H46">
+        <v>25</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K46" t="s">
+      <c r="J46" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L46" s="1">
@@ -3433,31 +3437,31 @@
       <c r="B47" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="C47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" t="s">
         <v>22</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" t="s">
         <v>32</v>
       </c>
-      <c r="H47" s="3">
-        <v>25</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="H47">
+        <v>25</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K47" t="s">
+      <c r="J47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L47" s="1">
@@ -3489,31 +3493,31 @@
       <c r="B48" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="C48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" t="s">
         <v>94</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" t="s">
         <v>95</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48">
         <v>27</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K48" t="s">
+      <c r="J48" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L48" s="1">
@@ -3545,31 +3549,31 @@
       <c r="B49" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="C49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" t="s">
         <v>32</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49">
         <v>27</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K49" t="s">
+      <c r="J49" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L49" s="1">
@@ -3601,31 +3605,31 @@
       <c r="B50" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="C50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" t="s">
         <v>94</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" t="s">
         <v>95</v>
       </c>
-      <c r="H50" s="3">
-        <v>28</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="H50">
+        <v>28</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="J50" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L50" s="1">
@@ -3657,31 +3661,31 @@
       <c r="B51" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="C51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" t="s">
         <v>32</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51">
         <v>1</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K51" t="s">
+      <c r="J51" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L51" s="1">
@@ -3713,31 +3717,31 @@
       <c r="B52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="C52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" t="s">
         <v>94</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" t="s">
         <v>95</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52">
         <v>3</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I52" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K52" t="s">
+      <c r="J52" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L52" s="1">
@@ -3769,31 +3773,31 @@
       <c r="B53" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="C53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" t="s">
         <v>22</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" t="s">
         <v>32</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53">
         <v>3</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K53" t="s">
+      <c r="J53" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L53" s="1">
@@ -3825,31 +3829,31 @@
       <c r="B54" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="C54" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" t="s">
         <v>22</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" t="s">
         <v>32</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54">
         <v>4</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K54" t="s">
+      <c r="J54" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L54" s="1">
@@ -3881,31 +3885,31 @@
       <c r="B55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="C55" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" t="s">
         <v>22</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" t="s">
         <v>32</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55">
         <v>4</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K55" t="s">
+      <c r="J55" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L55" s="1">
@@ -3937,31 +3941,31 @@
       <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="C56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" t="s">
         <v>22</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" t="s">
         <v>32</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56">
         <v>4</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K56" t="s">
+      <c r="J56" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L56" s="1">
@@ -3993,31 +3997,31 @@
       <c r="B57" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="C57" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" t="s">
         <v>94</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" t="s">
         <v>130</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57">
         <v>8</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K57" t="s">
+      <c r="J57" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L57" s="1">
@@ -4049,31 +4053,31 @@
       <c r="B58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="C58" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" t="s">
         <v>22</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" t="s">
         <v>32</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58">
         <v>8</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K58" t="s">
+      <c r="J58" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L58" s="1">
@@ -4105,31 +4109,31 @@
       <c r="B59" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" s="2" t="s">
+      <c r="C59" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" t="s">
         <v>94</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" t="s">
         <v>95</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59">
         <v>9</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K59" t="s">
+      <c r="J59" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L59" s="1">
@@ -4161,31 +4165,31 @@
       <c r="B60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="C60" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" t="s">
         <v>22</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" t="s">
         <v>32</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60">
         <v>9</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K60" t="s">
+      <c r="J60" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L60" s="1">
@@ -4217,31 +4221,31 @@
       <c r="B61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="C61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" t="s">
         <v>22</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" t="s">
         <v>43</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61">
         <v>10</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K61" t="s">
+      <c r="J61" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L61" s="1">
@@ -4273,31 +4277,31 @@
       <c r="B62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" s="2" t="s">
+      <c r="C62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" t="s">
         <v>22</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62">
         <v>11</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I62" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K62" t="s">
+      <c r="J62" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L62" s="1">
@@ -4329,31 +4333,31 @@
       <c r="B63" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" s="2" t="s">
+      <c r="C63" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" t="s">
         <v>22</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" t="s">
         <v>32</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63">
         <v>11</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I63" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K63" t="s">
+      <c r="J63" t="s">
+        <v>25</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L63" s="1">
@@ -4385,31 +4389,31 @@
       <c r="B64" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="2" t="s">
+      <c r="C64" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" t="s">
         <v>94</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" t="s">
         <v>95</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H64">
         <v>14</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K64" t="s">
+      <c r="J64" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L64" s="1">
@@ -4441,31 +4445,31 @@
       <c r="B65" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D65" s="2" t="s">
+      <c r="C65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" t="s">
         <v>22</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" t="s">
         <v>32</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65">
         <v>14</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K65" t="s">
+      <c r="J65" t="s">
+        <v>25</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L65" s="1">
@@ -4494,34 +4498,34 @@
       <c r="A66" t="s">
         <v>17</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D66" s="2" t="s">
+      <c r="C66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" t="s">
         <v>22</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" t="s">
         <v>23</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H66">
         <v>15</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I66" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K66" t="s">
+      <c r="J66" t="s">
+        <v>25</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L66" s="1">
@@ -4550,34 +4554,34 @@
       <c r="A67" t="s">
         <v>72</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D67" s="2" t="s">
+      <c r="C67" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" t="s">
         <v>94</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" t="s">
         <v>95</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67">
         <v>15</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J67" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K67" t="s">
+      <c r="J67" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L67" s="1">
@@ -4609,31 +4613,31 @@
       <c r="B68" t="s">
         <v>156</v>
       </c>
-      <c r="C68" t="s">
-        <v>19</v>
-      </c>
-      <c r="D68" s="2" t="s">
+      <c r="C68" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" t="s">
         <v>22</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" t="s">
         <v>32</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H68">
         <v>15</v>
       </c>
-      <c r="I68" t="s">
+      <c r="I68" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K68" t="s">
+      <c r="J68" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L68" s="1">
@@ -4665,31 +4669,31 @@
       <c r="B69" t="s">
         <v>157</v>
       </c>
-      <c r="C69" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="2" t="s">
+      <c r="C69" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" t="s">
         <v>94</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" t="s">
         <v>95</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H69">
         <v>16</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K69" t="s">
+      <c r="J69" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L69" s="1">
@@ -4721,31 +4725,31 @@
       <c r="B70" t="s">
         <v>159</v>
       </c>
-      <c r="C70" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70" s="2" t="s">
+      <c r="C70" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" t="s">
         <v>22</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" t="s">
         <v>43</v>
       </c>
-      <c r="H70" s="3">
+      <c r="H70">
         <v>17</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K70" t="s">
+      <c r="J70" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L70" s="1">
@@ -4777,31 +4781,31 @@
       <c r="B71" t="s">
         <v>160</v>
       </c>
-      <c r="C71" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" s="2" t="s">
+      <c r="C71" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" t="s">
         <v>94</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" t="s">
         <v>130</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H71">
         <v>17</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J71" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K71" t="s">
+      <c r="J71" t="s">
+        <v>25</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L71" s="1">
@@ -4833,31 +4837,31 @@
       <c r="B72" t="s">
         <v>161</v>
       </c>
-      <c r="C72" t="s">
-        <v>19</v>
-      </c>
-      <c r="D72" s="2" t="s">
+      <c r="C72" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" t="s">
         <v>22</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" t="s">
         <v>32</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72">
         <v>17</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I72" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J72" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K72" t="s">
+      <c r="J72" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L72" s="1">
@@ -4889,31 +4893,31 @@
       <c r="B73" t="s">
         <v>162</v>
       </c>
-      <c r="C73" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="2" t="s">
+      <c r="C73" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" t="s">
         <v>22</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73">
         <v>17</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I73" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K73" t="s">
+      <c r="J73" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L73" s="1">
@@ -4945,31 +4949,31 @@
       <c r="B74" t="s">
         <v>163</v>
       </c>
-      <c r="C74" t="s">
-        <v>19</v>
-      </c>
-      <c r="D74" s="2" t="s">
+      <c r="C74" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" t="s">
         <v>22</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G74" t="s">
         <v>32</v>
       </c>
-      <c r="H74" s="3">
+      <c r="H74">
         <v>18</v>
       </c>
-      <c r="I74" t="s">
+      <c r="I74" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K74" t="s">
+      <c r="J74" t="s">
+        <v>25</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L74" s="1">
@@ -4990,8 +4994,8 @@
       <c r="Q74" t="s">
         <v>28</v>
       </c>
-      <c r="R74" t="e">
-        <v>#N/A</v>
+      <c r="R74">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -5004,28 +5008,28 @@
       <c r="C75" t="s">
         <v>19</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" t="s">
         <v>94</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" t="s">
         <v>95</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75">
         <v>22</v>
       </c>
-      <c r="I75" t="s">
+      <c r="I75" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J75" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K75" t="s">
+      <c r="J75" t="s">
+        <v>25</v>
+      </c>
+      <c r="K75" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L75" s="1">
@@ -5041,7 +5045,7 @@
         <v>5.46</v>
       </c>
       <c r="P75" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q75" t="s">
         <v>28</v>
@@ -5060,28 +5064,28 @@
       <c r="C76" t="s">
         <v>19</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" t="s">
         <v>94</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" t="s">
         <v>95</v>
       </c>
-      <c r="H76" s="3">
+      <c r="H76">
         <v>22</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I76" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J76" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K76" t="s">
+      <c r="J76" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L76" s="1">
@@ -5102,8 +5106,8 @@
       <c r="Q76" t="s">
         <v>28</v>
       </c>
-      <c r="R76" t="e">
-        <v>#N/A</v>
+      <c r="R76">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -5125,10 +5129,10 @@
       <c r="F77" t="s">
         <v>22</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" t="s">
         <v>32</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H77">
         <v>22</v>
       </c>
       <c r="I77" t="s">
@@ -5137,7 +5141,7 @@
       <c r="J77" t="s">
         <v>25</v>
       </c>
-      <c r="K77" t="s">
+      <c r="K77" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L77" s="1">
@@ -5158,8 +5162,8 @@
       <c r="Q77" t="s">
         <v>28</v>
       </c>
-      <c r="R77" t="e">
-        <v>#N/A</v>
+      <c r="R77">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -5181,10 +5185,10 @@
       <c r="F78" t="s">
         <v>22</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" t="s">
         <v>32</v>
       </c>
-      <c r="H78" s="3">
+      <c r="H78">
         <v>22</v>
       </c>
       <c r="I78" t="s">
@@ -5193,7 +5197,7 @@
       <c r="J78" t="s">
         <v>25</v>
       </c>
-      <c r="K78" t="s">
+      <c r="K78" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L78" s="1">
@@ -5214,8 +5218,8 @@
       <c r="Q78" t="s">
         <v>28</v>
       </c>
-      <c r="R78" t="e">
-        <v>#N/A</v>
+      <c r="R78">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -5237,10 +5241,10 @@
       <c r="F79" t="s">
         <v>94</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" t="s">
         <v>95</v>
       </c>
-      <c r="H79" s="3">
+      <c r="H79">
         <v>23</v>
       </c>
       <c r="I79" t="s">
@@ -5249,7 +5253,7 @@
       <c r="J79" t="s">
         <v>25</v>
       </c>
-      <c r="K79" t="s">
+      <c r="K79" s="1" t="s">
         <v>26</v>
       </c>
       <c r="L79" s="1">
@@ -5271,6 +5275,118 @@
         <v>28</v>
       </c>
       <c r="R79" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>17</v>
+      </c>
+      <c r="B80" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" t="s">
+        <v>21</v>
+      </c>
+      <c r="F80" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80">
+        <v>24</v>
+      </c>
+      <c r="I80" t="s">
+        <v>122</v>
+      </c>
+      <c r="J80" t="s">
+        <v>25</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L80" s="1">
+        <v>46289</v>
+      </c>
+      <c r="M80">
+        <v>625164</v>
+      </c>
+      <c r="N80" t="s">
+        <v>136</v>
+      </c>
+      <c r="O80">
+        <v>29.19</v>
+      </c>
+      <c r="P80" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>28</v>
+      </c>
+      <c r="R80" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>29</v>
+      </c>
+      <c r="B81" t="s">
+        <v>171</v>
+      </c>
+      <c r="C81" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" t="s">
+        <v>31</v>
+      </c>
+      <c r="F81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" t="s">
+        <v>32</v>
+      </c>
+      <c r="H81">
+        <v>24</v>
+      </c>
+      <c r="I81" t="s">
+        <v>122</v>
+      </c>
+      <c r="J81" t="s">
+        <v>25</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="1">
+        <v>46289</v>
+      </c>
+      <c r="M81">
+        <v>625177</v>
+      </c>
+      <c r="N81" t="s">
+        <v>136</v>
+      </c>
+      <c r="O81">
+        <v>7.91</v>
+      </c>
+      <c r="P81" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>28</v>
+      </c>
+      <c r="R81" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5287,6 +5403,7 @@
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -6437,17 +6554,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6456,7 +6562,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -6717,18 +6823,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -6736,7 +6842,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6753,4 +6859,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1EEB364-71C0-4931-8CBA-A9375AA00135}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{017F9A6D-5334-4E3B-9332-A86BDEEB022C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="185">
   <si>
     <t>Usuário</t>
   </si>
@@ -557,6 +557,45 @@
   </si>
   <si>
     <t>ACREMICE MARIA DE MELO BARROS</t>
+  </si>
+  <si>
+    <t>PEDRO SOARES DE LIMA</t>
+  </si>
+  <si>
+    <t>Horizonte</t>
+  </si>
+  <si>
+    <t>VILLA BUFFET LTDA ME</t>
+  </si>
+  <si>
+    <t>TOBIAS FRANCISCO DE ABREU</t>
+  </si>
+  <si>
+    <t>COMERCIO E DISTRIBUICAO DG LTDA</t>
+  </si>
+  <si>
+    <t>NEGOCIAÇÃO QUENTE</t>
+  </si>
+  <si>
+    <t>THALISSON LUIZ ANDRADE MARTINS 021.518.823-30</t>
+  </si>
+  <si>
+    <t>PROSPECÇÃO VENDEDOR</t>
+  </si>
+  <si>
+    <t>CAMILA GOMES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>SALUSTIANO RIBEIRO DUARTE</t>
+  </si>
+  <si>
+    <t>IZABELA MENDES SILVA REIS</t>
+  </si>
+  <si>
+    <t>PAULA CRISTINA SOARES DE MELO</t>
+  </si>
+  <si>
+    <t>THAIS RODRIGUES DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -598,10 +637,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -882,12 +920,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R81"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -915,10 +953,10 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -953,13 +991,13 @@
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>31</v>
       </c>
       <c r="F2" t="s">
@@ -974,7 +1012,7 @@
       <c r="I2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -998,8 +1036,8 @@
       <c r="Q2" t="s">
         <v>142</v>
       </c>
-      <c r="R2" t="s">
-        <v>26</v>
+      <c r="R2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1009,13 +1047,13 @@
       <c r="B3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>31</v>
       </c>
       <c r="F3" t="s">
@@ -1030,7 +1068,7 @@
       <c r="I3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -1054,8 +1092,8 @@
       <c r="Q3" t="s">
         <v>143</v>
       </c>
-      <c r="R3" t="s">
-        <v>26</v>
+      <c r="R3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1065,13 +1103,13 @@
       <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>31</v>
       </c>
       <c r="F4" t="s">
@@ -1086,7 +1124,7 @@
       <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K4" s="1" t="s">
@@ -1107,8 +1145,8 @@
       <c r="P4" t="s">
         <v>28</v>
       </c>
-      <c r="R4" t="s">
-        <v>26</v>
+      <c r="R4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1118,13 +1156,13 @@
       <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
         <v>31</v>
       </c>
       <c r="F5" t="s">
@@ -1139,7 +1177,7 @@
       <c r="I5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -1163,8 +1201,8 @@
       <c r="Q5" t="s">
         <v>152</v>
       </c>
-      <c r="R5" t="s">
-        <v>26</v>
+      <c r="R5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1174,13 +1212,13 @@
       <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
       <c r="F6" t="s">
@@ -1195,7 +1233,7 @@
       <c r="I6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="1" t="s">
@@ -1204,20 +1242,20 @@
       <c r="L6" s="1">
         <v>46210</v>
       </c>
-      <c r="M6">
-        <v>588146</v>
+      <c r="M6" t="s">
+        <v>158</v>
       </c>
       <c r="N6" t="s">
-        <v>136</v>
-      </c>
-      <c r="O6">
-        <v>67.37</v>
+        <v>158</v>
+      </c>
+      <c r="O6" t="s">
+        <v>158</v>
       </c>
       <c r="P6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R6" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1227,13 +1265,13 @@
       <c r="B7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
         <v>31</v>
       </c>
       <c r="F7" t="s">
@@ -1248,7 +1286,7 @@
       <c r="I7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -1269,8 +1307,8 @@
       <c r="P7" t="s">
         <v>35</v>
       </c>
-      <c r="R7" t="s">
-        <v>26</v>
+      <c r="R7">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1280,13 +1318,13 @@
       <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
         <v>31</v>
       </c>
       <c r="F8" t="s">
@@ -1301,7 +1339,7 @@
       <c r="I8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K8" s="1" t="s">
@@ -1322,8 +1360,8 @@
       <c r="P8" t="s">
         <v>28</v>
       </c>
-      <c r="R8" t="s">
-        <v>26</v>
+      <c r="R8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1333,13 +1371,13 @@
       <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
         <v>31</v>
       </c>
       <c r="F9" t="s">
@@ -1354,7 +1392,7 @@
       <c r="I9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K9" s="1" t="s">
@@ -1375,8 +1413,8 @@
       <c r="P9" t="s">
         <v>35</v>
       </c>
-      <c r="R9" t="s">
-        <v>26</v>
+      <c r="R9">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1386,13 +1424,13 @@
       <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
         <v>31</v>
       </c>
       <c r="F10" t="s">
@@ -1407,7 +1445,7 @@
       <c r="I10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K10" s="1" t="s">
@@ -1428,8 +1466,8 @@
       <c r="P10" t="s">
         <v>28</v>
       </c>
-      <c r="R10" t="s">
-        <v>26</v>
+      <c r="R10">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1439,13 +1477,13 @@
       <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
         <v>31</v>
       </c>
       <c r="F11" t="s">
@@ -1460,7 +1498,7 @@
       <c r="I11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K11" s="1" t="s">
@@ -1481,8 +1519,8 @@
       <c r="P11" t="s">
         <v>28</v>
       </c>
-      <c r="R11" t="s">
-        <v>26</v>
+      <c r="R11">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1492,13 +1530,13 @@
       <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
         <v>31</v>
       </c>
       <c r="F12" t="s">
@@ -1513,7 +1551,7 @@
       <c r="I12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K12" s="1" t="s">
@@ -1534,8 +1572,8 @@
       <c r="P12" t="s">
         <v>28</v>
       </c>
-      <c r="R12" t="s">
-        <v>26</v>
+      <c r="R12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -1545,13 +1583,13 @@
       <c r="B13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
         <v>31</v>
       </c>
       <c r="F13" t="s">
@@ -1566,7 +1604,7 @@
       <c r="I13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K13" s="1" t="s">
@@ -1590,8 +1628,8 @@
       <c r="Q13" t="s">
         <v>153</v>
       </c>
-      <c r="R13" t="s">
-        <v>26</v>
+      <c r="R13">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1601,13 +1639,13 @@
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
         <v>31</v>
       </c>
       <c r="F14" t="s">
@@ -1622,7 +1660,7 @@
       <c r="I14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="1" t="s">
@@ -1643,8 +1681,8 @@
       <c r="P14" t="s">
         <v>28</v>
       </c>
-      <c r="R14" t="s">
-        <v>26</v>
+      <c r="R14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -1654,13 +1692,13 @@
       <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
         <v>31</v>
       </c>
       <c r="F15" t="s">
@@ -1675,7 +1713,7 @@
       <c r="I15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -1696,8 +1734,8 @@
       <c r="P15" t="s">
         <v>28</v>
       </c>
-      <c r="R15" t="s">
-        <v>26</v>
+      <c r="R15">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -1707,13 +1745,13 @@
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
         <v>31</v>
       </c>
       <c r="F16" t="s">
@@ -1728,7 +1766,7 @@
       <c r="I16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1747,10 +1785,10 @@
         <v>3.66</v>
       </c>
       <c r="P16" t="s">
-        <v>35</v>
-      </c>
-      <c r="R16" t="s">
-        <v>26</v>
+        <v>132</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -1760,13 +1798,13 @@
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
         <v>31</v>
       </c>
       <c r="F17" t="s">
@@ -1781,7 +1819,7 @@
       <c r="I17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -1805,8 +1843,8 @@
       <c r="Q17" t="s">
         <v>154</v>
       </c>
-      <c r="R17" t="s">
-        <v>26</v>
+      <c r="R17">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -1816,13 +1854,13 @@
       <c r="B18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
         <v>31</v>
       </c>
       <c r="F18" t="s">
@@ -1837,7 +1875,7 @@
       <c r="I18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K18" s="1" t="s">
@@ -1858,8 +1896,8 @@
       <c r="P18" t="s">
         <v>35</v>
       </c>
-      <c r="R18" t="s">
-        <v>26</v>
+      <c r="R18">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -1869,13 +1907,13 @@
       <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
         <v>31</v>
       </c>
       <c r="F19" t="s">
@@ -1890,7 +1928,7 @@
       <c r="I19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -1914,8 +1952,8 @@
       <c r="Q19" t="s">
         <v>155</v>
       </c>
-      <c r="R19" t="s">
-        <v>26</v>
+      <c r="R19">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -1925,13 +1963,13 @@
       <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
         <v>31</v>
       </c>
       <c r="F20" t="s">
@@ -1946,7 +1984,7 @@
       <c r="I20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -1955,23 +1993,23 @@
       <c r="L20" s="1">
         <v>46238</v>
       </c>
-      <c r="M20">
-        <v>601025</v>
+      <c r="M20" t="s">
+        <v>158</v>
       </c>
       <c r="N20" t="s">
-        <v>136</v>
-      </c>
-      <c r="O20">
-        <v>41.62</v>
+        <v>158</v>
+      </c>
+      <c r="O20" t="s">
+        <v>158</v>
       </c>
       <c r="P20" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q20" t="s">
         <v>28</v>
       </c>
-      <c r="R20" t="s">
-        <v>26</v>
+      <c r="R20">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -1981,13 +2019,13 @@
       <c r="B21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
         <v>31</v>
       </c>
       <c r="F21" t="s">
@@ -2002,7 +2040,7 @@
       <c r="I21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -2026,8 +2064,8 @@
       <c r="Q21" t="s">
         <v>28</v>
       </c>
-      <c r="R21" t="s">
-        <v>26</v>
+      <c r="R21">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2037,13 +2075,13 @@
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
         <v>31</v>
       </c>
       <c r="F22" t="s">
@@ -2058,7 +2096,7 @@
       <c r="I22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K22" s="1" t="s">
@@ -2082,8 +2120,8 @@
       <c r="Q22" t="s">
         <v>28</v>
       </c>
-      <c r="R22" t="s">
-        <v>26</v>
+      <c r="R22">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2093,13 +2131,13 @@
       <c r="B23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
         <v>31</v>
       </c>
       <c r="F23" t="s">
@@ -2114,7 +2152,7 @@
       <c r="I23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K23" s="1" t="s">
@@ -2138,8 +2176,8 @@
       <c r="Q23" t="s">
         <v>144</v>
       </c>
-      <c r="R23" t="s">
-        <v>26</v>
+      <c r="R23">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2149,13 +2187,13 @@
       <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
         <v>31</v>
       </c>
       <c r="F24" t="s">
@@ -2170,7 +2208,7 @@
       <c r="I24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K24" s="1" t="s">
@@ -2194,8 +2232,8 @@
       <c r="Q24" t="s">
         <v>28</v>
       </c>
-      <c r="R24" t="s">
-        <v>26</v>
+      <c r="R24">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2205,13 +2243,13 @@
       <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
         <v>31</v>
       </c>
       <c r="F25" t="s">
@@ -2226,7 +2264,7 @@
       <c r="I25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K25" s="1" t="s">
@@ -2245,13 +2283,13 @@
         <v>10.5</v>
       </c>
       <c r="P25" t="s">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="Q25" t="s">
         <v>28</v>
       </c>
-      <c r="R25" t="s">
-        <v>26</v>
+      <c r="R25">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -2261,13 +2299,13 @@
       <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
         <v>21</v>
       </c>
       <c r="F26" t="s">
@@ -2282,7 +2320,7 @@
       <c r="I26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K26" s="1" t="s">
@@ -2317,13 +2355,13 @@
       <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
         <v>31</v>
       </c>
       <c r="F27" t="s">
@@ -2338,7 +2376,7 @@
       <c r="I27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K27" s="1" t="s">
@@ -2362,8 +2400,8 @@
       <c r="Q27" t="s">
         <v>144</v>
       </c>
-      <c r="R27" t="s">
-        <v>26</v>
+      <c r="R27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -2373,13 +2411,13 @@
       <c r="B28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
         <v>93</v>
       </c>
       <c r="F28" t="s">
@@ -2394,7 +2432,7 @@
       <c r="I28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K28" s="1" t="s">
@@ -2418,8 +2456,8 @@
       <c r="Q28" t="s">
         <v>28</v>
       </c>
-      <c r="R28" t="s">
-        <v>26</v>
+      <c r="R28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -2429,13 +2467,13 @@
       <c r="B29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
         <v>31</v>
       </c>
       <c r="F29" t="s">
@@ -2450,7 +2488,7 @@
       <c r="I29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K29" s="1" t="s">
@@ -2459,23 +2497,23 @@
       <c r="L29" s="1">
         <v>46247</v>
       </c>
-      <c r="M29">
-        <v>605244</v>
+      <c r="M29" t="s">
+        <v>158</v>
       </c>
       <c r="N29" t="s">
-        <v>136</v>
-      </c>
-      <c r="O29">
-        <v>91.5</v>
+        <v>158</v>
+      </c>
+      <c r="O29" t="s">
+        <v>158</v>
       </c>
       <c r="P29" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q29" t="s">
         <v>28</v>
       </c>
-      <c r="R29" t="s">
-        <v>26</v>
+      <c r="R29">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -2485,13 +2523,13 @@
       <c r="B30" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
         <v>93</v>
       </c>
       <c r="F30" t="s">
@@ -2506,7 +2544,7 @@
       <c r="I30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K30" s="1" t="s">
@@ -2530,8 +2568,8 @@
       <c r="Q30" t="s">
         <v>28</v>
       </c>
-      <c r="R30" t="s">
-        <v>26</v>
+      <c r="R30">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -2541,13 +2579,13 @@
       <c r="B31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
         <v>31</v>
       </c>
       <c r="F31" t="s">
@@ -2562,7 +2600,7 @@
       <c r="I31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K31" s="1" t="s">
@@ -2586,8 +2624,8 @@
       <c r="Q31" t="s">
         <v>28</v>
       </c>
-      <c r="R31" t="s">
-        <v>26</v>
+      <c r="R31">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -2597,13 +2635,13 @@
       <c r="B32" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1" t="s">
+      <c r="C32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
         <v>31</v>
       </c>
       <c r="F32" t="s">
@@ -2618,7 +2656,7 @@
       <c r="I32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K32" s="1" t="s">
@@ -2642,8 +2680,8 @@
       <c r="Q32" t="s">
         <v>28</v>
       </c>
-      <c r="R32" t="s">
-        <v>26</v>
+      <c r="R32">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -2653,13 +2691,13 @@
       <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
         <v>93</v>
       </c>
       <c r="F33" t="s">
@@ -2674,7 +2712,7 @@
       <c r="I33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J33" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K33" s="1" t="s">
@@ -2698,8 +2736,8 @@
       <c r="Q33" t="s">
         <v>145</v>
       </c>
-      <c r="R33" t="s">
-        <v>26</v>
+      <c r="R33">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -2709,13 +2747,13 @@
       <c r="B34" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
         <v>31</v>
       </c>
       <c r="F34" t="s">
@@ -2730,7 +2768,7 @@
       <c r="I34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K34" s="1" t="s">
@@ -2754,8 +2792,8 @@
       <c r="Q34" t="s">
         <v>144</v>
       </c>
-      <c r="R34" t="s">
-        <v>26</v>
+      <c r="R34">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -2765,13 +2803,13 @@
       <c r="B35" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
         <v>93</v>
       </c>
       <c r="F35" t="s">
@@ -2786,7 +2824,7 @@
       <c r="I35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K35" s="1" t="s">
@@ -2810,8 +2848,8 @@
       <c r="Q35" t="s">
         <v>28</v>
       </c>
-      <c r="R35" t="s">
-        <v>26</v>
+      <c r="R35">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -2821,13 +2859,13 @@
       <c r="B36" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
         <v>93</v>
       </c>
       <c r="F36" t="s">
@@ -2842,7 +2880,7 @@
       <c r="I36" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K36" s="1" t="s">
@@ -2866,8 +2904,8 @@
       <c r="Q36" t="s">
         <v>146</v>
       </c>
-      <c r="R36" t="s">
-        <v>26</v>
+      <c r="R36">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -2877,13 +2915,13 @@
       <c r="B37" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
         <v>93</v>
       </c>
       <c r="F37" t="s">
@@ -2898,7 +2936,7 @@
       <c r="I37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K37" s="1" t="s">
@@ -2922,8 +2960,8 @@
       <c r="Q37" t="s">
         <v>145</v>
       </c>
-      <c r="R37" t="s">
-        <v>26</v>
+      <c r="R37">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -2933,13 +2971,13 @@
       <c r="B38" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
         <v>93</v>
       </c>
       <c r="F38" t="s">
@@ -2954,7 +2992,7 @@
       <c r="I38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K38" s="1" t="s">
@@ -2978,8 +3016,8 @@
       <c r="Q38" t="s">
         <v>28</v>
       </c>
-      <c r="R38" t="s">
-        <v>26</v>
+      <c r="R38">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -2989,13 +3027,13 @@
       <c r="B39" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
         <v>93</v>
       </c>
       <c r="F39" t="s">
@@ -3010,7 +3048,7 @@
       <c r="I39" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K39" s="1" t="s">
@@ -3034,8 +3072,8 @@
       <c r="Q39" t="s">
         <v>28</v>
       </c>
-      <c r="R39" t="s">
-        <v>26</v>
+      <c r="R39">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -3045,13 +3083,13 @@
       <c r="B40" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
         <v>93</v>
       </c>
       <c r="F40" t="s">
@@ -3066,7 +3104,7 @@
       <c r="I40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K40" s="1" t="s">
@@ -3090,8 +3128,8 @@
       <c r="Q40" t="s">
         <v>28</v>
       </c>
-      <c r="R40" t="s">
-        <v>26</v>
+      <c r="R40">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -3101,13 +3139,13 @@
       <c r="B41" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
         <v>93</v>
       </c>
       <c r="F41" t="s">
@@ -3122,7 +3160,7 @@
       <c r="I41" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K41" s="1" t="s">
@@ -3146,8 +3184,8 @@
       <c r="Q41" t="s">
         <v>147</v>
       </c>
-      <c r="R41" t="s">
-        <v>26</v>
+      <c r="R41">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -3157,13 +3195,13 @@
       <c r="B42" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
         <v>31</v>
       </c>
       <c r="F42" t="s">
@@ -3178,7 +3216,7 @@
       <c r="I42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K42" s="1" t="s">
@@ -3202,8 +3240,8 @@
       <c r="Q42" t="s">
         <v>144</v>
       </c>
-      <c r="R42" t="s">
-        <v>26</v>
+      <c r="R42">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -3213,13 +3251,13 @@
       <c r="B43" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="C43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
         <v>31</v>
       </c>
       <c r="F43" t="s">
@@ -3234,7 +3272,7 @@
       <c r="I43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K43" s="1" t="s">
@@ -3258,8 +3296,8 @@
       <c r="Q43" t="s">
         <v>28</v>
       </c>
-      <c r="R43" t="s">
-        <v>26</v>
+      <c r="R43">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -3269,13 +3307,13 @@
       <c r="B44" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
         <v>21</v>
       </c>
       <c r="F44" t="s">
@@ -3290,7 +3328,7 @@
       <c r="I44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K44" s="1" t="s">
@@ -3325,13 +3363,13 @@
       <c r="B45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
         <v>21</v>
       </c>
       <c r="F45" t="s">
@@ -3346,7 +3384,7 @@
       <c r="I45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K45" s="1" t="s">
@@ -3370,8 +3408,8 @@
       <c r="Q45" t="s">
         <v>28</v>
       </c>
-      <c r="R45" t="s">
-        <v>26</v>
+      <c r="R45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -3381,13 +3419,13 @@
       <c r="B46" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="s">
         <v>31</v>
       </c>
       <c r="F46" t="s">
@@ -3402,7 +3440,7 @@
       <c r="I46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K46" s="1" t="s">
@@ -3426,8 +3464,8 @@
       <c r="Q46" t="s">
         <v>146</v>
       </c>
-      <c r="R46" t="s">
-        <v>26</v>
+      <c r="R46">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -3437,13 +3475,13 @@
       <c r="B47" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
         <v>31</v>
       </c>
       <c r="F47" t="s">
@@ -3458,7 +3496,7 @@
       <c r="I47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K47" s="1" t="s">
@@ -3482,8 +3520,8 @@
       <c r="Q47" t="s">
         <v>28</v>
       </c>
-      <c r="R47" t="s">
-        <v>26</v>
+      <c r="R47">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -3493,13 +3531,13 @@
       <c r="B48" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
         <v>93</v>
       </c>
       <c r="F48" t="s">
@@ -3514,7 +3552,7 @@
       <c r="I48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K48" s="1" t="s">
@@ -3538,8 +3576,8 @@
       <c r="Q48" t="s">
         <v>145</v>
       </c>
-      <c r="R48" t="s">
-        <v>26</v>
+      <c r="R48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -3549,13 +3587,13 @@
       <c r="B49" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" t="s">
         <v>31</v>
       </c>
       <c r="F49" t="s">
@@ -3570,7 +3608,7 @@
       <c r="I49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K49" s="1" t="s">
@@ -3594,8 +3632,8 @@
       <c r="Q49" t="s">
         <v>28</v>
       </c>
-      <c r="R49" t="s">
-        <v>26</v>
+      <c r="R49">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -3605,13 +3643,13 @@
       <c r="B50" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
         <v>93</v>
       </c>
       <c r="F50" t="s">
@@ -3626,7 +3664,7 @@
       <c r="I50" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K50" s="1" t="s">
@@ -3650,8 +3688,8 @@
       <c r="Q50" t="s">
         <v>145</v>
       </c>
-      <c r="R50" t="s">
-        <v>26</v>
+      <c r="R50">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -3661,13 +3699,13 @@
       <c r="B51" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
         <v>31</v>
       </c>
       <c r="F51" t="s">
@@ -3682,7 +3720,7 @@
       <c r="I51" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K51" s="1" t="s">
@@ -3717,13 +3755,13 @@
       <c r="B52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" t="s">
         <v>93</v>
       </c>
       <c r="F52" t="s">
@@ -3738,7 +3776,7 @@
       <c r="I52" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K52" s="1" t="s">
@@ -3773,13 +3811,13 @@
       <c r="B53" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
         <v>31</v>
       </c>
       <c r="F53" t="s">
@@ -3794,7 +3832,7 @@
       <c r="I53" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K53" s="1" t="s">
@@ -3829,13 +3867,13 @@
       <c r="B54" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
         <v>31</v>
       </c>
       <c r="F54" t="s">
@@ -3850,7 +3888,7 @@
       <c r="I54" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K54" s="1" t="s">
@@ -3885,13 +3923,13 @@
       <c r="B55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
         <v>31</v>
       </c>
       <c r="F55" t="s">
@@ -3906,7 +3944,7 @@
       <c r="I55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K55" s="1" t="s">
@@ -3941,13 +3979,13 @@
       <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
         <v>31</v>
       </c>
       <c r="F56" t="s">
@@ -3962,7 +4000,7 @@
       <c r="I56" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K56" s="1" t="s">
@@ -3997,13 +4035,13 @@
       <c r="B57" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" s="1" t="s">
+      <c r="C57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
         <v>93</v>
       </c>
       <c r="F57" t="s">
@@ -4018,7 +4056,7 @@
       <c r="I57" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K57" s="1" t="s">
@@ -4053,13 +4091,13 @@
       <c r="B58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
         <v>31</v>
       </c>
       <c r="F58" t="s">
@@ -4074,7 +4112,7 @@
       <c r="I58" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J58" t="s">
+      <c r="J58" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K58" s="1" t="s">
@@ -4109,13 +4147,13 @@
       <c r="B59" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
         <v>93</v>
       </c>
       <c r="F59" t="s">
@@ -4130,7 +4168,7 @@
       <c r="I59" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J59" t="s">
+      <c r="J59" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K59" s="1" t="s">
@@ -4165,13 +4203,13 @@
       <c r="B60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
         <v>31</v>
       </c>
       <c r="F60" t="s">
@@ -4186,7 +4224,7 @@
       <c r="I60" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K60" s="1" t="s">
@@ -4205,7 +4243,7 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="P60" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q60" t="s">
         <v>28</v>
@@ -4221,13 +4259,13 @@
       <c r="B61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
         <v>31</v>
       </c>
       <c r="F61" t="s">
@@ -4242,7 +4280,7 @@
       <c r="I61" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K61" s="1" t="s">
@@ -4277,13 +4315,13 @@
       <c r="B62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" t="s">
         <v>21</v>
       </c>
       <c r="F62" t="s">
@@ -4298,7 +4336,7 @@
       <c r="I62" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K62" s="1" t="s">
@@ -4333,13 +4371,13 @@
       <c r="B63" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
         <v>31</v>
       </c>
       <c r="F63" t="s">
@@ -4354,7 +4392,7 @@
       <c r="I63" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K63" s="1" t="s">
@@ -4389,13 +4427,13 @@
       <c r="B64" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" s="1" t="s">
+      <c r="C64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
         <v>140</v>
       </c>
       <c r="F64" t="s">
@@ -4410,7 +4448,7 @@
       <c r="I64" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K64" s="1" t="s">
@@ -4445,13 +4483,13 @@
       <c r="B65" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
         <v>31</v>
       </c>
       <c r="F65" t="s">
@@ -4466,7 +4504,7 @@
       <c r="I65" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K65" s="1" t="s">
@@ -4501,13 +4539,13 @@
       <c r="B66" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
         <v>21</v>
       </c>
       <c r="F66" t="s">
@@ -4522,7 +4560,7 @@
       <c r="I66" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K66" s="1" t="s">
@@ -4557,13 +4595,13 @@
       <c r="B67" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" t="s">
         <v>151</v>
       </c>
       <c r="F67" t="s">
@@ -4578,7 +4616,7 @@
       <c r="I67" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K67" s="1" t="s">
@@ -4597,7 +4635,7 @@
         <v>6.46</v>
       </c>
       <c r="P67" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q67" t="s">
         <v>28</v>
@@ -4610,16 +4648,16 @@
       <c r="A68" t="s">
         <v>29</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
         <v>31</v>
       </c>
       <c r="F68" t="s">
@@ -4634,7 +4672,7 @@
       <c r="I68" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K68" s="1" t="s">
@@ -4666,16 +4704,16 @@
       <c r="A69" t="s">
         <v>72</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" t="s">
         <v>151</v>
       </c>
       <c r="F69" t="s">
@@ -4690,7 +4728,7 @@
       <c r="I69" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K69" s="1" t="s">
@@ -4709,7 +4747,7 @@
         <v>8.9600000000000009</v>
       </c>
       <c r="P69" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q69" t="s">
         <v>28</v>
@@ -4722,16 +4760,16 @@
       <c r="A70" t="s">
         <v>17</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" t="s">
         <v>21</v>
       </c>
       <c r="F70" t="s">
@@ -4746,7 +4784,7 @@
       <c r="I70" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K70" s="1" t="s">
@@ -4755,39 +4793,39 @@
       <c r="L70" s="1">
         <v>46282</v>
       </c>
-      <c r="M70">
-        <v>620938</v>
+      <c r="M70" t="s">
+        <v>158</v>
       </c>
       <c r="N70" t="s">
-        <v>136</v>
-      </c>
-      <c r="O70">
-        <v>11.75</v>
+        <v>158</v>
+      </c>
+      <c r="O70" t="s">
+        <v>158</v>
       </c>
       <c r="P70" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q70" t="s">
         <v>28</v>
       </c>
-      <c r="R70" t="e">
-        <v>#N/A</v>
+      <c r="R70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" t="s">
         <v>151</v>
       </c>
       <c r="F71" t="s">
@@ -4802,7 +4840,7 @@
       <c r="I71" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K71" s="1" t="s">
@@ -4821,7 +4859,7 @@
         <v>5.95</v>
       </c>
       <c r="P71" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q71" t="s">
         <v>28</v>
@@ -4834,16 +4872,16 @@
       <c r="A72" t="s">
         <v>29</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" t="s">
         <v>31</v>
       </c>
       <c r="F72" t="s">
@@ -4858,7 +4896,7 @@
       <c r="I72" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J72" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K72" s="1" t="s">
@@ -4890,16 +4928,16 @@
       <c r="A73" t="s">
         <v>29</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="C73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
         <v>31</v>
       </c>
       <c r="F73" t="s">
@@ -4914,7 +4952,7 @@
       <c r="I73" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J73" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K73" s="1" t="s">
@@ -4946,16 +4984,16 @@
       <c r="A74" t="s">
         <v>29</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
         <v>31</v>
       </c>
       <c r="F74" t="s">
@@ -4970,7 +5008,7 @@
       <c r="I74" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J74" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K74" s="1" t="s">
@@ -5002,16 +5040,16 @@
       <c r="A75" t="s">
         <v>72</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C75" t="s">
-        <v>19</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" t="s">
+        <v>20</v>
+      </c>
+      <c r="E75" t="s">
         <v>72</v>
       </c>
       <c r="F75" t="s">
@@ -5026,7 +5064,7 @@
       <c r="I75" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J75" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K75" s="1" t="s">
@@ -5036,38 +5074,38 @@
         <v>46287</v>
       </c>
       <c r="M75">
-        <v>624450</v>
+        <v>626221</v>
       </c>
       <c r="N75" t="s">
         <v>136</v>
       </c>
       <c r="O75">
-        <v>5.46</v>
+        <v>9.11</v>
       </c>
       <c r="P75" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="Q75" t="s">
         <v>28</v>
       </c>
-      <c r="R75" t="e">
-        <v>#N/A</v>
+      <c r="R75">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>72</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C76" t="s">
-        <v>19</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" t="s">
         <v>151</v>
       </c>
       <c r="F76" t="s">
@@ -5082,7 +5120,7 @@
       <c r="I76" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J76" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K76" s="1" t="s">
@@ -5101,7 +5139,7 @@
         <v>8.34</v>
       </c>
       <c r="P76" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q76" t="s">
         <v>28</v>
@@ -5135,10 +5173,10 @@
       <c r="H77">
         <v>22</v>
       </c>
-      <c r="I77" t="s">
+      <c r="I77" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J77" t="s">
+      <c r="J77" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K77" s="1" t="s">
@@ -5191,10 +5229,10 @@
       <c r="H78">
         <v>22</v>
       </c>
-      <c r="I78" t="s">
+      <c r="I78" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J78" t="s">
+      <c r="J78" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K78" s="1" t="s">
@@ -5247,10 +5285,10 @@
       <c r="H79">
         <v>23</v>
       </c>
-      <c r="I79" t="s">
+      <c r="I79" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J79" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K79" s="1" t="s">
@@ -5269,7 +5307,7 @@
         <v>22.65</v>
       </c>
       <c r="P79" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q79" t="s">
         <v>28</v>
@@ -5303,10 +5341,10 @@
       <c r="H80">
         <v>24</v>
       </c>
-      <c r="I80" t="s">
+      <c r="I80" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J80" t="s">
+      <c r="J80" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K80" s="1" t="s">
@@ -5359,10 +5397,10 @@
       <c r="H81">
         <v>24</v>
       </c>
-      <c r="I81" t="s">
+      <c r="I81" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J81" t="s">
+      <c r="J81" s="1" t="s">
         <v>25</v>
       </c>
       <c r="K81" s="1" t="s">
@@ -5378,15 +5416,575 @@
         <v>136</v>
       </c>
       <c r="O81">
-        <v>7.91</v>
+        <v>3.5</v>
       </c>
       <c r="P81" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>28</v>
+      </c>
+      <c r="R81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>72</v>
+      </c>
+      <c r="B82" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" t="s">
+        <v>151</v>
+      </c>
+      <c r="F82" t="s">
+        <v>94</v>
+      </c>
+      <c r="G82" t="s">
+        <v>173</v>
+      </c>
+      <c r="H82">
+        <v>25</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="1">
+        <v>46290</v>
+      </c>
+      <c r="M82">
+        <v>626032</v>
+      </c>
+      <c r="N82" t="s">
+        <v>136</v>
+      </c>
+      <c r="O82">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="P82" t="s">
         <v>27</v>
       </c>
-      <c r="Q81" t="s">
-        <v>28</v>
-      </c>
-      <c r="R81" t="e">
+      <c r="Q82" t="s">
+        <v>28</v>
+      </c>
+      <c r="R82" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>29</v>
+      </c>
+      <c r="B83" t="s">
+        <v>174</v>
+      </c>
+      <c r="C83" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" t="s">
+        <v>31</v>
+      </c>
+      <c r="F83" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" t="s">
+        <v>43</v>
+      </c>
+      <c r="H83">
+        <v>25</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="1">
+        <v>46290</v>
+      </c>
+      <c r="M83">
+        <v>626059</v>
+      </c>
+      <c r="N83" t="s">
+        <v>136</v>
+      </c>
+      <c r="O83">
+        <v>14.46</v>
+      </c>
+      <c r="P83" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>28</v>
+      </c>
+      <c r="R83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" t="s">
+        <v>31</v>
+      </c>
+      <c r="F84" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" t="s">
+        <v>32</v>
+      </c>
+      <c r="H84">
+        <v>28</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L84" s="1">
+        <v>46293</v>
+      </c>
+      <c r="M84">
+        <v>626925</v>
+      </c>
+      <c r="N84" t="s">
+        <v>136</v>
+      </c>
+      <c r="O84">
+        <v>17.84</v>
+      </c>
+      <c r="P84" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>28</v>
+      </c>
+      <c r="R84" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>29</v>
+      </c>
+      <c r="B85" t="s">
+        <v>176</v>
+      </c>
+      <c r="C85" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" t="s">
+        <v>31</v>
+      </c>
+      <c r="F85" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" t="s">
+        <v>43</v>
+      </c>
+      <c r="H85">
+        <v>28</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="1">
+        <v>46293</v>
+      </c>
+      <c r="M85">
+        <v>626887</v>
+      </c>
+      <c r="N85" t="s">
+        <v>136</v>
+      </c>
+      <c r="O85">
+        <v>16.39</v>
+      </c>
+      <c r="P85" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>28</v>
+      </c>
+      <c r="R85" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>72</v>
+      </c>
+      <c r="B86" t="s">
+        <v>178</v>
+      </c>
+      <c r="C86" t="s">
+        <v>179</v>
+      </c>
+      <c r="D86" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" t="s">
+        <v>151</v>
+      </c>
+      <c r="F86" t="s">
+        <v>94</v>
+      </c>
+      <c r="G86" t="s">
+        <v>108</v>
+      </c>
+      <c r="H86">
+        <v>29</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L86" s="1">
+        <v>46294</v>
+      </c>
+      <c r="M86">
+        <v>627609</v>
+      </c>
+      <c r="N86" t="s">
+        <v>136</v>
+      </c>
+      <c r="O86">
+        <v>11.61</v>
+      </c>
+      <c r="P86" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>28</v>
+      </c>
+      <c r="R86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>72</v>
+      </c>
+      <c r="B87" t="s">
+        <v>180</v>
+      </c>
+      <c r="C87" t="s">
+        <v>19</v>
+      </c>
+      <c r="D87" t="s">
+        <v>20</v>
+      </c>
+      <c r="E87" t="s">
+        <v>151</v>
+      </c>
+      <c r="F87" t="s">
+        <v>94</v>
+      </c>
+      <c r="G87" t="s">
+        <v>108</v>
+      </c>
+      <c r="H87">
+        <v>29</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="1">
+        <v>46294</v>
+      </c>
+      <c r="M87">
+        <v>627665</v>
+      </c>
+      <c r="N87" t="s">
+        <v>136</v>
+      </c>
+      <c r="O87">
+        <v>7.5</v>
+      </c>
+      <c r="P87" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>28</v>
+      </c>
+      <c r="R87" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>72</v>
+      </c>
+      <c r="B88" t="s">
+        <v>181</v>
+      </c>
+      <c r="C88" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" t="s">
+        <v>151</v>
+      </c>
+      <c r="F88" t="s">
+        <v>94</v>
+      </c>
+      <c r="G88" t="s">
+        <v>108</v>
+      </c>
+      <c r="H88">
+        <v>29</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L88" s="1">
+        <v>46294</v>
+      </c>
+      <c r="M88">
+        <v>627639</v>
+      </c>
+      <c r="N88" t="s">
+        <v>136</v>
+      </c>
+      <c r="O88">
+        <v>4.3</v>
+      </c>
+      <c r="P88" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>28</v>
+      </c>
+      <c r="R88" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>29</v>
+      </c>
+      <c r="B89" t="s">
+        <v>182</v>
+      </c>
+      <c r="C89" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" t="s">
+        <v>32</v>
+      </c>
+      <c r="H89">
+        <v>29</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="1">
+        <v>46294</v>
+      </c>
+      <c r="M89">
+        <v>627503</v>
+      </c>
+      <c r="N89" t="s">
+        <v>136</v>
+      </c>
+      <c r="O89">
+        <v>16.3</v>
+      </c>
+      <c r="P89" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>28</v>
+      </c>
+      <c r="R89" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>29</v>
+      </c>
+      <c r="B90" t="s">
+        <v>183</v>
+      </c>
+      <c r="C90" t="s">
+        <v>19</v>
+      </c>
+      <c r="D90" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" t="s">
+        <v>32</v>
+      </c>
+      <c r="H90">
+        <v>29</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L90" s="1">
+        <v>46294</v>
+      </c>
+      <c r="M90">
+        <v>627332</v>
+      </c>
+      <c r="N90" t="s">
+        <v>136</v>
+      </c>
+      <c r="O90">
+        <v>2.42</v>
+      </c>
+      <c r="P90" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>28</v>
+      </c>
+      <c r="R90" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>29</v>
+      </c>
+      <c r="B91" t="s">
+        <v>184</v>
+      </c>
+      <c r="C91" t="s">
+        <v>19</v>
+      </c>
+      <c r="D91" t="s">
+        <v>20</v>
+      </c>
+      <c r="E91" t="s">
+        <v>31</v>
+      </c>
+      <c r="F91" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91">
+        <v>29</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" s="1">
+        <v>46294</v>
+      </c>
+      <c r="M91">
+        <v>627521</v>
+      </c>
+      <c r="N91" t="s">
+        <v>136</v>
+      </c>
+      <c r="O91">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="P91" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>28</v>
+      </c>
+      <c r="R91" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -5398,7 +5996,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -6247,7 +6845,7 @@
         <v>46266</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
@@ -6285,7 +6883,7 @@
         <v>46266</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
         <v>85</v>
@@ -6329,31 +6927,31 @@
         <v>29</v>
       </c>
       <c r="D25">
-        <v>15.247999999999999</v>
+        <v>149.04499999999999</v>
       </c>
       <c r="E25">
-        <v>9.0090000000000003</v>
+        <v>97.015160000000009</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G25">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="I25">
-        <v>0.9</v>
+        <v>0.62</v>
       </c>
       <c r="J25">
-        <v>0.93333333333333335</v>
+        <v>0.96</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="L25">
-        <v>14</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -6370,28 +6968,28 @@
         <v>84</v>
       </c>
       <c r="E26">
-        <v>29.870720000000002</v>
+        <v>120.34451</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="G26">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="J26">
-        <v>6.6666666666666666E-2</v>
+        <v>0.72</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -6408,28 +7006,142 @@
         <v>84</v>
       </c>
       <c r="E27">
-        <v>12.771660000000001</v>
+        <v>69.378429999999994</v>
       </c>
       <c r="F27">
+        <v>50</v>
+      </c>
+      <c r="G27">
+        <v>60</v>
+      </c>
+      <c r="H27">
+        <v>13</v>
+      </c>
+      <c r="I27">
+        <v>0.26</v>
+      </c>
+      <c r="J27">
+        <v>0.75</v>
+      </c>
+      <c r="K27">
+        <v>32</v>
+      </c>
+      <c r="L27">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>8.0012899999999991</v>
+      </c>
+      <c r="F28">
         <v>10</v>
       </c>
-      <c r="G27">
+      <c r="G28">
         <v>15</v>
       </c>
-      <c r="H27">
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28">
+        <v>0.6</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>9</v>
+      </c>
+      <c r="L28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29">
+        <v>9.5742900000000013</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29">
         <v>0</v>
       </c>
-      <c r="I27">
+      <c r="I29">
         <v>0</v>
       </c>
-      <c r="J27">
+      <c r="J29">
         <v>0</v>
       </c>
-      <c r="K27">
+      <c r="K29">
         <v>0</v>
       </c>
-      <c r="L27">
+      <c r="L29">
         <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30">
+        <v>10.65812</v>
+      </c>
+      <c r="F30">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>15</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="K30">
+        <v>14</v>
+      </c>
+      <c r="L30">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{017F9A6D-5334-4E3B-9332-A86BDEEB022C}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03E1CEBC-4215-43B2-9227-7574B826D6A5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$A$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Rotas!$A$1:$L$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="180">
   <si>
     <t>Usuário</t>
   </si>
@@ -253,12 +254,6 @@
     <t>João Ricardo</t>
   </si>
   <si>
-    <t>Tiago Mol</t>
-  </si>
-  <si>
-    <t>Jacqson Ferreira</t>
-  </si>
-  <si>
     <t>Jefferson Mendonça</t>
   </si>
   <si>
@@ -292,15 +287,9 @@
     <t>Total de Visitas</t>
   </si>
   <si>
-    <t>Jefferson Mendonça Magalhães</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Jacqson Ferreira Maforte</t>
-  </si>
-  <si>
     <t>Renata Aparecida Moreira Magalhães</t>
   </si>
   <si>
@@ -539,9 +528,6 @@
   </si>
   <si>
     <t>RONY APARECIDA FEDOSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semana 3 </t>
   </si>
   <si>
     <t>DANTAS E DANTAS COMERCIO DE ALIMENTACAO LTDA</t>
@@ -981,7 +967,7 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -1034,7 +1020,7 @@
         <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1090,7 +1076,7 @@
         <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1199,7 +1185,7 @@
         <v>28</v>
       </c>
       <c r="Q5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -1243,13 +1229,13 @@
         <v>46210</v>
       </c>
       <c r="M6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P6" t="s">
         <v>28</v>
@@ -1299,7 +1285,7 @@
         <v>588663</v>
       </c>
       <c r="N7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O7">
         <v>35.78</v>
@@ -1405,7 +1391,7 @@
         <v>591481</v>
       </c>
       <c r="N9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1455,13 +1441,13 @@
         <v>46218</v>
       </c>
       <c r="M10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P10" t="s">
         <v>28</v>
@@ -1508,13 +1494,13 @@
         <v>46219</v>
       </c>
       <c r="M11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s">
         <v>28</v>
@@ -1626,7 +1612,7 @@
         <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -1670,13 +1656,13 @@
         <v>46225</v>
       </c>
       <c r="M14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P14" t="s">
         <v>28</v>
@@ -1779,13 +1765,13 @@
         <v>593213</v>
       </c>
       <c r="N16" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O16">
         <v>3.66</v>
       </c>
       <c r="P16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -1841,7 +1827,7 @@
         <v>28</v>
       </c>
       <c r="Q17" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -1888,7 +1874,7 @@
         <v>598353</v>
       </c>
       <c r="N18" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O18">
         <v>6.9</v>
@@ -1950,7 +1936,7 @@
         <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -1994,13 +1980,13 @@
         <v>46238</v>
       </c>
       <c r="M20" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N20" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O20" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P20" t="s">
         <v>28</v>
@@ -2053,7 +2039,7 @@
         <v>601537</v>
       </c>
       <c r="N21" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O21">
         <v>4.63</v>
@@ -2109,7 +2095,7 @@
         <v>601944</v>
       </c>
       <c r="N22" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O22">
         <v>1.96</v>
@@ -2174,7 +2160,7 @@
         <v>28</v>
       </c>
       <c r="Q23" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -2221,7 +2207,7 @@
         <v>602969</v>
       </c>
       <c r="N24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O24">
         <v>6.12</v>
@@ -2277,13 +2263,13 @@
         <v>603608</v>
       </c>
       <c r="N25" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O25">
         <v>10.5</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="Q25" t="s">
         <v>28</v>
@@ -2333,7 +2319,7 @@
         <v>604128</v>
       </c>
       <c r="N26" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O26">
         <v>8.3699999999999992</v>
@@ -2398,7 +2384,7 @@
         <v>28</v>
       </c>
       <c r="Q27" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -2406,10 +2392,10 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>19</v>
@@ -2418,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H28">
         <v>13</v>
@@ -2445,7 +2431,7 @@
         <v>605287</v>
       </c>
       <c r="N28" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O28">
         <v>61.58</v>
@@ -2465,7 +2451,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>19</v>
@@ -2498,13 +2484,13 @@
         <v>46247</v>
       </c>
       <c r="M29" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N29" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O29" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P29" t="s">
         <v>28</v>
@@ -2518,10 +2504,10 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>19</v>
@@ -2530,13 +2516,13 @@
         <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H30">
         <v>14</v>
@@ -2577,7 +2563,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>19</v>
@@ -2613,7 +2599,7 @@
         <v>606908</v>
       </c>
       <c r="N31" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O31">
         <v>37.299999999999997</v>
@@ -2633,7 +2619,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>19</v>
@@ -2669,7 +2655,7 @@
         <v>581722</v>
       </c>
       <c r="N32" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O32">
         <v>21.24</v>
@@ -2686,10 +2672,10 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>19</v>
@@ -2698,13 +2684,13 @@
         <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H33">
         <v>19</v>
@@ -2734,7 +2720,7 @@
         <v>28</v>
       </c>
       <c r="Q33" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -2745,7 +2731,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>19</v>
@@ -2790,7 +2776,7 @@
         <v>28</v>
       </c>
       <c r="Q34" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2798,10 +2784,10 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>19</v>
@@ -2810,13 +2796,13 @@
         <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H35">
         <v>20</v>
@@ -2854,10 +2840,10 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>19</v>
@@ -2866,13 +2852,13 @@
         <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H36">
         <v>21</v>
@@ -2902,7 +2888,7 @@
         <v>28</v>
       </c>
       <c r="Q36" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -2910,10 +2896,10 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>19</v>
@@ -2922,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F37" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H37">
         <v>21</v>
@@ -2958,7 +2944,7 @@
         <v>28</v>
       </c>
       <c r="Q37" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -2966,10 +2952,10 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>19</v>
@@ -2978,13 +2964,13 @@
         <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H38">
         <v>21</v>
@@ -3005,13 +2991,13 @@
         <v>609384</v>
       </c>
       <c r="N38" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O38">
         <v>3.39</v>
       </c>
       <c r="P38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Q38" t="s">
         <v>28</v>
@@ -3022,10 +3008,10 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>19</v>
@@ -3034,13 +3020,13 @@
         <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F39" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G39" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H39">
         <v>21</v>
@@ -3078,10 +3064,10 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>19</v>
@@ -3090,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="E40" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F40" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G40" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H40">
         <v>21</v>
@@ -3117,7 +3103,7 @@
         <v>604864</v>
       </c>
       <c r="N40" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O40">
         <v>19.47</v>
@@ -3134,10 +3120,10 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>19</v>
@@ -3146,13 +3132,13 @@
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F41" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H41">
         <v>21</v>
@@ -3182,7 +3168,7 @@
         <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -3193,7 +3179,7 @@
         <v>29</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>19</v>
@@ -3238,7 +3224,7 @@
         <v>28</v>
       </c>
       <c r="Q42" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -3249,7 +3235,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>19</v>
@@ -3285,7 +3271,7 @@
         <v>610104</v>
       </c>
       <c r="N43" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O43">
         <v>9.2200000000000006</v>
@@ -3305,7 +3291,7 @@
         <v>17</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>19</v>
@@ -3350,7 +3336,7 @@
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="R44" t="e">
         <v>#N/A</v>
@@ -3361,7 +3347,7 @@
         <v>17</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>19</v>
@@ -3397,7 +3383,7 @@
         <v>614542</v>
       </c>
       <c r="N45" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O45">
         <v>20.53</v>
@@ -3417,7 +3403,7 @@
         <v>29</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>19</v>
@@ -3462,7 +3448,7 @@
         <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -3473,7 +3459,7 @@
         <v>29</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>19</v>
@@ -3509,7 +3495,7 @@
         <v>610596</v>
       </c>
       <c r="N47" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O47">
         <v>4.17</v>
@@ -3526,10 +3512,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>19</v>
@@ -3538,13 +3524,13 @@
         <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F48" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H48">
         <v>27</v>
@@ -3574,7 +3560,7 @@
         <v>28</v>
       </c>
       <c r="Q48" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -3585,7 +3571,7 @@
         <v>29</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>19</v>
@@ -3621,7 +3607,7 @@
         <v>611797</v>
       </c>
       <c r="N49" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O49">
         <v>9.85</v>
@@ -3638,10 +3624,10 @@
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>19</v>
@@ -3650,13 +3636,13 @@
         <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F50" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H50">
         <v>28</v>
@@ -3686,7 +3672,7 @@
         <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -3697,7 +3683,7 @@
         <v>29</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>19</v>
@@ -3718,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>25</v>
@@ -3742,7 +3728,7 @@
         <v>28</v>
       </c>
       <c r="Q51" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -3750,10 +3736,10 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>19</v>
@@ -3762,19 +3748,19 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F52" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H52">
         <v>3</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>25</v>
@@ -3798,7 +3784,7 @@
         <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="R52">
         <v>1</v>
@@ -3809,7 +3795,7 @@
         <v>29</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>19</v>
@@ -3830,7 +3816,7 @@
         <v>3</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>25</v>
@@ -3845,7 +3831,7 @@
         <v>614995</v>
       </c>
       <c r="N53" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O53">
         <v>1.91</v>
@@ -3865,7 +3851,7 @@
         <v>29</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>19</v>
@@ -3886,7 +3872,7 @@
         <v>4</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>25</v>
@@ -3901,7 +3887,7 @@
         <v>615314</v>
       </c>
       <c r="N54" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O54">
         <v>12.23</v>
@@ -3921,7 +3907,7 @@
         <v>29</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>19</v>
@@ -3942,7 +3928,7 @@
         <v>4</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>25</v>
@@ -3957,7 +3943,7 @@
         <v>615322</v>
       </c>
       <c r="N55" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O55">
         <v>16.34</v>
@@ -3977,7 +3963,7 @@
         <v>29</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>19</v>
@@ -3998,7 +3984,7 @@
         <v>4</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>25</v>
@@ -4013,7 +3999,7 @@
         <v>615654</v>
       </c>
       <c r="N56" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O56">
         <v>11.93</v>
@@ -4030,10 +4016,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>19</v>
@@ -4042,19 +4028,19 @@
         <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F57" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G57" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H57">
         <v>8</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>25</v>
@@ -4069,7 +4055,7 @@
         <v>616899</v>
       </c>
       <c r="N57" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O57">
         <v>6.36</v>
@@ -4089,7 +4075,7 @@
         <v>29</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>19</v>
@@ -4110,7 +4096,7 @@
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>25</v>
@@ -4125,7 +4111,7 @@
         <v>616788</v>
       </c>
       <c r="N58" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O58">
         <v>32.82</v>
@@ -4142,10 +4128,10 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>19</v>
@@ -4154,19 +4140,19 @@
         <v>20</v>
       </c>
       <c r="E59" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F59" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G59" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H59">
         <v>9</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>25</v>
@@ -4181,7 +4167,7 @@
         <v>617206</v>
       </c>
       <c r="N59" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O59">
         <v>21.23</v>
@@ -4201,7 +4187,7 @@
         <v>29</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>19</v>
@@ -4222,7 +4208,7 @@
         <v>9</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>25</v>
@@ -4237,7 +4223,7 @@
         <v>617229</v>
       </c>
       <c r="N60" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O60">
         <v>2.2200000000000002</v>
@@ -4257,7 +4243,7 @@
         <v>29</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>19</v>
@@ -4278,7 +4264,7 @@
         <v>10</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>25</v>
@@ -4293,7 +4279,7 @@
         <v>617914</v>
       </c>
       <c r="N61" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O61">
         <v>8.4600000000000009</v>
@@ -4313,7 +4299,7 @@
         <v>17</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>19</v>
@@ -4334,7 +4320,7 @@
         <v>11</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>25</v>
@@ -4358,7 +4344,7 @@
         <v>28</v>
       </c>
       <c r="Q62" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -4369,7 +4355,7 @@
         <v>29</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>19</v>
@@ -4390,7 +4376,7 @@
         <v>11</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>25</v>
@@ -4405,7 +4391,7 @@
         <v>618930</v>
       </c>
       <c r="N63" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O63">
         <v>17.97</v>
@@ -4422,10 +4408,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>19</v>
@@ -4434,19 +4420,19 @@
         <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F64" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H64">
         <v>14</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>25</v>
@@ -4461,7 +4447,7 @@
         <v>619855</v>
       </c>
       <c r="N64" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O64">
         <v>4.68</v>
@@ -4481,7 +4467,7 @@
         <v>29</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>19</v>
@@ -4502,7 +4488,7 @@
         <v>14</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>25</v>
@@ -4517,7 +4503,7 @@
         <v>619980</v>
       </c>
       <c r="N65" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O65">
         <v>8.5399999999999991</v>
@@ -4537,7 +4523,7 @@
         <v>17</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>19</v>
@@ -4558,7 +4544,7 @@
         <v>15</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>25</v>
@@ -4590,10 +4576,10 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>19</v>
@@ -4602,19 +4588,19 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F67" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H67">
         <v>15</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J67" s="1" t="s">
         <v>25</v>
@@ -4629,7 +4615,7 @@
         <v>620157</v>
       </c>
       <c r="N67" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O67">
         <v>6.46</v>
@@ -4649,7 +4635,7 @@
         <v>29</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>19</v>
@@ -4670,7 +4656,7 @@
         <v>15</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>25</v>
@@ -4685,7 +4671,7 @@
         <v>620523</v>
       </c>
       <c r="N68" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O68">
         <v>8.57</v>
@@ -4702,10 +4688,10 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>19</v>
@@ -4714,19 +4700,19 @@
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H69">
         <v>16</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>25</v>
@@ -4741,7 +4727,7 @@
         <v>620676</v>
       </c>
       <c r="N69" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O69">
         <v>8.9600000000000009</v>
@@ -4761,7 +4747,7 @@
         <v>17</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>19</v>
@@ -4782,7 +4768,7 @@
         <v>17</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J70" s="1" t="s">
         <v>25</v>
@@ -4794,13 +4780,13 @@
         <v>46282</v>
       </c>
       <c r="M70" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N70" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="O70" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P70" t="s">
         <v>28</v>
@@ -4814,10 +4800,10 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>19</v>
@@ -4826,19 +4812,19 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F71" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H71">
         <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>25</v>
@@ -4853,7 +4839,7 @@
         <v>621205</v>
       </c>
       <c r="N71" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O71">
         <v>5.95</v>
@@ -4873,7 +4859,7 @@
         <v>29</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>19</v>
@@ -4894,7 +4880,7 @@
         <v>17</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>25</v>
@@ -4909,7 +4895,7 @@
         <v>621574</v>
       </c>
       <c r="N72" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O72">
         <v>3.78</v>
@@ -4929,7 +4915,7 @@
         <v>29</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>19</v>
@@ -4950,7 +4936,7 @@
         <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>25</v>
@@ -4965,7 +4951,7 @@
         <v>621242</v>
       </c>
       <c r="N73" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O73">
         <v>5.46</v>
@@ -4985,7 +4971,7 @@
         <v>29</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>19</v>
@@ -5006,7 +4992,7 @@
         <v>18</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>25</v>
@@ -5021,7 +5007,7 @@
         <v>622716</v>
       </c>
       <c r="N74" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O74">
         <v>5.33</v>
@@ -5038,10 +5024,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>19</v>
@@ -5050,19 +5036,19 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F75" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H75">
         <v>22</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>25</v>
@@ -5077,13 +5063,13 @@
         <v>626221</v>
       </c>
       <c r="N75" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O75">
         <v>9.11</v>
       </c>
       <c r="P75" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="Q75" t="s">
         <v>28</v>
@@ -5094,10 +5080,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>19</v>
@@ -5106,19 +5092,19 @@
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F76" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G76" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H76">
         <v>22</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>25</v>
@@ -5133,7 +5119,7 @@
         <v>624470</v>
       </c>
       <c r="N76" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O76">
         <v>8.34</v>
@@ -5153,7 +5139,7 @@
         <v>29</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C77" t="s">
         <v>19</v>
@@ -5174,7 +5160,7 @@
         <v>22</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>25</v>
@@ -5189,7 +5175,7 @@
         <v>624178</v>
       </c>
       <c r="N77" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O77">
         <v>12.79</v>
@@ -5209,7 +5195,7 @@
         <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C78" t="s">
         <v>19</v>
@@ -5230,7 +5216,7 @@
         <v>22</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>25</v>
@@ -5245,7 +5231,7 @@
         <v>624196</v>
       </c>
       <c r="N78" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O78">
         <v>3.73</v>
@@ -5262,10 +5248,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C79" t="s">
         <v>19</v>
@@ -5274,19 +5260,19 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F79" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G79" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H79">
         <v>23</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>25</v>
@@ -5301,7 +5287,7 @@
         <v>624882</v>
       </c>
       <c r="N79" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O79">
         <v>22.65</v>
@@ -5321,7 +5307,7 @@
         <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C80" t="s">
         <v>19</v>
@@ -5342,7 +5328,7 @@
         <v>24</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>25</v>
@@ -5357,7 +5343,7 @@
         <v>625164</v>
       </c>
       <c r="N80" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O80">
         <v>29.19</v>
@@ -5377,7 +5363,7 @@
         <v>29</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s">
         <v>19</v>
@@ -5398,7 +5384,7 @@
         <v>24</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>25</v>
@@ -5413,7 +5399,7 @@
         <v>625177</v>
       </c>
       <c r="N81" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O81">
         <v>3.5</v>
@@ -5430,10 +5416,10 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C82" t="s">
         <v>19</v>
@@ -5442,19 +5428,19 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F82" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G82" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H82">
         <v>25</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>25</v>
@@ -5469,7 +5455,7 @@
         <v>626032</v>
       </c>
       <c r="N82" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O82">
         <v>4.5199999999999996</v>
@@ -5489,7 +5475,7 @@
         <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C83" t="s">
         <v>19</v>
@@ -5510,7 +5496,7 @@
         <v>25</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>25</v>
@@ -5525,7 +5511,7 @@
         <v>626059</v>
       </c>
       <c r="N83" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O83">
         <v>14.46</v>
@@ -5545,7 +5531,7 @@
         <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C84" t="s">
         <v>19</v>
@@ -5566,7 +5552,7 @@
         <v>28</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>25</v>
@@ -5581,7 +5567,7 @@
         <v>626925</v>
       </c>
       <c r="N84" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O84">
         <v>17.84</v>
@@ -5601,7 +5587,7 @@
         <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C85" t="s">
         <v>19</v>
@@ -5622,7 +5608,7 @@
         <v>28</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>25</v>
@@ -5637,7 +5623,7 @@
         <v>626887</v>
       </c>
       <c r="N85" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O85">
         <v>16.39</v>
@@ -5654,31 +5640,31 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F86" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G86" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H86">
         <v>29</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>25</v>
@@ -5693,7 +5679,7 @@
         <v>627609</v>
       </c>
       <c r="N86" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O86">
         <v>11.61</v>
@@ -5710,10 +5696,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C87" t="s">
         <v>19</v>
@@ -5722,19 +5708,19 @@
         <v>20</v>
       </c>
       <c r="E87" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F87" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G87" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H87">
         <v>29</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>25</v>
@@ -5749,7 +5735,7 @@
         <v>627665</v>
       </c>
       <c r="N87" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O87">
         <v>7.5</v>
@@ -5766,10 +5752,10 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B88" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C88" t="s">
         <v>19</v>
@@ -5778,19 +5764,19 @@
         <v>20</v>
       </c>
       <c r="E88" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F88" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G88" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H88">
         <v>29</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>25</v>
@@ -5805,7 +5791,7 @@
         <v>627639</v>
       </c>
       <c r="N88" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O88">
         <v>4.3</v>
@@ -5825,7 +5811,7 @@
         <v>29</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C89" t="s">
         <v>19</v>
@@ -5846,7 +5832,7 @@
         <v>29</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>25</v>
@@ -5861,7 +5847,7 @@
         <v>627503</v>
       </c>
       <c r="N89" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O89">
         <v>16.3</v>
@@ -5881,7 +5867,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C90" t="s">
         <v>19</v>
@@ -5902,7 +5888,7 @@
         <v>29</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>25</v>
@@ -5917,7 +5903,7 @@
         <v>627332</v>
       </c>
       <c r="N90" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O90">
         <v>2.42</v>
@@ -5937,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C91" t="s">
         <v>19</v>
@@ -5958,7 +5944,7 @@
         <v>29</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>25</v>
@@ -5973,7 +5959,7 @@
         <v>627521</v>
       </c>
       <c r="N91" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="O91">
         <v>9.1300000000000008</v>
@@ -6009,37 +5995,37 @@
         <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>74</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>76</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>77</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>78</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>79</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>80</v>
-      </c>
-      <c r="K1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -6047,7 +6033,7 @@
         <v>46204</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
@@ -6085,7 +6071,7 @@
         <v>46235</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
@@ -6123,13 +6109,13 @@
         <v>46235</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E4">
         <v>51.615999999997996</v>
@@ -6147,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K4">
         <v>12</v>
@@ -6161,13 +6147,13 @@
         <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E5">
         <v>104.44589999999999</v>
@@ -6185,7 +6171,7 @@
         <v>4.0816326530612242E-2</v>
       </c>
       <c r="J5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K5">
         <v>13</v>
@@ -6199,13 +6185,13 @@
         <v>46235</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E6">
         <v>3.7643</v>
@@ -6223,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -6237,7 +6223,7 @@
         <v>46235</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
         <v>29</v>
@@ -6275,13 +6261,13 @@
         <v>46235</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E8">
         <v>242.07859999999999</v>
@@ -6313,13 +6299,13 @@
         <v>46235</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E9">
         <v>450.55970000000002</v>
@@ -6351,7 +6337,7 @@
         <v>46235</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
@@ -6389,13 +6375,13 @@
         <v>46235</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E11">
         <v>244.2174</v>
@@ -6427,13 +6413,13 @@
         <v>46235</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E12">
         <v>196.87350000000001</v>
@@ -6465,7 +6451,7 @@
         <v>46235</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
         <v>29</v>
@@ -6503,13 +6489,13 @@
         <v>46235</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E14">
         <v>37.135120000000001</v>
@@ -6541,13 +6527,13 @@
         <v>46235</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E15">
         <v>32.418210000000002</v>
@@ -6579,7 +6565,7 @@
         <v>46235</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
         <v>29</v>
@@ -6617,13 +6603,13 @@
         <v>46235</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E17">
         <v>7.3949699999999998</v>
@@ -6655,13 +6641,13 @@
         <v>46235</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E18">
         <v>43.323610000000002</v>
@@ -6693,7 +6679,7 @@
         <v>46266</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
@@ -6731,13 +6717,13 @@
         <v>46266</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E20">
         <v>64.229770000000002</v>
@@ -6769,13 +6755,13 @@
         <v>46266</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>141.77701999999999</v>
@@ -6807,7 +6793,7 @@
         <v>46266</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
@@ -6845,13 +6831,13 @@
         <v>46266</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E23">
         <v>54.846879999999999</v>
@@ -6883,13 +6869,13 @@
         <v>46266</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E24">
         <v>52.09149</v>
@@ -6921,7 +6907,7 @@
         <v>46266</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
         <v>29</v>
@@ -6959,13 +6945,13 @@
         <v>46266</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E26">
         <v>120.34451</v>
@@ -6997,13 +6983,13 @@
         <v>46266</v>
       </c>
       <c r="B27" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E27">
         <v>69.378429999999994</v>
@@ -7035,7 +7021,7 @@
         <v>46266</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C28" t="s">
         <v>29</v>
@@ -7073,13 +7059,13 @@
         <v>46266</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E29">
         <v>9.5742900000000013</v>
@@ -7111,13 +7097,13 @@
         <v>46266</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E30">
         <v>10.65812</v>
@@ -7145,6 +7131,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L30" xr:uid="{D915874B-C523-4CA2-B747-10EDBFE4BA91}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -7187,7 +7174,7 @@
         <v>46204</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>15</v>
@@ -7198,7 +7185,7 @@
         <v>46235</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -7209,7 +7196,7 @@
         <v>46235</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -7220,7 +7207,7 @@
         <v>46235</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -7231,7 +7218,7 @@
         <v>46266</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -7242,7 +7229,7 @@
         <v>46266</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C8">
         <v>18</v>
@@ -7253,7 +7240,7 @@
         <v>46266</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -7266,15 +7253,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -7535,6 +7513,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7547,14 +7534,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7573,6 +7552,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03E1CEBC-4215-43B2-9227-7574B826D6A5}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF5EACAC-0F11-4994-844A-0B1D2ECE3F09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="182">
   <si>
     <t>Usuário</t>
   </si>
@@ -428,9 +428,6 @@
     <t>ERICK FERREIRA DOS SANTOS</t>
   </si>
   <si>
-    <t>AGUARDANDO ASSINATURA</t>
-  </si>
-  <si>
     <t>JONH SANTOS MONTEIRO</t>
   </si>
   <si>
@@ -560,9 +557,6 @@
     <t>COMERCIO E DISTRIBUICAO DG LTDA</t>
   </si>
   <si>
-    <t>NEGOCIAÇÃO QUENTE</t>
-  </si>
-  <si>
     <t>THALISSON LUIZ ANDRADE MARTINS 021.518.823-30</t>
   </si>
   <si>
@@ -582,6 +576,18 @@
   </si>
   <si>
     <t>THAIS RODRIGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>BRUNA TUANNY LOPES DA SILVA</t>
+  </si>
+  <si>
+    <t>PEDRO PAULO DA SILVA</t>
+  </si>
+  <si>
+    <t>ELIETE PEREIRA LOPES DE OLIVERIA</t>
+  </si>
+  <si>
+    <t>TERESINHA MACIEL DE OLIVEIRA</t>
   </si>
 </sst>
 </file>
@@ -623,9 +629,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -906,11 +913,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -936,7 +944,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -977,7 +985,7 @@
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
@@ -992,7 +1000,7 @@
       <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -1020,7 +1028,7 @@
         <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -1033,7 +1041,7 @@
       <c r="B3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
       <c r="D3" t="s">
@@ -1048,7 +1056,7 @@
       <c r="G3" t="s">
         <v>54</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -1076,7 +1084,7 @@
         <v>28</v>
       </c>
       <c r="Q3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1089,7 +1097,7 @@
       <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
@@ -1104,7 +1112,7 @@
       <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -1142,7 +1150,7 @@
       <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
       <c r="D5" t="s">
@@ -1157,7 +1165,7 @@
       <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>6</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -1185,7 +1193,7 @@
         <v>28</v>
       </c>
       <c r="Q5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -1198,7 +1206,7 @@
       <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
       <c r="D6" t="s">
@@ -1213,7 +1221,7 @@
       <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>7</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1229,13 +1237,13 @@
         <v>46210</v>
       </c>
       <c r="M6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P6" t="s">
         <v>28</v>
@@ -1251,7 +1259,7 @@
       <c r="B7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
       <c r="D7" t="s">
@@ -1266,7 +1274,7 @@
       <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1285,7 +1293,7 @@
         <v>588663</v>
       </c>
       <c r="N7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O7">
         <v>35.78</v>
@@ -1304,7 +1312,7 @@
       <c r="B8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>49</v>
       </c>
       <c r="D8" t="s">
@@ -1319,7 +1327,7 @@
       <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1357,7 +1365,7 @@
       <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
       <c r="D9" t="s">
@@ -1372,7 +1380,7 @@
       <c r="G9" t="s">
         <v>40</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>15</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1391,7 +1399,7 @@
         <v>591481</v>
       </c>
       <c r="N9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O9">
         <v>10</v>
@@ -1410,7 +1418,7 @@
       <c r="B10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
@@ -1425,7 +1433,7 @@
       <c r="G10" t="s">
         <v>32</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1441,13 +1449,13 @@
         <v>46218</v>
       </c>
       <c r="M10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P10" t="s">
         <v>28</v>
@@ -1463,7 +1471,7 @@
       <c r="B11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11" t="s">
@@ -1478,7 +1486,7 @@
       <c r="G11" t="s">
         <v>32</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1494,13 +1502,13 @@
         <v>46219</v>
       </c>
       <c r="M11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s">
         <v>28</v>
@@ -1516,7 +1524,7 @@
       <c r="B12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" t="s">
@@ -1531,7 +1539,7 @@
       <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1569,7 +1577,7 @@
       <c r="B13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
@@ -1584,7 +1592,7 @@
       <c r="G13" t="s">
         <v>32</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>21</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1612,7 +1620,7 @@
         <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -1625,7 +1633,7 @@
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14" t="s">
@@ -1640,7 +1648,7 @@
       <c r="G14" t="s">
         <v>32</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>22</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1656,13 +1664,13 @@
         <v>46225</v>
       </c>
       <c r="M14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P14" t="s">
         <v>28</v>
@@ -1678,7 +1686,7 @@
       <c r="B15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
@@ -1693,7 +1701,7 @@
       <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -1731,7 +1739,7 @@
       <c r="B16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
@@ -1746,7 +1754,7 @@
       <c r="G16" t="s">
         <v>32</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>28</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1761,17 +1769,17 @@
       <c r="L16" s="1">
         <v>46231</v>
       </c>
-      <c r="M16">
-        <v>593213</v>
+      <c r="M16" t="s">
+        <v>153</v>
       </c>
       <c r="N16" t="s">
-        <v>132</v>
-      </c>
-      <c r="O16">
-        <v>3.66</v>
+        <v>153</v>
+      </c>
+      <c r="O16" t="s">
+        <v>153</v>
       </c>
       <c r="P16" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -1784,7 +1792,7 @@
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>19</v>
       </c>
       <c r="D17" t="s">
@@ -1799,7 +1807,7 @@
       <c r="G17" t="s">
         <v>43</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -1827,7 +1835,7 @@
         <v>28</v>
       </c>
       <c r="Q17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -1840,7 +1848,7 @@
       <c r="B18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>19</v>
       </c>
       <c r="D18" t="s">
@@ -1855,7 +1863,7 @@
       <c r="G18" t="s">
         <v>23</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -1874,7 +1882,7 @@
         <v>598353</v>
       </c>
       <c r="N18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O18">
         <v>6.9</v>
@@ -1893,7 +1901,7 @@
       <c r="B19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>19</v>
       </c>
       <c r="D19" t="s">
@@ -1908,7 +1916,7 @@
       <c r="G19" t="s">
         <v>43</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -1936,7 +1944,7 @@
         <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -1949,7 +1957,7 @@
       <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>19</v>
       </c>
       <c r="D20" t="s">
@@ -1964,7 +1972,7 @@
       <c r="G20" t="s">
         <v>32</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -1980,13 +1988,13 @@
         <v>46238</v>
       </c>
       <c r="M20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P20" t="s">
         <v>28</v>
@@ -2005,7 +2013,7 @@
       <c r="B21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>19</v>
       </c>
       <c r="D21" t="s">
@@ -2020,7 +2028,7 @@
       <c r="G21" t="s">
         <v>43</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>5</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -2039,7 +2047,7 @@
         <v>601537</v>
       </c>
       <c r="N21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O21">
         <v>4.63</v>
@@ -2061,7 +2069,7 @@
       <c r="B22" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" t="s">
@@ -2076,7 +2084,7 @@
       <c r="G22" t="s">
         <v>32</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>6</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -2095,7 +2103,7 @@
         <v>601944</v>
       </c>
       <c r="N22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O22">
         <v>1.96</v>
@@ -2117,7 +2125,7 @@
       <c r="B23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>19</v>
       </c>
       <c r="D23" t="s">
@@ -2132,7 +2140,7 @@
       <c r="G23" t="s">
         <v>32</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>7</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -2160,7 +2168,7 @@
         <v>28</v>
       </c>
       <c r="Q23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -2173,7 +2181,7 @@
       <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>19</v>
       </c>
       <c r="D24" t="s">
@@ -2188,7 +2196,7 @@
       <c r="G24" t="s">
         <v>43</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="2">
         <v>7</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2207,7 +2215,7 @@
         <v>602969</v>
       </c>
       <c r="N24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O24">
         <v>6.12</v>
@@ -2229,7 +2237,7 @@
       <c r="B25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>19</v>
       </c>
       <c r="D25" t="s">
@@ -2244,7 +2252,7 @@
       <c r="G25" t="s">
         <v>32</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -2259,17 +2267,17 @@
       <c r="L25" s="1">
         <v>46244</v>
       </c>
-      <c r="M25">
-        <v>603608</v>
+      <c r="M25" t="s">
+        <v>153</v>
       </c>
       <c r="N25" t="s">
-        <v>132</v>
-      </c>
-      <c r="O25">
-        <v>10.5</v>
+        <v>153</v>
+      </c>
+      <c r="O25" t="s">
+        <v>153</v>
       </c>
       <c r="P25" t="s">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="Q25" t="s">
         <v>28</v>
@@ -2285,7 +2293,7 @@
       <c r="B26" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" t="s">
         <v>19</v>
       </c>
       <c r="D26" t="s">
@@ -2300,7 +2308,7 @@
       <c r="G26" t="s">
         <v>23</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="2">
         <v>11</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -2319,7 +2327,7 @@
         <v>604128</v>
       </c>
       <c r="N26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O26">
         <v>8.3699999999999992</v>
@@ -2341,7 +2349,7 @@
       <c r="B27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
         <v>19</v>
       </c>
       <c r="D27" t="s">
@@ -2356,7 +2364,7 @@
       <c r="G27" t="s">
         <v>32</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="2">
         <v>11</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2384,7 +2392,7 @@
         <v>28</v>
       </c>
       <c r="Q27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -2397,7 +2405,7 @@
       <c r="B28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
         <v>19</v>
       </c>
       <c r="D28" t="s">
@@ -2412,7 +2420,7 @@
       <c r="G28" t="s">
         <v>91</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="2">
         <v>13</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2431,7 +2439,7 @@
         <v>605287</v>
       </c>
       <c r="N28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O28">
         <v>61.58</v>
@@ -2453,7 +2461,7 @@
       <c r="B29" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
         <v>19</v>
       </c>
       <c r="D29" t="s">
@@ -2468,7 +2476,7 @@
       <c r="G29" t="s">
         <v>43</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="2">
         <v>13</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2484,13 +2492,13 @@
         <v>46247</v>
       </c>
       <c r="M29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P29" t="s">
         <v>28</v>
@@ -2509,7 +2517,7 @@
       <c r="B30" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
         <v>19</v>
       </c>
       <c r="D30" t="s">
@@ -2524,7 +2532,7 @@
       <c r="G30" t="s">
         <v>91</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="2">
         <v>14</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2565,7 +2573,7 @@
       <c r="B31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31" t="s">
@@ -2580,7 +2588,7 @@
       <c r="G31" t="s">
         <v>32</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="2">
         <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2599,7 +2607,7 @@
         <v>606908</v>
       </c>
       <c r="N31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O31">
         <v>37.299999999999997</v>
@@ -2621,7 +2629,7 @@
       <c r="B32" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>19</v>
       </c>
       <c r="D32" t="s">
@@ -2636,7 +2644,7 @@
       <c r="G32" t="s">
         <v>32</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="2">
         <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -2651,17 +2659,17 @@
       <c r="L32" s="1">
         <v>46252</v>
       </c>
-      <c r="M32">
-        <v>581722</v>
+      <c r="M32" t="s">
+        <v>153</v>
       </c>
       <c r="N32" t="s">
-        <v>132</v>
-      </c>
-      <c r="O32">
-        <v>21.24</v>
+        <v>153</v>
+      </c>
+      <c r="O32" t="s">
+        <v>153</v>
       </c>
       <c r="P32" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q32" t="s">
         <v>28</v>
@@ -2677,7 +2685,7 @@
       <c r="B33" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" t="s">
         <v>19</v>
       </c>
       <c r="D33" t="s">
@@ -2692,7 +2700,7 @@
       <c r="G33" t="s">
         <v>91</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="2">
         <v>19</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -2720,7 +2728,7 @@
         <v>28</v>
       </c>
       <c r="Q33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -2733,7 +2741,7 @@
       <c r="B34" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>19</v>
       </c>
       <c r="D34" t="s">
@@ -2748,7 +2756,7 @@
       <c r="G34" t="s">
         <v>43</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="2">
         <v>19</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -2776,7 +2784,7 @@
         <v>28</v>
       </c>
       <c r="Q34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -2789,7 +2797,7 @@
       <c r="B35" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" t="s">
         <v>19</v>
       </c>
       <c r="D35" t="s">
@@ -2804,7 +2812,7 @@
       <c r="G35" t="s">
         <v>91</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="2">
         <v>20</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -2845,7 +2853,7 @@
       <c r="B36" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" t="s">
         <v>19</v>
       </c>
       <c r="D36" t="s">
@@ -2860,7 +2868,7 @@
       <c r="G36" t="s">
         <v>91</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="2">
         <v>21</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -2888,7 +2896,7 @@
         <v>28</v>
       </c>
       <c r="Q36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -2901,7 +2909,7 @@
       <c r="B37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" t="s">
         <v>19</v>
       </c>
       <c r="D37" t="s">
@@ -2916,7 +2924,7 @@
       <c r="G37" t="s">
         <v>91</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="2">
         <v>21</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -2944,7 +2952,7 @@
         <v>28</v>
       </c>
       <c r="Q37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -2957,7 +2965,7 @@
       <c r="B38" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>19</v>
       </c>
       <c r="D38" t="s">
@@ -2972,7 +2980,7 @@
       <c r="G38" t="s">
         <v>91</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="2">
         <v>21</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -2987,17 +2995,17 @@
       <c r="L38" s="1">
         <v>46255</v>
       </c>
-      <c r="M38">
-        <v>609384</v>
+      <c r="M38" t="s">
+        <v>153</v>
       </c>
       <c r="N38" t="s">
-        <v>132</v>
-      </c>
-      <c r="O38">
-        <v>3.39</v>
+        <v>153</v>
+      </c>
+      <c r="O38" t="s">
+        <v>153</v>
       </c>
       <c r="P38" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="Q38" t="s">
         <v>28</v>
@@ -3013,7 +3021,7 @@
       <c r="B39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>19</v>
       </c>
       <c r="D39" t="s">
@@ -3028,7 +3036,7 @@
       <c r="G39" t="s">
         <v>104</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="2">
         <v>21</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -3069,7 +3077,7 @@
       <c r="B40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" t="s">
         <v>19</v>
       </c>
       <c r="D40" t="s">
@@ -3084,7 +3092,7 @@
       <c r="G40" t="s">
         <v>91</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="2">
         <v>21</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -3103,7 +3111,7 @@
         <v>604864</v>
       </c>
       <c r="N40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O40">
         <v>19.47</v>
@@ -3125,7 +3133,7 @@
       <c r="B41" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>19</v>
       </c>
       <c r="D41" t="s">
@@ -3140,7 +3148,7 @@
       <c r="G41" t="s">
         <v>91</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="2">
         <v>21</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -3168,7 +3176,7 @@
         <v>28</v>
       </c>
       <c r="Q41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -3181,7 +3189,7 @@
       <c r="B42" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" t="s">
         <v>19</v>
       </c>
       <c r="D42" t="s">
@@ -3196,7 +3204,7 @@
       <c r="G42" t="s">
         <v>32</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="2">
         <v>21</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -3224,7 +3232,7 @@
         <v>28</v>
       </c>
       <c r="Q42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -3237,7 +3245,7 @@
       <c r="B43" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" t="s">
         <v>19</v>
       </c>
       <c r="D43" t="s">
@@ -3252,7 +3260,7 @@
       <c r="G43" t="s">
         <v>32</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="2">
         <v>24</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -3271,7 +3279,7 @@
         <v>610104</v>
       </c>
       <c r="N43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O43">
         <v>9.2200000000000006</v>
@@ -3293,7 +3301,7 @@
       <c r="B44" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" t="s">
         <v>19</v>
       </c>
       <c r="D44" t="s">
@@ -3308,7 +3316,7 @@
       <c r="G44" t="s">
         <v>23</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="2">
         <v>25</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -3336,7 +3344,7 @@
         <v>28</v>
       </c>
       <c r="Q44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R44" t="e">
         <v>#N/A</v>
@@ -3349,7 +3357,7 @@
       <c r="B45" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" t="s">
         <v>19</v>
       </c>
       <c r="D45" t="s">
@@ -3364,7 +3372,7 @@
       <c r="G45" t="s">
         <v>23</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="2">
         <v>25</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -3383,13 +3391,13 @@
         <v>614542</v>
       </c>
       <c r="N45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O45">
         <v>20.53</v>
       </c>
       <c r="P45" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q45" t="s">
         <v>28</v>
@@ -3405,7 +3413,7 @@
       <c r="B46" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" t="s">
         <v>19</v>
       </c>
       <c r="D46" t="s">
@@ -3420,7 +3428,7 @@
       <c r="G46" t="s">
         <v>43</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="2">
         <v>25</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -3448,7 +3456,7 @@
         <v>28</v>
       </c>
       <c r="Q46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -3461,7 +3469,7 @@
       <c r="B47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" t="s">
         <v>19</v>
       </c>
       <c r="D47" t="s">
@@ -3476,7 +3484,7 @@
       <c r="G47" t="s">
         <v>32</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="2">
         <v>25</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -3495,7 +3503,7 @@
         <v>610596</v>
       </c>
       <c r="N47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O47">
         <v>4.17</v>
@@ -3517,7 +3525,7 @@
       <c r="B48" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" t="s">
         <v>19</v>
       </c>
       <c r="D48" t="s">
@@ -3532,7 +3540,7 @@
       <c r="G48" t="s">
         <v>91</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="2">
         <v>27</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -3560,7 +3568,7 @@
         <v>28</v>
       </c>
       <c r="Q48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -3573,7 +3581,7 @@
       <c r="B49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" t="s">
         <v>19</v>
       </c>
       <c r="D49" t="s">
@@ -3588,7 +3596,7 @@
       <c r="G49" t="s">
         <v>32</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="2">
         <v>27</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -3607,7 +3615,7 @@
         <v>611797</v>
       </c>
       <c r="N49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O49">
         <v>9.85</v>
@@ -3629,7 +3637,7 @@
       <c r="B50" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" t="s">
         <v>19</v>
       </c>
       <c r="D50" t="s">
@@ -3644,7 +3652,7 @@
       <c r="G50" t="s">
         <v>91</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="2">
         <v>28</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -3672,7 +3680,7 @@
         <v>28</v>
       </c>
       <c r="Q50" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -3685,7 +3693,7 @@
       <c r="B51" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" t="s">
         <v>19</v>
       </c>
       <c r="D51" t="s">
@@ -3700,7 +3708,7 @@
       <c r="G51" t="s">
         <v>32</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="2">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -3728,7 +3736,7 @@
         <v>28</v>
       </c>
       <c r="Q51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -3741,7 +3749,7 @@
       <c r="B52" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" t="s">
         <v>19</v>
       </c>
       <c r="D52" t="s">
@@ -3756,7 +3764,7 @@
       <c r="G52" t="s">
         <v>91</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="2">
         <v>3</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -3784,7 +3792,7 @@
         <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R52">
         <v>1</v>
@@ -3797,7 +3805,7 @@
       <c r="B53" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" t="s">
         <v>19</v>
       </c>
       <c r="D53" t="s">
@@ -3812,7 +3820,7 @@
       <c r="G53" t="s">
         <v>32</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="2">
         <v>3</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -3831,7 +3839,7 @@
         <v>614995</v>
       </c>
       <c r="N53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O53">
         <v>1.91</v>
@@ -3853,7 +3861,7 @@
       <c r="B54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" t="s">
         <v>19</v>
       </c>
       <c r="D54" t="s">
@@ -3868,7 +3876,7 @@
       <c r="G54" t="s">
         <v>32</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="2">
         <v>4</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -3887,7 +3895,7 @@
         <v>615314</v>
       </c>
       <c r="N54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O54">
         <v>12.23</v>
@@ -3909,7 +3917,7 @@
       <c r="B55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" t="s">
         <v>19</v>
       </c>
       <c r="D55" t="s">
@@ -3924,7 +3932,7 @@
       <c r="G55" t="s">
         <v>32</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="2">
         <v>4</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -3943,7 +3951,7 @@
         <v>615322</v>
       </c>
       <c r="N55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O55">
         <v>16.34</v>
@@ -3965,7 +3973,7 @@
       <c r="B56" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" t="s">
         <v>19</v>
       </c>
       <c r="D56" t="s">
@@ -3980,7 +3988,7 @@
       <c r="G56" t="s">
         <v>32</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="2">
         <v>4</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -3999,16 +4007,16 @@
         <v>615654</v>
       </c>
       <c r="N56" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="O56">
         <v>11.93</v>
       </c>
       <c r="P56" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q56" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -4021,7 +4029,7 @@
       <c r="B57" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>19</v>
       </c>
       <c r="D57" t="s">
@@ -4036,7 +4044,7 @@
       <c r="G57" t="s">
         <v>126</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="2">
         <v>8</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -4055,7 +4063,7 @@
         <v>616899</v>
       </c>
       <c r="N57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O57">
         <v>6.36</v>
@@ -4066,8 +4074,8 @@
       <c r="Q57" t="s">
         <v>28</v>
       </c>
-      <c r="R57" t="e">
-        <v>#N/A</v>
+      <c r="R57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
@@ -4077,7 +4085,7 @@
       <c r="B58" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" t="s">
         <v>19</v>
       </c>
       <c r="D58" t="s">
@@ -4092,7 +4100,7 @@
       <c r="G58" t="s">
         <v>32</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="2">
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -4111,7 +4119,7 @@
         <v>616788</v>
       </c>
       <c r="N58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O58">
         <v>32.82</v>
@@ -4131,9 +4139,9 @@
         <v>70</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C59" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" t="s">
         <v>19</v>
       </c>
       <c r="D59" t="s">
@@ -4148,7 +4156,7 @@
       <c r="G59" t="s">
         <v>91</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="2">
         <v>9</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -4167,7 +4175,7 @@
         <v>617206</v>
       </c>
       <c r="N59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O59">
         <v>21.23</v>
@@ -4187,9 +4195,9 @@
         <v>29</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" t="s">
         <v>19</v>
       </c>
       <c r="D60" t="s">
@@ -4204,7 +4212,7 @@
       <c r="G60" t="s">
         <v>32</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="2">
         <v>9</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -4223,7 +4231,7 @@
         <v>617229</v>
       </c>
       <c r="N60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O60">
         <v>2.2200000000000002</v>
@@ -4243,9 +4251,9 @@
         <v>29</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C61" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" t="s">
         <v>19</v>
       </c>
       <c r="D61" t="s">
@@ -4260,7 +4268,7 @@
       <c r="G61" t="s">
         <v>43</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="2">
         <v>10</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -4279,7 +4287,7 @@
         <v>617914</v>
       </c>
       <c r="N61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O61">
         <v>8.4600000000000009</v>
@@ -4299,9 +4307,9 @@
         <v>17</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C62" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" t="s">
         <v>19</v>
       </c>
       <c r="D62" t="s">
@@ -4316,7 +4324,7 @@
       <c r="G62" t="s">
         <v>43</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="2">
         <v>11</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -4344,7 +4352,7 @@
         <v>28</v>
       </c>
       <c r="Q62" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -4355,9 +4363,9 @@
         <v>29</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" t="s">
         <v>19</v>
       </c>
       <c r="D63" t="s">
@@ -4372,7 +4380,7 @@
       <c r="G63" t="s">
         <v>32</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="2">
         <v>11</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -4391,7 +4399,7 @@
         <v>618930</v>
       </c>
       <c r="N63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O63">
         <v>17.97</v>
@@ -4411,16 +4419,16 @@
         <v>70</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
         <v>135</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" t="s">
-        <v>20</v>
-      </c>
-      <c r="E64" t="s">
-        <v>136</v>
       </c>
       <c r="F64" t="s">
         <v>90</v>
@@ -4428,7 +4436,7 @@
       <c r="G64" t="s">
         <v>91</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="2">
         <v>14</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -4447,7 +4455,7 @@
         <v>619855</v>
       </c>
       <c r="N64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O64">
         <v>4.68</v>
@@ -4458,8 +4466,8 @@
       <c r="Q64" t="s">
         <v>28</v>
       </c>
-      <c r="R64" t="e">
-        <v>#N/A</v>
+      <c r="R64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -4467,9 +4475,9 @@
         <v>29</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C65" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" t="s">
         <v>19</v>
       </c>
       <c r="D65" t="s">
@@ -4484,7 +4492,7 @@
       <c r="G65" t="s">
         <v>32</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="2">
         <v>14</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -4503,13 +4511,13 @@
         <v>619980</v>
       </c>
       <c r="N65" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="O65">
         <v>8.5399999999999991</v>
       </c>
       <c r="P65" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q65" t="s">
         <v>28</v>
@@ -4523,9 +4531,9 @@
         <v>17</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C66" t="s">
         <v>19</v>
       </c>
       <c r="D66" t="s">
@@ -4540,7 +4548,7 @@
       <c r="G66" t="s">
         <v>23</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="2">
         <v>15</v>
       </c>
       <c r="I66" s="1" t="s">
@@ -4579,16 +4587,16 @@
         <v>70</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" t="s">
         <v>146</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D67" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" t="s">
-        <v>147</v>
       </c>
       <c r="F67" t="s">
         <v>90</v>
@@ -4596,7 +4604,7 @@
       <c r="G67" t="s">
         <v>91</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="2">
         <v>15</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -4615,7 +4623,7 @@
         <v>620157</v>
       </c>
       <c r="N67" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O67">
         <v>6.46</v>
@@ -4635,9 +4643,9 @@
         <v>29</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C68" t="s">
         <v>19</v>
       </c>
       <c r="D68" t="s">
@@ -4652,7 +4660,7 @@
       <c r="G68" t="s">
         <v>32</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="2">
         <v>15</v>
       </c>
       <c r="I68" s="1" t="s">
@@ -4671,7 +4679,7 @@
         <v>620523</v>
       </c>
       <c r="N68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O68">
         <v>8.57</v>
@@ -4691,16 +4699,16 @@
         <v>70</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C69" t="s">
         <v>19</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F69" t="s">
         <v>90</v>
@@ -4708,7 +4716,7 @@
       <c r="G69" t="s">
         <v>91</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="2">
         <v>16</v>
       </c>
       <c r="I69" s="1" t="s">
@@ -4727,7 +4735,7 @@
         <v>620676</v>
       </c>
       <c r="N69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O69">
         <v>8.9600000000000009</v>
@@ -4747,9 +4755,9 @@
         <v>17</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C70" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" t="s">
         <v>19</v>
       </c>
       <c r="D70" t="s">
@@ -4764,7 +4772,7 @@
       <c r="G70" t="s">
         <v>43</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="2">
         <v>17</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -4779,14 +4787,14 @@
       <c r="L70" s="1">
         <v>46282</v>
       </c>
-      <c r="M70" t="s">
-        <v>154</v>
+      <c r="M70">
+        <v>620938</v>
       </c>
       <c r="N70" t="s">
-        <v>154</v>
-      </c>
-      <c r="O70" t="s">
-        <v>154</v>
+        <v>59</v>
+      </c>
+      <c r="O70">
+        <v>11.75</v>
       </c>
       <c r="P70" t="s">
         <v>28</v>
@@ -4803,16 +4811,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C71" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" t="s">
         <v>19</v>
       </c>
       <c r="D71" t="s">
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F71" t="s">
         <v>90</v>
@@ -4820,7 +4828,7 @@
       <c r="G71" t="s">
         <v>126</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="2">
         <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
@@ -4839,7 +4847,7 @@
         <v>621205</v>
       </c>
       <c r="N71" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O71">
         <v>5.95</v>
@@ -4859,9 +4867,9 @@
         <v>29</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C72" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" t="s">
         <v>19</v>
       </c>
       <c r="D72" t="s">
@@ -4876,7 +4884,7 @@
       <c r="G72" t="s">
         <v>32</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="2">
         <v>17</v>
       </c>
       <c r="I72" s="1" t="s">
@@ -4895,7 +4903,7 @@
         <v>621574</v>
       </c>
       <c r="N72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O72">
         <v>3.78</v>
@@ -4915,9 +4923,9 @@
         <v>29</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C73" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" t="s">
         <v>19</v>
       </c>
       <c r="D73" t="s">
@@ -4932,7 +4940,7 @@
       <c r="G73" t="s">
         <v>32</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="2">
         <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
@@ -4951,7 +4959,7 @@
         <v>621242</v>
       </c>
       <c r="N73" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O73">
         <v>5.46</v>
@@ -4971,9 +4979,9 @@
         <v>29</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C74" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" t="s">
         <v>19</v>
       </c>
       <c r="D74" t="s">
@@ -4988,7 +4996,7 @@
       <c r="G74" t="s">
         <v>32</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="2">
         <v>18</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -5007,7 +5015,7 @@
         <v>622716</v>
       </c>
       <c r="N74" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O74">
         <v>5.33</v>
@@ -5027,9 +5035,9 @@
         <v>70</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" t="s">
         <v>19</v>
       </c>
       <c r="D75" t="s">
@@ -5044,7 +5052,7 @@
       <c r="G75" t="s">
         <v>91</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="2">
         <v>22</v>
       </c>
       <c r="I75" s="1" t="s">
@@ -5063,13 +5071,13 @@
         <v>626221</v>
       </c>
       <c r="N75" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="O75">
         <v>9.11</v>
       </c>
       <c r="P75" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="Q75" t="s">
         <v>28</v>
@@ -5083,16 +5091,16 @@
         <v>70</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C76" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" t="s">
         <v>19</v>
       </c>
       <c r="D76" t="s">
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F76" t="s">
         <v>90</v>
@@ -5100,7 +5108,7 @@
       <c r="G76" t="s">
         <v>91</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="2">
         <v>22</v>
       </c>
       <c r="I76" s="1" t="s">
@@ -5119,7 +5127,7 @@
         <v>624470</v>
       </c>
       <c r="N76" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O76">
         <v>8.34</v>
@@ -5139,7 +5147,7 @@
         <v>29</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
         <v>19</v>
@@ -5156,7 +5164,7 @@
       <c r="G77" t="s">
         <v>32</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="2">
         <v>22</v>
       </c>
       <c r="I77" s="1" t="s">
@@ -5175,7 +5183,7 @@
         <v>624178</v>
       </c>
       <c r="N77" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O77">
         <v>12.79</v>
@@ -5195,7 +5203,7 @@
         <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C78" t="s">
         <v>19</v>
@@ -5212,7 +5220,7 @@
       <c r="G78" t="s">
         <v>32</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="2">
         <v>22</v>
       </c>
       <c r="I78" s="1" t="s">
@@ -5231,7 +5239,7 @@
         <v>624196</v>
       </c>
       <c r="N78" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O78">
         <v>3.73</v>
@@ -5251,7 +5259,7 @@
         <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C79" t="s">
         <v>19</v>
@@ -5260,7 +5268,7 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F79" t="s">
         <v>90</v>
@@ -5268,7 +5276,7 @@
       <c r="G79" t="s">
         <v>91</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="2">
         <v>23</v>
       </c>
       <c r="I79" s="1" t="s">
@@ -5287,7 +5295,7 @@
         <v>624882</v>
       </c>
       <c r="N79" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O79">
         <v>22.65</v>
@@ -5298,8 +5306,8 @@
       <c r="Q79" t="s">
         <v>28</v>
       </c>
-      <c r="R79" t="e">
-        <v>#N/A</v>
+      <c r="R79">
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -5307,7 +5315,7 @@
         <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C80" t="s">
         <v>19</v>
@@ -5324,7 +5332,7 @@
       <c r="G80" t="s">
         <v>23</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="2">
         <v>24</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -5343,7 +5351,7 @@
         <v>625164</v>
       </c>
       <c r="N80" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O80">
         <v>29.19</v>
@@ -5354,8 +5362,8 @@
       <c r="Q80" t="s">
         <v>28</v>
       </c>
-      <c r="R80" t="e">
-        <v>#N/A</v>
+      <c r="R80">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -5363,7 +5371,7 @@
         <v>29</v>
       </c>
       <c r="B81" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C81" t="s">
         <v>19</v>
@@ -5380,7 +5388,7 @@
       <c r="G81" t="s">
         <v>32</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="2">
         <v>24</v>
       </c>
       <c r="I81" s="1" t="s">
@@ -5399,7 +5407,7 @@
         <v>625177</v>
       </c>
       <c r="N81" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O81">
         <v>3.5</v>
@@ -5419,7 +5427,7 @@
         <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
         <v>19</v>
@@ -5428,15 +5436,15 @@
         <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F82" t="s">
         <v>90</v>
       </c>
       <c r="G82" t="s">
-        <v>168</v>
-      </c>
-      <c r="H82">
+        <v>167</v>
+      </c>
+      <c r="H82" s="2">
         <v>25</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -5455,7 +5463,7 @@
         <v>626032</v>
       </c>
       <c r="N82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O82">
         <v>4.5199999999999996</v>
@@ -5466,8 +5474,8 @@
       <c r="Q82" t="s">
         <v>28</v>
       </c>
-      <c r="R82" t="e">
-        <v>#N/A</v>
+      <c r="R82">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -5475,7 +5483,7 @@
         <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C83" t="s">
         <v>19</v>
@@ -5492,7 +5500,7 @@
       <c r="G83" t="s">
         <v>43</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="2">
         <v>25</v>
       </c>
       <c r="I83" s="1" t="s">
@@ -5511,13 +5519,13 @@
         <v>626059</v>
       </c>
       <c r="N83" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="O83">
         <v>14.46</v>
       </c>
       <c r="P83" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q83" t="s">
         <v>28</v>
@@ -5531,7 +5539,7 @@
         <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C84" t="s">
         <v>19</v>
@@ -5548,7 +5556,7 @@
       <c r="G84" t="s">
         <v>32</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="2">
         <v>28</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -5567,7 +5575,7 @@
         <v>626925</v>
       </c>
       <c r="N84" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O84">
         <v>17.84</v>
@@ -5578,8 +5586,8 @@
       <c r="Q84" t="s">
         <v>28</v>
       </c>
-      <c r="R84" t="e">
-        <v>#N/A</v>
+      <c r="R84">
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
@@ -5587,7 +5595,7 @@
         <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C85" t="s">
         <v>19</v>
@@ -5604,7 +5612,7 @@
       <c r="G85" t="s">
         <v>43</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="2">
         <v>28</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -5623,7 +5631,7 @@
         <v>626887</v>
       </c>
       <c r="N85" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O85">
         <v>16.39</v>
@@ -5634,8 +5642,8 @@
       <c r="Q85" t="s">
         <v>28</v>
       </c>
-      <c r="R85" t="e">
-        <v>#N/A</v>
+      <c r="R85">
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
@@ -5643,16 +5651,16 @@
         <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C86" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F86" t="s">
         <v>90</v>
@@ -5660,7 +5668,7 @@
       <c r="G86" t="s">
         <v>104</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="2">
         <v>29</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -5679,13 +5687,13 @@
         <v>627609</v>
       </c>
       <c r="N86" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O86">
         <v>11.61</v>
       </c>
       <c r="P86" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q86" t="s">
         <v>28</v>
@@ -5699,7 +5707,7 @@
         <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C87" t="s">
         <v>19</v>
@@ -5708,7 +5716,7 @@
         <v>20</v>
       </c>
       <c r="E87" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F87" t="s">
         <v>90</v>
@@ -5716,7 +5724,7 @@
       <c r="G87" t="s">
         <v>104</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="2">
         <v>29</v>
       </c>
       <c r="I87" s="1" t="s">
@@ -5735,19 +5743,19 @@
         <v>627665</v>
       </c>
       <c r="N87" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O87">
         <v>7.5</v>
       </c>
       <c r="P87" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q87" t="s">
         <v>28</v>
       </c>
-      <c r="R87" t="e">
-        <v>#N/A</v>
+      <c r="R87">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
@@ -5755,7 +5763,7 @@
         <v>70</v>
       </c>
       <c r="B88" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
         <v>19</v>
@@ -5764,7 +5772,7 @@
         <v>20</v>
       </c>
       <c r="E88" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F88" t="s">
         <v>90</v>
@@ -5772,7 +5780,7 @@
       <c r="G88" t="s">
         <v>104</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="2">
         <v>29</v>
       </c>
       <c r="I88" s="1" t="s">
@@ -5791,19 +5799,19 @@
         <v>627639</v>
       </c>
       <c r="N88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O88">
         <v>4.3</v>
       </c>
       <c r="P88" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q88" t="s">
         <v>28</v>
       </c>
-      <c r="R88" t="e">
-        <v>#N/A</v>
+      <c r="R88">
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
@@ -5811,7 +5819,7 @@
         <v>29</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C89" t="s">
         <v>19</v>
@@ -5828,7 +5836,7 @@
       <c r="G89" t="s">
         <v>32</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="2">
         <v>29</v>
       </c>
       <c r="I89" s="1" t="s">
@@ -5847,19 +5855,19 @@
         <v>627503</v>
       </c>
       <c r="N89" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O89">
         <v>16.3</v>
       </c>
       <c r="P89" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q89" t="s">
         <v>28</v>
       </c>
-      <c r="R89" t="e">
-        <v>#N/A</v>
+      <c r="R89">
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
@@ -5867,7 +5875,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C90" t="s">
         <v>19</v>
@@ -5884,7 +5892,7 @@
       <c r="G90" t="s">
         <v>32</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="2">
         <v>29</v>
       </c>
       <c r="I90" s="1" t="s">
@@ -5903,19 +5911,19 @@
         <v>627332</v>
       </c>
       <c r="N90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O90">
         <v>2.42</v>
       </c>
       <c r="P90" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q90" t="s">
         <v>28</v>
       </c>
-      <c r="R90" t="e">
-        <v>#N/A</v>
+      <c r="R90">
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
@@ -5923,7 +5931,7 @@
         <v>29</v>
       </c>
       <c r="B91" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C91" t="s">
         <v>19</v>
@@ -5940,7 +5948,7 @@
       <c r="G91" t="s">
         <v>32</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="2">
         <v>29</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -5959,19 +5967,243 @@
         <v>627521</v>
       </c>
       <c r="N91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O91">
         <v>9.1300000000000008</v>
       </c>
       <c r="P91" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>28</v>
+      </c>
+      <c r="R91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92" t="s">
+        <v>178</v>
+      </c>
+      <c r="C92" t="s">
+        <v>19</v>
+      </c>
+      <c r="D92" t="s">
+        <v>20</v>
+      </c>
+      <c r="E92" t="s">
+        <v>146</v>
+      </c>
+      <c r="F92" t="s">
+        <v>90</v>
+      </c>
+      <c r="G92" t="s">
+        <v>104</v>
+      </c>
+      <c r="H92" s="2">
+        <v>30</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L92" s="1">
+        <v>46295</v>
+      </c>
+      <c r="M92">
+        <v>628148</v>
+      </c>
+      <c r="N92" t="s">
+        <v>131</v>
+      </c>
+      <c r="O92">
+        <v>3.88</v>
+      </c>
+      <c r="P92" t="s">
         <v>27</v>
       </c>
-      <c r="Q91" t="s">
-        <v>28</v>
-      </c>
-      <c r="R91" t="e">
+      <c r="Q92" t="s">
+        <v>28</v>
+      </c>
+      <c r="R92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93" t="s">
+        <v>179</v>
+      </c>
+      <c r="C93" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" t="s">
+        <v>20</v>
+      </c>
+      <c r="E93" t="s">
+        <v>146</v>
+      </c>
+      <c r="F93" t="s">
+        <v>90</v>
+      </c>
+      <c r="G93" t="s">
+        <v>91</v>
+      </c>
+      <c r="H93" s="2">
+        <v>30</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" s="1">
+        <v>46295</v>
+      </c>
+      <c r="M93">
+        <v>627870</v>
+      </c>
+      <c r="N93" t="s">
+        <v>131</v>
+      </c>
+      <c r="O93">
+        <v>1.42</v>
+      </c>
+      <c r="P93" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>28</v>
+      </c>
+      <c r="R93" t="e">
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" t="s">
+        <v>146</v>
+      </c>
+      <c r="F94" t="s">
+        <v>90</v>
+      </c>
+      <c r="G94" t="s">
+        <v>91</v>
+      </c>
+      <c r="H94" s="2">
+        <v>30</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L94" s="1">
+        <v>46295</v>
+      </c>
+      <c r="M94">
+        <v>628106</v>
+      </c>
+      <c r="N94" t="s">
+        <v>131</v>
+      </c>
+      <c r="O94">
+        <v>5.22</v>
+      </c>
+      <c r="P94" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>28</v>
+      </c>
+      <c r="R94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" t="s">
+        <v>20</v>
+      </c>
+      <c r="E95" t="s">
+        <v>146</v>
+      </c>
+      <c r="F95" t="s">
+        <v>90</v>
+      </c>
+      <c r="G95" t="s">
+        <v>104</v>
+      </c>
+      <c r="H95" s="2">
+        <v>30</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="1">
+        <v>46295</v>
+      </c>
+      <c r="M95">
+        <v>628137</v>
+      </c>
+      <c r="N95" t="s">
+        <v>131</v>
+      </c>
+      <c r="O95">
+        <v>7.93</v>
+      </c>
+      <c r="P95" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>28</v>
+      </c>
+      <c r="R95">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7027,31 +7259,31 @@
         <v>29</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>168.39300000000003</v>
       </c>
       <c r="E28">
-        <v>8.0012899999999991</v>
+        <v>73.276610000000005</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G28">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H28">
         <v>6</v>
       </c>
       <c r="I28">
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0.62666666666666671</v>
       </c>
       <c r="K28">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="L28">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -7068,28 +7300,28 @@
         <v>81</v>
       </c>
       <c r="E29">
-        <v>9.5742900000000013</v>
+        <v>88.13288</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G29">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -7106,28 +7338,28 @@
         <v>81</v>
       </c>
       <c r="E30">
-        <v>10.65812</v>
+        <v>71.785119999999992</v>
       </c>
       <c r="F30">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G30">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="J30">
-        <v>0.93333333333333335</v>
+        <v>0.92</v>
       </c>
       <c r="K30">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="L30">
-        <v>14</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -7253,6 +7485,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -7513,27 +7765,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7550,23 +7801,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF5EACAC-0F11-4994-844A-0B1D2ECE3F09}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23BEB972-BF6A-43A7-8FE8-7C5BBF619B0C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="185">
   <si>
     <t>Usuário</t>
   </si>
@@ -588,6 +588,15 @@
   </si>
   <si>
     <t>TERESINHA MACIEL DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>AGUARDANDO FATURA</t>
+  </si>
+  <si>
+    <t>JOAO PAULO DE SOUZA CLEMENTINO LTDA</t>
+  </si>
+  <si>
+    <t>OCT</t>
   </si>
 </sst>
 </file>
@@ -913,11 +922,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:R96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -982,7 +992,7 @@
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
@@ -1038,7 +1048,7 @@
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3" t="s">
@@ -1094,7 +1104,7 @@
       <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>58</v>
       </c>
       <c r="C4" t="s">
@@ -1147,7 +1157,7 @@
       <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5" t="s">
@@ -1203,7 +1213,7 @@
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>36</v>
       </c>
       <c r="C6" t="s">
@@ -1256,7 +1266,7 @@
       <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7" t="s">
@@ -1309,7 +1319,7 @@
       <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>48</v>
       </c>
       <c r="C8" t="s">
@@ -1362,7 +1372,7 @@
       <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
@@ -1415,7 +1425,7 @@
       <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>64</v>
       </c>
       <c r="C10" t="s">
@@ -1468,7 +1478,7 @@
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>45</v>
       </c>
       <c r="C11" t="s">
@@ -1521,7 +1531,7 @@
       <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="s">
@@ -1574,7 +1584,7 @@
       <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>61</v>
       </c>
       <c r="C13" t="s">
@@ -1630,7 +1640,7 @@
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
@@ -1683,7 +1693,7 @@
       <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>65</v>
       </c>
       <c r="C15" t="s">
@@ -1736,7 +1746,7 @@
       <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>30</v>
       </c>
       <c r="C16" t="s">
@@ -1789,7 +1799,7 @@
       <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>50</v>
       </c>
       <c r="C17" t="s">
@@ -1845,7 +1855,7 @@
       <c r="A18" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>52</v>
       </c>
       <c r="C18" t="s">
@@ -1898,7 +1908,7 @@
       <c r="A19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>42</v>
       </c>
       <c r="C19" t="s">
@@ -1954,7 +1964,7 @@
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>41</v>
       </c>
       <c r="C20" t="s">
@@ -2010,7 +2020,7 @@
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>62</v>
       </c>
       <c r="C21" t="s">
@@ -2066,7 +2076,7 @@
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" t="s">
@@ -2122,7 +2132,7 @@
       <c r="A23" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>37</v>
       </c>
       <c r="C23" t="s">
@@ -2178,7 +2188,7 @@
       <c r="A24" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>60</v>
       </c>
       <c r="C24" t="s">
@@ -2234,7 +2244,7 @@
       <c r="A25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>46</v>
       </c>
       <c r="C25" t="s">
@@ -2290,7 +2300,7 @@
       <c r="A26" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>18</v>
       </c>
       <c r="C26" t="s">
@@ -2323,17 +2333,17 @@
       <c r="L26" s="1">
         <v>46245</v>
       </c>
-      <c r="M26">
-        <v>604128</v>
+      <c r="M26" t="s">
+        <v>153</v>
       </c>
       <c r="N26" t="s">
-        <v>131</v>
-      </c>
-      <c r="O26">
-        <v>8.3699999999999992</v>
+        <v>153</v>
+      </c>
+      <c r="O26" t="s">
+        <v>153</v>
       </c>
       <c r="P26" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q26" t="s">
         <v>28</v>
@@ -2346,7 +2356,7 @@
       <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>47</v>
       </c>
       <c r="C27" t="s">
@@ -2402,7 +2412,7 @@
       <c r="A28" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>88</v>
       </c>
       <c r="C28" t="s">
@@ -2458,7 +2468,7 @@
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>92</v>
       </c>
       <c r="C29" t="s">
@@ -2514,7 +2524,7 @@
       <c r="A30" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>93</v>
       </c>
       <c r="C30" t="s">
@@ -2570,7 +2580,7 @@
       <c r="A31" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>94</v>
       </c>
       <c r="C31" t="s">
@@ -2626,7 +2636,7 @@
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>95</v>
       </c>
       <c r="C32" t="s">
@@ -2682,7 +2692,7 @@
       <c r="A33" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>98</v>
       </c>
       <c r="C33" t="s">
@@ -2738,7 +2748,7 @@
       <c r="A34" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>97</v>
       </c>
       <c r="C34" t="s">
@@ -2794,7 +2804,7 @@
       <c r="A35" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>99</v>
       </c>
       <c r="C35" t="s">
@@ -2850,7 +2860,7 @@
       <c r="A36" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>100</v>
       </c>
       <c r="C36" t="s">
@@ -2906,7 +2916,7 @@
       <c r="A37" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>101</v>
       </c>
       <c r="C37" t="s">
@@ -2962,7 +2972,7 @@
       <c r="A38" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>102</v>
       </c>
       <c r="C38" t="s">
@@ -3018,7 +3028,7 @@
       <c r="A39" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>103</v>
       </c>
       <c r="C39" t="s">
@@ -3074,7 +3084,7 @@
       <c r="A40" t="s">
         <v>70</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>105</v>
       </c>
       <c r="C40" t="s">
@@ -3130,7 +3140,7 @@
       <c r="A41" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>106</v>
       </c>
       <c r="C41" t="s">
@@ -3186,7 +3196,7 @@
       <c r="A42" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>107</v>
       </c>
       <c r="C42" t="s">
@@ -3242,7 +3252,7 @@
       <c r="A43" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>108</v>
       </c>
       <c r="C43" t="s">
@@ -3298,7 +3308,7 @@
       <c r="A44" t="s">
         <v>17</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>109</v>
       </c>
       <c r="C44" t="s">
@@ -3354,7 +3364,7 @@
       <c r="A45" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>110</v>
       </c>
       <c r="C45" t="s">
@@ -3410,7 +3420,7 @@
       <c r="A46" t="s">
         <v>29</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>111</v>
       </c>
       <c r="C46" t="s">
@@ -3466,7 +3476,7 @@
       <c r="A47" t="s">
         <v>29</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>112</v>
       </c>
       <c r="C47" t="s">
@@ -3522,7 +3532,7 @@
       <c r="A48" t="s">
         <v>70</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>113</v>
       </c>
       <c r="C48" t="s">
@@ -3578,7 +3588,7 @@
       <c r="A49" t="s">
         <v>29</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>114</v>
       </c>
       <c r="C49" t="s">
@@ -3634,7 +3644,7 @@
       <c r="A50" t="s">
         <v>70</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>116</v>
       </c>
       <c r="C50" t="s">
@@ -3690,7 +3700,7 @@
       <c r="A51" t="s">
         <v>29</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>117</v>
       </c>
       <c r="C51" t="s">
@@ -3746,7 +3756,7 @@
       <c r="A52" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>119</v>
       </c>
       <c r="C52" t="s">
@@ -3802,7 +3812,7 @@
       <c r="A53" t="s">
         <v>29</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
         <v>120</v>
       </c>
       <c r="C53" t="s">
@@ -3858,7 +3868,7 @@
       <c r="A54" t="s">
         <v>29</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
         <v>121</v>
       </c>
       <c r="C54" t="s">
@@ -3914,7 +3924,7 @@
       <c r="A55" t="s">
         <v>29</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>122</v>
       </c>
       <c r="C55" t="s">
@@ -3970,7 +3980,7 @@
       <c r="A56" t="s">
         <v>29</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>124</v>
       </c>
       <c r="C56" t="s">
@@ -4026,7 +4036,7 @@
       <c r="A57" t="s">
         <v>70</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>125</v>
       </c>
       <c r="C57" t="s">
@@ -4082,7 +4092,7 @@
       <c r="A58" t="s">
         <v>29</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" t="s">
         <v>127</v>
       </c>
       <c r="C58" t="s">
@@ -4138,7 +4148,7 @@
       <c r="A59" t="s">
         <v>70</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
         <v>128</v>
       </c>
       <c r="C59" t="s">
@@ -4194,7 +4204,7 @@
       <c r="A60" t="s">
         <v>29</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" t="s">
         <v>129</v>
       </c>
       <c r="C60" t="s">
@@ -4250,7 +4260,7 @@
       <c r="A61" t="s">
         <v>29</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
         <v>130</v>
       </c>
       <c r="C61" t="s">
@@ -4306,7 +4316,7 @@
       <c r="A62" t="s">
         <v>17</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>132</v>
       </c>
       <c r="C62" t="s">
@@ -4362,7 +4372,7 @@
       <c r="A63" t="s">
         <v>29</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" t="s">
         <v>133</v>
       </c>
       <c r="C63" t="s">
@@ -4399,13 +4409,13 @@
         <v>618930</v>
       </c>
       <c r="N63" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O63">
-        <v>17.97</v>
+        <v>14.6</v>
       </c>
       <c r="P63" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q63" t="s">
         <v>28</v>
@@ -4418,7 +4428,7 @@
       <c r="A64" t="s">
         <v>70</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" t="s">
         <v>134</v>
       </c>
       <c r="C64" t="s">
@@ -4474,7 +4484,7 @@
       <c r="A65" t="s">
         <v>29</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
         <v>136</v>
       </c>
       <c r="C65" t="s">
@@ -4530,7 +4540,7 @@
       <c r="A66" t="s">
         <v>17</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
         <v>144</v>
       </c>
       <c r="C66" t="s">
@@ -4586,7 +4596,7 @@
       <c r="A67" t="s">
         <v>70</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
         <v>145</v>
       </c>
       <c r="C67" t="s">
@@ -4642,7 +4652,7 @@
       <c r="A68" t="s">
         <v>29</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
         <v>151</v>
       </c>
       <c r="C68" t="s">
@@ -4698,7 +4708,7 @@
       <c r="A69" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" t="s">
         <v>152</v>
       </c>
       <c r="C69" t="s">
@@ -4754,7 +4764,7 @@
       <c r="A70" t="s">
         <v>17</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" t="s">
         <v>154</v>
       </c>
       <c r="C70" t="s">
@@ -4810,7 +4820,7 @@
       <c r="A71" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" t="s">
         <v>155</v>
       </c>
       <c r="C71" t="s">
@@ -4866,7 +4876,7 @@
       <c r="A72" t="s">
         <v>29</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" t="s">
         <v>156</v>
       </c>
       <c r="C72" t="s">
@@ -4922,7 +4932,7 @@
       <c r="A73" t="s">
         <v>29</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" t="s">
         <v>157</v>
       </c>
       <c r="C73" t="s">
@@ -4978,7 +4988,7 @@
       <c r="A74" t="s">
         <v>29</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" t="s">
         <v>158</v>
       </c>
       <c r="C74" t="s">
@@ -5034,7 +5044,7 @@
       <c r="A75" t="s">
         <v>70</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" t="s">
         <v>161</v>
       </c>
       <c r="C75" t="s">
@@ -5090,7 +5100,7 @@
       <c r="A76" t="s">
         <v>70</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" t="s">
         <v>162</v>
       </c>
       <c r="C76" t="s">
@@ -5357,7 +5367,7 @@
         <v>29.19</v>
       </c>
       <c r="P80" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="Q80" t="s">
         <v>28</v>
@@ -6090,8 +6100,8 @@
       <c r="Q93" t="s">
         <v>28</v>
       </c>
-      <c r="R93" t="e">
-        <v>#N/A</v>
+      <c r="R93">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
@@ -6204,6 +6214,62 @@
       </c>
       <c r="R95">
         <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" t="s">
+        <v>20</v>
+      </c>
+      <c r="E96" t="s">
+        <v>146</v>
+      </c>
+      <c r="F96" t="s">
+        <v>90</v>
+      </c>
+      <c r="G96" t="s">
+        <v>91</v>
+      </c>
+      <c r="H96" s="2">
+        <v>7</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" s="1">
+        <v>46302</v>
+      </c>
+      <c r="M96">
+        <v>631043</v>
+      </c>
+      <c r="N96" t="s">
+        <v>131</v>
+      </c>
+      <c r="O96">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="P96" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>28</v>
+      </c>
+      <c r="R96" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -7485,6 +7551,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
@@ -7493,15 +7568,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7766,20 +7832,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
     <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23BEB972-BF6A-43A7-8FE8-7C5BBF619B0C}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0819BC1B-6996-4344-8F9D-7C78E9950D1E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="192">
   <si>
     <t>Usuário</t>
   </si>
@@ -597,6 +597,27 @@
   </si>
   <si>
     <t>OCT</t>
+  </si>
+  <si>
+    <t>NEGOCIAÇÃO QUENTE</t>
+  </si>
+  <si>
+    <t>SEM RETORNO CLIENTE-TENTATIVAS EXCED SLA</t>
+  </si>
+  <si>
+    <t>FRANCISCO VALDEMIR OLIVEIRA</t>
+  </si>
+  <si>
+    <t>ALEXSANDRO MENDES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>BLUE STAR CENTRO EMPREENDIMENTOS IMOB</t>
+  </si>
+  <si>
+    <t>ROGERIO SILVA COSTA</t>
+  </si>
+  <si>
+    <t>Pindoretama</t>
   </si>
 </sst>
 </file>
@@ -922,12 +943,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -1888,17 +1909,17 @@
       <c r="L18" s="1">
         <v>46231</v>
       </c>
-      <c r="M18">
-        <v>598353</v>
+      <c r="M18" t="s">
+        <v>153</v>
       </c>
       <c r="N18" t="s">
-        <v>131</v>
-      </c>
-      <c r="O18">
-        <v>6.9</v>
+        <v>153</v>
+      </c>
+      <c r="O18" t="s">
+        <v>153</v>
       </c>
       <c r="P18" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -2231,7 +2252,7 @@
         <v>6.12</v>
       </c>
       <c r="P24" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q24" t="s">
         <v>28</v>
@@ -3286,7 +3307,7 @@
         <v>46258</v>
       </c>
       <c r="M43">
-        <v>610104</v>
+        <v>634413</v>
       </c>
       <c r="N43" t="s">
         <v>131</v>
@@ -3397,17 +3418,17 @@
       <c r="L45" s="1">
         <v>46259</v>
       </c>
-      <c r="M45">
-        <v>614542</v>
+      <c r="M45" t="s">
+        <v>153</v>
       </c>
       <c r="N45" t="s">
-        <v>131</v>
-      </c>
-      <c r="O45">
-        <v>20.53</v>
+        <v>153</v>
+      </c>
+      <c r="O45" t="s">
+        <v>153</v>
       </c>
       <c r="P45" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q45" t="s">
         <v>28</v>
@@ -3519,7 +3540,7 @@
         <v>4.17</v>
       </c>
       <c r="P47" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q47" t="s">
         <v>28</v>
@@ -4689,16 +4710,16 @@
         <v>620523</v>
       </c>
       <c r="N68" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O68">
         <v>8.57</v>
       </c>
       <c r="P68" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q68" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="R68">
         <v>1</v>
@@ -4919,7 +4940,7 @@
         <v>3.78</v>
       </c>
       <c r="P72" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="Q72" t="s">
         <v>28</v>
@@ -5479,7 +5500,7 @@
         <v>4.5199999999999996</v>
       </c>
       <c r="P82" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q82" t="s">
         <v>28</v>
@@ -5862,7 +5883,7 @@
         <v>46294</v>
       </c>
       <c r="M89">
-        <v>627503</v>
+        <v>634381</v>
       </c>
       <c r="N89" t="s">
         <v>131</v>
@@ -6033,16 +6054,16 @@
         <v>628148</v>
       </c>
       <c r="N92" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O92">
         <v>3.88</v>
       </c>
       <c r="P92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q92" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="R92">
         <v>1</v>
@@ -6095,7 +6116,7 @@
         <v>1.42</v>
       </c>
       <c r="P93" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q93" t="s">
         <v>28</v>
@@ -6145,16 +6166,16 @@
         <v>628106</v>
       </c>
       <c r="N94" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O94">
         <v>5.22</v>
       </c>
       <c r="P94" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q94" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="R94">
         <v>1</v>
@@ -6201,16 +6222,16 @@
         <v>628137</v>
       </c>
       <c r="N95" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O95">
         <v>7.93</v>
       </c>
       <c r="P95" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q95" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="R95">
         <v>1</v>
@@ -6260,15 +6281,239 @@
         <v>131</v>
       </c>
       <c r="O96">
-        <v>8.3800000000000008</v>
+        <v>14.23</v>
       </c>
       <c r="P96" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>28</v>
+      </c>
+      <c r="R96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" t="s">
+        <v>187</v>
+      </c>
+      <c r="C97" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" t="s">
+        <v>146</v>
+      </c>
+      <c r="F97" t="s">
+        <v>90</v>
+      </c>
+      <c r="G97" t="s">
+        <v>91</v>
+      </c>
+      <c r="H97" s="2">
+        <v>9</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="1">
+        <v>46304</v>
+      </c>
+      <c r="M97">
+        <v>631720</v>
+      </c>
+      <c r="N97" t="s">
+        <v>131</v>
+      </c>
+      <c r="O97">
+        <v>2.34</v>
+      </c>
+      <c r="P97" t="s">
         <v>27</v>
       </c>
-      <c r="Q96" t="s">
-        <v>28</v>
-      </c>
-      <c r="R96" t="e">
+      <c r="Q97" t="s">
+        <v>28</v>
+      </c>
+      <c r="R97" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" t="s">
+        <v>188</v>
+      </c>
+      <c r="C98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" t="s">
+        <v>20</v>
+      </c>
+      <c r="E98" t="s">
+        <v>21</v>
+      </c>
+      <c r="F98" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="2">
+        <v>13</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L98" s="1">
+        <v>46308</v>
+      </c>
+      <c r="M98">
+        <v>632724</v>
+      </c>
+      <c r="N98" t="s">
+        <v>131</v>
+      </c>
+      <c r="O98">
+        <v>8.07</v>
+      </c>
+      <c r="P98" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>28</v>
+      </c>
+      <c r="R98" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>70</v>
+      </c>
+      <c r="B99" t="s">
+        <v>189</v>
+      </c>
+      <c r="C99" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" t="s">
+        <v>146</v>
+      </c>
+      <c r="F99" t="s">
+        <v>90</v>
+      </c>
+      <c r="G99" t="s">
+        <v>104</v>
+      </c>
+      <c r="H99" s="2">
+        <v>14</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="1">
+        <v>46309</v>
+      </c>
+      <c r="M99">
+        <v>634211</v>
+      </c>
+      <c r="N99" t="s">
+        <v>131</v>
+      </c>
+      <c r="O99">
+        <v>3.01</v>
+      </c>
+      <c r="P99" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>28</v>
+      </c>
+      <c r="R99" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>70</v>
+      </c>
+      <c r="B100" t="s">
+        <v>190</v>
+      </c>
+      <c r="C100" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" t="s">
+        <v>20</v>
+      </c>
+      <c r="E100" t="s">
+        <v>146</v>
+      </c>
+      <c r="F100" t="s">
+        <v>90</v>
+      </c>
+      <c r="G100" t="s">
+        <v>191</v>
+      </c>
+      <c r="H100" s="2">
+        <v>14</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L100" s="1">
+        <v>46309</v>
+      </c>
+      <c r="M100">
+        <v>634159</v>
+      </c>
+      <c r="N100" t="s">
+        <v>131</v>
+      </c>
+      <c r="O100">
+        <v>3.6</v>
+      </c>
+      <c r="P100" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>28</v>
+      </c>
+      <c r="R100" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -7437,7 +7682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03D8E35-98BA-491C-80D3-FD8BDE5E2A5E}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -7544,6 +7789,28 @@
         <v>15</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7551,15 +7818,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
@@ -7570,7 +7828,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -7831,15 +8089,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7850,7 +8109,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7867,4 +8126,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0819BC1B-6996-4344-8F9D-7C78E9950D1E}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32DD6DD8-3881-469F-81B9-599B71783E29}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="235">
   <si>
     <t>Usuário</t>
   </si>
@@ -590,9 +590,6 @@
     <t>TERESINHA MACIEL DE OLIVEIRA</t>
   </si>
   <si>
-    <t>AGUARDANDO FATURA</t>
-  </si>
-  <si>
     <t>JOAO PAULO DE SOUZA CLEMENTINO LTDA</t>
   </si>
   <si>
@@ -618,6 +615,138 @@
   </si>
   <si>
     <t>Pindoretama</t>
+  </si>
+  <si>
+    <t>FECHOU COM A CONCORRÊNCIA</t>
+  </si>
+  <si>
+    <t>Daniela Campos</t>
+  </si>
+  <si>
+    <t>REALIZE INN ADMINISTRACAO E PARTICIPACAO HOTELEIRA LTDA</t>
+  </si>
+  <si>
+    <t>PROSPECÇÃO SDR</t>
+  </si>
+  <si>
+    <t>Dayane Cruz</t>
+  </si>
+  <si>
+    <t>Uberlândia</t>
+  </si>
+  <si>
+    <t>612268 - CAFETERIA TEATRO CENTRAL LTDA</t>
+  </si>
+  <si>
+    <t>Dayane Rezende</t>
+  </si>
+  <si>
+    <t>Juiz de Fora</t>
+  </si>
+  <si>
+    <t>612223 - MERCEARIA FORTALEZA</t>
+  </si>
+  <si>
+    <t>Caio Mauro Miguel Silva</t>
+  </si>
+  <si>
+    <t>612623 - CASA NOVA COMERCIO DE ALUMINIO LTDA</t>
+  </si>
+  <si>
+    <t>LANCHONETE TATA BATATA LTDA</t>
+  </si>
+  <si>
+    <t>Henrique Matheus</t>
+  </si>
+  <si>
+    <t>TREM PAULISTA LTDA</t>
+  </si>
+  <si>
+    <t>Shirley Brito</t>
+  </si>
+  <si>
+    <t>AGUARDANDO ASSINATURA</t>
+  </si>
+  <si>
+    <t>FDG SORVETES</t>
+  </si>
+  <si>
+    <t>FABRICIO SORVETERIA LTDA</t>
+  </si>
+  <si>
+    <t>GODINHO SORVETES LTDA</t>
+  </si>
+  <si>
+    <t>611065 - EMPORIO MINAS</t>
+  </si>
+  <si>
+    <t>THYRSO PAULO DE AGOSTINI</t>
+  </si>
+  <si>
+    <t>612265 - MARY MILK LANCHES</t>
+  </si>
+  <si>
+    <t>PORTA RAPIDA LTDA</t>
+  </si>
+  <si>
+    <t>MACA VERDE SORVETES LTDA</t>
+  </si>
+  <si>
+    <t>MENDONCA JML COMERCIO DE PESCADOS LTDA</t>
+  </si>
+  <si>
+    <t>Maysa Albuquerque</t>
+  </si>
+  <si>
+    <t>RIGA - SERVICOS DE BAR E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>Priscila Morais</t>
+  </si>
+  <si>
+    <t>ROSSANA FIGUEIREDO COSTA</t>
+  </si>
+  <si>
+    <t>RICARDO DE ALMEIDA MAGALHAES</t>
+  </si>
+  <si>
+    <t>Maria Rita Souza Borges</t>
+  </si>
+  <si>
+    <t>MARIA EDUARDA DE OLIVEIRA SPACEK</t>
+  </si>
+  <si>
+    <t>Alisson Teixeira</t>
+  </si>
+  <si>
+    <t>SIMONE ALVES DA SILVA</t>
+  </si>
+  <si>
+    <t>Taise Alcantara</t>
+  </si>
+  <si>
+    <t>GABRIEL BARBOSA</t>
+  </si>
+  <si>
+    <t>LOURDES ISABEL DA SILVA</t>
+  </si>
+  <si>
+    <t>MARIA AUDILENE SILVA SOUSA</t>
+  </si>
+  <si>
+    <t>(vazio)</t>
+  </si>
+  <si>
+    <t>CONDOMINIO DO EDIFICIO VERSATTO</t>
+  </si>
+  <si>
+    <t>Canal</t>
+  </si>
+  <si>
+    <t>Externo</t>
+  </si>
+  <si>
+    <t>Interno</t>
   </si>
 </sst>
 </file>
@@ -659,10 +788,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -943,13 +1071,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -975,7 +1101,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1031,7 +1157,7 @@
       <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -1087,7 +1213,7 @@
       <c r="G3" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -1143,7 +1269,7 @@
       <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4">
         <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -1196,7 +1322,7 @@
       <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <v>6</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -1252,7 +1378,7 @@
       <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <v>7</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1267,14 +1393,14 @@
       <c r="L6" s="1">
         <v>46210</v>
       </c>
-      <c r="M6" t="s">
-        <v>153</v>
+      <c r="M6">
+        <v>588146</v>
       </c>
       <c r="N6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O6" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="O6">
+        <v>67.37</v>
       </c>
       <c r="P6" t="s">
         <v>28</v>
@@ -1305,7 +1431,7 @@
       <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7">
         <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1336,7 +1462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1358,7 +1484,7 @@
       <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1411,7 +1537,7 @@
       <c r="G9" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9">
         <v>15</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1464,7 +1590,7 @@
       <c r="G10" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10">
         <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1479,14 +1605,14 @@
       <c r="L10" s="1">
         <v>46218</v>
       </c>
-      <c r="M10" t="s">
-        <v>153</v>
+      <c r="M10">
+        <v>591629</v>
       </c>
       <c r="N10" t="s">
-        <v>153</v>
-      </c>
-      <c r="O10" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="O10">
+        <v>10.44</v>
       </c>
       <c r="P10" t="s">
         <v>28</v>
@@ -1517,7 +1643,7 @@
       <c r="G11" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11">
         <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1532,14 +1658,14 @@
       <c r="L11" s="1">
         <v>46219</v>
       </c>
-      <c r="M11" t="s">
-        <v>153</v>
+      <c r="M11">
+        <v>592165</v>
       </c>
       <c r="N11" t="s">
-        <v>153</v>
-      </c>
-      <c r="O11" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="O11">
+        <v>7</v>
       </c>
       <c r="P11" t="s">
         <v>28</v>
@@ -1570,7 +1696,7 @@
       <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1623,7 +1749,7 @@
       <c r="G13" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13">
         <v>21</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1679,7 +1805,7 @@
       <c r="G14" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14">
         <v>22</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1732,7 +1858,7 @@
       <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -1785,7 +1911,7 @@
       <c r="G16" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16">
         <v>28</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1800,14 +1926,14 @@
       <c r="L16" s="1">
         <v>46231</v>
       </c>
-      <c r="M16" t="s">
-        <v>153</v>
+      <c r="M16">
+        <v>593213</v>
       </c>
       <c r="N16" t="s">
-        <v>153</v>
-      </c>
-      <c r="O16" t="s">
-        <v>153</v>
+        <v>59</v>
+      </c>
+      <c r="O16">
+        <v>3.66</v>
       </c>
       <c r="P16" t="s">
         <v>28</v>
@@ -1838,7 +1964,7 @@
       <c r="G17" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -1894,7 +2020,7 @@
       <c r="G18" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18">
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -1909,14 +2035,14 @@
       <c r="L18" s="1">
         <v>46231</v>
       </c>
-      <c r="M18" t="s">
-        <v>153</v>
+      <c r="M18">
+        <v>598353</v>
       </c>
       <c r="N18" t="s">
-        <v>153</v>
-      </c>
-      <c r="O18" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="O18">
+        <v>6.9</v>
       </c>
       <c r="P18" t="s">
         <v>28</v>
@@ -1947,7 +2073,7 @@
       <c r="G19" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19">
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -2003,7 +2129,7 @@
       <c r="G20" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20">
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -2018,20 +2144,20 @@
       <c r="L20" s="1">
         <v>46238</v>
       </c>
-      <c r="M20" t="s">
-        <v>153</v>
+      <c r="M20">
+        <v>601025</v>
       </c>
       <c r="N20" t="s">
-        <v>153</v>
-      </c>
-      <c r="O20" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="O20">
+        <v>41.62</v>
       </c>
       <c r="P20" t="s">
         <v>28</v>
       </c>
       <c r="Q20" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -2059,7 +2185,7 @@
       <c r="G21" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21">
         <v>5</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -2115,7 +2241,7 @@
       <c r="G22" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22">
         <v>6</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -2171,7 +2297,7 @@
       <c r="G23" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23">
         <v>7</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -2227,7 +2353,7 @@
       <c r="G24" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24">
         <v>7</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2283,7 +2409,7 @@
       <c r="G25" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25">
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -2298,14 +2424,14 @@
       <c r="L25" s="1">
         <v>46244</v>
       </c>
-      <c r="M25" t="s">
-        <v>153</v>
+      <c r="M25">
+        <v>603608</v>
       </c>
       <c r="N25" t="s">
-        <v>153</v>
-      </c>
-      <c r="O25" t="s">
-        <v>153</v>
+        <v>59</v>
+      </c>
+      <c r="O25">
+        <v>10.5</v>
       </c>
       <c r="P25" t="s">
         <v>28</v>
@@ -2339,7 +2465,7 @@
       <c r="G26" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26">
         <v>11</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -2354,20 +2480,20 @@
       <c r="L26" s="1">
         <v>46245</v>
       </c>
-      <c r="M26" t="s">
-        <v>153</v>
+      <c r="M26">
+        <v>604128</v>
       </c>
       <c r="N26" t="s">
-        <v>153</v>
-      </c>
-      <c r="O26" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="O26">
+        <v>8.3699999999999992</v>
       </c>
       <c r="P26" t="s">
         <v>28</v>
       </c>
       <c r="Q26" t="s">
-        <v>28</v>
+        <v>191</v>
       </c>
       <c r="R26" t="e">
         <v>#N/A</v>
@@ -2395,7 +2521,7 @@
       <c r="G27" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27">
         <v>11</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2451,7 +2577,7 @@
       <c r="G28" t="s">
         <v>91</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28">
         <v>13</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2507,7 +2633,7 @@
       <c r="G29" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29">
         <v>13</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2522,20 +2648,20 @@
       <c r="L29" s="1">
         <v>46247</v>
       </c>
-      <c r="M29" t="s">
-        <v>153</v>
+      <c r="M29">
+        <v>605244</v>
       </c>
       <c r="N29" t="s">
-        <v>153</v>
-      </c>
-      <c r="O29" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="O29">
+        <v>91.5</v>
       </c>
       <c r="P29" t="s">
         <v>28</v>
       </c>
       <c r="Q29" t="s">
-        <v>28</v>
+        <v>191</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -2563,7 +2689,7 @@
       <c r="G30" t="s">
         <v>91</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30">
         <v>14</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2619,7 +2745,7 @@
       <c r="G31" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31">
         <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2675,7 +2801,7 @@
       <c r="G32" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32">
         <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -2731,7 +2857,7 @@
       <c r="G33" t="s">
         <v>91</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33">
         <v>19</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -2787,7 +2913,7 @@
       <c r="G34" t="s">
         <v>43</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34">
         <v>19</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -2843,7 +2969,7 @@
       <c r="G35" t="s">
         <v>91</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35">
         <v>20</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -2899,7 +3025,7 @@
       <c r="G36" t="s">
         <v>91</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36">
         <v>21</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -2955,7 +3081,7 @@
       <c r="G37" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37">
         <v>21</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -3011,7 +3137,7 @@
       <c r="G38" t="s">
         <v>91</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38">
         <v>21</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -3026,14 +3152,14 @@
       <c r="L38" s="1">
         <v>46255</v>
       </c>
-      <c r="M38" t="s">
-        <v>153</v>
+      <c r="M38">
+        <v>609384</v>
       </c>
       <c r="N38" t="s">
-        <v>153</v>
-      </c>
-      <c r="O38" t="s">
-        <v>153</v>
+        <v>59</v>
+      </c>
+      <c r="O38">
+        <v>3.39</v>
       </c>
       <c r="P38" t="s">
         <v>28</v>
@@ -3067,7 +3193,7 @@
       <c r="G39" t="s">
         <v>104</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39">
         <v>21</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -3123,7 +3249,7 @@
       <c r="G40" t="s">
         <v>91</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40">
         <v>21</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -3179,7 +3305,7 @@
       <c r="G41" t="s">
         <v>91</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41">
         <v>21</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -3235,7 +3361,7 @@
       <c r="G42" t="s">
         <v>32</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42">
         <v>21</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -3291,7 +3417,7 @@
       <c r="G43" t="s">
         <v>32</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43">
         <v>24</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -3347,7 +3473,7 @@
       <c r="G44" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44">
         <v>25</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -3403,7 +3529,7 @@
       <c r="G45" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45">
         <v>25</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -3418,20 +3544,20 @@
       <c r="L45" s="1">
         <v>46259</v>
       </c>
-      <c r="M45" t="s">
-        <v>153</v>
+      <c r="M45">
+        <v>605659</v>
       </c>
       <c r="N45" t="s">
-        <v>153</v>
-      </c>
-      <c r="O45" t="s">
-        <v>153</v>
+        <v>44</v>
+      </c>
+      <c r="O45">
+        <v>20.53</v>
       </c>
       <c r="P45" t="s">
         <v>28</v>
       </c>
       <c r="Q45" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -3459,7 +3585,7 @@
       <c r="G46" t="s">
         <v>43</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46">
         <v>25</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -3515,7 +3641,7 @@
       <c r="G47" t="s">
         <v>32</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47">
         <v>25</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -3571,7 +3697,7 @@
       <c r="G48" t="s">
         <v>91</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48">
         <v>27</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -3627,7 +3753,7 @@
       <c r="G49" t="s">
         <v>32</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49">
         <v>27</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -3683,7 +3809,7 @@
       <c r="G50" t="s">
         <v>91</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50">
         <v>28</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -3739,7 +3865,7 @@
       <c r="G51" t="s">
         <v>32</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -3795,7 +3921,7 @@
       <c r="G52" t="s">
         <v>91</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52">
         <v>3</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -3851,7 +3977,7 @@
       <c r="G53" t="s">
         <v>32</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53">
         <v>3</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -3907,7 +4033,7 @@
       <c r="G54" t="s">
         <v>32</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54">
         <v>4</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -3963,7 +4089,7 @@
       <c r="G55" t="s">
         <v>32</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55">
         <v>4</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -4019,7 +4145,7 @@
       <c r="G56" t="s">
         <v>32</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56">
         <v>4</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -4075,7 +4201,7 @@
       <c r="G57" t="s">
         <v>126</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57">
         <v>8</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -4131,7 +4257,7 @@
       <c r="G58" t="s">
         <v>32</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58">
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -4187,7 +4313,7 @@
       <c r="G59" t="s">
         <v>91</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H59">
         <v>9</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -4243,7 +4369,7 @@
       <c r="G60" t="s">
         <v>32</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H60">
         <v>9</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -4299,7 +4425,7 @@
       <c r="G61" t="s">
         <v>43</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H61">
         <v>10</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -4355,7 +4481,7 @@
       <c r="G62" t="s">
         <v>43</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H62">
         <v>11</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -4411,7 +4537,7 @@
       <c r="G63" t="s">
         <v>32</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H63">
         <v>11</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -4467,7 +4593,7 @@
       <c r="G64" t="s">
         <v>91</v>
       </c>
-      <c r="H64" s="2">
+      <c r="H64">
         <v>14</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -4523,7 +4649,7 @@
       <c r="G65" t="s">
         <v>32</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65">
         <v>14</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -4579,7 +4705,7 @@
       <c r="G66" t="s">
         <v>23</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66">
         <v>15</v>
       </c>
       <c r="I66" s="1" t="s">
@@ -4635,7 +4761,7 @@
       <c r="G67" t="s">
         <v>91</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67">
         <v>15</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -4691,7 +4817,7 @@
       <c r="G68" t="s">
         <v>32</v>
       </c>
-      <c r="H68" s="2">
+      <c r="H68">
         <v>15</v>
       </c>
       <c r="I68" s="1" t="s">
@@ -4747,7 +4873,7 @@
       <c r="G69" t="s">
         <v>91</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69">
         <v>16</v>
       </c>
       <c r="I69" s="1" t="s">
@@ -4803,7 +4929,7 @@
       <c r="G70" t="s">
         <v>43</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70">
         <v>17</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -4859,7 +4985,7 @@
       <c r="G71" t="s">
         <v>126</v>
       </c>
-      <c r="H71" s="2">
+      <c r="H71">
         <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
@@ -4915,7 +5041,7 @@
       <c r="G72" t="s">
         <v>32</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72">
         <v>17</v>
       </c>
       <c r="I72" s="1" t="s">
@@ -4940,7 +5066,7 @@
         <v>3.78</v>
       </c>
       <c r="P72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q72" t="s">
         <v>28</v>
@@ -4971,7 +5097,7 @@
       <c r="G73" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73">
         <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
@@ -5027,7 +5153,7 @@
       <c r="G74" t="s">
         <v>32</v>
       </c>
-      <c r="H74" s="2">
+      <c r="H74">
         <v>18</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -5083,7 +5209,7 @@
       <c r="G75" t="s">
         <v>91</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75">
         <v>22</v>
       </c>
       <c r="I75" s="1" t="s">
@@ -5139,7 +5265,7 @@
       <c r="G76" t="s">
         <v>91</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76">
         <v>22</v>
       </c>
       <c r="I76" s="1" t="s">
@@ -5195,7 +5321,7 @@
       <c r="G77" t="s">
         <v>32</v>
       </c>
-      <c r="H77" s="2">
+      <c r="H77">
         <v>22</v>
       </c>
       <c r="I77" s="1" t="s">
@@ -5251,7 +5377,7 @@
       <c r="G78" t="s">
         <v>32</v>
       </c>
-      <c r="H78" s="2">
+      <c r="H78">
         <v>22</v>
       </c>
       <c r="I78" s="1" t="s">
@@ -5307,7 +5433,7 @@
       <c r="G79" t="s">
         <v>91</v>
       </c>
-      <c r="H79" s="2">
+      <c r="H79">
         <v>23</v>
       </c>
       <c r="I79" s="1" t="s">
@@ -5363,7 +5489,7 @@
       <c r="G80" t="s">
         <v>23</v>
       </c>
-      <c r="H80" s="2">
+      <c r="H80">
         <v>24</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -5379,7 +5505,7 @@
         <v>46289</v>
       </c>
       <c r="M80">
-        <v>625164</v>
+        <v>636005</v>
       </c>
       <c r="N80" t="s">
         <v>131</v>
@@ -5388,7 +5514,7 @@
         <v>29.19</v>
       </c>
       <c r="P80" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="Q80" t="s">
         <v>28</v>
@@ -5419,7 +5545,7 @@
       <c r="G81" t="s">
         <v>32</v>
       </c>
-      <c r="H81" s="2">
+      <c r="H81">
         <v>24</v>
       </c>
       <c r="I81" s="1" t="s">
@@ -5475,7 +5601,7 @@
       <c r="G82" t="s">
         <v>167</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82">
         <v>25</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -5531,7 +5657,7 @@
       <c r="G83" t="s">
         <v>43</v>
       </c>
-      <c r="H83" s="2">
+      <c r="H83">
         <v>25</v>
       </c>
       <c r="I83" s="1" t="s">
@@ -5587,7 +5713,7 @@
       <c r="G84" t="s">
         <v>32</v>
       </c>
-      <c r="H84" s="2">
+      <c r="H84">
         <v>28</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -5643,7 +5769,7 @@
       <c r="G85" t="s">
         <v>43</v>
       </c>
-      <c r="H85" s="2">
+      <c r="H85">
         <v>28</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -5699,7 +5825,7 @@
       <c r="G86" t="s">
         <v>104</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86">
         <v>29</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -5755,7 +5881,7 @@
       <c r="G87" t="s">
         <v>104</v>
       </c>
-      <c r="H87" s="2">
+      <c r="H87">
         <v>29</v>
       </c>
       <c r="I87" s="1" t="s">
@@ -5811,7 +5937,7 @@
       <c r="G88" t="s">
         <v>104</v>
       </c>
-      <c r="H88" s="2">
+      <c r="H88">
         <v>29</v>
       </c>
       <c r="I88" s="1" t="s">
@@ -5867,7 +5993,7 @@
       <c r="G89" t="s">
         <v>32</v>
       </c>
-      <c r="H89" s="2">
+      <c r="H89">
         <v>29</v>
       </c>
       <c r="I89" s="1" t="s">
@@ -5923,7 +6049,7 @@
       <c r="G90" t="s">
         <v>32</v>
       </c>
-      <c r="H90" s="2">
+      <c r="H90">
         <v>29</v>
       </c>
       <c r="I90" s="1" t="s">
@@ -5979,7 +6105,7 @@
       <c r="G91" t="s">
         <v>32</v>
       </c>
-      <c r="H91" s="2">
+      <c r="H91">
         <v>29</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -6035,7 +6161,7 @@
       <c r="G92" t="s">
         <v>104</v>
       </c>
-      <c r="H92" s="2">
+      <c r="H92">
         <v>30</v>
       </c>
       <c r="I92" s="1" t="s">
@@ -6063,7 +6189,7 @@
         <v>28</v>
       </c>
       <c r="Q92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R92">
         <v>1</v>
@@ -6091,7 +6217,7 @@
       <c r="G93" t="s">
         <v>91</v>
       </c>
-      <c r="H93" s="2">
+      <c r="H93">
         <v>30</v>
       </c>
       <c r="I93" s="1" t="s">
@@ -6147,7 +6273,7 @@
       <c r="G94" t="s">
         <v>91</v>
       </c>
-      <c r="H94" s="2">
+      <c r="H94">
         <v>30</v>
       </c>
       <c r="I94" s="1" t="s">
@@ -6203,7 +6329,7 @@
       <c r="G95" t="s">
         <v>104</v>
       </c>
-      <c r="H95" s="2">
+      <c r="H95">
         <v>30</v>
       </c>
       <c r="I95" s="1" t="s">
@@ -6242,7 +6368,7 @@
         <v>70</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C96" t="s">
         <v>19</v>
@@ -6259,11 +6385,11 @@
       <c r="G96" t="s">
         <v>91</v>
       </c>
-      <c r="H96" s="2">
+      <c r="H96">
         <v>7</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>25</v>
@@ -6298,7 +6424,7 @@
         <v>70</v>
       </c>
       <c r="B97" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C97" t="s">
         <v>19</v>
@@ -6315,11 +6441,11 @@
       <c r="G97" t="s">
         <v>91</v>
       </c>
-      <c r="H97" s="2">
+      <c r="H97">
         <v>9</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>25</v>
@@ -6340,13 +6466,13 @@
         <v>2.34</v>
       </c>
       <c r="P97" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q97" t="s">
         <v>28</v>
       </c>
-      <c r="R97" t="e">
-        <v>#N/A</v>
+      <c r="R97">
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
@@ -6354,7 +6480,7 @@
         <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C98" t="s">
         <v>19</v>
@@ -6371,11 +6497,11 @@
       <c r="G98" t="s">
         <v>23</v>
       </c>
-      <c r="H98" s="2">
+      <c r="H98">
         <v>13</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>25</v>
@@ -6410,7 +6536,7 @@
         <v>70</v>
       </c>
       <c r="B99" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C99" t="s">
         <v>19</v>
@@ -6427,11 +6553,11 @@
       <c r="G99" t="s">
         <v>104</v>
       </c>
-      <c r="H99" s="2">
+      <c r="H99">
         <v>14</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>25</v>
@@ -6457,8 +6583,8 @@
       <c r="Q99" t="s">
         <v>28</v>
       </c>
-      <c r="R99" t="e">
-        <v>#N/A</v>
+      <c r="R99">
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
@@ -6466,7 +6592,7 @@
         <v>70</v>
       </c>
       <c r="B100" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C100" t="s">
         <v>19</v>
@@ -6481,13 +6607,13 @@
         <v>90</v>
       </c>
       <c r="G100" t="s">
-        <v>191</v>
-      </c>
-      <c r="H100" s="2">
+        <v>190</v>
+      </c>
+      <c r="H100">
         <v>14</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>25</v>
@@ -6514,6 +6640,1350 @@
         <v>28</v>
       </c>
       <c r="R100" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>192</v>
+      </c>
+      <c r="B101" t="s">
+        <v>193</v>
+      </c>
+      <c r="C101" t="s">
+        <v>194</v>
+      </c>
+      <c r="D101" t="s">
+        <v>20</v>
+      </c>
+      <c r="E101" t="s">
+        <v>195</v>
+      </c>
+      <c r="F101" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" t="s">
+        <v>196</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L101" s="1">
+        <v>46266</v>
+      </c>
+      <c r="M101">
+        <v>607987</v>
+      </c>
+      <c r="N101" t="s">
+        <v>59</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>28</v>
+      </c>
+      <c r="R101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>192</v>
+      </c>
+      <c r="B102" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" t="s">
+        <v>49</v>
+      </c>
+      <c r="D102" t="s">
+        <v>20</v>
+      </c>
+      <c r="E102" t="s">
+        <v>198</v>
+      </c>
+      <c r="F102" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" t="s">
+        <v>199</v>
+      </c>
+      <c r="H102">
+        <v>8</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L102" s="1">
+        <v>46273</v>
+      </c>
+      <c r="M102">
+        <v>612268</v>
+      </c>
+      <c r="N102" t="s">
+        <v>44</v>
+      </c>
+      <c r="O102">
+        <v>35.65</v>
+      </c>
+      <c r="P102" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>191</v>
+      </c>
+      <c r="R102" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>192</v>
+      </c>
+      <c r="B103" t="s">
+        <v>200</v>
+      </c>
+      <c r="C103" t="s">
+        <v>49</v>
+      </c>
+      <c r="D103" t="s">
+        <v>20</v>
+      </c>
+      <c r="E103" t="s">
+        <v>201</v>
+      </c>
+      <c r="F103" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" t="s">
+        <v>199</v>
+      </c>
+      <c r="H103">
+        <v>15</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L103" s="1">
+        <v>46280</v>
+      </c>
+      <c r="M103">
+        <v>612223</v>
+      </c>
+      <c r="N103" t="s">
+        <v>131</v>
+      </c>
+      <c r="O103">
+        <v>104.04</v>
+      </c>
+      <c r="P103" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>28</v>
+      </c>
+      <c r="R103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>192</v>
+      </c>
+      <c r="B104" t="s">
+        <v>202</v>
+      </c>
+      <c r="C104" t="s">
+        <v>49</v>
+      </c>
+      <c r="D104" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" t="s">
+        <v>201</v>
+      </c>
+      <c r="F104" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104" t="s">
+        <v>199</v>
+      </c>
+      <c r="H104">
+        <v>15</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L104" s="1">
+        <v>46280</v>
+      </c>
+      <c r="M104">
+        <v>612623</v>
+      </c>
+      <c r="N104" t="s">
+        <v>131</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>28</v>
+      </c>
+      <c r="R104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>192</v>
+      </c>
+      <c r="B105" t="s">
+        <v>203</v>
+      </c>
+      <c r="C105" t="s">
+        <v>194</v>
+      </c>
+      <c r="D105" t="s">
+        <v>20</v>
+      </c>
+      <c r="E105" t="s">
+        <v>204</v>
+      </c>
+      <c r="F105" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105" t="s">
+        <v>43</v>
+      </c>
+      <c r="H105">
+        <v>22</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L105" s="1">
+        <v>46287</v>
+      </c>
+      <c r="M105">
+        <v>624356</v>
+      </c>
+      <c r="N105" t="s">
+        <v>59</v>
+      </c>
+      <c r="O105">
+        <v>38.840000000000003</v>
+      </c>
+      <c r="P105" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>28</v>
+      </c>
+      <c r="R105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>192</v>
+      </c>
+      <c r="B106" t="s">
+        <v>205</v>
+      </c>
+      <c r="C106" t="s">
+        <v>194</v>
+      </c>
+      <c r="D106" t="s">
+        <v>20</v>
+      </c>
+      <c r="E106" t="s">
+        <v>206</v>
+      </c>
+      <c r="F106" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106" t="s">
+        <v>196</v>
+      </c>
+      <c r="H106">
+        <v>22</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L106" s="1">
+        <v>46287</v>
+      </c>
+      <c r="M106">
+        <v>622609</v>
+      </c>
+      <c r="N106" t="s">
+        <v>131</v>
+      </c>
+      <c r="O106">
+        <v>118.5</v>
+      </c>
+      <c r="P106" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>28</v>
+      </c>
+      <c r="R106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>192</v>
+      </c>
+      <c r="B107" t="s">
+        <v>208</v>
+      </c>
+      <c r="C107" t="s">
+        <v>194</v>
+      </c>
+      <c r="D107" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" t="s">
+        <v>206</v>
+      </c>
+      <c r="F107" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" t="s">
+        <v>196</v>
+      </c>
+      <c r="H107">
+        <v>24</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L107" s="1">
+        <v>46289</v>
+      </c>
+      <c r="M107">
+        <v>623818</v>
+      </c>
+      <c r="N107" t="s">
+        <v>59</v>
+      </c>
+      <c r="O107">
+        <v>42.8</v>
+      </c>
+      <c r="P107" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>28</v>
+      </c>
+      <c r="R107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>192</v>
+      </c>
+      <c r="B108" t="s">
+        <v>209</v>
+      </c>
+      <c r="C108" t="s">
+        <v>194</v>
+      </c>
+      <c r="D108" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108" t="s">
+        <v>204</v>
+      </c>
+      <c r="F108" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108" t="s">
+        <v>196</v>
+      </c>
+      <c r="H108">
+        <v>29</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" s="1">
+        <v>46294</v>
+      </c>
+      <c r="M108">
+        <v>625426</v>
+      </c>
+      <c r="N108" t="s">
+        <v>59</v>
+      </c>
+      <c r="O108">
+        <v>38.840000000000003</v>
+      </c>
+      <c r="P108" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>28</v>
+      </c>
+      <c r="R108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>192</v>
+      </c>
+      <c r="B109" t="s">
+        <v>210</v>
+      </c>
+      <c r="C109" t="s">
+        <v>194</v>
+      </c>
+      <c r="D109" t="s">
+        <v>20</v>
+      </c>
+      <c r="E109" t="s">
+        <v>204</v>
+      </c>
+      <c r="F109" t="s">
+        <v>22</v>
+      </c>
+      <c r="G109" t="s">
+        <v>196</v>
+      </c>
+      <c r="H109">
+        <v>29</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L109" s="1">
+        <v>46294</v>
+      </c>
+      <c r="M109">
+        <v>625413</v>
+      </c>
+      <c r="N109" t="s">
+        <v>59</v>
+      </c>
+      <c r="O109">
+        <v>38.840000000000003</v>
+      </c>
+      <c r="P109" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>28</v>
+      </c>
+      <c r="R109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>192</v>
+      </c>
+      <c r="B110" t="s">
+        <v>211</v>
+      </c>
+      <c r="C110" t="s">
+        <v>49</v>
+      </c>
+      <c r="D110" t="s">
+        <v>20</v>
+      </c>
+      <c r="E110" t="s">
+        <v>198</v>
+      </c>
+      <c r="F110" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" t="s">
+        <v>196</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L110" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M110">
+        <v>625286</v>
+      </c>
+      <c r="N110" t="s">
+        <v>131</v>
+      </c>
+      <c r="O110">
+        <v>78.47</v>
+      </c>
+      <c r="P110" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>28</v>
+      </c>
+      <c r="R110" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>192</v>
+      </c>
+      <c r="B111" t="s">
+        <v>212</v>
+      </c>
+      <c r="C111" t="s">
+        <v>194</v>
+      </c>
+      <c r="D111" t="s">
+        <v>20</v>
+      </c>
+      <c r="E111" t="s">
+        <v>204</v>
+      </c>
+      <c r="F111" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" t="s">
+        <v>196</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L111" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M111">
+        <v>628039</v>
+      </c>
+      <c r="N111" t="s">
+        <v>59</v>
+      </c>
+      <c r="O111">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="P111" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>28</v>
+      </c>
+      <c r="R111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>192</v>
+      </c>
+      <c r="B112" t="s">
+        <v>213</v>
+      </c>
+      <c r="C112" t="s">
+        <v>49</v>
+      </c>
+      <c r="D112" t="s">
+        <v>20</v>
+      </c>
+      <c r="E112" t="s">
+        <v>198</v>
+      </c>
+      <c r="F112" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112" t="s">
+        <v>199</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L112" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M112">
+        <v>612265</v>
+      </c>
+      <c r="N112" t="s">
+        <v>131</v>
+      </c>
+      <c r="O112">
+        <v>38.659999999999997</v>
+      </c>
+      <c r="P112" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>28</v>
+      </c>
+      <c r="R112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>192</v>
+      </c>
+      <c r="B113" t="s">
+        <v>214</v>
+      </c>
+      <c r="C113" t="s">
+        <v>194</v>
+      </c>
+      <c r="D113" t="s">
+        <v>20</v>
+      </c>
+      <c r="E113" t="s">
+        <v>204</v>
+      </c>
+      <c r="F113" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" t="s">
+        <v>196</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L113" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M113">
+        <v>626295</v>
+      </c>
+      <c r="N113" t="s">
+        <v>59</v>
+      </c>
+      <c r="O113">
+        <v>15.06</v>
+      </c>
+      <c r="P113" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>28</v>
+      </c>
+      <c r="R113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>192</v>
+      </c>
+      <c r="B114" t="s">
+        <v>215</v>
+      </c>
+      <c r="C114" t="s">
+        <v>194</v>
+      </c>
+      <c r="D114" t="s">
+        <v>20</v>
+      </c>
+      <c r="E114" t="s">
+        <v>206</v>
+      </c>
+      <c r="F114" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" t="s">
+        <v>196</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L114" s="1">
+        <v>46296</v>
+      </c>
+      <c r="M114">
+        <v>627041</v>
+      </c>
+      <c r="N114" t="s">
+        <v>131</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>28</v>
+      </c>
+      <c r="R114" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>192</v>
+      </c>
+      <c r="B115" t="s">
+        <v>216</v>
+      </c>
+      <c r="C115" t="s">
+        <v>194</v>
+      </c>
+      <c r="D115" t="s">
+        <v>20</v>
+      </c>
+      <c r="E115" t="s">
+        <v>204</v>
+      </c>
+      <c r="F115" t="s">
+        <v>22</v>
+      </c>
+      <c r="G115" t="s">
+        <v>196</v>
+      </c>
+      <c r="H115">
+        <v>6</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L115" s="1">
+        <v>46301</v>
+      </c>
+      <c r="M115">
+        <v>630590</v>
+      </c>
+      <c r="N115" t="s">
+        <v>131</v>
+      </c>
+      <c r="O115">
+        <v>118.1</v>
+      </c>
+      <c r="P115" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>28</v>
+      </c>
+      <c r="R115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>217</v>
+      </c>
+      <c r="B116" t="s">
+        <v>218</v>
+      </c>
+      <c r="C116" t="s">
+        <v>194</v>
+      </c>
+      <c r="D116" t="s">
+        <v>20</v>
+      </c>
+      <c r="E116" t="s">
+        <v>219</v>
+      </c>
+      <c r="F116" t="s">
+        <v>22</v>
+      </c>
+      <c r="G116" t="s">
+        <v>43</v>
+      </c>
+      <c r="H116">
+        <v>6</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L116" s="1">
+        <v>46301</v>
+      </c>
+      <c r="M116">
+        <v>630717</v>
+      </c>
+      <c r="N116" t="s">
+        <v>131</v>
+      </c>
+      <c r="O116">
+        <v>6.36</v>
+      </c>
+      <c r="P116" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>28</v>
+      </c>
+      <c r="R116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>217</v>
+      </c>
+      <c r="B117" t="s">
+        <v>220</v>
+      </c>
+      <c r="C117" t="s">
+        <v>194</v>
+      </c>
+      <c r="D117" t="s">
+        <v>20</v>
+      </c>
+      <c r="E117" t="s">
+        <v>219</v>
+      </c>
+      <c r="F117" t="s">
+        <v>22</v>
+      </c>
+      <c r="G117" t="s">
+        <v>43</v>
+      </c>
+      <c r="H117">
+        <v>7</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K117" s="1">
+        <v>1</v>
+      </c>
+      <c r="L117" s="1">
+        <v>46302</v>
+      </c>
+      <c r="M117">
+        <v>631099</v>
+      </c>
+      <c r="N117" t="s">
+        <v>44</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>142</v>
+      </c>
+      <c r="R117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>217</v>
+      </c>
+      <c r="B118" t="s">
+        <v>221</v>
+      </c>
+      <c r="C118" t="s">
+        <v>194</v>
+      </c>
+      <c r="D118" t="s">
+        <v>20</v>
+      </c>
+      <c r="E118" t="s">
+        <v>219</v>
+      </c>
+      <c r="F118" t="s">
+        <v>22</v>
+      </c>
+      <c r="G118" t="s">
+        <v>43</v>
+      </c>
+      <c r="H118">
+        <v>7</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L118" s="1">
+        <v>46302</v>
+      </c>
+      <c r="M118">
+        <v>631115</v>
+      </c>
+      <c r="N118" t="s">
+        <v>131</v>
+      </c>
+      <c r="O118">
+        <v>3.64</v>
+      </c>
+      <c r="P118" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>28</v>
+      </c>
+      <c r="R118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>222</v>
+      </c>
+      <c r="B119" t="s">
+        <v>223</v>
+      </c>
+      <c r="C119" t="s">
+        <v>194</v>
+      </c>
+      <c r="D119" t="s">
+        <v>20</v>
+      </c>
+      <c r="E119" t="s">
+        <v>224</v>
+      </c>
+      <c r="F119" t="s">
+        <v>22</v>
+      </c>
+      <c r="G119" t="s">
+        <v>196</v>
+      </c>
+      <c r="H119">
+        <v>8</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L119" s="1">
+        <v>46303</v>
+      </c>
+      <c r="M119">
+        <v>631302</v>
+      </c>
+      <c r="N119" t="s">
+        <v>59</v>
+      </c>
+      <c r="O119">
+        <v>3.34</v>
+      </c>
+      <c r="P119" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>28</v>
+      </c>
+      <c r="R119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>222</v>
+      </c>
+      <c r="B120" t="s">
+        <v>225</v>
+      </c>
+      <c r="C120" t="s">
+        <v>194</v>
+      </c>
+      <c r="D120" t="s">
+        <v>20</v>
+      </c>
+      <c r="E120" t="s">
+        <v>226</v>
+      </c>
+      <c r="F120" t="s">
+        <v>22</v>
+      </c>
+      <c r="G120" t="s">
+        <v>196</v>
+      </c>
+      <c r="H120">
+        <v>8</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L120" s="1">
+        <v>46303</v>
+      </c>
+      <c r="M120">
+        <v>635101</v>
+      </c>
+      <c r="N120" t="s">
+        <v>131</v>
+      </c>
+      <c r="O120">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="P120" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>28</v>
+      </c>
+      <c r="R120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>192</v>
+      </c>
+      <c r="B121" t="s">
+        <v>227</v>
+      </c>
+      <c r="C121" t="s">
+        <v>194</v>
+      </c>
+      <c r="D121" t="s">
+        <v>20</v>
+      </c>
+      <c r="E121" t="s">
+        <v>204</v>
+      </c>
+      <c r="F121" t="s">
+        <v>22</v>
+      </c>
+      <c r="G121" t="s">
+        <v>196</v>
+      </c>
+      <c r="H121">
+        <v>14</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L121" s="1">
+        <v>46309</v>
+      </c>
+      <c r="M121">
+        <v>630814</v>
+      </c>
+      <c r="N121" t="s">
+        <v>131</v>
+      </c>
+      <c r="O121">
+        <v>7.53</v>
+      </c>
+      <c r="P121" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>28</v>
+      </c>
+      <c r="R121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>192</v>
+      </c>
+      <c r="B122" t="s">
+        <v>228</v>
+      </c>
+      <c r="C122" t="s">
+        <v>49</v>
+      </c>
+      <c r="D122" t="s">
+        <v>20</v>
+      </c>
+      <c r="E122" t="s">
+        <v>195</v>
+      </c>
+      <c r="F122" t="s">
+        <v>22</v>
+      </c>
+      <c r="G122" t="s">
+        <v>196</v>
+      </c>
+      <c r="H122">
+        <v>14</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L122" s="1">
+        <v>46309</v>
+      </c>
+      <c r="M122">
+        <v>627337</v>
+      </c>
+      <c r="N122" t="s">
+        <v>131</v>
+      </c>
+      <c r="O122">
+        <v>80.19</v>
+      </c>
+      <c r="P122" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>28</v>
+      </c>
+      <c r="R122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>222</v>
+      </c>
+      <c r="B123" t="s">
+        <v>229</v>
+      </c>
+      <c r="C123" t="s">
+        <v>194</v>
+      </c>
+      <c r="D123" t="s">
+        <v>20</v>
+      </c>
+      <c r="E123" t="s">
+        <v>224</v>
+      </c>
+      <c r="F123" t="s">
+        <v>230</v>
+      </c>
+      <c r="G123" t="s">
+        <v>230</v>
+      </c>
+      <c r="H123">
+        <v>15</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L123" s="1">
+        <v>46310</v>
+      </c>
+      <c r="M123" t="s">
+        <v>153</v>
+      </c>
+      <c r="N123" t="s">
+        <v>153</v>
+      </c>
+      <c r="O123" t="s">
+        <v>153</v>
+      </c>
+      <c r="P123" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>28</v>
+      </c>
+      <c r="R123" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>192</v>
+      </c>
+      <c r="B124" t="s">
+        <v>231</v>
+      </c>
+      <c r="C124" t="s">
+        <v>194</v>
+      </c>
+      <c r="D124" t="s">
+        <v>20</v>
+      </c>
+      <c r="E124" t="s">
+        <v>204</v>
+      </c>
+      <c r="F124" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" t="s">
+        <v>196</v>
+      </c>
+      <c r="H124">
+        <v>16</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L124" s="1">
+        <v>46311</v>
+      </c>
+      <c r="M124">
+        <v>635112</v>
+      </c>
+      <c r="N124" t="s">
+        <v>131</v>
+      </c>
+      <c r="O124">
+        <v>102.64</v>
+      </c>
+      <c r="P124" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>28</v>
+      </c>
+      <c r="R124" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -7682,7 +9152,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D03D8E35-98BA-491C-80D3-FD8BDE5E2A5E}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -7690,7 +9160,7 @@
     <col min="3" max="3" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>68</v>
       </c>
@@ -7700,8 +9170,11 @@
       <c r="C1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46204</v>
       </c>
@@ -7711,8 +9184,11 @@
       <c r="C2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46204</v>
       </c>
@@ -7722,8 +9198,11 @@
       <c r="C3">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46235</v>
       </c>
@@ -7733,8 +9212,11 @@
       <c r="C4">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46235</v>
       </c>
@@ -7744,8 +9226,11 @@
       <c r="C5">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46235</v>
       </c>
@@ -7755,8 +9240,11 @@
       <c r="C6">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46266</v>
       </c>
@@ -7766,8 +9254,11 @@
       <c r="C7">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46266</v>
       </c>
@@ -7777,8 +9268,11 @@
       <c r="C8">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46266</v>
       </c>
@@ -7788,8 +9282,11 @@
       <c r="C9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46296</v>
       </c>
@@ -7799,8 +9296,11 @@
       <c r="C10">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46296</v>
       </c>
@@ -7809,6 +9309,65 @@
       </c>
       <c r="C11">
         <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B14" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32DD6DD8-3881-469F-81B9-599B71783E29}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38386CE1-E05F-4431-9BAA-375B79C025C4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="237">
   <si>
     <t>Usuário</t>
   </si>
@@ -734,9 +734,6 @@
     <t>MARIA AUDILENE SILVA SOUSA</t>
   </si>
   <si>
-    <t>(vazio)</t>
-  </si>
-  <si>
     <t>CONDOMINIO DO EDIFICIO VERSATTO</t>
   </si>
   <si>
@@ -747,6 +744,15 @@
   </si>
   <si>
     <t>Interno</t>
+  </si>
+  <si>
+    <t>OMAR BONATO GUIMARAES</t>
+  </si>
+  <si>
+    <t>Patrícia Paula</t>
+  </si>
+  <si>
+    <t>ADNIR JOSE DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -788,9 +794,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1071,11 +1078,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R124"/>
+  <dimension ref="A1:R126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1101,7 +1109,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1157,7 +1165,7 @@
       <c r="G2" t="s">
         <v>54</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -1213,7 +1221,7 @@
       <c r="G3" t="s">
         <v>54</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>2</v>
       </c>
       <c r="I3" s="1" t="s">
@@ -1269,7 +1277,7 @@
       <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -1322,7 +1330,7 @@
       <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>6</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -1378,7 +1386,7 @@
       <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>7</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1431,7 +1439,7 @@
       <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1484,7 +1492,7 @@
       <c r="G8" t="s">
         <v>32</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>10</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1537,7 +1545,7 @@
       <c r="G9" t="s">
         <v>40</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>15</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1590,7 +1598,7 @@
       <c r="G10" t="s">
         <v>32</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1643,7 +1651,7 @@
       <c r="G11" t="s">
         <v>32</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1696,7 +1704,7 @@
       <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1749,7 +1757,7 @@
       <c r="G13" t="s">
         <v>32</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>21</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1805,7 +1813,7 @@
       <c r="G14" t="s">
         <v>32</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>22</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1858,7 +1866,7 @@
       <c r="G15" t="s">
         <v>32</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -1911,7 +1919,7 @@
       <c r="G16" t="s">
         <v>32</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>28</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1964,7 +1972,7 @@
       <c r="G17" t="s">
         <v>43</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="2">
         <v>28</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -2020,7 +2028,7 @@
       <c r="G18" t="s">
         <v>23</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="2">
         <v>28</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -2073,7 +2081,7 @@
       <c r="G19" t="s">
         <v>43</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="2">
         <v>3</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -2129,7 +2137,7 @@
       <c r="G20" t="s">
         <v>32</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="2">
         <v>4</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -2185,7 +2193,7 @@
       <c r="G21" t="s">
         <v>43</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="2">
         <v>5</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -2241,7 +2249,7 @@
       <c r="G22" t="s">
         <v>32</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="2">
         <v>6</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -2297,7 +2305,7 @@
       <c r="G23" t="s">
         <v>32</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="2">
         <v>7</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -2353,7 +2361,7 @@
       <c r="G24" t="s">
         <v>43</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="2">
         <v>7</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2409,7 +2417,7 @@
       <c r="G25" t="s">
         <v>32</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="2">
         <v>10</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -2465,7 +2473,7 @@
       <c r="G26" t="s">
         <v>23</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="2">
         <v>11</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -2521,7 +2529,7 @@
       <c r="G27" t="s">
         <v>32</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="2">
         <v>11</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2577,7 +2585,7 @@
       <c r="G28" t="s">
         <v>91</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="2">
         <v>13</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2633,7 +2641,7 @@
       <c r="G29" t="s">
         <v>43</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="2">
         <v>13</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2689,7 +2697,7 @@
       <c r="G30" t="s">
         <v>91</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="2">
         <v>14</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2745,7 +2753,7 @@
       <c r="G31" t="s">
         <v>32</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="2">
         <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2801,7 +2809,7 @@
       <c r="G32" t="s">
         <v>32</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="2">
         <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -2857,7 +2865,7 @@
       <c r="G33" t="s">
         <v>91</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="2">
         <v>19</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -2913,7 +2921,7 @@
       <c r="G34" t="s">
         <v>43</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="2">
         <v>19</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -2969,7 +2977,7 @@
       <c r="G35" t="s">
         <v>91</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="2">
         <v>20</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -3025,7 +3033,7 @@
       <c r="G36" t="s">
         <v>91</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="2">
         <v>21</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -3081,7 +3089,7 @@
       <c r="G37" t="s">
         <v>91</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="2">
         <v>21</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -3137,7 +3145,7 @@
       <c r="G38" t="s">
         <v>91</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="2">
         <v>21</v>
       </c>
       <c r="I38" s="1" t="s">
@@ -3193,7 +3201,7 @@
       <c r="G39" t="s">
         <v>104</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="2">
         <v>21</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -3249,7 +3257,7 @@
       <c r="G40" t="s">
         <v>91</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="2">
         <v>21</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -3305,7 +3313,7 @@
       <c r="G41" t="s">
         <v>91</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="2">
         <v>21</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -3361,7 +3369,7 @@
       <c r="G42" t="s">
         <v>32</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="2">
         <v>21</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -3417,7 +3425,7 @@
       <c r="G43" t="s">
         <v>32</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="2">
         <v>24</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -3473,7 +3481,7 @@
       <c r="G44" t="s">
         <v>23</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="2">
         <v>25</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -3529,7 +3537,7 @@
       <c r="G45" t="s">
         <v>23</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="2">
         <v>25</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -3585,7 +3593,7 @@
       <c r="G46" t="s">
         <v>43</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="2">
         <v>25</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -3641,7 +3649,7 @@
       <c r="G47" t="s">
         <v>32</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="2">
         <v>25</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -3697,7 +3705,7 @@
       <c r="G48" t="s">
         <v>91</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="2">
         <v>27</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -3753,7 +3761,7 @@
       <c r="G49" t="s">
         <v>32</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="2">
         <v>27</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -3809,7 +3817,7 @@
       <c r="G50" t="s">
         <v>91</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="2">
         <v>28</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -3845,27 +3853,27 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="B51" t="s">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="F51" t="s">
         <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
-      </c>
-      <c r="H51">
+        <v>196</v>
+      </c>
+      <c r="H51" s="2">
         <v>1</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -3881,19 +3889,19 @@
         <v>46266</v>
       </c>
       <c r="M51">
-        <v>614020</v>
+        <v>607987</v>
       </c>
       <c r="N51" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="O51">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P51" t="s">
         <v>28</v>
       </c>
       <c r="Q51" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -3901,10 +3909,10 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
         <v>19</v>
@@ -3913,16 +3921,16 @@
         <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="F52" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
-      </c>
-      <c r="H52">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="H52" s="2">
+        <v>1</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>118</v>
@@ -3934,22 +3942,22 @@
         <v>26</v>
       </c>
       <c r="L52" s="1">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="M52">
-        <v>615019</v>
+        <v>614020</v>
       </c>
       <c r="N52" t="s">
         <v>44</v>
       </c>
       <c r="O52">
-        <v>7.95</v>
+        <v>2.33</v>
       </c>
       <c r="P52" t="s">
         <v>28</v>
       </c>
       <c r="Q52" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="R52">
         <v>1</v>
@@ -3957,10 +3965,10 @@
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C53" t="s">
         <v>19</v>
@@ -3969,15 +3977,15 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="F53" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s">
-        <v>32</v>
-      </c>
-      <c r="H53">
+        <v>91</v>
+      </c>
+      <c r="H53" s="2">
         <v>3</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -3993,19 +4001,19 @@
         <v>46268</v>
       </c>
       <c r="M53">
-        <v>614995</v>
+        <v>615019</v>
       </c>
       <c r="N53" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O53">
-        <v>1.91</v>
+        <v>7.95</v>
       </c>
       <c r="P53" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q53" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="R53">
         <v>1</v>
@@ -4016,7 +4024,7 @@
         <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C54" t="s">
         <v>19</v>
@@ -4033,8 +4041,8 @@
       <c r="G54" t="s">
         <v>32</v>
       </c>
-      <c r="H54">
-        <v>4</v>
+      <c r="H54" s="2">
+        <v>3</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>118</v>
@@ -4046,16 +4054,16 @@
         <v>26</v>
       </c>
       <c r="L54" s="1">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="M54">
-        <v>615314</v>
+        <v>614995</v>
       </c>
       <c r="N54" t="s">
         <v>131</v>
       </c>
       <c r="O54">
-        <v>12.23</v>
+        <v>1.91</v>
       </c>
       <c r="P54" t="s">
         <v>35</v>
@@ -4072,7 +4080,7 @@
         <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55" t="s">
         <v>19</v>
@@ -4089,7 +4097,7 @@
       <c r="G55" t="s">
         <v>32</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="2">
         <v>4</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -4105,13 +4113,13 @@
         <v>46269</v>
       </c>
       <c r="M55">
-        <v>615322</v>
+        <v>615314</v>
       </c>
       <c r="N55" t="s">
         <v>131</v>
       </c>
       <c r="O55">
-        <v>16.34</v>
+        <v>12.23</v>
       </c>
       <c r="P55" t="s">
         <v>35</v>
@@ -4128,7 +4136,7 @@
         <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C56" t="s">
         <v>19</v>
@@ -4145,7 +4153,7 @@
       <c r="G56" t="s">
         <v>32</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="2">
         <v>4</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -4161,19 +4169,19 @@
         <v>46269</v>
       </c>
       <c r="M56">
-        <v>615654</v>
+        <v>615322</v>
       </c>
       <c r="N56" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O56">
-        <v>11.93</v>
+        <v>16.34</v>
       </c>
       <c r="P56" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q56" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -4181,10 +4189,10 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C57" t="s">
         <v>19</v>
@@ -4193,16 +4201,16 @@
         <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="F57" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
-      </c>
-      <c r="H57">
-        <v>8</v>
+        <v>32</v>
+      </c>
+      <c r="H57" s="2">
+        <v>4</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>118</v>
@@ -4214,22 +4222,22 @@
         <v>26</v>
       </c>
       <c r="L57" s="1">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="M57">
-        <v>616899</v>
+        <v>615654</v>
       </c>
       <c r="N57" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O57">
-        <v>6.36</v>
+        <v>11.93</v>
       </c>
       <c r="P57" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q57" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="R57">
         <v>1</v>
@@ -4237,27 +4245,27 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D58" t="s">
         <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>31</v>
+        <v>198</v>
       </c>
       <c r="F58" t="s">
         <v>22</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
-      </c>
-      <c r="H58">
+        <v>199</v>
+      </c>
+      <c r="H58" s="2">
         <v>8</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -4273,22 +4281,22 @@
         <v>46273</v>
       </c>
       <c r="M58">
-        <v>616788</v>
+        <v>612268</v>
       </c>
       <c r="N58" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O58">
-        <v>32.82</v>
+        <v>35.65</v>
       </c>
       <c r="P58" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q58" t="s">
-        <v>28</v>
-      </c>
-      <c r="R58">
-        <v>1</v>
+        <v>191</v>
+      </c>
+      <c r="R58" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
@@ -4296,7 +4304,7 @@
         <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C59" t="s">
         <v>19</v>
@@ -4311,10 +4319,10 @@
         <v>90</v>
       </c>
       <c r="G59" t="s">
-        <v>91</v>
-      </c>
-      <c r="H59">
-        <v>9</v>
+        <v>126</v>
+      </c>
+      <c r="H59" s="2">
+        <v>8</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>118</v>
@@ -4326,19 +4334,19 @@
         <v>26</v>
       </c>
       <c r="L59" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="M59">
-        <v>617206</v>
+        <v>616899</v>
       </c>
       <c r="N59" t="s">
         <v>131</v>
       </c>
       <c r="O59">
-        <v>21.23</v>
+        <v>6.36</v>
       </c>
       <c r="P59" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q59" t="s">
         <v>28</v>
@@ -4352,7 +4360,7 @@
         <v>29</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
         <v>19</v>
@@ -4369,8 +4377,8 @@
       <c r="G60" t="s">
         <v>32</v>
       </c>
-      <c r="H60">
-        <v>9</v>
+      <c r="H60" s="2">
+        <v>8</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>118</v>
@@ -4382,19 +4390,19 @@
         <v>26</v>
       </c>
       <c r="L60" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="M60">
-        <v>617229</v>
+        <v>616788</v>
       </c>
       <c r="N60" t="s">
         <v>131</v>
       </c>
       <c r="O60">
-        <v>2.2200000000000002</v>
+        <v>32.82</v>
       </c>
       <c r="P60" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q60" t="s">
         <v>28</v>
@@ -4405,10 +4413,10 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
         <v>19</v>
@@ -4417,16 +4425,16 @@
         <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="F61" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s">
-        <v>43</v>
-      </c>
-      <c r="H61">
-        <v>10</v>
+        <v>91</v>
+      </c>
+      <c r="H61" s="2">
+        <v>9</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>118</v>
@@ -4438,16 +4446,16 @@
         <v>26</v>
       </c>
       <c r="L61" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="M61">
-        <v>617914</v>
+        <v>617206</v>
       </c>
       <c r="N61" t="s">
         <v>131</v>
       </c>
       <c r="O61">
-        <v>8.4600000000000009</v>
+        <v>21.23</v>
       </c>
       <c r="P61" t="s">
         <v>35</v>
@@ -4461,10 +4469,10 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C62" t="s">
         <v>19</v>
@@ -4473,16 +4481,16 @@
         <v>20</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F62" t="s">
         <v>22</v>
       </c>
       <c r="G62" t="s">
-        <v>43</v>
-      </c>
-      <c r="H62">
-        <v>11</v>
+        <v>32</v>
+      </c>
+      <c r="H62" s="2">
+        <v>9</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>118</v>
@@ -4494,22 +4502,22 @@
         <v>26</v>
       </c>
       <c r="L62" s="1">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="M62">
-        <v>615347</v>
+        <v>617229</v>
       </c>
       <c r="N62" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O62">
-        <v>2.76</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="P62" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Q62" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -4520,7 +4528,7 @@
         <v>29</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
         <v>19</v>
@@ -4535,10 +4543,10 @@
         <v>22</v>
       </c>
       <c r="G63" t="s">
-        <v>32</v>
-      </c>
-      <c r="H63">
-        <v>11</v>
+        <v>43</v>
+      </c>
+      <c r="H63" s="2">
+        <v>10</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>118</v>
@@ -4550,19 +4558,19 @@
         <v>26</v>
       </c>
       <c r="L63" s="1">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="M63">
-        <v>618930</v>
+        <v>617914</v>
       </c>
       <c r="N63" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O63">
-        <v>14.6</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="P63" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q63" t="s">
         <v>28</v>
@@ -4573,10 +4581,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
         <v>19</v>
@@ -4585,16 +4593,16 @@
         <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="F64" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G64" t="s">
-        <v>91</v>
-      </c>
-      <c r="H64">
-        <v>14</v>
+        <v>43</v>
+      </c>
+      <c r="H64" s="2">
+        <v>11</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>118</v>
@@ -4606,22 +4614,22 @@
         <v>26</v>
       </c>
       <c r="L64" s="1">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="M64">
-        <v>619855</v>
+        <v>615347</v>
       </c>
       <c r="N64" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O64">
-        <v>4.68</v>
+        <v>2.76</v>
       </c>
       <c r="P64" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q64" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="R64">
         <v>1</v>
@@ -4632,7 +4640,7 @@
         <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
         <v>19</v>
@@ -4649,8 +4657,8 @@
       <c r="G65" t="s">
         <v>32</v>
       </c>
-      <c r="H65">
-        <v>14</v>
+      <c r="H65" s="2">
+        <v>11</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>118</v>
@@ -4662,16 +4670,16 @@
         <v>26</v>
       </c>
       <c r="L65" s="1">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="M65">
-        <v>619980</v>
+        <v>618930</v>
       </c>
       <c r="N65" t="s">
         <v>59</v>
       </c>
       <c r="O65">
-        <v>8.5399999999999991</v>
+        <v>14.6</v>
       </c>
       <c r="P65" t="s">
         <v>28</v>
@@ -4685,10 +4693,10 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C66" t="s">
         <v>19</v>
@@ -4697,16 +4705,16 @@
         <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G66" t="s">
-        <v>23</v>
-      </c>
-      <c r="H66">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="H66" s="2">
+        <v>14</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>118</v>
@@ -4718,19 +4726,19 @@
         <v>26</v>
       </c>
       <c r="L66" s="1">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="M66">
-        <v>617205</v>
+        <v>619855</v>
       </c>
       <c r="N66" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O66">
-        <v>14.62</v>
+        <v>4.68</v>
       </c>
       <c r="P66" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q66" t="s">
         <v>28</v>
@@ -4741,10 +4749,10 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C67" t="s">
         <v>19</v>
@@ -4753,16 +4761,16 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F67" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G67" t="s">
-        <v>91</v>
-      </c>
-      <c r="H67">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="H67" s="2">
+        <v>14</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>118</v>
@@ -4774,19 +4782,19 @@
         <v>26</v>
       </c>
       <c r="L67" s="1">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="M67">
-        <v>620157</v>
+        <v>619980</v>
       </c>
       <c r="N67" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O67">
-        <v>6.46</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="P67" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q67" t="s">
         <v>28</v>
@@ -4797,27 +4805,27 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="C68" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>31</v>
+        <v>201</v>
       </c>
       <c r="F68" t="s">
         <v>22</v>
       </c>
       <c r="G68" t="s">
-        <v>32</v>
-      </c>
-      <c r="H68">
+        <v>199</v>
+      </c>
+      <c r="H68" s="2">
         <v>15</v>
       </c>
       <c r="I68" s="1" t="s">
@@ -4833,19 +4841,19 @@
         <v>46280</v>
       </c>
       <c r="M68">
-        <v>620523</v>
+        <v>612223</v>
       </c>
       <c r="N68" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O68">
-        <v>8.57</v>
+        <v>104.04</v>
       </c>
       <c r="P68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q68" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="R68">
         <v>1</v>
@@ -4853,28 +4861,28 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="B69" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="C69" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D69" t="s">
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>146</v>
+        <v>201</v>
       </c>
       <c r="F69" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G69" t="s">
-        <v>91</v>
-      </c>
-      <c r="H69">
-        <v>16</v>
+        <v>199</v>
+      </c>
+      <c r="H69" s="2">
+        <v>15</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>118</v>
@@ -4886,16 +4894,16 @@
         <v>26</v>
       </c>
       <c r="L69" s="1">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="M69">
-        <v>620676</v>
+        <v>612623</v>
       </c>
       <c r="N69" t="s">
         <v>131</v>
       </c>
       <c r="O69">
-        <v>8.9600000000000009</v>
+        <v>0</v>
       </c>
       <c r="P69" t="s">
         <v>55</v>
@@ -4912,7 +4920,7 @@
         <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s">
         <v>19</v>
@@ -4927,10 +4935,10 @@
         <v>22</v>
       </c>
       <c r="G70" t="s">
-        <v>43</v>
-      </c>
-      <c r="H70">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="H70" s="2">
+        <v>15</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>118</v>
@@ -4942,16 +4950,16 @@
         <v>26</v>
       </c>
       <c r="L70" s="1">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="M70">
-        <v>620938</v>
+        <v>617205</v>
       </c>
       <c r="N70" t="s">
         <v>59</v>
       </c>
       <c r="O70">
-        <v>11.75</v>
+        <v>14.62</v>
       </c>
       <c r="P70" t="s">
         <v>28</v>
@@ -4968,7 +4976,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s">
         <v>19</v>
@@ -4983,10 +4991,10 @@
         <v>90</v>
       </c>
       <c r="G71" t="s">
-        <v>126</v>
-      </c>
-      <c r="H71">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="H71" s="2">
+        <v>15</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>118</v>
@@ -4998,16 +5006,16 @@
         <v>26</v>
       </c>
       <c r="L71" s="1">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="M71">
-        <v>621205</v>
+        <v>620157</v>
       </c>
       <c r="N71" t="s">
         <v>131</v>
       </c>
       <c r="O71">
-        <v>5.95</v>
+        <v>6.46</v>
       </c>
       <c r="P71" t="s">
         <v>55</v>
@@ -5024,7 +5032,7 @@
         <v>29</v>
       </c>
       <c r="B72" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
         <v>19</v>
@@ -5041,8 +5049,8 @@
       <c r="G72" t="s">
         <v>32</v>
       </c>
-      <c r="H72">
-        <v>17</v>
+      <c r="H72" s="2">
+        <v>15</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>118</v>
@@ -5054,22 +5062,22 @@
         <v>26</v>
       </c>
       <c r="L72" s="1">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="M72">
-        <v>621574</v>
+        <v>620523</v>
       </c>
       <c r="N72" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O72">
-        <v>3.78</v>
+        <v>8.57</v>
       </c>
       <c r="P72" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="Q72" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="R72">
         <v>1</v>
@@ -5077,10 +5085,10 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
         <v>19</v>
@@ -5089,16 +5097,16 @@
         <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="F73" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G73" t="s">
-        <v>32</v>
-      </c>
-      <c r="H73">
-        <v>17</v>
+        <v>91</v>
+      </c>
+      <c r="H73" s="2">
+        <v>16</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>118</v>
@@ -5110,19 +5118,19 @@
         <v>26</v>
       </c>
       <c r="L73" s="1">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="M73">
-        <v>621242</v>
+        <v>620676</v>
       </c>
       <c r="N73" t="s">
         <v>131</v>
       </c>
       <c r="O73">
-        <v>5.46</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="P73" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q73" t="s">
         <v>28</v>
@@ -5133,10 +5141,10 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
         <v>19</v>
@@ -5145,16 +5153,16 @@
         <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F74" t="s">
         <v>22</v>
       </c>
       <c r="G74" t="s">
-        <v>32</v>
-      </c>
-      <c r="H74">
-        <v>18</v>
+        <v>43</v>
+      </c>
+      <c r="H74" s="2">
+        <v>17</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>118</v>
@@ -5166,19 +5174,19 @@
         <v>26</v>
       </c>
       <c r="L74" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="M74">
-        <v>622716</v>
+        <v>620938</v>
       </c>
       <c r="N74" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O74">
-        <v>5.33</v>
+        <v>11.75</v>
       </c>
       <c r="P74" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q74" t="s">
         <v>28</v>
@@ -5192,7 +5200,7 @@
         <v>70</v>
       </c>
       <c r="B75" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C75" t="s">
         <v>19</v>
@@ -5201,16 +5209,16 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="F75" t="s">
         <v>90</v>
       </c>
       <c r="G75" t="s">
-        <v>91</v>
-      </c>
-      <c r="H75">
-        <v>22</v>
+        <v>126</v>
+      </c>
+      <c r="H75" s="2">
+        <v>17</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>118</v>
@@ -5222,19 +5230,19 @@
         <v>26</v>
       </c>
       <c r="L75" s="1">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="M75">
-        <v>626221</v>
+        <v>621205</v>
       </c>
       <c r="N75" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O75">
-        <v>9.11</v>
+        <v>5.95</v>
       </c>
       <c r="P75" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Q75" t="s">
         <v>28</v>
@@ -5245,10 +5253,10 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B76" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s">
         <v>19</v>
@@ -5257,16 +5265,16 @@
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F76" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G76" t="s">
-        <v>91</v>
-      </c>
-      <c r="H76">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="H76" s="2">
+        <v>17</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>118</v>
@@ -5278,19 +5286,19 @@
         <v>26</v>
       </c>
       <c r="L76" s="1">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="M76">
-        <v>624470</v>
+        <v>621574</v>
       </c>
       <c r="N76" t="s">
         <v>131</v>
       </c>
       <c r="O76">
-        <v>8.34</v>
+        <v>3.78</v>
       </c>
       <c r="P76" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="Q76" t="s">
         <v>28</v>
@@ -5304,7 +5312,7 @@
         <v>29</v>
       </c>
       <c r="B77" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C77" t="s">
         <v>19</v>
@@ -5321,8 +5329,8 @@
       <c r="G77" t="s">
         <v>32</v>
       </c>
-      <c r="H77">
-        <v>22</v>
+      <c r="H77" s="2">
+        <v>17</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>118</v>
@@ -5334,16 +5342,16 @@
         <v>26</v>
       </c>
       <c r="L77" s="1">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="M77">
-        <v>624178</v>
+        <v>621242</v>
       </c>
       <c r="N77" t="s">
         <v>131</v>
       </c>
       <c r="O77">
-        <v>12.79</v>
+        <v>5.46</v>
       </c>
       <c r="P77" t="s">
         <v>35</v>
@@ -5360,7 +5368,7 @@
         <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C78" t="s">
         <v>19</v>
@@ -5377,8 +5385,8 @@
       <c r="G78" t="s">
         <v>32</v>
       </c>
-      <c r="H78">
-        <v>22</v>
+      <c r="H78" s="2">
+        <v>18</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>118</v>
@@ -5390,16 +5398,16 @@
         <v>26</v>
       </c>
       <c r="L78" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="M78">
-        <v>624196</v>
+        <v>622716</v>
       </c>
       <c r="N78" t="s">
         <v>131</v>
       </c>
       <c r="O78">
-        <v>3.73</v>
+        <v>5.33</v>
       </c>
       <c r="P78" t="s">
         <v>35</v>
@@ -5413,28 +5421,28 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="B79" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="C79" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="D79" t="s">
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="F79" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G79" t="s">
-        <v>91</v>
-      </c>
-      <c r="H79">
-        <v>23</v>
+        <v>43</v>
+      </c>
+      <c r="H79" s="2">
+        <v>22</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>118</v>
@@ -5446,19 +5454,19 @@
         <v>26</v>
       </c>
       <c r="L79" s="1">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="M79">
-        <v>624882</v>
+        <v>624356</v>
       </c>
       <c r="N79" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O79">
-        <v>22.65</v>
+        <v>38.840000000000003</v>
       </c>
       <c r="P79" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q79" t="s">
         <v>28</v>
@@ -5469,28 +5477,28 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
       <c r="B80" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="C80" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="D80" t="s">
         <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="F80" t="s">
         <v>22</v>
       </c>
       <c r="G80" t="s">
-        <v>23</v>
-      </c>
-      <c r="H80">
-        <v>24</v>
+        <v>196</v>
+      </c>
+      <c r="H80" s="2">
+        <v>22</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>118</v>
@@ -5502,19 +5510,19 @@
         <v>26</v>
       </c>
       <c r="L80" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="M80">
-        <v>636005</v>
+        <v>622609</v>
       </c>
       <c r="N80" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O80">
-        <v>29.19</v>
+        <v>118.5</v>
       </c>
       <c r="P80" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q80" t="s">
         <v>28</v>
@@ -5525,10 +5533,10 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C81" t="s">
         <v>19</v>
@@ -5537,16 +5545,16 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="F81" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G81" t="s">
-        <v>32</v>
-      </c>
-      <c r="H81">
-        <v>24</v>
+        <v>91</v>
+      </c>
+      <c r="H81" s="2">
+        <v>22</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>118</v>
@@ -5558,19 +5566,19 @@
         <v>26</v>
       </c>
       <c r="L81" s="1">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="M81">
-        <v>625177</v>
+        <v>626221</v>
       </c>
       <c r="N81" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>9.11</v>
       </c>
       <c r="P81" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q81" t="s">
         <v>28</v>
@@ -5584,7 +5592,7 @@
         <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C82" t="s">
         <v>19</v>
@@ -5599,10 +5607,10 @@
         <v>90</v>
       </c>
       <c r="G82" t="s">
-        <v>167</v>
-      </c>
-      <c r="H82">
-        <v>25</v>
+        <v>91</v>
+      </c>
+      <c r="H82" s="2">
+        <v>22</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>118</v>
@@ -5614,19 +5622,19 @@
         <v>26</v>
       </c>
       <c r="L82" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="M82">
-        <v>626032</v>
+        <v>624470</v>
       </c>
       <c r="N82" t="s">
         <v>131</v>
       </c>
       <c r="O82">
-        <v>4.5199999999999996</v>
+        <v>8.34</v>
       </c>
       <c r="P82" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q82" t="s">
         <v>28</v>
@@ -5640,7 +5648,7 @@
         <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C83" t="s">
         <v>19</v>
@@ -5655,10 +5663,10 @@
         <v>22</v>
       </c>
       <c r="G83" t="s">
-        <v>43</v>
-      </c>
-      <c r="H83">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="H83" s="2">
+        <v>22</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>118</v>
@@ -5670,19 +5678,19 @@
         <v>26</v>
       </c>
       <c r="L83" s="1">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="M83">
-        <v>626059</v>
+        <v>624178</v>
       </c>
       <c r="N83" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O83">
-        <v>14.46</v>
+        <v>12.79</v>
       </c>
       <c r="P83" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q83" t="s">
         <v>28</v>
@@ -5696,7 +5704,7 @@
         <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C84" t="s">
         <v>19</v>
@@ -5713,8 +5721,8 @@
       <c r="G84" t="s">
         <v>32</v>
       </c>
-      <c r="H84">
-        <v>28</v>
+      <c r="H84" s="2">
+        <v>22</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>118</v>
@@ -5726,16 +5734,16 @@
         <v>26</v>
       </c>
       <c r="L84" s="1">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="M84">
-        <v>626925</v>
+        <v>624196</v>
       </c>
       <c r="N84" t="s">
         <v>131</v>
       </c>
       <c r="O84">
-        <v>17.84</v>
+        <v>3.73</v>
       </c>
       <c r="P84" t="s">
         <v>35</v>
@@ -5749,10 +5757,10 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C85" t="s">
         <v>19</v>
@@ -5761,16 +5769,16 @@
         <v>20</v>
       </c>
       <c r="E85" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
       <c r="F85" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G85" t="s">
-        <v>43</v>
-      </c>
-      <c r="H85">
-        <v>28</v>
+        <v>91</v>
+      </c>
+      <c r="H85" s="2">
+        <v>23</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>118</v>
@@ -5782,16 +5790,16 @@
         <v>26</v>
       </c>
       <c r="L85" s="1">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="M85">
-        <v>626887</v>
+        <v>624882</v>
       </c>
       <c r="N85" t="s">
         <v>131</v>
       </c>
       <c r="O85">
-        <v>16.39</v>
+        <v>22.65</v>
       </c>
       <c r="P85" t="s">
         <v>35</v>
@@ -5805,28 +5813,28 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="C86" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="F86" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G86" t="s">
-        <v>104</v>
-      </c>
-      <c r="H86">
-        <v>29</v>
+        <v>196</v>
+      </c>
+      <c r="H86" s="2">
+        <v>24</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>118</v>
@@ -5838,19 +5846,19 @@
         <v>26</v>
       </c>
       <c r="L86" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="M86">
-        <v>627609</v>
+        <v>623818</v>
       </c>
       <c r="N86" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O86">
-        <v>11.61</v>
+        <v>42.8</v>
       </c>
       <c r="P86" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q86" t="s">
         <v>28</v>
@@ -5861,10 +5869,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C87" t="s">
         <v>19</v>
@@ -5873,16 +5881,16 @@
         <v>20</v>
       </c>
       <c r="E87" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G87" t="s">
-        <v>104</v>
-      </c>
-      <c r="H87">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="H87" s="2">
+        <v>24</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>118</v>
@@ -5894,19 +5902,19 @@
         <v>26</v>
       </c>
       <c r="L87" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="M87">
-        <v>627665</v>
+        <v>636005</v>
       </c>
       <c r="N87" t="s">
         <v>131</v>
       </c>
       <c r="O87">
-        <v>7.5</v>
+        <v>29.19</v>
       </c>
       <c r="P87" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q87" t="s">
         <v>28</v>
@@ -5917,10 +5925,10 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B88" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C88" t="s">
         <v>19</v>
@@ -5929,16 +5937,16 @@
         <v>20</v>
       </c>
       <c r="E88" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F88" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G88" t="s">
-        <v>104</v>
-      </c>
-      <c r="H88">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="H88" s="2">
+        <v>24</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>118</v>
@@ -5950,16 +5958,16 @@
         <v>26</v>
       </c>
       <c r="L88" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="M88">
-        <v>627639</v>
+        <v>625177</v>
       </c>
       <c r="N88" t="s">
         <v>131</v>
       </c>
       <c r="O88">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P88" t="s">
         <v>35</v>
@@ -5973,10 +5981,10 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C89" t="s">
         <v>19</v>
@@ -5985,16 +5993,16 @@
         <v>20</v>
       </c>
       <c r="E89" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="F89" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G89" t="s">
-        <v>32</v>
-      </c>
-      <c r="H89">
-        <v>29</v>
+        <v>167</v>
+      </c>
+      <c r="H89" s="2">
+        <v>25</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>118</v>
@@ -6006,19 +6014,19 @@
         <v>26</v>
       </c>
       <c r="L89" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
       <c r="M89">
-        <v>634381</v>
+        <v>626032</v>
       </c>
       <c r="N89" t="s">
         <v>131</v>
       </c>
       <c r="O89">
-        <v>16.3</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="P89" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q89" t="s">
         <v>28</v>
@@ -6032,7 +6040,7 @@
         <v>29</v>
       </c>
       <c r="B90" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C90" t="s">
         <v>19</v>
@@ -6047,10 +6055,10 @@
         <v>22</v>
       </c>
       <c r="G90" t="s">
-        <v>32</v>
-      </c>
-      <c r="H90">
-        <v>29</v>
+        <v>43</v>
+      </c>
+      <c r="H90" s="2">
+        <v>25</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>118</v>
@@ -6062,19 +6070,19 @@
         <v>26</v>
       </c>
       <c r="L90" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
       <c r="M90">
-        <v>627332</v>
+        <v>626059</v>
       </c>
       <c r="N90" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O90">
-        <v>2.42</v>
+        <v>14.46</v>
       </c>
       <c r="P90" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q90" t="s">
         <v>28</v>
@@ -6088,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C91" t="s">
         <v>19</v>
@@ -6105,8 +6113,8 @@
       <c r="G91" t="s">
         <v>32</v>
       </c>
-      <c r="H91">
-        <v>29</v>
+      <c r="H91" s="2">
+        <v>28</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>118</v>
@@ -6118,16 +6126,16 @@
         <v>26</v>
       </c>
       <c r="L91" s="1">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="M91">
-        <v>627521</v>
+        <v>626925</v>
       </c>
       <c r="N91" t="s">
         <v>131</v>
       </c>
       <c r="O91">
-        <v>9.1300000000000008</v>
+        <v>17.84</v>
       </c>
       <c r="P91" t="s">
         <v>35</v>
@@ -6141,10 +6149,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B92" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C92" t="s">
         <v>19</v>
@@ -6153,16 +6161,16 @@
         <v>20</v>
       </c>
       <c r="E92" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F92" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G92" t="s">
-        <v>104</v>
-      </c>
-      <c r="H92">
-        <v>30</v>
+        <v>43</v>
+      </c>
+      <c r="H92" s="2">
+        <v>28</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>118</v>
@@ -6174,22 +6182,22 @@
         <v>26</v>
       </c>
       <c r="L92" s="1">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="M92">
-        <v>628148</v>
+        <v>626887</v>
       </c>
       <c r="N92" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O92">
-        <v>3.88</v>
+        <v>16.39</v>
       </c>
       <c r="P92" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q92" t="s">
-        <v>185</v>
+        <v>28</v>
       </c>
       <c r="R92">
         <v>1</v>
@@ -6197,28 +6205,28 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="B93" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="C93" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="D93" t="s">
         <v>20</v>
       </c>
       <c r="E93" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="F93" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G93" t="s">
-        <v>91</v>
-      </c>
-      <c r="H93">
-        <v>30</v>
+        <v>196</v>
+      </c>
+      <c r="H93" s="2">
+        <v>29</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>118</v>
@@ -6230,19 +6238,19 @@
         <v>26</v>
       </c>
       <c r="L93" s="1">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="M93">
-        <v>627870</v>
+        <v>625426</v>
       </c>
       <c r="N93" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O93">
-        <v>1.42</v>
+        <v>38.840000000000003</v>
       </c>
       <c r="P93" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q93" t="s">
         <v>28</v>
@@ -6253,28 +6261,28 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="D94" t="s">
         <v>20</v>
       </c>
       <c r="E94" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="F94" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G94" t="s">
-        <v>91</v>
-      </c>
-      <c r="H94">
-        <v>30</v>
+        <v>196</v>
+      </c>
+      <c r="H94" s="2">
+        <v>29</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>118</v>
@@ -6286,22 +6294,22 @@
         <v>26</v>
       </c>
       <c r="L94" s="1">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="M94">
-        <v>628106</v>
+        <v>625413</v>
       </c>
       <c r="N94" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="O94">
-        <v>5.22</v>
+        <v>38.840000000000003</v>
       </c>
       <c r="P94" t="s">
         <v>28</v>
       </c>
       <c r="Q94" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="R94">
         <v>1</v>
@@ -6312,10 +6320,10 @@
         <v>70</v>
       </c>
       <c r="B95" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C95" t="s">
-        <v>19</v>
+        <v>172</v>
       </c>
       <c r="D95" t="s">
         <v>20</v>
@@ -6329,8 +6337,8 @@
       <c r="G95" t="s">
         <v>104</v>
       </c>
-      <c r="H95">
-        <v>30</v>
+      <c r="H95" s="2">
+        <v>29</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>118</v>
@@ -6342,22 +6350,22 @@
         <v>26</v>
       </c>
       <c r="L95" s="1">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="M95">
-        <v>628137</v>
+        <v>627609</v>
       </c>
       <c r="N95" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O95">
-        <v>7.93</v>
+        <v>11.61</v>
       </c>
       <c r="P95" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q95" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="R95">
         <v>1</v>
@@ -6368,7 +6376,7 @@
         <v>70</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C96" t="s">
         <v>19</v>
@@ -6383,13 +6391,13 @@
         <v>90</v>
       </c>
       <c r="G96" t="s">
-        <v>91</v>
-      </c>
-      <c r="H96">
-        <v>7</v>
+        <v>104</v>
+      </c>
+      <c r="H96" s="2">
+        <v>29</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>25</v>
@@ -6398,16 +6406,16 @@
         <v>26</v>
       </c>
       <c r="L96" s="1">
-        <v>46302</v>
+        <v>46294</v>
       </c>
       <c r="M96">
-        <v>631043</v>
+        <v>627665</v>
       </c>
       <c r="N96" t="s">
         <v>131</v>
       </c>
       <c r="O96">
-        <v>14.23</v>
+        <v>7.5</v>
       </c>
       <c r="P96" t="s">
         <v>35</v>
@@ -6424,7 +6432,7 @@
         <v>70</v>
       </c>
       <c r="B97" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C97" t="s">
         <v>19</v>
@@ -6439,13 +6447,13 @@
         <v>90</v>
       </c>
       <c r="G97" t="s">
-        <v>91</v>
-      </c>
-      <c r="H97">
-        <v>9</v>
+        <v>104</v>
+      </c>
+      <c r="H97" s="2">
+        <v>29</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>25</v>
@@ -6454,19 +6462,19 @@
         <v>26</v>
       </c>
       <c r="L97" s="1">
-        <v>46304</v>
+        <v>46294</v>
       </c>
       <c r="M97">
-        <v>631720</v>
+        <v>627639</v>
       </c>
       <c r="N97" t="s">
         <v>131</v>
       </c>
       <c r="O97">
-        <v>2.34</v>
+        <v>4.3</v>
       </c>
       <c r="P97" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q97" t="s">
         <v>28</v>
@@ -6477,10 +6485,10 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C98" t="s">
         <v>19</v>
@@ -6489,19 +6497,19 @@
         <v>20</v>
       </c>
       <c r="E98" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F98" t="s">
         <v>22</v>
       </c>
       <c r="G98" t="s">
-        <v>23</v>
-      </c>
-      <c r="H98">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="H98" s="2">
+        <v>29</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>25</v>
@@ -6510,16 +6518,16 @@
         <v>26</v>
       </c>
       <c r="L98" s="1">
-        <v>46308</v>
+        <v>46294</v>
       </c>
       <c r="M98">
-        <v>632724</v>
+        <v>634381</v>
       </c>
       <c r="N98" t="s">
         <v>131</v>
       </c>
       <c r="O98">
-        <v>8.07</v>
+        <v>16.3</v>
       </c>
       <c r="P98" t="s">
         <v>35</v>
@@ -6527,16 +6535,16 @@
       <c r="Q98" t="s">
         <v>28</v>
       </c>
-      <c r="R98" t="e">
-        <v>#N/A</v>
+      <c r="R98">
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B99" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C99" t="s">
         <v>19</v>
@@ -6545,19 +6553,19 @@
         <v>20</v>
       </c>
       <c r="E99" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F99" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G99" t="s">
-        <v>104</v>
-      </c>
-      <c r="H99">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="H99" s="2">
+        <v>29</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>25</v>
@@ -6566,19 +6574,19 @@
         <v>26</v>
       </c>
       <c r="L99" s="1">
-        <v>46309</v>
+        <v>46294</v>
       </c>
       <c r="M99">
-        <v>634211</v>
+        <v>627332</v>
       </c>
       <c r="N99" t="s">
         <v>131</v>
       </c>
       <c r="O99">
-        <v>3.01</v>
+        <v>2.42</v>
       </c>
       <c r="P99" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q99" t="s">
         <v>28</v>
@@ -6589,10 +6597,10 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="B100" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C100" t="s">
         <v>19</v>
@@ -6601,19 +6609,19 @@
         <v>20</v>
       </c>
       <c r="E100" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F100" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G100" t="s">
-        <v>190</v>
-      </c>
-      <c r="H100">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="H100" s="2">
+        <v>29</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>25</v>
@@ -6622,51 +6630,51 @@
         <v>26</v>
       </c>
       <c r="L100" s="1">
-        <v>46309</v>
+        <v>46294</v>
       </c>
       <c r="M100">
-        <v>634159</v>
+        <v>627521</v>
       </c>
       <c r="N100" t="s">
         <v>131</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="P100" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q100" t="s">
         <v>28</v>
       </c>
-      <c r="R100" t="e">
-        <v>#N/A</v>
+      <c r="R100">
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="B101" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C101" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="D101" t="s">
         <v>20</v>
       </c>
       <c r="E101" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
       <c r="F101" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G101" t="s">
-        <v>196</v>
-      </c>
-      <c r="H101">
-        <v>1</v>
+        <v>104</v>
+      </c>
+      <c r="H101" s="2">
+        <v>30</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>118</v>
@@ -6678,22 +6686,22 @@
         <v>26</v>
       </c>
       <c r="L101" s="1">
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="M101">
-        <v>607987</v>
+        <v>628148</v>
       </c>
       <c r="N101" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P101" t="s">
         <v>28</v>
       </c>
       <c r="Q101" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="R101">
         <v>1</v>
@@ -6701,28 +6709,28 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="B102" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="C102" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D102" t="s">
         <v>20</v>
       </c>
       <c r="E102" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="F102" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G102" t="s">
-        <v>199</v>
-      </c>
-      <c r="H102">
-        <v>8</v>
+        <v>91</v>
+      </c>
+      <c r="H102" s="2">
+        <v>30</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>118</v>
@@ -6734,51 +6742,51 @@
         <v>26</v>
       </c>
       <c r="L102" s="1">
-        <v>46273</v>
+        <v>46295</v>
       </c>
       <c r="M102">
-        <v>612268</v>
+        <v>627870</v>
       </c>
       <c r="N102" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O102">
-        <v>35.65</v>
+        <v>1.42</v>
       </c>
       <c r="P102" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q102" t="s">
-        <v>191</v>
-      </c>
-      <c r="R102" t="e">
-        <v>#N/A</v>
+        <v>28</v>
+      </c>
+      <c r="R102">
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="B103" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C103" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D103" t="s">
         <v>20</v>
       </c>
       <c r="E103" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="F103" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G103" t="s">
-        <v>199</v>
-      </c>
-      <c r="H103">
-        <v>15</v>
+        <v>91</v>
+      </c>
+      <c r="H103" s="2">
+        <v>30</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>118</v>
@@ -6790,22 +6798,22 @@
         <v>26</v>
       </c>
       <c r="L103" s="1">
-        <v>46280</v>
+        <v>46295</v>
       </c>
       <c r="M103">
-        <v>612223</v>
+        <v>628106</v>
       </c>
       <c r="N103" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O103">
-        <v>104.04</v>
+        <v>5.22</v>
       </c>
       <c r="P103" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q103" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="R103">
         <v>1</v>
@@ -6813,28 +6821,28 @@
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="B104" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="C104" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D104" t="s">
         <v>20</v>
       </c>
       <c r="E104" t="s">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="F104" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G104" t="s">
-        <v>199</v>
-      </c>
-      <c r="H104">
-        <v>15</v>
+        <v>104</v>
+      </c>
+      <c r="H104" s="2">
+        <v>30</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>118</v>
@@ -6846,22 +6854,22 @@
         <v>26</v>
       </c>
       <c r="L104" s="1">
-        <v>46280</v>
+        <v>46295</v>
       </c>
       <c r="M104">
-        <v>612623</v>
+        <v>628137</v>
       </c>
       <c r="N104" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>7.93</v>
       </c>
       <c r="P104" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q104" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="R104">
         <v>1</v>
@@ -6872,28 +6880,28 @@
         <v>192</v>
       </c>
       <c r="B105" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C105" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="D105" t="s">
         <v>20</v>
       </c>
       <c r="E105" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F105" t="s">
         <v>22</v>
       </c>
       <c r="G105" t="s">
-        <v>43</v>
-      </c>
-      <c r="H105">
-        <v>22</v>
+        <v>196</v>
+      </c>
+      <c r="H105" s="2">
+        <v>1</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>25</v>
@@ -6902,25 +6910,25 @@
         <v>26</v>
       </c>
       <c r="L105" s="1">
-        <v>46287</v>
+        <v>46296</v>
       </c>
       <c r="M105">
-        <v>624356</v>
+        <v>625286</v>
       </c>
       <c r="N105" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O105">
-        <v>38.840000000000003</v>
+        <v>78.47</v>
       </c>
       <c r="P105" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q105" t="s">
         <v>28</v>
       </c>
-      <c r="R105">
-        <v>1</v>
+      <c r="R105" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
@@ -6928,7 +6936,7 @@
         <v>192</v>
       </c>
       <c r="B106" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C106" t="s">
         <v>194</v>
@@ -6937,7 +6945,7 @@
         <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F106" t="s">
         <v>22</v>
@@ -6945,11 +6953,11 @@
       <c r="G106" t="s">
         <v>196</v>
       </c>
-      <c r="H106">
-        <v>22</v>
+      <c r="H106" s="2">
+        <v>1</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>25</v>
@@ -6958,19 +6966,19 @@
         <v>26</v>
       </c>
       <c r="L106" s="1">
-        <v>46287</v>
+        <v>46296</v>
       </c>
       <c r="M106">
-        <v>622609</v>
+        <v>628039</v>
       </c>
       <c r="N106" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O106">
-        <v>118.5</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="P106" t="s">
-        <v>207</v>
+        <v>28</v>
       </c>
       <c r="Q106" t="s">
         <v>28</v>
@@ -6984,28 +6992,28 @@
         <v>192</v>
       </c>
       <c r="B107" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C107" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="D107" t="s">
         <v>20</v>
       </c>
       <c r="E107" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F107" t="s">
         <v>22</v>
       </c>
       <c r="G107" t="s">
-        <v>196</v>
-      </c>
-      <c r="H107">
-        <v>24</v>
+        <v>199</v>
+      </c>
+      <c r="H107" s="2">
+        <v>1</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>25</v>
@@ -7014,19 +7022,19 @@
         <v>26</v>
       </c>
       <c r="L107" s="1">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="M107">
-        <v>623818</v>
+        <v>612265</v>
       </c>
       <c r="N107" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O107">
-        <v>42.8</v>
+        <v>38.659999999999997</v>
       </c>
       <c r="P107" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q107" t="s">
         <v>28</v>
@@ -7040,7 +7048,7 @@
         <v>192</v>
       </c>
       <c r="B108" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C108" t="s">
         <v>194</v>
@@ -7057,11 +7065,11 @@
       <c r="G108" t="s">
         <v>196</v>
       </c>
-      <c r="H108">
-        <v>29</v>
+      <c r="H108" s="2">
+        <v>1</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>25</v>
@@ -7070,16 +7078,16 @@
         <v>26</v>
       </c>
       <c r="L108" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="M108">
-        <v>625426</v>
+        <v>626295</v>
       </c>
       <c r="N108" t="s">
         <v>59</v>
       </c>
       <c r="O108">
-        <v>38.840000000000003</v>
+        <v>15.06</v>
       </c>
       <c r="P108" t="s">
         <v>28</v>
@@ -7096,7 +7104,7 @@
         <v>192</v>
       </c>
       <c r="B109" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C109" t="s">
         <v>194</v>
@@ -7105,7 +7113,7 @@
         <v>20</v>
       </c>
       <c r="E109" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F109" t="s">
         <v>22</v>
@@ -7113,11 +7121,11 @@
       <c r="G109" t="s">
         <v>196</v>
       </c>
-      <c r="H109">
-        <v>29</v>
+      <c r="H109" s="2">
+        <v>1</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>25</v>
@@ -7126,25 +7134,25 @@
         <v>26</v>
       </c>
       <c r="L109" s="1">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="M109">
-        <v>625413</v>
+        <v>627041</v>
       </c>
       <c r="N109" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O109">
-        <v>38.840000000000003</v>
+        <v>0</v>
       </c>
       <c r="P109" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Q109" t="s">
         <v>28</v>
       </c>
-      <c r="R109">
-        <v>1</v>
+      <c r="R109" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
@@ -7152,16 +7160,16 @@
         <v>192</v>
       </c>
       <c r="B110" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
       <c r="D110" t="s">
         <v>20</v>
       </c>
       <c r="E110" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F110" t="s">
         <v>22</v>
@@ -7169,8 +7177,8 @@
       <c r="G110" t="s">
         <v>196</v>
       </c>
-      <c r="H110">
-        <v>1</v>
+      <c r="H110" s="2">
+        <v>6</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>183</v>
@@ -7182,16 +7190,16 @@
         <v>26</v>
       </c>
       <c r="L110" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="M110">
-        <v>625286</v>
+        <v>630590</v>
       </c>
       <c r="N110" t="s">
         <v>131</v>
       </c>
       <c r="O110">
-        <v>78.47</v>
+        <v>118.1</v>
       </c>
       <c r="P110" t="s">
         <v>35</v>
@@ -7199,16 +7207,16 @@
       <c r="Q110" t="s">
         <v>28</v>
       </c>
-      <c r="R110" t="e">
-        <v>#N/A</v>
+      <c r="R110">
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="B111" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C111" t="s">
         <v>194</v>
@@ -7217,16 +7225,16 @@
         <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F111" t="s">
         <v>22</v>
       </c>
       <c r="G111" t="s">
-        <v>196</v>
-      </c>
-      <c r="H111">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="H111" s="2">
+        <v>6</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>183</v>
@@ -7238,19 +7246,19 @@
         <v>26</v>
       </c>
       <c r="L111" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="M111">
-        <v>628039</v>
+        <v>630717</v>
       </c>
       <c r="N111" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O111">
-        <v>4.3600000000000003</v>
+        <v>6.36</v>
       </c>
       <c r="P111" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="Q111" t="s">
         <v>28</v>
@@ -7261,28 +7269,28 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="B112" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="C112" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D112" t="s">
         <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="F112" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G112" t="s">
-        <v>199</v>
-      </c>
-      <c r="H112">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="H112" s="2">
+        <v>7</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>183</v>
@@ -7294,16 +7302,16 @@
         <v>26</v>
       </c>
       <c r="L112" s="1">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="M112">
-        <v>612265</v>
+        <v>631043</v>
       </c>
       <c r="N112" t="s">
         <v>131</v>
       </c>
       <c r="O112">
-        <v>38.659999999999997</v>
+        <v>14.23</v>
       </c>
       <c r="P112" t="s">
         <v>35</v>
@@ -7317,10 +7325,10 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="B113" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C113" t="s">
         <v>194</v>
@@ -7329,16 +7337,16 @@
         <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F113" t="s">
         <v>22</v>
       </c>
       <c r="G113" t="s">
-        <v>196</v>
-      </c>
-      <c r="H113">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="H113" s="2">
+        <v>7</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>183</v>
@@ -7350,22 +7358,22 @@
         <v>26</v>
       </c>
       <c r="L113" s="1">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="M113">
-        <v>626295</v>
+        <v>631099</v>
       </c>
       <c r="N113" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="O113">
-        <v>15.06</v>
+        <v>0</v>
       </c>
       <c r="P113" t="s">
         <v>28</v>
       </c>
       <c r="Q113" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="R113">
         <v>1</v>
@@ -7373,10 +7381,10 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="B114" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C114" t="s">
         <v>194</v>
@@ -7385,16 +7393,16 @@
         <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F114" t="s">
         <v>22</v>
       </c>
       <c r="G114" t="s">
-        <v>196</v>
-      </c>
-      <c r="H114">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="H114" s="2">
+        <v>7</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>183</v>
@@ -7406,33 +7414,33 @@
         <v>26</v>
       </c>
       <c r="L114" s="1">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="M114">
-        <v>627041</v>
+        <v>631115</v>
       </c>
       <c r="N114" t="s">
         <v>131</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P114" t="s">
-        <v>55</v>
+        <v>207</v>
       </c>
       <c r="Q114" t="s">
         <v>28</v>
       </c>
-      <c r="R114" t="e">
-        <v>#N/A</v>
+      <c r="R114">
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="B115" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C115" t="s">
         <v>194</v>
@@ -7441,7 +7449,7 @@
         <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="F115" t="s">
         <v>22</v>
@@ -7449,8 +7457,8 @@
       <c r="G115" t="s">
         <v>196</v>
       </c>
-      <c r="H115">
-        <v>6</v>
+      <c r="H115" s="2">
+        <v>8</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>183</v>
@@ -7462,19 +7470,19 @@
         <v>26</v>
       </c>
       <c r="L115" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="M115">
-        <v>630590</v>
+        <v>631302</v>
       </c>
       <c r="N115" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O115">
-        <v>118.1</v>
+        <v>3.34</v>
       </c>
       <c r="P115" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q115" t="s">
         <v>28</v>
@@ -7485,10 +7493,10 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B116" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C116" t="s">
         <v>194</v>
@@ -7497,16 +7505,16 @@
         <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="F116" t="s">
         <v>22</v>
       </c>
       <c r="G116" t="s">
-        <v>43</v>
-      </c>
-      <c r="H116">
-        <v>6</v>
+        <v>196</v>
+      </c>
+      <c r="H116" s="2">
+        <v>8</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>183</v>
@@ -7518,19 +7526,19 @@
         <v>26</v>
       </c>
       <c r="L116" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="M116">
-        <v>630717</v>
+        <v>635101</v>
       </c>
       <c r="N116" t="s">
         <v>131</v>
       </c>
       <c r="O116">
-        <v>6.36</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="P116" t="s">
-        <v>207</v>
+        <v>35</v>
       </c>
       <c r="Q116" t="s">
         <v>28</v>
@@ -7541,28 +7549,28 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="B117" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="C117" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="D117" t="s">
         <v>20</v>
       </c>
       <c r="E117" t="s">
-        <v>219</v>
+        <v>146</v>
       </c>
       <c r="F117" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G117" t="s">
-        <v>43</v>
-      </c>
-      <c r="H117">
-        <v>7</v>
+        <v>91</v>
+      </c>
+      <c r="H117" s="2">
+        <v>9</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>183</v>
@@ -7570,26 +7578,26 @@
       <c r="J117" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K117" s="1">
-        <v>1</v>
+      <c r="K117" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="L117" s="1">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="M117">
-        <v>631099</v>
+        <v>631720</v>
       </c>
       <c r="N117" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="P117" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Q117" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="R117">
         <v>1</v>
@@ -7597,28 +7605,28 @@
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="C118" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="D118" t="s">
         <v>20</v>
       </c>
       <c r="E118" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="F118" t="s">
         <v>22</v>
       </c>
       <c r="G118" t="s">
-        <v>43</v>
-      </c>
-      <c r="H118">
-        <v>7</v>
+        <v>23</v>
+      </c>
+      <c r="H118" s="2">
+        <v>13</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>183</v>
@@ -7630,33 +7638,33 @@
         <v>26</v>
       </c>
       <c r="L118" s="1">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="M118">
-        <v>631115</v>
+        <v>632724</v>
       </c>
       <c r="N118" t="s">
         <v>131</v>
       </c>
       <c r="O118">
-        <v>3.64</v>
+        <v>8.07</v>
       </c>
       <c r="P118" t="s">
-        <v>207</v>
+        <v>35</v>
       </c>
       <c r="Q118" t="s">
         <v>28</v>
       </c>
-      <c r="R118">
-        <v>1</v>
+      <c r="R118" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="B119" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C119" t="s">
         <v>194</v>
@@ -7665,7 +7673,7 @@
         <v>20</v>
       </c>
       <c r="E119" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="F119" t="s">
         <v>22</v>
@@ -7673,8 +7681,8 @@
       <c r="G119" t="s">
         <v>196</v>
       </c>
-      <c r="H119">
-        <v>8</v>
+      <c r="H119" s="2">
+        <v>14</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>183</v>
@@ -7686,19 +7694,19 @@
         <v>26</v>
       </c>
       <c r="L119" s="1">
-        <v>46303</v>
+        <v>46309</v>
       </c>
       <c r="M119">
-        <v>631302</v>
+        <v>630814</v>
       </c>
       <c r="N119" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O119">
-        <v>3.34</v>
+        <v>7.53</v>
       </c>
       <c r="P119" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q119" t="s">
         <v>28</v>
@@ -7709,19 +7717,19 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="B120" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C120" t="s">
-        <v>194</v>
+        <v>49</v>
       </c>
       <c r="D120" t="s">
         <v>20</v>
       </c>
       <c r="E120" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="F120" t="s">
         <v>22</v>
@@ -7729,8 +7737,8 @@
       <c r="G120" t="s">
         <v>196</v>
       </c>
-      <c r="H120">
-        <v>8</v>
+      <c r="H120" s="2">
+        <v>14</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>183</v>
@@ -7742,16 +7750,16 @@
         <v>26</v>
       </c>
       <c r="L120" s="1">
-        <v>46303</v>
+        <v>46309</v>
       </c>
       <c r="M120">
-        <v>635101</v>
+        <v>627337</v>
       </c>
       <c r="N120" t="s">
         <v>131</v>
       </c>
       <c r="O120">
-        <v>4.1900000000000004</v>
+        <v>80.19</v>
       </c>
       <c r="P120" t="s">
         <v>35</v>
@@ -7765,27 +7773,27 @@
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="B121" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
       <c r="C121" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="D121" t="s">
         <v>20</v>
       </c>
       <c r="E121" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
       <c r="F121" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G121" t="s">
-        <v>196</v>
-      </c>
-      <c r="H121">
+        <v>104</v>
+      </c>
+      <c r="H121" s="2">
         <v>14</v>
       </c>
       <c r="I121" s="1" t="s">
@@ -7801,16 +7809,16 @@
         <v>46309</v>
       </c>
       <c r="M121">
-        <v>630814</v>
+        <v>634211</v>
       </c>
       <c r="N121" t="s">
         <v>131</v>
       </c>
       <c r="O121">
-        <v>7.53</v>
+        <v>3.01</v>
       </c>
       <c r="P121" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="Q121" t="s">
         <v>28</v>
@@ -7821,27 +7829,27 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="C122" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D122" t="s">
         <v>20</v>
       </c>
       <c r="E122" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
       <c r="F122" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G122" t="s">
-        <v>196</v>
-      </c>
-      <c r="H122">
+        <v>190</v>
+      </c>
+      <c r="H122" s="2">
         <v>14</v>
       </c>
       <c r="I122" s="1" t="s">
@@ -7857,22 +7865,22 @@
         <v>46309</v>
       </c>
       <c r="M122">
-        <v>627337</v>
+        <v>634159</v>
       </c>
       <c r="N122" t="s">
         <v>131</v>
       </c>
       <c r="O122">
-        <v>80.19</v>
+        <v>3.6</v>
       </c>
       <c r="P122" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="Q122" t="s">
         <v>28</v>
       </c>
-      <c r="R122">
-        <v>1</v>
+      <c r="R122" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
@@ -7892,12 +7900,12 @@
         <v>224</v>
       </c>
       <c r="F123" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
       <c r="G123" t="s">
-        <v>230</v>
-      </c>
-      <c r="H123">
+        <v>196</v>
+      </c>
+      <c r="H123" s="2">
         <v>15</v>
       </c>
       <c r="I123" s="1" t="s">
@@ -7936,7 +7944,7 @@
         <v>192</v>
       </c>
       <c r="B124" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C124" t="s">
         <v>194</v>
@@ -7953,7 +7961,7 @@
       <c r="G124" t="s">
         <v>196</v>
       </c>
-      <c r="H124">
+      <c r="H124" s="2">
         <v>16</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -7983,7 +7991,119 @@
       <c r="Q124" t="s">
         <v>28</v>
       </c>
-      <c r="R124" t="e">
+      <c r="R124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>222</v>
+      </c>
+      <c r="B125" t="s">
+        <v>234</v>
+      </c>
+      <c r="C125" t="s">
+        <v>194</v>
+      </c>
+      <c r="D125" t="s">
+        <v>20</v>
+      </c>
+      <c r="E125" t="s">
+        <v>235</v>
+      </c>
+      <c r="F125" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" t="s">
+        <v>196</v>
+      </c>
+      <c r="H125" s="2">
+        <v>20</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L125" s="1">
+        <v>46315</v>
+      </c>
+      <c r="M125">
+        <v>637473</v>
+      </c>
+      <c r="N125" t="s">
+        <v>131</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>28</v>
+      </c>
+      <c r="R125" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>222</v>
+      </c>
+      <c r="B126" t="s">
+        <v>236</v>
+      </c>
+      <c r="C126" t="s">
+        <v>194</v>
+      </c>
+      <c r="D126" t="s">
+        <v>20</v>
+      </c>
+      <c r="E126" t="s">
+        <v>226</v>
+      </c>
+      <c r="F126" t="s">
+        <v>22</v>
+      </c>
+      <c r="G126" t="s">
+        <v>32</v>
+      </c>
+      <c r="H126" s="2">
+        <v>20</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L126" s="1">
+        <v>46315</v>
+      </c>
+      <c r="M126" t="s">
+        <v>153</v>
+      </c>
+      <c r="N126" t="s">
+        <v>153</v>
+      </c>
+      <c r="O126" t="s">
+        <v>153</v>
+      </c>
+      <c r="P126" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>28</v>
+      </c>
+      <c r="R126" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -9171,7 +9291,7 @@
         <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9185,7 +9305,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9199,7 +9319,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -9213,7 +9333,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -9227,7 +9347,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -9241,7 +9361,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -9255,7 +9375,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -9269,7 +9389,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9283,7 +9403,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -9297,7 +9417,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -9311,7 +9431,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -9325,7 +9445,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9339,7 +9459,7 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9353,7 +9473,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9367,7 +9487,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -9377,14 +9497,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9649,21 +9767,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9688,9 +9805,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38386CE1-E05F-4431-9BAA-375B79C025C4}"/>
+  <xr:revisionPtr revIDLastSave="281" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CD152CE-F191-4E6C-A00B-E03508CF9BAF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="244">
   <si>
     <t>Usuário</t>
   </si>
@@ -596,9 +596,6 @@
     <t>OCT</t>
   </si>
   <si>
-    <t>NEGOCIAÇÃO QUENTE</t>
-  </si>
-  <si>
     <t>SEM RETORNO CLIENTE-TENTATIVAS EXCED SLA</t>
   </si>
   <si>
@@ -753,6 +750,30 @@
   </si>
   <si>
     <t>ADNIR JOSE DA SILVA</t>
+  </si>
+  <si>
+    <t>LINE ESPLANADA LTDA</t>
+  </si>
+  <si>
+    <t>Divinópolis</t>
+  </si>
+  <si>
+    <t>QUALITY RESTAURANTES MATISSE</t>
+  </si>
+  <si>
+    <t>MAREAR KITE CLUB LTDA</t>
+  </si>
+  <si>
+    <t>MIRIA RAQUEL RIBEIRO GOMES</t>
+  </si>
+  <si>
+    <t>LAVANDERIA FAST TROPICAL CLEAN LTDA</t>
+  </si>
+  <si>
+    <t>Nova Serrana</t>
+  </si>
+  <si>
+    <t>AJUSTE DE DOCUMENTAÇÃO</t>
   </si>
 </sst>
 </file>
@@ -1078,11 +1099,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R126"/>
+  <dimension ref="A1:R131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -2501,7 +2521,7 @@
         <v>28</v>
       </c>
       <c r="Q26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R26" t="e">
         <v>#N/A</v>
@@ -2669,7 +2689,7 @@
         <v>28</v>
       </c>
       <c r="Q29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -3853,25 +3873,25 @@
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>191</v>
+      </c>
+      <c r="B51" t="s">
         <v>192</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>193</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" t="s">
         <v>194</v>
-      </c>
-      <c r="D51" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" t="s">
-        <v>195</v>
       </c>
       <c r="F51" t="s">
         <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H51" s="2">
         <v>1</v>
@@ -4245,10 +4265,10 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C58" t="s">
         <v>49</v>
@@ -4257,13 +4277,13 @@
         <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F58" t="s">
         <v>22</v>
       </c>
       <c r="G58" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H58" s="2">
         <v>8</v>
@@ -4293,7 +4313,7 @@
         <v>28</v>
       </c>
       <c r="Q58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="R58" t="e">
         <v>#N/A</v>
@@ -4514,7 +4534,7 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="P62" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q62" t="s">
         <v>28</v>
@@ -4805,10 +4825,10 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B68" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C68" t="s">
         <v>49</v>
@@ -4817,13 +4837,13 @@
         <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F68" t="s">
         <v>22</v>
       </c>
       <c r="G68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H68" s="2">
         <v>15</v>
@@ -4861,10 +4881,10 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B69" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C69" t="s">
         <v>49</v>
@@ -4873,13 +4893,13 @@
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F69" t="s">
         <v>22</v>
       </c>
       <c r="G69" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H69" s="2">
         <v>15</v>
@@ -5298,7 +5318,7 @@
         <v>3.78</v>
       </c>
       <c r="P76" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="Q76" t="s">
         <v>28</v>
@@ -5421,19 +5441,19 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B79" t="s">
+        <v>202</v>
+      </c>
+      <c r="C79" t="s">
+        <v>193</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
         <v>203</v>
-      </c>
-      <c r="C79" t="s">
-        <v>194</v>
-      </c>
-      <c r="D79" t="s">
-        <v>20</v>
-      </c>
-      <c r="E79" t="s">
-        <v>204</v>
       </c>
       <c r="F79" t="s">
         <v>22</v>
@@ -5477,25 +5497,25 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B80" t="s">
+        <v>204</v>
+      </c>
+      <c r="C80" t="s">
+        <v>193</v>
+      </c>
+      <c r="D80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" t="s">
         <v>205</v>
-      </c>
-      <c r="C80" t="s">
-        <v>194</v>
-      </c>
-      <c r="D80" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" t="s">
-        <v>206</v>
       </c>
       <c r="F80" t="s">
         <v>22</v>
       </c>
       <c r="G80" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H80" s="2">
         <v>22</v>
@@ -5813,25 +5833,25 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B86" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C86" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D86" t="s">
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F86" t="s">
         <v>22</v>
       </c>
       <c r="G86" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H86" s="2">
         <v>24</v>
@@ -6205,25 +6225,25 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B93" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D93" t="s">
         <v>20</v>
       </c>
       <c r="E93" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F93" t="s">
         <v>22</v>
       </c>
       <c r="G93" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H93" s="2">
         <v>29</v>
@@ -6261,25 +6281,25 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B94" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C94" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D94" t="s">
         <v>20</v>
       </c>
       <c r="E94" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F94" t="s">
         <v>22</v>
       </c>
       <c r="G94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H94" s="2">
         <v>29</v>
@@ -6701,7 +6721,7 @@
         <v>28</v>
       </c>
       <c r="Q101" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="R101">
         <v>1</v>
@@ -6877,10 +6897,10 @@
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C105" t="s">
         <v>49</v>
@@ -6889,13 +6909,13 @@
         <v>20</v>
       </c>
       <c r="E105" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F105" t="s">
         <v>22</v>
       </c>
       <c r="G105" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H105" s="2">
         <v>1</v>
@@ -6933,25 +6953,25 @@
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C106" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D106" t="s">
         <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F106" t="s">
         <v>22</v>
       </c>
       <c r="G106" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H106" s="2">
         <v>1</v>
@@ -6989,10 +7009,10 @@
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C107" t="s">
         <v>49</v>
@@ -7001,13 +7021,13 @@
         <v>20</v>
       </c>
       <c r="E107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F107" t="s">
         <v>22</v>
       </c>
       <c r="G107" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H107" s="2">
         <v>1</v>
@@ -7045,25 +7065,25 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B108" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D108" t="s">
         <v>20</v>
       </c>
       <c r="E108" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F108" t="s">
         <v>22</v>
       </c>
       <c r="G108" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H108" s="2">
         <v>1</v>
@@ -7101,25 +7121,25 @@
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B109" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C109" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D109" t="s">
         <v>20</v>
       </c>
       <c r="E109" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F109" t="s">
         <v>22</v>
       </c>
       <c r="G109" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H109" s="2">
         <v>1</v>
@@ -7151,31 +7171,31 @@
       <c r="Q109" t="s">
         <v>28</v>
       </c>
-      <c r="R109" t="e">
-        <v>#N/A</v>
+      <c r="R109">
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B110" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C110" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D110" t="s">
         <v>20</v>
       </c>
       <c r="E110" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F110" t="s">
         <v>22</v>
       </c>
       <c r="G110" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H110" s="2">
         <v>6</v>
@@ -7213,19 +7233,19 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>216</v>
+      </c>
+      <c r="B111" t="s">
         <v>217</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
+        <v>193</v>
+      </c>
+      <c r="D111" t="s">
+        <v>20</v>
+      </c>
+      <c r="E111" t="s">
         <v>218</v>
-      </c>
-      <c r="C111" t="s">
-        <v>194</v>
-      </c>
-      <c r="D111" t="s">
-        <v>20</v>
-      </c>
-      <c r="E111" t="s">
-        <v>219</v>
       </c>
       <c r="F111" t="s">
         <v>22</v>
@@ -7258,7 +7278,7 @@
         <v>6.36</v>
       </c>
       <c r="P111" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q111" t="s">
         <v>28</v>
@@ -7325,19 +7345,19 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B113" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C113" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D113" t="s">
         <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F113" t="s">
         <v>22</v>
@@ -7381,19 +7401,19 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B114" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C114" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D114" t="s">
         <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F114" t="s">
         <v>22</v>
@@ -7426,7 +7446,7 @@
         <v>3.64</v>
       </c>
       <c r="P114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q114" t="s">
         <v>28</v>
@@ -7437,25 +7457,25 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>221</v>
+      </c>
+      <c r="B115" t="s">
         <v>222</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
+        <v>193</v>
+      </c>
+      <c r="D115" t="s">
+        <v>20</v>
+      </c>
+      <c r="E115" t="s">
         <v>223</v>
-      </c>
-      <c r="C115" t="s">
-        <v>194</v>
-      </c>
-      <c r="D115" t="s">
-        <v>20</v>
-      </c>
-      <c r="E115" t="s">
-        <v>224</v>
       </c>
       <c r="F115" t="s">
         <v>22</v>
       </c>
       <c r="G115" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H115" s="2">
         <v>8</v>
@@ -7493,25 +7513,25 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B116" t="s">
+        <v>224</v>
+      </c>
+      <c r="C116" t="s">
+        <v>193</v>
+      </c>
+      <c r="D116" t="s">
+        <v>20</v>
+      </c>
+      <c r="E116" t="s">
         <v>225</v>
-      </c>
-      <c r="C116" t="s">
-        <v>194</v>
-      </c>
-      <c r="D116" t="s">
-        <v>20</v>
-      </c>
-      <c r="E116" t="s">
-        <v>226</v>
       </c>
       <c r="F116" t="s">
         <v>22</v>
       </c>
       <c r="G116" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H116" s="2">
         <v>8</v>
@@ -7552,7 +7572,7 @@
         <v>70</v>
       </c>
       <c r="B117" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C117" t="s">
         <v>19</v>
@@ -7608,7 +7628,7 @@
         <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C118" t="s">
         <v>19</v>
@@ -7661,25 +7681,25 @@
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B119" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C119" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D119" t="s">
         <v>20</v>
       </c>
       <c r="E119" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F119" t="s">
         <v>22</v>
       </c>
       <c r="G119" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H119" s="2">
         <v>14</v>
@@ -7717,10 +7737,10 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B120" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C120" t="s">
         <v>49</v>
@@ -7729,13 +7749,13 @@
         <v>20</v>
       </c>
       <c r="E120" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F120" t="s">
         <v>22</v>
       </c>
       <c r="G120" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H120" s="2">
         <v>14</v>
@@ -7776,7 +7796,7 @@
         <v>70</v>
       </c>
       <c r="B121" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C121" t="s">
         <v>19</v>
@@ -7832,7 +7852,7 @@
         <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C122" t="s">
         <v>19</v>
@@ -7847,7 +7867,7 @@
         <v>90</v>
       </c>
       <c r="G122" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H122" s="2">
         <v>14</v>
@@ -7885,25 +7905,25 @@
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B123" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C123" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D123" t="s">
         <v>20</v>
       </c>
       <c r="E123" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F123" t="s">
         <v>22</v>
       </c>
       <c r="G123" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H123" s="2">
         <v>15</v>
@@ -7920,17 +7940,17 @@
       <c r="L123" s="1">
         <v>46310</v>
       </c>
-      <c r="M123" t="s">
-        <v>153</v>
+      <c r="M123">
+        <v>637667</v>
       </c>
       <c r="N123" t="s">
-        <v>153</v>
-      </c>
-      <c r="O123" t="s">
-        <v>153</v>
+        <v>131</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
       </c>
       <c r="P123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q123" t="s">
         <v>28</v>
@@ -7941,25 +7961,25 @@
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B124" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C124" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D124" t="s">
         <v>20</v>
       </c>
       <c r="E124" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F124" t="s">
         <v>22</v>
       </c>
       <c r="G124" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H124" s="2">
         <v>16</v>
@@ -7997,25 +8017,25 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B125" t="s">
+        <v>233</v>
+      </c>
+      <c r="C125" t="s">
+        <v>193</v>
+      </c>
+      <c r="D125" t="s">
+        <v>20</v>
+      </c>
+      <c r="E125" t="s">
         <v>234</v>
-      </c>
-      <c r="C125" t="s">
-        <v>194</v>
-      </c>
-      <c r="D125" t="s">
-        <v>20</v>
-      </c>
-      <c r="E125" t="s">
-        <v>235</v>
       </c>
       <c r="F125" t="s">
         <v>22</v>
       </c>
       <c r="G125" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H125" s="2">
         <v>20</v>
@@ -8039,33 +8059,33 @@
         <v>131</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>85.98</v>
       </c>
       <c r="P125" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q125" t="s">
         <v>28</v>
       </c>
-      <c r="R125" t="e">
-        <v>#N/A</v>
+      <c r="R125">
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B126" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C126" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D126" t="s">
         <v>20</v>
       </c>
       <c r="E126" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F126" t="s">
         <v>22</v>
@@ -8088,27 +8108,306 @@
       <c r="L126" s="1">
         <v>46315</v>
       </c>
-      <c r="M126" t="s">
-        <v>153</v>
+      <c r="M126">
+        <v>637657</v>
       </c>
       <c r="N126" t="s">
-        <v>153</v>
-      </c>
-      <c r="O126" t="s">
-        <v>153</v>
+        <v>131</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q126" t="s">
         <v>28</v>
       </c>
-      <c r="R126" t="e">
+      <c r="R126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>221</v>
+      </c>
+      <c r="B127" t="s">
+        <v>236</v>
+      </c>
+      <c r="C127" t="s">
+        <v>193</v>
+      </c>
+      <c r="D127" t="s">
+        <v>20</v>
+      </c>
+      <c r="E127" t="s">
+        <v>31</v>
+      </c>
+      <c r="F127" t="s">
+        <v>22</v>
+      </c>
+      <c r="G127" t="s">
+        <v>237</v>
+      </c>
+      <c r="H127" s="2">
+        <v>20</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L127" s="1">
+        <v>46315</v>
+      </c>
+      <c r="M127">
+        <v>637739</v>
+      </c>
+      <c r="N127" t="s">
+        <v>131</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>28</v>
+      </c>
+      <c r="R127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>70</v>
+      </c>
+      <c r="B128" t="s">
+        <v>238</v>
+      </c>
+      <c r="C128" t="s">
+        <v>19</v>
+      </c>
+      <c r="D128" t="s">
+        <v>20</v>
+      </c>
+      <c r="E128" t="s">
+        <v>146</v>
+      </c>
+      <c r="F128" t="s">
+        <v>90</v>
+      </c>
+      <c r="G128" t="s">
+        <v>91</v>
+      </c>
+      <c r="H128" s="2">
+        <v>21</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L128" s="1">
+        <v>46316</v>
+      </c>
+      <c r="M128">
+        <v>637939</v>
+      </c>
+      <c r="N128" t="s">
+        <v>131</v>
+      </c>
+      <c r="O128">
+        <v>39.24</v>
+      </c>
+      <c r="P128" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>28</v>
+      </c>
+      <c r="R128" t="e">
         <v>#N/A</v>
       </c>
     </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>70</v>
+      </c>
+      <c r="B129" t="s">
+        <v>239</v>
+      </c>
+      <c r="C129" t="s">
+        <v>19</v>
+      </c>
+      <c r="D129" t="s">
+        <v>20</v>
+      </c>
+      <c r="E129" t="s">
+        <v>146</v>
+      </c>
+      <c r="F129" t="s">
+        <v>90</v>
+      </c>
+      <c r="G129" t="s">
+        <v>91</v>
+      </c>
+      <c r="H129" s="2">
+        <v>21</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L129" s="1">
+        <v>46316</v>
+      </c>
+      <c r="M129">
+        <v>638118</v>
+      </c>
+      <c r="N129" t="s">
+        <v>131</v>
+      </c>
+      <c r="O129">
+        <v>43.4</v>
+      </c>
+      <c r="P129" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>28</v>
+      </c>
+      <c r="R129" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>70</v>
+      </c>
+      <c r="B130" t="s">
+        <v>240</v>
+      </c>
+      <c r="C130" t="s">
+        <v>19</v>
+      </c>
+      <c r="D130" t="s">
+        <v>20</v>
+      </c>
+      <c r="E130" t="s">
+        <v>146</v>
+      </c>
+      <c r="F130" t="s">
+        <v>90</v>
+      </c>
+      <c r="G130" t="s">
+        <v>91</v>
+      </c>
+      <c r="H130" s="2">
+        <v>21</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J130" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L130" s="1">
+        <v>46316</v>
+      </c>
+      <c r="M130">
+        <v>637919</v>
+      </c>
+      <c r="N130" t="s">
+        <v>131</v>
+      </c>
+      <c r="O130">
+        <v>4.38</v>
+      </c>
+      <c r="P130" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>28</v>
+      </c>
+      <c r="R130" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>221</v>
+      </c>
+      <c r="B131" t="s">
+        <v>241</v>
+      </c>
+      <c r="C131" t="s">
+        <v>193</v>
+      </c>
+      <c r="D131" t="s">
+        <v>20</v>
+      </c>
+      <c r="E131" t="s">
+        <v>225</v>
+      </c>
+      <c r="F131" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" t="s">
+        <v>242</v>
+      </c>
+      <c r="H131" s="2">
+        <v>21</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L131" s="1">
+        <v>46316</v>
+      </c>
+      <c r="M131">
+        <v>638228</v>
+      </c>
+      <c r="N131" t="s">
+        <v>131</v>
+      </c>
+      <c r="O131">
+        <v>7.02</v>
+      </c>
+      <c r="P131" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>28</v>
+      </c>
+      <c r="R131" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A43" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9291,7 +9590,7 @@
         <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9305,7 +9604,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9319,7 +9618,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -9333,7 +9632,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -9347,7 +9646,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -9361,7 +9660,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -9375,7 +9674,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -9389,7 +9688,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -9403,7 +9702,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -9417,7 +9716,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -9431,7 +9730,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -9439,13 +9738,13 @@
         <v>46266</v>
       </c>
       <c r="B12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C12">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9453,13 +9752,13 @@
         <v>46296</v>
       </c>
       <c r="B13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C13">
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9467,13 +9766,13 @@
         <v>46296</v>
       </c>
       <c r="B14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C14">
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9481,13 +9780,13 @@
         <v>46296</v>
       </c>
       <c r="B15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -9506,6 +9805,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -9766,17 +10076,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
@@ -9786,6 +10085,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9802,15 +10112,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="281" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CD152CE-F191-4E6C-A00B-E03508CF9BAF}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{294C6BD2-9187-4816-BB7B-19CB41A64639}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="252">
   <si>
     <t>Usuário</t>
   </si>
@@ -774,6 +774,30 @@
   </si>
   <si>
     <t>AJUSTE DE DOCUMENTAÇÃO</t>
+  </si>
+  <si>
+    <t>PRETENDE CONSTRUIR USINA</t>
+  </si>
+  <si>
+    <t>ANALISE DE CRÉDITO</t>
+  </si>
+  <si>
+    <t>RACOES L.D.</t>
+  </si>
+  <si>
+    <t>MAILING IM - ENRIQUECIMENTO LEMIT</t>
+  </si>
+  <si>
+    <t>Pratinha</t>
+  </si>
+  <si>
+    <t>KARINE LAISSA SILVA LOPES HACKBARTH</t>
+  </si>
+  <si>
+    <t>Aquiraz</t>
+  </si>
+  <si>
+    <t>FRAEVA - PRODUTOS E SERVICOS LTDA.</t>
   </si>
 </sst>
 </file>
@@ -1099,10 +1123,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R131"/>
+  <dimension ref="A1:R134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
@@ -5315,10 +5339,10 @@
         <v>131</v>
       </c>
       <c r="O76">
-        <v>3.78</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="P76" t="s">
-        <v>243</v>
+        <v>35</v>
       </c>
       <c r="Q76" t="s">
         <v>28</v>
@@ -7328,16 +7352,16 @@
         <v>631043</v>
       </c>
       <c r="N112" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O112">
         <v>14.23</v>
       </c>
       <c r="P112" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q112" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="R112">
         <v>1</v>
@@ -7446,7 +7470,7 @@
         <v>3.64</v>
       </c>
       <c r="P114" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="Q114" t="s">
         <v>28</v>
@@ -7944,16 +7968,16 @@
         <v>637667</v>
       </c>
       <c r="N123" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O123">
         <v>0</v>
       </c>
       <c r="P123" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q123" t="s">
-        <v>28</v>
+        <v>244</v>
       </c>
       <c r="R123" t="e">
         <v>#N/A</v>
@@ -8003,10 +8027,10 @@
         <v>131</v>
       </c>
       <c r="O124">
-        <v>102.64</v>
+        <v>76.19</v>
       </c>
       <c r="P124" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="Q124" t="s">
         <v>28</v>
@@ -8235,8 +8259,8 @@
       <c r="Q128" t="s">
         <v>28</v>
       </c>
-      <c r="R128" t="e">
-        <v>#N/A</v>
+      <c r="R128">
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
@@ -8291,8 +8315,8 @@
       <c r="Q129" t="s">
         <v>28</v>
       </c>
-      <c r="R129" t="e">
-        <v>#N/A</v>
+      <c r="R129">
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
@@ -8347,8 +8371,8 @@
       <c r="Q130" t="s">
         <v>28</v>
       </c>
-      <c r="R130" t="e">
-        <v>#N/A</v>
+      <c r="R130">
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
@@ -8398,12 +8422,180 @@
         <v>7.02</v>
       </c>
       <c r="P131" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>28</v>
+      </c>
+      <c r="R131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>191</v>
+      </c>
+      <c r="B132" t="s">
+        <v>246</v>
+      </c>
+      <c r="C132" t="s">
+        <v>247</v>
+      </c>
+      <c r="D132" t="s">
+        <v>20</v>
+      </c>
+      <c r="E132" t="s">
+        <v>203</v>
+      </c>
+      <c r="F132" t="s">
+        <v>22</v>
+      </c>
+      <c r="G132" t="s">
+        <v>248</v>
+      </c>
+      <c r="H132" s="2">
+        <v>22</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L132" s="1">
+        <v>46317</v>
+      </c>
+      <c r="M132" t="s">
+        <v>153</v>
+      </c>
+      <c r="N132" t="s">
+        <v>153</v>
+      </c>
+      <c r="O132" t="s">
+        <v>153</v>
+      </c>
+      <c r="P132" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>28</v>
+      </c>
+      <c r="R132" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>70</v>
+      </c>
+      <c r="B133" t="s">
+        <v>249</v>
+      </c>
+      <c r="C133" t="s">
+        <v>19</v>
+      </c>
+      <c r="D133" t="s">
+        <v>20</v>
+      </c>
+      <c r="E133" t="s">
+        <v>146</v>
+      </c>
+      <c r="F133" t="s">
+        <v>90</v>
+      </c>
+      <c r="G133" t="s">
+        <v>250</v>
+      </c>
+      <c r="H133" s="2">
+        <v>22</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L133" s="1">
+        <v>46317</v>
+      </c>
+      <c r="M133" t="s">
+        <v>153</v>
+      </c>
+      <c r="N133" t="s">
+        <v>153</v>
+      </c>
+      <c r="O133" t="s">
+        <v>153</v>
+      </c>
+      <c r="P133" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>28</v>
+      </c>
+      <c r="R133" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>221</v>
+      </c>
+      <c r="B134" t="s">
+        <v>251</v>
+      </c>
+      <c r="C134" t="s">
+        <v>193</v>
+      </c>
+      <c r="D134" t="s">
+        <v>20</v>
+      </c>
+      <c r="E134" t="s">
+        <v>31</v>
+      </c>
+      <c r="F134" t="s">
+        <v>22</v>
+      </c>
+      <c r="G134" t="s">
+        <v>237</v>
+      </c>
+      <c r="H134" s="2">
+        <v>22</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L134" s="1">
+        <v>46317</v>
+      </c>
+      <c r="M134">
+        <v>638503</v>
+      </c>
+      <c r="N134" t="s">
+        <v>131</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134" t="s">
         <v>55</v>
       </c>
-      <c r="Q131" t="s">
-        <v>28</v>
-      </c>
-      <c r="R131" t="e">
+      <c r="Q134" t="s">
+        <v>28</v>
+      </c>
+      <c r="R134" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -9796,26 +9988,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -10076,10 +10248,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10096,20 +10299,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{294C6BD2-9187-4816-BB7B-19CB41A64639}"/>
+  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01B447FB-12B8-4C16-BDD7-97798803C173}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="257">
   <si>
     <t>Usuário</t>
   </si>
@@ -779,9 +779,6 @@
     <t>PRETENDE CONSTRUIR USINA</t>
   </si>
   <si>
-    <t>ANALISE DE CRÉDITO</t>
-  </si>
-  <si>
     <t>RACOES L.D.</t>
   </si>
   <si>
@@ -798,6 +795,24 @@
   </si>
   <si>
     <t>FRAEVA - PRODUTOS E SERVICOS LTDA.</t>
+  </si>
+  <si>
+    <t>CLIENTE FECHOU EM OUTRA TITULARIDADE</t>
+  </si>
+  <si>
+    <t>NEGOCIAÇÃO QUENTE</t>
+  </si>
+  <si>
+    <t>MODULOS CONSTRUCOES E ENGENHARIA LTDA</t>
+  </si>
+  <si>
+    <t>OSMAR CARVALHO MACHADO JUNIOR</t>
+  </si>
+  <si>
+    <t>RAFAEL DAVANCO SILVA</t>
+  </si>
+  <si>
+    <t>Andradas</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R134"/>
+  <dimension ref="A1:R137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -3939,7 +3954,7 @@
         <v>59</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="P51" t="s">
         <v>28</v>
@@ -5342,7 +5357,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="P76" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="Q76" t="s">
         <v>28</v>
@@ -6960,16 +6975,16 @@
         <v>625286</v>
       </c>
       <c r="N105" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O105">
         <v>78.47</v>
       </c>
       <c r="P105" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q105" t="s">
-        <v>28</v>
+        <v>251</v>
       </c>
       <c r="R105" t="e">
         <v>#N/A</v>
@@ -7302,7 +7317,7 @@
         <v>6.36</v>
       </c>
       <c r="P111" t="s">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="Q111" t="s">
         <v>28</v>
@@ -7688,16 +7703,16 @@
         <v>632724</v>
       </c>
       <c r="N118" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O118">
         <v>8.07</v>
       </c>
       <c r="P118" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q118" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="R118" t="e">
         <v>#N/A</v>
@@ -7923,8 +7938,8 @@
       <c r="Q122" t="s">
         <v>28</v>
       </c>
-      <c r="R122" t="e">
-        <v>#N/A</v>
+      <c r="R122">
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
@@ -8030,7 +8045,7 @@
         <v>76.19</v>
       </c>
       <c r="P124" t="s">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="Q124" t="s">
         <v>28</v>
@@ -8195,7 +8210,7 @@
         <v>131</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>10.29</v>
       </c>
       <c r="P127" t="s">
         <v>27</v>
@@ -8251,7 +8266,7 @@
         <v>131</v>
       </c>
       <c r="O128">
-        <v>39.24</v>
+        <v>43.16</v>
       </c>
       <c r="P128" t="s">
         <v>27</v>
@@ -8436,10 +8451,10 @@
         <v>191</v>
       </c>
       <c r="B132" t="s">
+        <v>245</v>
+      </c>
+      <c r="C132" t="s">
         <v>246</v>
-      </c>
-      <c r="C132" t="s">
-        <v>247</v>
       </c>
       <c r="D132" t="s">
         <v>20</v>
@@ -8451,7 +8466,7 @@
         <v>22</v>
       </c>
       <c r="G132" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H132" s="2">
         <v>22</v>
@@ -8468,17 +8483,17 @@
       <c r="L132" s="1">
         <v>46317</v>
       </c>
-      <c r="M132" t="s">
-        <v>153</v>
+      <c r="M132">
+        <v>587871</v>
       </c>
       <c r="N132" t="s">
-        <v>153</v>
-      </c>
-      <c r="O132" t="s">
-        <v>153</v>
+        <v>131</v>
+      </c>
+      <c r="O132">
+        <v>35.64</v>
       </c>
       <c r="P132" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Q132" t="s">
         <v>28</v>
@@ -8492,7 +8507,7 @@
         <v>70</v>
       </c>
       <c r="B133" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C133" t="s">
         <v>19</v>
@@ -8507,7 +8522,7 @@
         <v>90</v>
       </c>
       <c r="G133" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H133" s="2">
         <v>22</v>
@@ -8524,17 +8539,17 @@
       <c r="L133" s="1">
         <v>46317</v>
       </c>
-      <c r="M133" t="s">
-        <v>153</v>
+      <c r="M133">
+        <v>638510</v>
       </c>
       <c r="N133" t="s">
-        <v>153</v>
-      </c>
-      <c r="O133" t="s">
-        <v>153</v>
+        <v>131</v>
+      </c>
+      <c r="O133">
+        <v>2.71</v>
       </c>
       <c r="P133" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q133" t="s">
         <v>28</v>
@@ -8548,7 +8563,7 @@
         <v>221</v>
       </c>
       <c r="B134" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C134" t="s">
         <v>193</v>
@@ -8590,12 +8605,180 @@
         <v>0</v>
       </c>
       <c r="P134" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="Q134" t="s">
         <v>28</v>
       </c>
-      <c r="R134" t="e">
+      <c r="R134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>70</v>
+      </c>
+      <c r="B135" t="s">
+        <v>253</v>
+      </c>
+      <c r="C135" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" t="s">
+        <v>20</v>
+      </c>
+      <c r="E135" t="s">
+        <v>146</v>
+      </c>
+      <c r="F135" t="s">
+        <v>90</v>
+      </c>
+      <c r="G135" t="s">
+        <v>104</v>
+      </c>
+      <c r="H135" s="2">
+        <v>23</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L135" s="1">
+        <v>46318</v>
+      </c>
+      <c r="M135">
+        <v>639513</v>
+      </c>
+      <c r="N135" t="s">
+        <v>131</v>
+      </c>
+      <c r="O135">
+        <v>3.99</v>
+      </c>
+      <c r="P135" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>28</v>
+      </c>
+      <c r="R135" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>70</v>
+      </c>
+      <c r="B136" t="s">
+        <v>254</v>
+      </c>
+      <c r="C136" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" t="s">
+        <v>20</v>
+      </c>
+      <c r="E136" t="s">
+        <v>146</v>
+      </c>
+      <c r="F136" t="s">
+        <v>90</v>
+      </c>
+      <c r="G136" t="s">
+        <v>104</v>
+      </c>
+      <c r="H136" s="2">
+        <v>23</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J136" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L136" s="1">
+        <v>46318</v>
+      </c>
+      <c r="M136">
+        <v>639446</v>
+      </c>
+      <c r="N136" t="s">
+        <v>131</v>
+      </c>
+      <c r="O136">
+        <v>3.31</v>
+      </c>
+      <c r="P136" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>28</v>
+      </c>
+      <c r="R136" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>191</v>
+      </c>
+      <c r="B137" t="s">
+        <v>255</v>
+      </c>
+      <c r="C137" t="s">
+        <v>193</v>
+      </c>
+      <c r="D137" t="s">
+        <v>20</v>
+      </c>
+      <c r="E137" t="s">
+        <v>205</v>
+      </c>
+      <c r="F137" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" t="s">
+        <v>256</v>
+      </c>
+      <c r="H137" s="2">
+        <v>26</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L137" s="1">
+        <v>46321</v>
+      </c>
+      <c r="M137">
+        <v>640237</v>
+      </c>
+      <c r="N137" t="s">
+        <v>131</v>
+      </c>
+      <c r="O137">
+        <v>3.78</v>
+      </c>
+      <c r="P137" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>28</v>
+      </c>
+      <c r="R137" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -9988,6 +10171,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -10248,17 +10442,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10269,6 +10452,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10287,17 +10481,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01B447FB-12B8-4C16-BDD7-97798803C173}"/>
+  <xr:revisionPtr revIDLastSave="297" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4BACB2F-0C34-4C1F-B903-31DE490C5182}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="261">
   <si>
     <t>Usuário</t>
   </si>
@@ -773,9 +773,6 @@
     <t>Nova Serrana</t>
   </si>
   <si>
-    <t>AJUSTE DE DOCUMENTAÇÃO</t>
-  </si>
-  <si>
     <t>PRETENDE CONSTRUIR USINA</t>
   </si>
   <si>
@@ -813,6 +810,21 @@
   </si>
   <si>
     <t>Andradas</t>
+  </si>
+  <si>
+    <t>INELEGÍVEL - CARACTERÍSTICAS INVIÁVEIS</t>
+  </si>
+  <si>
+    <t>EDUARDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>JOAO CARLOS JUNIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>(vazio)</t>
+  </si>
+  <si>
+    <t>SANTA TERRA ATACADISTA DE CEREAIS LTDA</t>
   </si>
 </sst>
 </file>
@@ -1138,12 +1150,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R137"/>
+  <dimension ref="A1:R140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1189,7 +1202,7 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -1245,7 +1258,7 @@
       <c r="N2" t="s">
         <v>44</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="2">
         <v>1.41</v>
       </c>
       <c r="P2" t="s">
@@ -1301,7 +1314,7 @@
       <c r="N3" t="s">
         <v>44</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="2">
         <v>34.979999999999997</v>
       </c>
       <c r="P3" t="s">
@@ -1357,7 +1370,7 @@
       <c r="N4" t="s">
         <v>59</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="2">
         <v>30.92</v>
       </c>
       <c r="P4" t="s">
@@ -1410,7 +1423,7 @@
       <c r="N5" t="s">
         <v>44</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="2">
         <v>7.85</v>
       </c>
       <c r="P5" t="s">
@@ -1466,7 +1479,7 @@
       <c r="N6" t="s">
         <v>44</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="2">
         <v>67.37</v>
       </c>
       <c r="P6" t="s">
@@ -1514,16 +1527,16 @@
         <v>46211</v>
       </c>
       <c r="M7">
-        <v>588663</v>
+        <v>641016</v>
       </c>
       <c r="N7" t="s">
         <v>131</v>
       </c>
-      <c r="O7">
-        <v>35.78</v>
+      <c r="O7" s="2">
+        <v>36.31</v>
       </c>
       <c r="P7" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -1572,7 +1585,7 @@
       <c r="N8" t="s">
         <v>44</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="2">
         <v>27.46</v>
       </c>
       <c r="P8" t="s">
@@ -1625,7 +1638,7 @@
       <c r="N9" t="s">
         <v>131</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="2">
         <v>10</v>
       </c>
       <c r="P9" t="s">
@@ -1678,7 +1691,7 @@
       <c r="N10" t="s">
         <v>44</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="2">
         <v>10.44</v>
       </c>
       <c r="P10" t="s">
@@ -1731,7 +1744,7 @@
       <c r="N11" t="s">
         <v>44</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="2">
         <v>7</v>
       </c>
       <c r="P11" t="s">
@@ -1784,7 +1797,7 @@
       <c r="N12" t="s">
         <v>59</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="2">
         <v>41.35</v>
       </c>
       <c r="P12" t="s">
@@ -1837,7 +1850,7 @@
       <c r="N13" t="s">
         <v>44</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="2">
         <v>3.5</v>
       </c>
       <c r="P13" t="s">
@@ -1893,7 +1906,7 @@
       <c r="N14" t="s">
         <v>153</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="2" t="s">
         <v>153</v>
       </c>
       <c r="P14" t="s">
@@ -1946,7 +1959,7 @@
       <c r="N15" t="s">
         <v>59</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="2">
         <v>7.87</v>
       </c>
       <c r="P15" t="s">
@@ -1999,7 +2012,7 @@
       <c r="N16" t="s">
         <v>59</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="2">
         <v>3.66</v>
       </c>
       <c r="P16" t="s">
@@ -2052,7 +2065,7 @@
       <c r="N17" t="s">
         <v>44</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="2">
         <v>9.7899999999999991</v>
       </c>
       <c r="P17" t="s">
@@ -2108,7 +2121,7 @@
       <c r="N18" t="s">
         <v>44</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="2">
         <v>6.9</v>
       </c>
       <c r="P18" t="s">
@@ -2161,7 +2174,7 @@
       <c r="N19" t="s">
         <v>44</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="2">
         <v>102.72</v>
       </c>
       <c r="P19" t="s">
@@ -2217,7 +2230,7 @@
       <c r="N20" t="s">
         <v>44</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="2">
         <v>41.62</v>
       </c>
       <c r="P20" t="s">
@@ -2273,7 +2286,7 @@
       <c r="N21" t="s">
         <v>131</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="2">
         <v>4.63</v>
       </c>
       <c r="P21" t="s">
@@ -2329,7 +2342,7 @@
       <c r="N22" t="s">
         <v>131</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="2">
         <v>1.96</v>
       </c>
       <c r="P22" t="s">
@@ -2385,7 +2398,7 @@
       <c r="N23" t="s">
         <v>44</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="2">
         <v>1.89</v>
       </c>
       <c r="P23" t="s">
@@ -2441,7 +2454,7 @@
       <c r="N24" t="s">
         <v>131</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="2">
         <v>6.12</v>
       </c>
       <c r="P24" t="s">
@@ -2497,7 +2510,7 @@
       <c r="N25" t="s">
         <v>59</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="2">
         <v>10.5</v>
       </c>
       <c r="P25" t="s">
@@ -2553,7 +2566,7 @@
       <c r="N26" t="s">
         <v>44</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="2">
         <v>8.3699999999999992</v>
       </c>
       <c r="P26" t="s">
@@ -2609,7 +2622,7 @@
       <c r="N27" t="s">
         <v>44</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="2">
         <v>2.98</v>
       </c>
       <c r="P27" t="s">
@@ -2665,7 +2678,7 @@
       <c r="N28" t="s">
         <v>131</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="2">
         <v>61.58</v>
       </c>
       <c r="P28" t="s">
@@ -2721,7 +2734,7 @@
       <c r="N29" t="s">
         <v>44</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="2">
         <v>91.5</v>
       </c>
       <c r="P29" t="s">
@@ -2777,7 +2790,7 @@
       <c r="N30" t="s">
         <v>59</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="2">
         <v>5.13</v>
       </c>
       <c r="P30" t="s">
@@ -2833,7 +2846,7 @@
       <c r="N31" t="s">
         <v>131</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="2">
         <v>37.299999999999997</v>
       </c>
       <c r="P31" t="s">
@@ -2889,7 +2902,7 @@
       <c r="N32" t="s">
         <v>153</v>
       </c>
-      <c r="O32" t="s">
+      <c r="O32" s="2" t="s">
         <v>153</v>
       </c>
       <c r="P32" t="s">
@@ -2945,7 +2958,7 @@
       <c r="N33" t="s">
         <v>44</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="2">
         <v>3.73</v>
       </c>
       <c r="P33" t="s">
@@ -3001,7 +3014,7 @@
       <c r="N34" t="s">
         <v>44</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="2">
         <v>4.54</v>
       </c>
       <c r="P34" t="s">
@@ -3057,7 +3070,7 @@
       <c r="N35" t="s">
         <v>59</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="2">
         <v>20.25</v>
       </c>
       <c r="P35" t="s">
@@ -3113,7 +3126,7 @@
       <c r="N36" t="s">
         <v>44</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="2">
         <v>6.23</v>
       </c>
       <c r="P36" t="s">
@@ -3169,7 +3182,7 @@
       <c r="N37" t="s">
         <v>44</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="2">
         <v>0</v>
       </c>
       <c r="P37" t="s">
@@ -3225,7 +3238,7 @@
       <c r="N38" t="s">
         <v>59</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="2">
         <v>3.39</v>
       </c>
       <c r="P38" t="s">
@@ -3281,7 +3294,7 @@
       <c r="N39" t="s">
         <v>59</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="2">
         <v>10.9</v>
       </c>
       <c r="P39" t="s">
@@ -3337,7 +3350,7 @@
       <c r="N40" t="s">
         <v>131</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="2">
         <v>19.47</v>
       </c>
       <c r="P40" t="s">
@@ -3393,7 +3406,7 @@
       <c r="N41" t="s">
         <v>44</v>
       </c>
-      <c r="O41">
+      <c r="O41" s="2">
         <v>3.19</v>
       </c>
       <c r="P41" t="s">
@@ -3449,7 +3462,7 @@
       <c r="N42" t="s">
         <v>44</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="2">
         <v>7.15</v>
       </c>
       <c r="P42" t="s">
@@ -3505,7 +3518,7 @@
       <c r="N43" t="s">
         <v>131</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="2">
         <v>9.2200000000000006</v>
       </c>
       <c r="P43" t="s">
@@ -3561,7 +3574,7 @@
       <c r="N44" t="s">
         <v>44</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="2">
         <v>4.63</v>
       </c>
       <c r="P44" t="s">
@@ -3617,7 +3630,7 @@
       <c r="N45" t="s">
         <v>44</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="2">
         <v>20.53</v>
       </c>
       <c r="P45" t="s">
@@ -3673,7 +3686,7 @@
       <c r="N46" t="s">
         <v>44</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="2">
         <v>8.44</v>
       </c>
       <c r="P46" t="s">
@@ -3729,7 +3742,7 @@
       <c r="N47" t="s">
         <v>131</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="2">
         <v>4.17</v>
       </c>
       <c r="P47" t="s">
@@ -3785,7 +3798,7 @@
       <c r="N48" t="s">
         <v>44</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="2">
         <v>10.1</v>
       </c>
       <c r="P48" t="s">
@@ -3841,7 +3854,7 @@
       <c r="N49" t="s">
         <v>131</v>
       </c>
-      <c r="O49">
+      <c r="O49" s="2">
         <v>9.85</v>
       </c>
       <c r="P49" t="s">
@@ -3897,7 +3910,7 @@
       <c r="N50" t="s">
         <v>44</v>
       </c>
-      <c r="O50">
+      <c r="O50" s="2">
         <v>2.89</v>
       </c>
       <c r="P50" t="s">
@@ -3953,7 +3966,7 @@
       <c r="N51" t="s">
         <v>59</v>
       </c>
-      <c r="O51">
+      <c r="O51" s="2">
         <v>441</v>
       </c>
       <c r="P51" t="s">
@@ -4009,7 +4022,7 @@
       <c r="N52" t="s">
         <v>44</v>
       </c>
-      <c r="O52">
+      <c r="O52" s="2">
         <v>2.33</v>
       </c>
       <c r="P52" t="s">
@@ -4065,7 +4078,7 @@
       <c r="N53" t="s">
         <v>44</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="2">
         <v>7.95</v>
       </c>
       <c r="P53" t="s">
@@ -4121,7 +4134,7 @@
       <c r="N54" t="s">
         <v>131</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="2">
         <v>1.91</v>
       </c>
       <c r="P54" t="s">
@@ -4177,7 +4190,7 @@
       <c r="N55" t="s">
         <v>131</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="2">
         <v>12.23</v>
       </c>
       <c r="P55" t="s">
@@ -4233,7 +4246,7 @@
       <c r="N56" t="s">
         <v>131</v>
       </c>
-      <c r="O56">
+      <c r="O56" s="2">
         <v>16.34</v>
       </c>
       <c r="P56" t="s">
@@ -4289,7 +4302,7 @@
       <c r="N57" t="s">
         <v>44</v>
       </c>
-      <c r="O57">
+      <c r="O57" s="2">
         <v>11.93</v>
       </c>
       <c r="P57" t="s">
@@ -4345,7 +4358,7 @@
       <c r="N58" t="s">
         <v>44</v>
       </c>
-      <c r="O58">
+      <c r="O58" s="2">
         <v>35.65</v>
       </c>
       <c r="P58" t="s">
@@ -4401,7 +4414,7 @@
       <c r="N59" t="s">
         <v>131</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="2">
         <v>6.36</v>
       </c>
       <c r="P59" t="s">
@@ -4457,7 +4470,7 @@
       <c r="N60" t="s">
         <v>131</v>
       </c>
-      <c r="O60">
+      <c r="O60" s="2">
         <v>32.82</v>
       </c>
       <c r="P60" t="s">
@@ -4513,7 +4526,7 @@
       <c r="N61" t="s">
         <v>131</v>
       </c>
-      <c r="O61">
+      <c r="O61" s="2">
         <v>21.23</v>
       </c>
       <c r="P61" t="s">
@@ -4569,7 +4582,7 @@
       <c r="N62" t="s">
         <v>131</v>
       </c>
-      <c r="O62">
+      <c r="O62" s="2">
         <v>2.2200000000000002</v>
       </c>
       <c r="P62" t="s">
@@ -4625,7 +4638,7 @@
       <c r="N63" t="s">
         <v>131</v>
       </c>
-      <c r="O63">
+      <c r="O63" s="2">
         <v>8.4600000000000009</v>
       </c>
       <c r="P63" t="s">
@@ -4681,7 +4694,7 @@
       <c r="N64" t="s">
         <v>44</v>
       </c>
-      <c r="O64">
+      <c r="O64" s="2">
         <v>2.76</v>
       </c>
       <c r="P64" t="s">
@@ -4737,7 +4750,7 @@
       <c r="N65" t="s">
         <v>59</v>
       </c>
-      <c r="O65">
+      <c r="O65" s="2">
         <v>14.6</v>
       </c>
       <c r="P65" t="s">
@@ -4793,7 +4806,7 @@
       <c r="N66" t="s">
         <v>131</v>
       </c>
-      <c r="O66">
+      <c r="O66" s="2">
         <v>4.68</v>
       </c>
       <c r="P66" t="s">
@@ -4849,7 +4862,7 @@
       <c r="N67" t="s">
         <v>59</v>
       </c>
-      <c r="O67">
+      <c r="O67" s="2">
         <v>8.5399999999999991</v>
       </c>
       <c r="P67" t="s">
@@ -4905,7 +4918,7 @@
       <c r="N68" t="s">
         <v>131</v>
       </c>
-      <c r="O68">
+      <c r="O68" s="2">
         <v>104.04</v>
       </c>
       <c r="P68" t="s">
@@ -4961,7 +4974,7 @@
       <c r="N69" t="s">
         <v>131</v>
       </c>
-      <c r="O69">
+      <c r="O69" s="2">
         <v>0</v>
       </c>
       <c r="P69" t="s">
@@ -5017,7 +5030,7 @@
       <c r="N70" t="s">
         <v>59</v>
       </c>
-      <c r="O70">
+      <c r="O70" s="2">
         <v>14.62</v>
       </c>
       <c r="P70" t="s">
@@ -5073,7 +5086,7 @@
       <c r="N71" t="s">
         <v>131</v>
       </c>
-      <c r="O71">
+      <c r="O71" s="2">
         <v>6.46</v>
       </c>
       <c r="P71" t="s">
@@ -5129,7 +5142,7 @@
       <c r="N72" t="s">
         <v>44</v>
       </c>
-      <c r="O72">
+      <c r="O72" s="2">
         <v>8.57</v>
       </c>
       <c r="P72" t="s">
@@ -5185,7 +5198,7 @@
       <c r="N73" t="s">
         <v>131</v>
       </c>
-      <c r="O73">
+      <c r="O73" s="2">
         <v>8.9600000000000009</v>
       </c>
       <c r="P73" t="s">
@@ -5241,7 +5254,7 @@
       <c r="N74" t="s">
         <v>59</v>
       </c>
-      <c r="O74">
+      <c r="O74" s="2">
         <v>11.75</v>
       </c>
       <c r="P74" t="s">
@@ -5297,7 +5310,7 @@
       <c r="N75" t="s">
         <v>131</v>
       </c>
-      <c r="O75">
+      <c r="O75" s="2">
         <v>5.95</v>
       </c>
       <c r="P75" t="s">
@@ -5353,7 +5366,7 @@
       <c r="N76" t="s">
         <v>131</v>
       </c>
-      <c r="O76">
+      <c r="O76" s="2">
         <v>4.0999999999999996</v>
       </c>
       <c r="P76" t="s">
@@ -5409,7 +5422,7 @@
       <c r="N77" t="s">
         <v>131</v>
       </c>
-      <c r="O77">
+      <c r="O77" s="2">
         <v>5.46</v>
       </c>
       <c r="P77" t="s">
@@ -5465,7 +5478,7 @@
       <c r="N78" t="s">
         <v>131</v>
       </c>
-      <c r="O78">
+      <c r="O78" s="2">
         <v>5.33</v>
       </c>
       <c r="P78" t="s">
@@ -5521,7 +5534,7 @@
       <c r="N79" t="s">
         <v>59</v>
       </c>
-      <c r="O79">
+      <c r="O79" s="2">
         <v>38.840000000000003</v>
       </c>
       <c r="P79" t="s">
@@ -5577,7 +5590,7 @@
       <c r="N80" t="s">
         <v>59</v>
       </c>
-      <c r="O80">
+      <c r="O80" s="2">
         <v>118.5</v>
       </c>
       <c r="P80" t="s">
@@ -5633,7 +5646,7 @@
       <c r="N81" t="s">
         <v>59</v>
       </c>
-      <c r="O81">
+      <c r="O81" s="2">
         <v>9.11</v>
       </c>
       <c r="P81" t="s">
@@ -5689,7 +5702,7 @@
       <c r="N82" t="s">
         <v>131</v>
       </c>
-      <c r="O82">
+      <c r="O82" s="2">
         <v>8.34</v>
       </c>
       <c r="P82" t="s">
@@ -5745,7 +5758,7 @@
       <c r="N83" t="s">
         <v>131</v>
       </c>
-      <c r="O83">
+      <c r="O83" s="2">
         <v>12.79</v>
       </c>
       <c r="P83" t="s">
@@ -5801,7 +5814,7 @@
       <c r="N84" t="s">
         <v>131</v>
       </c>
-      <c r="O84">
+      <c r="O84" s="2">
         <v>3.73</v>
       </c>
       <c r="P84" t="s">
@@ -5857,7 +5870,7 @@
       <c r="N85" t="s">
         <v>131</v>
       </c>
-      <c r="O85">
+      <c r="O85" s="2">
         <v>22.65</v>
       </c>
       <c r="P85" t="s">
@@ -5913,7 +5926,7 @@
       <c r="N86" t="s">
         <v>59</v>
       </c>
-      <c r="O86">
+      <c r="O86" s="2">
         <v>42.8</v>
       </c>
       <c r="P86" t="s">
@@ -5969,7 +5982,7 @@
       <c r="N87" t="s">
         <v>131</v>
       </c>
-      <c r="O87">
+      <c r="O87" s="2">
         <v>29.19</v>
       </c>
       <c r="P87" t="s">
@@ -6025,7 +6038,7 @@
       <c r="N88" t="s">
         <v>131</v>
       </c>
-      <c r="O88">
+      <c r="O88" s="2">
         <v>3.5</v>
       </c>
       <c r="P88" t="s">
@@ -6081,7 +6094,7 @@
       <c r="N89" t="s">
         <v>131</v>
       </c>
-      <c r="O89">
+      <c r="O89" s="2">
         <v>4.5199999999999996</v>
       </c>
       <c r="P89" t="s">
@@ -6137,7 +6150,7 @@
       <c r="N90" t="s">
         <v>59</v>
       </c>
-      <c r="O90">
+      <c r="O90" s="2">
         <v>14.46</v>
       </c>
       <c r="P90" t="s">
@@ -6193,7 +6206,7 @@
       <c r="N91" t="s">
         <v>131</v>
       </c>
-      <c r="O91">
+      <c r="O91" s="2">
         <v>17.84</v>
       </c>
       <c r="P91" t="s">
@@ -6249,7 +6262,7 @@
       <c r="N92" t="s">
         <v>131</v>
       </c>
-      <c r="O92">
+      <c r="O92" s="2">
         <v>16.39</v>
       </c>
       <c r="P92" t="s">
@@ -6305,7 +6318,7 @@
       <c r="N93" t="s">
         <v>59</v>
       </c>
-      <c r="O93">
+      <c r="O93" s="2">
         <v>38.840000000000003</v>
       </c>
       <c r="P93" t="s">
@@ -6361,7 +6374,7 @@
       <c r="N94" t="s">
         <v>59</v>
       </c>
-      <c r="O94">
+      <c r="O94" s="2">
         <v>38.840000000000003</v>
       </c>
       <c r="P94" t="s">
@@ -6417,7 +6430,7 @@
       <c r="N95" t="s">
         <v>131</v>
       </c>
-      <c r="O95">
+      <c r="O95" s="2">
         <v>11.61</v>
       </c>
       <c r="P95" t="s">
@@ -6473,7 +6486,7 @@
       <c r="N96" t="s">
         <v>131</v>
       </c>
-      <c r="O96">
+      <c r="O96" s="2">
         <v>7.5</v>
       </c>
       <c r="P96" t="s">
@@ -6529,7 +6542,7 @@
       <c r="N97" t="s">
         <v>131</v>
       </c>
-      <c r="O97">
+      <c r="O97" s="2">
         <v>4.3</v>
       </c>
       <c r="P97" t="s">
@@ -6585,7 +6598,7 @@
       <c r="N98" t="s">
         <v>131</v>
       </c>
-      <c r="O98">
+      <c r="O98" s="2">
         <v>16.3</v>
       </c>
       <c r="P98" t="s">
@@ -6641,11 +6654,11 @@
       <c r="N99" t="s">
         <v>131</v>
       </c>
-      <c r="O99">
+      <c r="O99" s="2">
         <v>2.42</v>
       </c>
       <c r="P99" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q99" t="s">
         <v>28</v>
@@ -6697,7 +6710,7 @@
       <c r="N100" t="s">
         <v>131</v>
       </c>
-      <c r="O100">
+      <c r="O100" s="2">
         <v>9.1300000000000008</v>
       </c>
       <c r="P100" t="s">
@@ -6753,7 +6766,7 @@
       <c r="N101" t="s">
         <v>44</v>
       </c>
-      <c r="O101">
+      <c r="O101" s="2">
         <v>3.88</v>
       </c>
       <c r="P101" t="s">
@@ -6809,11 +6822,11 @@
       <c r="N102" t="s">
         <v>131</v>
       </c>
-      <c r="O102">
+      <c r="O102" s="2">
         <v>1.42</v>
       </c>
       <c r="P102" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q102" t="s">
         <v>28</v>
@@ -6865,7 +6878,7 @@
       <c r="N103" t="s">
         <v>44</v>
       </c>
-      <c r="O103">
+      <c r="O103" s="2">
         <v>5.22</v>
       </c>
       <c r="P103" t="s">
@@ -6921,7 +6934,7 @@
       <c r="N104" t="s">
         <v>44</v>
       </c>
-      <c r="O104">
+      <c r="O104" s="2">
         <v>7.93</v>
       </c>
       <c r="P104" t="s">
@@ -6977,14 +6990,14 @@
       <c r="N105" t="s">
         <v>44</v>
       </c>
-      <c r="O105">
+      <c r="O105" s="2">
         <v>78.47</v>
       </c>
       <c r="P105" t="s">
         <v>28</v>
       </c>
       <c r="Q105" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R105" t="e">
         <v>#N/A</v>
@@ -7033,7 +7046,7 @@
       <c r="N106" t="s">
         <v>59</v>
       </c>
-      <c r="O106">
+      <c r="O106" s="2">
         <v>4.3600000000000003</v>
       </c>
       <c r="P106" t="s">
@@ -7089,7 +7102,7 @@
       <c r="N107" t="s">
         <v>131</v>
       </c>
-      <c r="O107">
+      <c r="O107" s="2">
         <v>38.659999999999997</v>
       </c>
       <c r="P107" t="s">
@@ -7145,7 +7158,7 @@
       <c r="N108" t="s">
         <v>59</v>
       </c>
-      <c r="O108">
+      <c r="O108" s="2">
         <v>15.06</v>
       </c>
       <c r="P108" t="s">
@@ -7201,7 +7214,7 @@
       <c r="N109" t="s">
         <v>131</v>
       </c>
-      <c r="O109">
+      <c r="O109" s="2">
         <v>0</v>
       </c>
       <c r="P109" t="s">
@@ -7257,7 +7270,7 @@
       <c r="N110" t="s">
         <v>131</v>
       </c>
-      <c r="O110">
+      <c r="O110" s="2">
         <v>118.1</v>
       </c>
       <c r="P110" t="s">
@@ -7313,11 +7326,11 @@
       <c r="N111" t="s">
         <v>131</v>
       </c>
-      <c r="O111">
+      <c r="O111" s="2">
         <v>6.36</v>
       </c>
       <c r="P111" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q111" t="s">
         <v>28</v>
@@ -7369,7 +7382,7 @@
       <c r="N112" t="s">
         <v>44</v>
       </c>
-      <c r="O112">
+      <c r="O112" s="2">
         <v>14.23</v>
       </c>
       <c r="P112" t="s">
@@ -7425,7 +7438,7 @@
       <c r="N113" t="s">
         <v>44</v>
       </c>
-      <c r="O113">
+      <c r="O113" s="2">
         <v>0</v>
       </c>
       <c r="P113" t="s">
@@ -7479,13 +7492,13 @@
         <v>631115</v>
       </c>
       <c r="N114" t="s">
-        <v>131</v>
-      </c>
-      <c r="O114">
-        <v>3.64</v>
+        <v>59</v>
+      </c>
+      <c r="O114" s="2">
+        <v>2.0499999999999998</v>
       </c>
       <c r="P114" t="s">
-        <v>243</v>
+        <v>28</v>
       </c>
       <c r="Q114" t="s">
         <v>28</v>
@@ -7537,7 +7550,7 @@
       <c r="N115" t="s">
         <v>59</v>
       </c>
-      <c r="O115">
+      <c r="O115" s="2">
         <v>3.34</v>
       </c>
       <c r="P115" t="s">
@@ -7593,7 +7606,7 @@
       <c r="N116" t="s">
         <v>131</v>
       </c>
-      <c r="O116">
+      <c r="O116" s="2">
         <v>4.1900000000000004</v>
       </c>
       <c r="P116" t="s">
@@ -7649,7 +7662,7 @@
       <c r="N117" t="s">
         <v>131</v>
       </c>
-      <c r="O117">
+      <c r="O117" s="2">
         <v>2.34</v>
       </c>
       <c r="P117" t="s">
@@ -7705,7 +7718,7 @@
       <c r="N118" t="s">
         <v>44</v>
       </c>
-      <c r="O118">
+      <c r="O118" s="2">
         <v>8.07</v>
       </c>
       <c r="P118" t="s">
@@ -7761,7 +7774,7 @@
       <c r="N119" t="s">
         <v>131</v>
       </c>
-      <c r="O119">
+      <c r="O119" s="2">
         <v>7.53</v>
       </c>
       <c r="P119" t="s">
@@ -7817,7 +7830,7 @@
       <c r="N120" t="s">
         <v>131</v>
       </c>
-      <c r="O120">
+      <c r="O120" s="2">
         <v>80.19</v>
       </c>
       <c r="P120" t="s">
@@ -7873,11 +7886,11 @@
       <c r="N121" t="s">
         <v>131</v>
       </c>
-      <c r="O121">
+      <c r="O121" s="2">
         <v>3.01</v>
       </c>
       <c r="P121" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q121" t="s">
         <v>28</v>
@@ -7929,11 +7942,11 @@
       <c r="N122" t="s">
         <v>131</v>
       </c>
-      <c r="O122">
+      <c r="O122" s="2">
         <v>3.6</v>
       </c>
       <c r="P122" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q122" t="s">
         <v>28</v>
@@ -7985,14 +7998,14 @@
       <c r="N123" t="s">
         <v>44</v>
       </c>
-      <c r="O123">
+      <c r="O123" s="2">
         <v>0</v>
       </c>
       <c r="P123" t="s">
         <v>28</v>
       </c>
       <c r="Q123" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R123" t="e">
         <v>#N/A</v>
@@ -8041,11 +8054,11 @@
       <c r="N124" t="s">
         <v>131</v>
       </c>
-      <c r="O124">
+      <c r="O124" s="2">
         <v>76.19</v>
       </c>
       <c r="P124" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="Q124" t="s">
         <v>28</v>
@@ -8097,7 +8110,7 @@
       <c r="N125" t="s">
         <v>131</v>
       </c>
-      <c r="O125">
+      <c r="O125" s="2">
         <v>85.98</v>
       </c>
       <c r="P125" t="s">
@@ -8153,11 +8166,11 @@
       <c r="N126" t="s">
         <v>131</v>
       </c>
-      <c r="O126">
-        <v>0</v>
+      <c r="O126" s="2">
+        <v>3.61</v>
       </c>
       <c r="P126" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q126" t="s">
         <v>28</v>
@@ -8209,7 +8222,7 @@
       <c r="N127" t="s">
         <v>131</v>
       </c>
-      <c r="O127">
+      <c r="O127" s="2">
         <v>10.29</v>
       </c>
       <c r="P127" t="s">
@@ -8265,7 +8278,7 @@
       <c r="N128" t="s">
         <v>131</v>
       </c>
-      <c r="O128">
+      <c r="O128" s="2">
         <v>43.16</v>
       </c>
       <c r="P128" t="s">
@@ -8321,7 +8334,7 @@
       <c r="N129" t="s">
         <v>131</v>
       </c>
-      <c r="O129">
+      <c r="O129" s="2">
         <v>43.4</v>
       </c>
       <c r="P129" t="s">
@@ -8377,7 +8390,7 @@
       <c r="N130" t="s">
         <v>131</v>
       </c>
-      <c r="O130">
+      <c r="O130" s="2">
         <v>4.38</v>
       </c>
       <c r="P130" t="s">
@@ -8433,7 +8446,7 @@
       <c r="N131" t="s">
         <v>131</v>
       </c>
-      <c r="O131">
+      <c r="O131" s="2">
         <v>7.02</v>
       </c>
       <c r="P131" t="s">
@@ -8451,10 +8464,10 @@
         <v>191</v>
       </c>
       <c r="B132" t="s">
+        <v>244</v>
+      </c>
+      <c r="C132" t="s">
         <v>245</v>
-      </c>
-      <c r="C132" t="s">
-        <v>246</v>
       </c>
       <c r="D132" t="s">
         <v>20</v>
@@ -8466,7 +8479,7 @@
         <v>22</v>
       </c>
       <c r="G132" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H132" s="2">
         <v>22</v>
@@ -8489,7 +8502,7 @@
       <c r="N132" t="s">
         <v>131</v>
       </c>
-      <c r="O132">
+      <c r="O132" s="2">
         <v>35.64</v>
       </c>
       <c r="P132" t="s">
@@ -8498,8 +8511,8 @@
       <c r="Q132" t="s">
         <v>28</v>
       </c>
-      <c r="R132" t="e">
-        <v>#N/A</v>
+      <c r="R132">
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
@@ -8507,7 +8520,7 @@
         <v>70</v>
       </c>
       <c r="B133" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C133" t="s">
         <v>19</v>
@@ -8522,7 +8535,7 @@
         <v>90</v>
       </c>
       <c r="G133" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H133" s="2">
         <v>22</v>
@@ -8545,7 +8558,7 @@
       <c r="N133" t="s">
         <v>131</v>
       </c>
-      <c r="O133">
+      <c r="O133" s="2">
         <v>2.71</v>
       </c>
       <c r="P133" t="s">
@@ -8554,8 +8567,8 @@
       <c r="Q133" t="s">
         <v>28</v>
       </c>
-      <c r="R133" t="e">
-        <v>#N/A</v>
+      <c r="R133">
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
@@ -8563,7 +8576,7 @@
         <v>221</v>
       </c>
       <c r="B134" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C134" t="s">
         <v>193</v>
@@ -8601,7 +8614,7 @@
       <c r="N134" t="s">
         <v>131</v>
       </c>
-      <c r="O134">
+      <c r="O134" s="2">
         <v>0</v>
       </c>
       <c r="P134" t="s">
@@ -8619,7 +8632,7 @@
         <v>70</v>
       </c>
       <c r="B135" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C135" t="s">
         <v>19</v>
@@ -8657,7 +8670,7 @@
       <c r="N135" t="s">
         <v>131</v>
       </c>
-      <c r="O135">
+      <c r="O135" s="2">
         <v>3.99</v>
       </c>
       <c r="P135" t="s">
@@ -8666,8 +8679,8 @@
       <c r="Q135" t="s">
         <v>28</v>
       </c>
-      <c r="R135" t="e">
-        <v>#N/A</v>
+      <c r="R135">
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
@@ -8675,7 +8688,7 @@
         <v>70</v>
       </c>
       <c r="B136" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C136" t="s">
         <v>19</v>
@@ -8713,7 +8726,7 @@
       <c r="N136" t="s">
         <v>131</v>
       </c>
-      <c r="O136">
+      <c r="O136" s="2">
         <v>3.31</v>
       </c>
       <c r="P136" t="s">
@@ -8722,8 +8735,8 @@
       <c r="Q136" t="s">
         <v>28</v>
       </c>
-      <c r="R136" t="e">
-        <v>#N/A</v>
+      <c r="R136">
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.25">
@@ -8731,7 +8744,7 @@
         <v>191</v>
       </c>
       <c r="B137" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C137" t="s">
         <v>193</v>
@@ -8746,7 +8759,7 @@
         <v>22</v>
       </c>
       <c r="G137" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H137" s="2">
         <v>26</v>
@@ -8767,19 +8780,187 @@
         <v>640237</v>
       </c>
       <c r="N137" t="s">
+        <v>44</v>
+      </c>
+      <c r="O137" s="2">
+        <v>3.78</v>
+      </c>
+      <c r="P137" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>256</v>
+      </c>
+      <c r="R137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>191</v>
+      </c>
+      <c r="B138" t="s">
+        <v>257</v>
+      </c>
+      <c r="C138" t="s">
+        <v>193</v>
+      </c>
+      <c r="D138" t="s">
+        <v>20</v>
+      </c>
+      <c r="E138" t="s">
+        <v>194</v>
+      </c>
+      <c r="F138" t="s">
+        <v>90</v>
+      </c>
+      <c r="G138" t="s">
+        <v>91</v>
+      </c>
+      <c r="H138" s="2">
+        <v>27</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L138" s="1">
+        <v>46322</v>
+      </c>
+      <c r="M138">
+        <v>640462</v>
+      </c>
+      <c r="N138" t="s">
         <v>131</v>
       </c>
-      <c r="O137">
-        <v>3.78</v>
-      </c>
-      <c r="P137" t="s">
+      <c r="O138" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="P138" t="s">
         <v>35</v>
       </c>
-      <c r="Q137" t="s">
-        <v>28</v>
-      </c>
-      <c r="R137" t="e">
+      <c r="Q138" t="s">
+        <v>28</v>
+      </c>
+      <c r="R138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>221</v>
+      </c>
+      <c r="B139" t="s">
+        <v>258</v>
+      </c>
+      <c r="C139" t="s">
+        <v>193</v>
+      </c>
+      <c r="D139" t="s">
+        <v>20</v>
+      </c>
+      <c r="E139" t="s">
+        <v>234</v>
+      </c>
+      <c r="F139" t="s">
+        <v>259</v>
+      </c>
+      <c r="G139" t="s">
+        <v>259</v>
+      </c>
+      <c r="H139" s="2">
+        <v>27</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L139" s="1">
+        <v>46322</v>
+      </c>
+      <c r="M139">
+        <v>641061</v>
+      </c>
+      <c r="N139" t="s">
+        <v>131</v>
+      </c>
+      <c r="O139" s="2">
+        <v>5.15</v>
+      </c>
+      <c r="P139" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>28</v>
+      </c>
+      <c r="R139" t="e">
         <v>#N/A</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>216</v>
+      </c>
+      <c r="B140" t="s">
+        <v>260</v>
+      </c>
+      <c r="C140" t="s">
+        <v>193</v>
+      </c>
+      <c r="D140" t="s">
+        <v>20</v>
+      </c>
+      <c r="E140" t="s">
+        <v>203</v>
+      </c>
+      <c r="F140" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" t="s">
+        <v>195</v>
+      </c>
+      <c r="H140" s="2">
+        <v>27</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L140" s="1">
+        <v>46322</v>
+      </c>
+      <c r="M140">
+        <v>640827</v>
+      </c>
+      <c r="N140" t="s">
+        <v>131</v>
+      </c>
+      <c r="O140" s="2">
+        <v>0</v>
+      </c>
+      <c r="P140" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>28</v>
+      </c>
+      <c r="R140">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10171,14 +10352,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10443,21 +10622,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10482,9 +10660,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="297" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4BACB2F-0C34-4C1F-B903-31DE490C5182}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E5122A9-57CD-43F5-B45C-65BEADDAAD6E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="263">
   <si>
     <t>Usuário</t>
   </si>
@@ -821,10 +821,16 @@
     <t>JOAO CARLOS JUNIO DOS SANTOS</t>
   </si>
   <si>
-    <t>(vazio)</t>
-  </si>
-  <si>
     <t>SANTA TERRA ATACADISTA DE CEREAIS LTDA</t>
+  </si>
+  <si>
+    <t>TROCA DE CARTERIA</t>
+  </si>
+  <si>
+    <t>DAVID GREGORIO SILVA CARRANZA</t>
+  </si>
+  <si>
+    <t>MARIA VANIA ROCHA DA CRUZ</t>
   </si>
 </sst>
 </file>
@@ -1150,13 +1156,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:R142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1202,7 +1207,7 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
@@ -1258,7 +1263,7 @@
       <c r="N2" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2">
         <v>1.41</v>
       </c>
       <c r="P2" t="s">
@@ -1314,7 +1319,7 @@
       <c r="N3" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3">
         <v>34.979999999999997</v>
       </c>
       <c r="P3" t="s">
@@ -1370,7 +1375,7 @@
       <c r="N4" t="s">
         <v>59</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4">
         <v>30.92</v>
       </c>
       <c r="P4" t="s">
@@ -1423,7 +1428,7 @@
       <c r="N5" t="s">
         <v>44</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5">
         <v>7.85</v>
       </c>
       <c r="P5" t="s">
@@ -1479,7 +1484,7 @@
       <c r="N6" t="s">
         <v>44</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6">
         <v>67.37</v>
       </c>
       <c r="P6" t="s">
@@ -1532,7 +1537,7 @@
       <c r="N7" t="s">
         <v>131</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7">
         <v>36.31</v>
       </c>
       <c r="P7" t="s">
@@ -1585,7 +1590,7 @@
       <c r="N8" t="s">
         <v>44</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8">
         <v>27.46</v>
       </c>
       <c r="P8" t="s">
@@ -1638,7 +1643,7 @@
       <c r="N9" t="s">
         <v>131</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9">
         <v>10</v>
       </c>
       <c r="P9" t="s">
@@ -1691,7 +1696,7 @@
       <c r="N10" t="s">
         <v>44</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10">
         <v>10.44</v>
       </c>
       <c r="P10" t="s">
@@ -1744,7 +1749,7 @@
       <c r="N11" t="s">
         <v>44</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11">
         <v>7</v>
       </c>
       <c r="P11" t="s">
@@ -1797,7 +1802,7 @@
       <c r="N12" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12">
         <v>41.35</v>
       </c>
       <c r="P12" t="s">
@@ -1850,7 +1855,7 @@
       <c r="N13" t="s">
         <v>44</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13">
         <v>3.5</v>
       </c>
       <c r="P13" t="s">
@@ -1906,7 +1911,7 @@
       <c r="N14" t="s">
         <v>153</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="O14" t="s">
         <v>153</v>
       </c>
       <c r="P14" t="s">
@@ -1959,7 +1964,7 @@
       <c r="N15" t="s">
         <v>59</v>
       </c>
-      <c r="O15" s="2">
+      <c r="O15">
         <v>7.87</v>
       </c>
       <c r="P15" t="s">
@@ -2012,7 +2017,7 @@
       <c r="N16" t="s">
         <v>59</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16">
         <v>3.66</v>
       </c>
       <c r="P16" t="s">
@@ -2065,7 +2070,7 @@
       <c r="N17" t="s">
         <v>44</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17">
         <v>9.7899999999999991</v>
       </c>
       <c r="P17" t="s">
@@ -2121,7 +2126,7 @@
       <c r="N18" t="s">
         <v>44</v>
       </c>
-      <c r="O18" s="2">
+      <c r="O18">
         <v>6.9</v>
       </c>
       <c r="P18" t="s">
@@ -2174,7 +2179,7 @@
       <c r="N19" t="s">
         <v>44</v>
       </c>
-      <c r="O19" s="2">
+      <c r="O19">
         <v>102.72</v>
       </c>
       <c r="P19" t="s">
@@ -2230,7 +2235,7 @@
       <c r="N20" t="s">
         <v>44</v>
       </c>
-      <c r="O20" s="2">
+      <c r="O20">
         <v>41.62</v>
       </c>
       <c r="P20" t="s">
@@ -2286,7 +2291,7 @@
       <c r="N21" t="s">
         <v>131</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21">
         <v>4.63</v>
       </c>
       <c r="P21" t="s">
@@ -2342,7 +2347,7 @@
       <c r="N22" t="s">
         <v>131</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22">
         <v>1.96</v>
       </c>
       <c r="P22" t="s">
@@ -2398,7 +2403,7 @@
       <c r="N23" t="s">
         <v>44</v>
       </c>
-      <c r="O23" s="2">
+      <c r="O23">
         <v>1.89</v>
       </c>
       <c r="P23" t="s">
@@ -2454,7 +2459,7 @@
       <c r="N24" t="s">
         <v>131</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24">
         <v>6.12</v>
       </c>
       <c r="P24" t="s">
@@ -2510,7 +2515,7 @@
       <c r="N25" t="s">
         <v>59</v>
       </c>
-      <c r="O25" s="2">
+      <c r="O25">
         <v>10.5</v>
       </c>
       <c r="P25" t="s">
@@ -2566,7 +2571,7 @@
       <c r="N26" t="s">
         <v>44</v>
       </c>
-      <c r="O26" s="2">
+      <c r="O26">
         <v>8.3699999999999992</v>
       </c>
       <c r="P26" t="s">
@@ -2622,7 +2627,7 @@
       <c r="N27" t="s">
         <v>44</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O27">
         <v>2.98</v>
       </c>
       <c r="P27" t="s">
@@ -2678,7 +2683,7 @@
       <c r="N28" t="s">
         <v>131</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O28">
         <v>61.58</v>
       </c>
       <c r="P28" t="s">
@@ -2734,7 +2739,7 @@
       <c r="N29" t="s">
         <v>44</v>
       </c>
-      <c r="O29" s="2">
+      <c r="O29">
         <v>91.5</v>
       </c>
       <c r="P29" t="s">
@@ -2790,7 +2795,7 @@
       <c r="N30" t="s">
         <v>59</v>
       </c>
-      <c r="O30" s="2">
+      <c r="O30">
         <v>5.13</v>
       </c>
       <c r="P30" t="s">
@@ -2846,7 +2851,7 @@
       <c r="N31" t="s">
         <v>131</v>
       </c>
-      <c r="O31" s="2">
+      <c r="O31">
         <v>37.299999999999997</v>
       </c>
       <c r="P31" t="s">
@@ -2902,7 +2907,7 @@
       <c r="N32" t="s">
         <v>153</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="O32" t="s">
         <v>153</v>
       </c>
       <c r="P32" t="s">
@@ -2958,7 +2963,7 @@
       <c r="N33" t="s">
         <v>44</v>
       </c>
-      <c r="O33" s="2">
+      <c r="O33">
         <v>3.73</v>
       </c>
       <c r="P33" t="s">
@@ -3014,7 +3019,7 @@
       <c r="N34" t="s">
         <v>44</v>
       </c>
-      <c r="O34" s="2">
+      <c r="O34">
         <v>4.54</v>
       </c>
       <c r="P34" t="s">
@@ -3070,7 +3075,7 @@
       <c r="N35" t="s">
         <v>59</v>
       </c>
-      <c r="O35" s="2">
+      <c r="O35">
         <v>20.25</v>
       </c>
       <c r="P35" t="s">
@@ -3126,7 +3131,7 @@
       <c r="N36" t="s">
         <v>44</v>
       </c>
-      <c r="O36" s="2">
+      <c r="O36">
         <v>6.23</v>
       </c>
       <c r="P36" t="s">
@@ -3182,7 +3187,7 @@
       <c r="N37" t="s">
         <v>44</v>
       </c>
-      <c r="O37" s="2">
+      <c r="O37">
         <v>0</v>
       </c>
       <c r="P37" t="s">
@@ -3238,7 +3243,7 @@
       <c r="N38" t="s">
         <v>59</v>
       </c>
-      <c r="O38" s="2">
+      <c r="O38">
         <v>3.39</v>
       </c>
       <c r="P38" t="s">
@@ -3294,7 +3299,7 @@
       <c r="N39" t="s">
         <v>59</v>
       </c>
-      <c r="O39" s="2">
+      <c r="O39">
         <v>10.9</v>
       </c>
       <c r="P39" t="s">
@@ -3350,7 +3355,7 @@
       <c r="N40" t="s">
         <v>131</v>
       </c>
-      <c r="O40" s="2">
+      <c r="O40">
         <v>19.47</v>
       </c>
       <c r="P40" t="s">
@@ -3406,7 +3411,7 @@
       <c r="N41" t="s">
         <v>44</v>
       </c>
-      <c r="O41" s="2">
+      <c r="O41">
         <v>3.19</v>
       </c>
       <c r="P41" t="s">
@@ -3462,7 +3467,7 @@
       <c r="N42" t="s">
         <v>44</v>
       </c>
-      <c r="O42" s="2">
+      <c r="O42">
         <v>7.15</v>
       </c>
       <c r="P42" t="s">
@@ -3518,7 +3523,7 @@
       <c r="N43" t="s">
         <v>131</v>
       </c>
-      <c r="O43" s="2">
+      <c r="O43">
         <v>9.2200000000000006</v>
       </c>
       <c r="P43" t="s">
@@ -3574,7 +3579,7 @@
       <c r="N44" t="s">
         <v>44</v>
       </c>
-      <c r="O44" s="2">
+      <c r="O44">
         <v>4.63</v>
       </c>
       <c r="P44" t="s">
@@ -3630,7 +3635,7 @@
       <c r="N45" t="s">
         <v>44</v>
       </c>
-      <c r="O45" s="2">
+      <c r="O45">
         <v>20.53</v>
       </c>
       <c r="P45" t="s">
@@ -3686,7 +3691,7 @@
       <c r="N46" t="s">
         <v>44</v>
       </c>
-      <c r="O46" s="2">
+      <c r="O46">
         <v>8.44</v>
       </c>
       <c r="P46" t="s">
@@ -3742,7 +3747,7 @@
       <c r="N47" t="s">
         <v>131</v>
       </c>
-      <c r="O47" s="2">
+      <c r="O47">
         <v>4.17</v>
       </c>
       <c r="P47" t="s">
@@ -3798,7 +3803,7 @@
       <c r="N48" t="s">
         <v>44</v>
       </c>
-      <c r="O48" s="2">
+      <c r="O48">
         <v>10.1</v>
       </c>
       <c r="P48" t="s">
@@ -3852,16 +3857,16 @@
         <v>611797</v>
       </c>
       <c r="N49" t="s">
-        <v>131</v>
-      </c>
-      <c r="O49" s="2">
+        <v>44</v>
+      </c>
+      <c r="O49">
         <v>9.85</v>
       </c>
       <c r="P49" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q49" t="s">
-        <v>28</v>
+        <v>260</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -3910,7 +3915,7 @@
       <c r="N50" t="s">
         <v>44</v>
       </c>
-      <c r="O50" s="2">
+      <c r="O50">
         <v>2.89</v>
       </c>
       <c r="P50" t="s">
@@ -3966,7 +3971,7 @@
       <c r="N51" t="s">
         <v>59</v>
       </c>
-      <c r="O51" s="2">
+      <c r="O51">
         <v>441</v>
       </c>
       <c r="P51" t="s">
@@ -4022,7 +4027,7 @@
       <c r="N52" t="s">
         <v>44</v>
       </c>
-      <c r="O52" s="2">
+      <c r="O52">
         <v>2.33</v>
       </c>
       <c r="P52" t="s">
@@ -4078,7 +4083,7 @@
       <c r="N53" t="s">
         <v>44</v>
       </c>
-      <c r="O53" s="2">
+      <c r="O53">
         <v>7.95</v>
       </c>
       <c r="P53" t="s">
@@ -4134,7 +4139,7 @@
       <c r="N54" t="s">
         <v>131</v>
       </c>
-      <c r="O54" s="2">
+      <c r="O54">
         <v>1.91</v>
       </c>
       <c r="P54" t="s">
@@ -4190,7 +4195,7 @@
       <c r="N55" t="s">
         <v>131</v>
       </c>
-      <c r="O55" s="2">
+      <c r="O55">
         <v>12.23</v>
       </c>
       <c r="P55" t="s">
@@ -4246,7 +4251,7 @@
       <c r="N56" t="s">
         <v>131</v>
       </c>
-      <c r="O56" s="2">
+      <c r="O56">
         <v>16.34</v>
       </c>
       <c r="P56" t="s">
@@ -4302,7 +4307,7 @@
       <c r="N57" t="s">
         <v>44</v>
       </c>
-      <c r="O57" s="2">
+      <c r="O57">
         <v>11.93</v>
       </c>
       <c r="P57" t="s">
@@ -4358,7 +4363,7 @@
       <c r="N58" t="s">
         <v>44</v>
       </c>
-      <c r="O58" s="2">
+      <c r="O58">
         <v>35.65</v>
       </c>
       <c r="P58" t="s">
@@ -4414,7 +4419,7 @@
       <c r="N59" t="s">
         <v>131</v>
       </c>
-      <c r="O59" s="2">
+      <c r="O59">
         <v>6.36</v>
       </c>
       <c r="P59" t="s">
@@ -4470,7 +4475,7 @@
       <c r="N60" t="s">
         <v>131</v>
       </c>
-      <c r="O60" s="2">
+      <c r="O60">
         <v>32.82</v>
       </c>
       <c r="P60" t="s">
@@ -4526,7 +4531,7 @@
       <c r="N61" t="s">
         <v>131</v>
       </c>
-      <c r="O61" s="2">
+      <c r="O61">
         <v>21.23</v>
       </c>
       <c r="P61" t="s">
@@ -4582,7 +4587,7 @@
       <c r="N62" t="s">
         <v>131</v>
       </c>
-      <c r="O62" s="2">
+      <c r="O62">
         <v>2.2200000000000002</v>
       </c>
       <c r="P62" t="s">
@@ -4638,7 +4643,7 @@
       <c r="N63" t="s">
         <v>131</v>
       </c>
-      <c r="O63" s="2">
+      <c r="O63">
         <v>8.4600000000000009</v>
       </c>
       <c r="P63" t="s">
@@ -4694,7 +4699,7 @@
       <c r="N64" t="s">
         <v>44</v>
       </c>
-      <c r="O64" s="2">
+      <c r="O64">
         <v>2.76</v>
       </c>
       <c r="P64" t="s">
@@ -4750,7 +4755,7 @@
       <c r="N65" t="s">
         <v>59</v>
       </c>
-      <c r="O65" s="2">
+      <c r="O65">
         <v>14.6</v>
       </c>
       <c r="P65" t="s">
@@ -4806,7 +4811,7 @@
       <c r="N66" t="s">
         <v>131</v>
       </c>
-      <c r="O66" s="2">
+      <c r="O66">
         <v>4.68</v>
       </c>
       <c r="P66" t="s">
@@ -4862,7 +4867,7 @@
       <c r="N67" t="s">
         <v>59</v>
       </c>
-      <c r="O67" s="2">
+      <c r="O67">
         <v>8.5399999999999991</v>
       </c>
       <c r="P67" t="s">
@@ -4918,7 +4923,7 @@
       <c r="N68" t="s">
         <v>131</v>
       </c>
-      <c r="O68" s="2">
+      <c r="O68">
         <v>104.04</v>
       </c>
       <c r="P68" t="s">
@@ -4974,7 +4979,7 @@
       <c r="N69" t="s">
         <v>131</v>
       </c>
-      <c r="O69" s="2">
+      <c r="O69">
         <v>0</v>
       </c>
       <c r="P69" t="s">
@@ -5030,7 +5035,7 @@
       <c r="N70" t="s">
         <v>59</v>
       </c>
-      <c r="O70" s="2">
+      <c r="O70">
         <v>14.62</v>
       </c>
       <c r="P70" t="s">
@@ -5086,7 +5091,7 @@
       <c r="N71" t="s">
         <v>131</v>
       </c>
-      <c r="O71" s="2">
+      <c r="O71">
         <v>6.46</v>
       </c>
       <c r="P71" t="s">
@@ -5142,7 +5147,7 @@
       <c r="N72" t="s">
         <v>44</v>
       </c>
-      <c r="O72" s="2">
+      <c r="O72">
         <v>8.57</v>
       </c>
       <c r="P72" t="s">
@@ -5198,7 +5203,7 @@
       <c r="N73" t="s">
         <v>131</v>
       </c>
-      <c r="O73" s="2">
+      <c r="O73">
         <v>8.9600000000000009</v>
       </c>
       <c r="P73" t="s">
@@ -5254,7 +5259,7 @@
       <c r="N74" t="s">
         <v>59</v>
       </c>
-      <c r="O74" s="2">
+      <c r="O74">
         <v>11.75</v>
       </c>
       <c r="P74" t="s">
@@ -5310,7 +5315,7 @@
       <c r="N75" t="s">
         <v>131</v>
       </c>
-      <c r="O75" s="2">
+      <c r="O75">
         <v>5.95</v>
       </c>
       <c r="P75" t="s">
@@ -5366,7 +5371,7 @@
       <c r="N76" t="s">
         <v>131</v>
       </c>
-      <c r="O76" s="2">
+      <c r="O76">
         <v>4.0999999999999996</v>
       </c>
       <c r="P76" t="s">
@@ -5422,7 +5427,7 @@
       <c r="N77" t="s">
         <v>131</v>
       </c>
-      <c r="O77" s="2">
+      <c r="O77">
         <v>5.46</v>
       </c>
       <c r="P77" t="s">
@@ -5478,7 +5483,7 @@
       <c r="N78" t="s">
         <v>131</v>
       </c>
-      <c r="O78" s="2">
+      <c r="O78">
         <v>5.33</v>
       </c>
       <c r="P78" t="s">
@@ -5534,7 +5539,7 @@
       <c r="N79" t="s">
         <v>59</v>
       </c>
-      <c r="O79" s="2">
+      <c r="O79">
         <v>38.840000000000003</v>
       </c>
       <c r="P79" t="s">
@@ -5590,7 +5595,7 @@
       <c r="N80" t="s">
         <v>59</v>
       </c>
-      <c r="O80" s="2">
+      <c r="O80">
         <v>118.5</v>
       </c>
       <c r="P80" t="s">
@@ -5646,7 +5651,7 @@
       <c r="N81" t="s">
         <v>59</v>
       </c>
-      <c r="O81" s="2">
+      <c r="O81">
         <v>9.11</v>
       </c>
       <c r="P81" t="s">
@@ -5702,7 +5707,7 @@
       <c r="N82" t="s">
         <v>131</v>
       </c>
-      <c r="O82" s="2">
+      <c r="O82">
         <v>8.34</v>
       </c>
       <c r="P82" t="s">
@@ -5758,7 +5763,7 @@
       <c r="N83" t="s">
         <v>131</v>
       </c>
-      <c r="O83" s="2">
+      <c r="O83">
         <v>12.79</v>
       </c>
       <c r="P83" t="s">
@@ -5814,7 +5819,7 @@
       <c r="N84" t="s">
         <v>131</v>
       </c>
-      <c r="O84" s="2">
+      <c r="O84">
         <v>3.73</v>
       </c>
       <c r="P84" t="s">
@@ -5870,7 +5875,7 @@
       <c r="N85" t="s">
         <v>131</v>
       </c>
-      <c r="O85" s="2">
+      <c r="O85">
         <v>22.65</v>
       </c>
       <c r="P85" t="s">
@@ -5926,7 +5931,7 @@
       <c r="N86" t="s">
         <v>59</v>
       </c>
-      <c r="O86" s="2">
+      <c r="O86">
         <v>42.8</v>
       </c>
       <c r="P86" t="s">
@@ -5982,7 +5987,7 @@
       <c r="N87" t="s">
         <v>131</v>
       </c>
-      <c r="O87" s="2">
+      <c r="O87">
         <v>29.19</v>
       </c>
       <c r="P87" t="s">
@@ -6038,7 +6043,7 @@
       <c r="N88" t="s">
         <v>131</v>
       </c>
-      <c r="O88" s="2">
+      <c r="O88">
         <v>3.5</v>
       </c>
       <c r="P88" t="s">
@@ -6094,7 +6099,7 @@
       <c r="N89" t="s">
         <v>131</v>
       </c>
-      <c r="O89" s="2">
+      <c r="O89">
         <v>4.5199999999999996</v>
       </c>
       <c r="P89" t="s">
@@ -6150,7 +6155,7 @@
       <c r="N90" t="s">
         <v>59</v>
       </c>
-      <c r="O90" s="2">
+      <c r="O90">
         <v>14.46</v>
       </c>
       <c r="P90" t="s">
@@ -6206,7 +6211,7 @@
       <c r="N91" t="s">
         <v>131</v>
       </c>
-      <c r="O91" s="2">
+      <c r="O91">
         <v>17.84</v>
       </c>
       <c r="P91" t="s">
@@ -6262,7 +6267,7 @@
       <c r="N92" t="s">
         <v>131</v>
       </c>
-      <c r="O92" s="2">
+      <c r="O92">
         <v>16.39</v>
       </c>
       <c r="P92" t="s">
@@ -6318,7 +6323,7 @@
       <c r="N93" t="s">
         <v>59</v>
       </c>
-      <c r="O93" s="2">
+      <c r="O93">
         <v>38.840000000000003</v>
       </c>
       <c r="P93" t="s">
@@ -6374,7 +6379,7 @@
       <c r="N94" t="s">
         <v>59</v>
       </c>
-      <c r="O94" s="2">
+      <c r="O94">
         <v>38.840000000000003</v>
       </c>
       <c r="P94" t="s">
@@ -6430,7 +6435,7 @@
       <c r="N95" t="s">
         <v>131</v>
       </c>
-      <c r="O95" s="2">
+      <c r="O95">
         <v>11.61</v>
       </c>
       <c r="P95" t="s">
@@ -6486,7 +6491,7 @@
       <c r="N96" t="s">
         <v>131</v>
       </c>
-      <c r="O96" s="2">
+      <c r="O96">
         <v>7.5</v>
       </c>
       <c r="P96" t="s">
@@ -6542,7 +6547,7 @@
       <c r="N97" t="s">
         <v>131</v>
       </c>
-      <c r="O97" s="2">
+      <c r="O97">
         <v>4.3</v>
       </c>
       <c r="P97" t="s">
@@ -6598,7 +6603,7 @@
       <c r="N98" t="s">
         <v>131</v>
       </c>
-      <c r="O98" s="2">
+      <c r="O98">
         <v>16.3</v>
       </c>
       <c r="P98" t="s">
@@ -6654,7 +6659,7 @@
       <c r="N99" t="s">
         <v>131</v>
       </c>
-      <c r="O99" s="2">
+      <c r="O99">
         <v>2.42</v>
       </c>
       <c r="P99" t="s">
@@ -6710,7 +6715,7 @@
       <c r="N100" t="s">
         <v>131</v>
       </c>
-      <c r="O100" s="2">
+      <c r="O100">
         <v>9.1300000000000008</v>
       </c>
       <c r="P100" t="s">
@@ -6766,7 +6771,7 @@
       <c r="N101" t="s">
         <v>44</v>
       </c>
-      <c r="O101" s="2">
+      <c r="O101">
         <v>3.88</v>
       </c>
       <c r="P101" t="s">
@@ -6822,7 +6827,7 @@
       <c r="N102" t="s">
         <v>131</v>
       </c>
-      <c r="O102" s="2">
+      <c r="O102">
         <v>1.42</v>
       </c>
       <c r="P102" t="s">
@@ -6878,7 +6883,7 @@
       <c r="N103" t="s">
         <v>44</v>
       </c>
-      <c r="O103" s="2">
+      <c r="O103">
         <v>5.22</v>
       </c>
       <c r="P103" t="s">
@@ -6934,7 +6939,7 @@
       <c r="N104" t="s">
         <v>44</v>
       </c>
-      <c r="O104" s="2">
+      <c r="O104">
         <v>7.93</v>
       </c>
       <c r="P104" t="s">
@@ -6990,7 +6995,7 @@
       <c r="N105" t="s">
         <v>44</v>
       </c>
-      <c r="O105" s="2">
+      <c r="O105">
         <v>78.47</v>
       </c>
       <c r="P105" t="s">
@@ -7046,7 +7051,7 @@
       <c r="N106" t="s">
         <v>59</v>
       </c>
-      <c r="O106" s="2">
+      <c r="O106">
         <v>4.3600000000000003</v>
       </c>
       <c r="P106" t="s">
@@ -7102,7 +7107,7 @@
       <c r="N107" t="s">
         <v>131</v>
       </c>
-      <c r="O107" s="2">
+      <c r="O107">
         <v>38.659999999999997</v>
       </c>
       <c r="P107" t="s">
@@ -7158,7 +7163,7 @@
       <c r="N108" t="s">
         <v>59</v>
       </c>
-      <c r="O108" s="2">
+      <c r="O108">
         <v>15.06</v>
       </c>
       <c r="P108" t="s">
@@ -7214,7 +7219,7 @@
       <c r="N109" t="s">
         <v>131</v>
       </c>
-      <c r="O109" s="2">
+      <c r="O109">
         <v>0</v>
       </c>
       <c r="P109" t="s">
@@ -7270,7 +7275,7 @@
       <c r="N110" t="s">
         <v>131</v>
       </c>
-      <c r="O110" s="2">
+      <c r="O110">
         <v>118.1</v>
       </c>
       <c r="P110" t="s">
@@ -7326,7 +7331,7 @@
       <c r="N111" t="s">
         <v>131</v>
       </c>
-      <c r="O111" s="2">
+      <c r="O111">
         <v>6.36</v>
       </c>
       <c r="P111" t="s">
@@ -7382,7 +7387,7 @@
       <c r="N112" t="s">
         <v>44</v>
       </c>
-      <c r="O112" s="2">
+      <c r="O112">
         <v>14.23</v>
       </c>
       <c r="P112" t="s">
@@ -7438,7 +7443,7 @@
       <c r="N113" t="s">
         <v>44</v>
       </c>
-      <c r="O113" s="2">
+      <c r="O113">
         <v>0</v>
       </c>
       <c r="P113" t="s">
@@ -7494,7 +7499,7 @@
       <c r="N114" t="s">
         <v>59</v>
       </c>
-      <c r="O114" s="2">
+      <c r="O114">
         <v>2.0499999999999998</v>
       </c>
       <c r="P114" t="s">
@@ -7550,7 +7555,7 @@
       <c r="N115" t="s">
         <v>59</v>
       </c>
-      <c r="O115" s="2">
+      <c r="O115">
         <v>3.34</v>
       </c>
       <c r="P115" t="s">
@@ -7606,7 +7611,7 @@
       <c r="N116" t="s">
         <v>131</v>
       </c>
-      <c r="O116" s="2">
+      <c r="O116">
         <v>4.1900000000000004</v>
       </c>
       <c r="P116" t="s">
@@ -7662,7 +7667,7 @@
       <c r="N117" t="s">
         <v>131</v>
       </c>
-      <c r="O117" s="2">
+      <c r="O117">
         <v>2.34</v>
       </c>
       <c r="P117" t="s">
@@ -7718,7 +7723,7 @@
       <c r="N118" t="s">
         <v>44</v>
       </c>
-      <c r="O118" s="2">
+      <c r="O118">
         <v>8.07</v>
       </c>
       <c r="P118" t="s">
@@ -7774,7 +7779,7 @@
       <c r="N119" t="s">
         <v>131</v>
       </c>
-      <c r="O119" s="2">
+      <c r="O119">
         <v>7.53</v>
       </c>
       <c r="P119" t="s">
@@ -7830,7 +7835,7 @@
       <c r="N120" t="s">
         <v>131</v>
       </c>
-      <c r="O120" s="2">
+      <c r="O120">
         <v>80.19</v>
       </c>
       <c r="P120" t="s">
@@ -7886,7 +7891,7 @@
       <c r="N121" t="s">
         <v>131</v>
       </c>
-      <c r="O121" s="2">
+      <c r="O121">
         <v>3.01</v>
       </c>
       <c r="P121" t="s">
@@ -7942,7 +7947,7 @@
       <c r="N122" t="s">
         <v>131</v>
       </c>
-      <c r="O122" s="2">
+      <c r="O122">
         <v>3.6</v>
       </c>
       <c r="P122" t="s">
@@ -7998,7 +8003,7 @@
       <c r="N123" t="s">
         <v>44</v>
       </c>
-      <c r="O123" s="2">
+      <c r="O123">
         <v>0</v>
       </c>
       <c r="P123" t="s">
@@ -8054,7 +8059,7 @@
       <c r="N124" t="s">
         <v>131</v>
       </c>
-      <c r="O124" s="2">
+      <c r="O124">
         <v>76.19</v>
       </c>
       <c r="P124" t="s">
@@ -8110,7 +8115,7 @@
       <c r="N125" t="s">
         <v>131</v>
       </c>
-      <c r="O125" s="2">
+      <c r="O125">
         <v>85.98</v>
       </c>
       <c r="P125" t="s">
@@ -8166,7 +8171,7 @@
       <c r="N126" t="s">
         <v>131</v>
       </c>
-      <c r="O126" s="2">
+      <c r="O126">
         <v>3.61</v>
       </c>
       <c r="P126" t="s">
@@ -8222,7 +8227,7 @@
       <c r="N127" t="s">
         <v>131</v>
       </c>
-      <c r="O127" s="2">
+      <c r="O127">
         <v>10.29</v>
       </c>
       <c r="P127" t="s">
@@ -8278,7 +8283,7 @@
       <c r="N128" t="s">
         <v>131</v>
       </c>
-      <c r="O128" s="2">
+      <c r="O128">
         <v>43.16</v>
       </c>
       <c r="P128" t="s">
@@ -8334,7 +8339,7 @@
       <c r="N129" t="s">
         <v>131</v>
       </c>
-      <c r="O129" s="2">
+      <c r="O129">
         <v>43.4</v>
       </c>
       <c r="P129" t="s">
@@ -8390,7 +8395,7 @@
       <c r="N130" t="s">
         <v>131</v>
       </c>
-      <c r="O130" s="2">
+      <c r="O130">
         <v>4.38</v>
       </c>
       <c r="P130" t="s">
@@ -8441,13 +8446,13 @@
         <v>46316</v>
       </c>
       <c r="M131">
-        <v>638228</v>
+        <v>641470</v>
       </c>
       <c r="N131" t="s">
         <v>131</v>
       </c>
-      <c r="O131" s="2">
-        <v>7.02</v>
+      <c r="O131">
+        <v>12.34</v>
       </c>
       <c r="P131" t="s">
         <v>35</v>
@@ -8502,7 +8507,7 @@
       <c r="N132" t="s">
         <v>131</v>
       </c>
-      <c r="O132" s="2">
+      <c r="O132">
         <v>35.64</v>
       </c>
       <c r="P132" t="s">
@@ -8558,7 +8563,7 @@
       <c r="N133" t="s">
         <v>131</v>
       </c>
-      <c r="O133" s="2">
+      <c r="O133">
         <v>2.71</v>
       </c>
       <c r="P133" t="s">
@@ -8614,7 +8619,7 @@
       <c r="N134" t="s">
         <v>131</v>
       </c>
-      <c r="O134" s="2">
+      <c r="O134">
         <v>0</v>
       </c>
       <c r="P134" t="s">
@@ -8670,7 +8675,7 @@
       <c r="N135" t="s">
         <v>131</v>
       </c>
-      <c r="O135" s="2">
+      <c r="O135">
         <v>3.99</v>
       </c>
       <c r="P135" t="s">
@@ -8726,7 +8731,7 @@
       <c r="N136" t="s">
         <v>131</v>
       </c>
-      <c r="O136" s="2">
+      <c r="O136">
         <v>3.31</v>
       </c>
       <c r="P136" t="s">
@@ -8782,7 +8787,7 @@
       <c r="N137" t="s">
         <v>44</v>
       </c>
-      <c r="O137" s="2">
+      <c r="O137">
         <v>3.78</v>
       </c>
       <c r="P137" t="s">
@@ -8838,7 +8843,7 @@
       <c r="N138" t="s">
         <v>131</v>
       </c>
-      <c r="O138" s="2">
+      <c r="O138">
         <v>2.5</v>
       </c>
       <c r="P138" t="s">
@@ -8868,10 +8873,10 @@
         <v>234</v>
       </c>
       <c r="F139" t="s">
-        <v>259</v>
+        <v>22</v>
       </c>
       <c r="G139" t="s">
-        <v>259</v>
+        <v>195</v>
       </c>
       <c r="H139" s="2">
         <v>27</v>
@@ -8894,7 +8899,7 @@
       <c r="N139" t="s">
         <v>131</v>
       </c>
-      <c r="O139" s="2">
+      <c r="O139">
         <v>5.15</v>
       </c>
       <c r="P139" t="s">
@@ -8912,7 +8917,7 @@
         <v>216</v>
       </c>
       <c r="B140" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C140" t="s">
         <v>193</v>
@@ -8950,7 +8955,7 @@
       <c r="N140" t="s">
         <v>131</v>
       </c>
-      <c r="O140" s="2">
+      <c r="O140">
         <v>0</v>
       </c>
       <c r="P140" t="s">
@@ -8961,6 +8966,118 @@
       </c>
       <c r="R140">
         <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>70</v>
+      </c>
+      <c r="B141" t="s">
+        <v>261</v>
+      </c>
+      <c r="C141" t="s">
+        <v>19</v>
+      </c>
+      <c r="D141" t="s">
+        <v>20</v>
+      </c>
+      <c r="E141" t="s">
+        <v>146</v>
+      </c>
+      <c r="F141" t="s">
+        <v>90</v>
+      </c>
+      <c r="G141" t="s">
+        <v>104</v>
+      </c>
+      <c r="H141" s="2">
+        <v>28</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L141" s="1">
+        <v>46323</v>
+      </c>
+      <c r="M141">
+        <v>641279</v>
+      </c>
+      <c r="N141" t="s">
+        <v>131</v>
+      </c>
+      <c r="O141">
+        <v>3.34</v>
+      </c>
+      <c r="P141" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>28</v>
+      </c>
+      <c r="R141" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>70</v>
+      </c>
+      <c r="B142" t="s">
+        <v>262</v>
+      </c>
+      <c r="C142" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" t="s">
+        <v>20</v>
+      </c>
+      <c r="E142" t="s">
+        <v>146</v>
+      </c>
+      <c r="F142" t="s">
+        <v>90</v>
+      </c>
+      <c r="G142" t="s">
+        <v>248</v>
+      </c>
+      <c r="H142" s="2">
+        <v>28</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L142" s="1">
+        <v>46323</v>
+      </c>
+      <c r="M142">
+        <v>641267</v>
+      </c>
+      <c r="N142" t="s">
+        <v>131</v>
+      </c>
+      <c r="O142">
+        <v>9.19</v>
+      </c>
+      <c r="P142" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>28</v>
+      </c>
+      <c r="R142" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
@@ -10352,15 +10469,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -10621,6 +10729,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10633,14 +10750,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10659,6 +10768,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E5122A9-57CD-43F5-B45C-65BEADDAAD6E}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6A18119-3B35-4F27-AA54-9EDCF517E32E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="266">
   <si>
     <t>Usuário</t>
   </si>
@@ -831,6 +831,15 @@
   </si>
   <si>
     <t>MARIA VANIA ROCHA DA CRUZ</t>
+  </si>
+  <si>
+    <t>TEREZA CRISTINA SAHDO FERREIRA FREIRE</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO HERMON LTDA</t>
+  </si>
+  <si>
+    <t>Três Marias</t>
   </si>
 </sst>
 </file>
@@ -1156,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R142"/>
+  <dimension ref="A1:R144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -4249,16 +4258,16 @@
         <v>615322</v>
       </c>
       <c r="N56" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O56">
         <v>16.34</v>
       </c>
       <c r="P56" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q56" t="s">
-        <v>28</v>
+        <v>243</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -8231,7 +8240,7 @@
         <v>10.29</v>
       </c>
       <c r="P127" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q127" t="s">
         <v>28</v>
@@ -8900,7 +8909,7 @@
         <v>131</v>
       </c>
       <c r="O139">
-        <v>5.15</v>
+        <v>5.34</v>
       </c>
       <c r="P139" t="s">
         <v>35</v>
@@ -8908,8 +8917,8 @@
       <c r="Q139" t="s">
         <v>28</v>
       </c>
-      <c r="R139" t="e">
-        <v>#N/A</v>
+      <c r="R139">
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
@@ -8949,17 +8958,17 @@
       <c r="L140" s="1">
         <v>46322</v>
       </c>
-      <c r="M140">
-        <v>640827</v>
+      <c r="M140" t="s">
+        <v>153</v>
       </c>
       <c r="N140" t="s">
-        <v>131</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="O140" t="s">
+        <v>153</v>
       </c>
       <c r="P140" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q140" t="s">
         <v>28</v>
@@ -9020,8 +9029,8 @@
       <c r="Q141" t="s">
         <v>28</v>
       </c>
-      <c r="R141" t="e">
-        <v>#N/A</v>
+      <c r="R141">
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:18" x14ac:dyDescent="0.25">
@@ -9076,7 +9085,119 @@
       <c r="Q142" t="s">
         <v>28</v>
       </c>
-      <c r="R142" t="e">
+      <c r="R142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>70</v>
+      </c>
+      <c r="B143" t="s">
+        <v>263</v>
+      </c>
+      <c r="C143" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" t="s">
+        <v>20</v>
+      </c>
+      <c r="E143" t="s">
+        <v>146</v>
+      </c>
+      <c r="F143" t="s">
+        <v>90</v>
+      </c>
+      <c r="G143" t="s">
+        <v>91</v>
+      </c>
+      <c r="H143" s="2">
+        <v>29</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L143" s="1">
+        <v>46324</v>
+      </c>
+      <c r="M143">
+        <v>641780</v>
+      </c>
+      <c r="N143" t="s">
+        <v>131</v>
+      </c>
+      <c r="O143">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P143" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>28</v>
+      </c>
+      <c r="R143" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>216</v>
+      </c>
+      <c r="B144" t="s">
+        <v>264</v>
+      </c>
+      <c r="C144" t="s">
+        <v>193</v>
+      </c>
+      <c r="D144" t="s">
+        <v>20</v>
+      </c>
+      <c r="E144" t="s">
+        <v>203</v>
+      </c>
+      <c r="F144" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144" t="s">
+        <v>265</v>
+      </c>
+      <c r="H144" s="2">
+        <v>29</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L144" s="1">
+        <v>46324</v>
+      </c>
+      <c r="M144">
+        <v>641950</v>
+      </c>
+      <c r="N144" t="s">
+        <v>131</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>28</v>
+      </c>
+      <c r="R144" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -10469,6 +10590,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -10729,27 +10870,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10766,23 +10906,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6A18119-3B35-4F27-AA54-9EDCF517E32E}"/>
+  <xr:revisionPtr revIDLastSave="312" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7ED296-5F35-46ED-A88F-B8FB63EA2383}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1995" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="268">
   <si>
     <t>Usuário</t>
   </si>
@@ -674,9 +674,6 @@
     <t>GODINHO SORVETES LTDA</t>
   </si>
   <si>
-    <t>611065 - EMPORIO MINAS</t>
-  </si>
-  <si>
     <t>THYRSO PAULO DE AGOSTINI</t>
   </si>
   <si>
@@ -794,9 +791,6 @@
     <t>FRAEVA - PRODUTOS E SERVICOS LTDA.</t>
   </si>
   <si>
-    <t>CLIENTE FECHOU EM OUTRA TITULARIDADE</t>
-  </si>
-  <si>
     <t>NEGOCIAÇÃO QUENTE</t>
   </si>
   <si>
@@ -840,6 +834,18 @@
   </si>
   <si>
     <t>Três Marias</t>
+  </si>
+  <si>
+    <t>SLA EXPIRADO</t>
+  </si>
+  <si>
+    <t>AJUSTE DE DOCUMENTAÇÃO</t>
+  </si>
+  <si>
+    <t>FELIPE DA CUNHA SILVA</t>
+  </si>
+  <si>
+    <t>ROMILDO DE ALMEIDA MOREIRA</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R144"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -3875,7 +3881,7 @@
         <v>28</v>
       </c>
       <c r="Q49" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -4267,7 +4273,7 @@
         <v>28</v>
       </c>
       <c r="Q56" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -5991,19 +5997,19 @@
         <v>46289</v>
       </c>
       <c r="M87">
-        <v>636005</v>
+        <v>625164</v>
       </c>
       <c r="N87" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O87">
         <v>29.19</v>
       </c>
       <c r="P87" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q87" t="s">
-        <v>28</v>
+        <v>264</v>
       </c>
       <c r="R87">
         <v>1</v>
@@ -6969,13 +6975,13 @@
         <v>210</v>
       </c>
       <c r="C105" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
       <c r="D105" t="s">
         <v>20</v>
       </c>
       <c r="E105" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F105" t="s">
         <v>22</v>
@@ -6999,22 +7005,22 @@
         <v>46296</v>
       </c>
       <c r="M105">
-        <v>625286</v>
+        <v>628039</v>
       </c>
       <c r="N105" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="O105">
-        <v>78.47</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="P105" t="s">
         <v>28</v>
       </c>
       <c r="Q105" t="s">
-        <v>250</v>
-      </c>
-      <c r="R105" t="e">
-        <v>#N/A</v>
+        <v>28</v>
+      </c>
+      <c r="R105">
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
@@ -7025,19 +7031,19 @@
         <v>211</v>
       </c>
       <c r="C106" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="D106" t="s">
         <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F106" t="s">
         <v>22</v>
       </c>
       <c r="G106" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H106" s="2">
         <v>1</v>
@@ -7055,16 +7061,16 @@
         <v>46296</v>
       </c>
       <c r="M106">
-        <v>628039</v>
+        <v>612265</v>
       </c>
       <c r="N106" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O106">
-        <v>4.3600000000000003</v>
+        <v>38.659999999999997</v>
       </c>
       <c r="P106" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q106" t="s">
         <v>28</v>
@@ -7081,19 +7087,19 @@
         <v>212</v>
       </c>
       <c r="C107" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
       <c r="D107" t="s">
         <v>20</v>
       </c>
       <c r="E107" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F107" t="s">
         <v>22</v>
       </c>
       <c r="G107" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H107" s="2">
         <v>1</v>
@@ -7111,16 +7117,16 @@
         <v>46296</v>
       </c>
       <c r="M107">
-        <v>612265</v>
+        <v>626295</v>
       </c>
       <c r="N107" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O107">
-        <v>38.659999999999997</v>
+        <v>15.06</v>
       </c>
       <c r="P107" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q107" t="s">
         <v>28</v>
@@ -7143,7 +7149,7 @@
         <v>20</v>
       </c>
       <c r="E108" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F108" t="s">
         <v>22</v>
@@ -7167,16 +7173,16 @@
         <v>46296</v>
       </c>
       <c r="M108">
-        <v>626295</v>
+        <v>627041</v>
       </c>
       <c r="N108" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O108">
-        <v>15.06</v>
+        <v>0</v>
       </c>
       <c r="P108" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Q108" t="s">
         <v>28</v>
@@ -7199,7 +7205,7 @@
         <v>20</v>
       </c>
       <c r="E109" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F109" t="s">
         <v>22</v>
@@ -7208,7 +7214,7 @@
         <v>195</v>
       </c>
       <c r="H109" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>183</v>
@@ -7220,19 +7226,19 @@
         <v>26</v>
       </c>
       <c r="L109" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="M109">
-        <v>627041</v>
+        <v>630590</v>
       </c>
       <c r="N109" t="s">
         <v>131</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>118.1</v>
       </c>
       <c r="P109" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q109" t="s">
         <v>28</v>
@@ -7243,10 +7249,10 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="B110" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C110" t="s">
         <v>193</v>
@@ -7255,13 +7261,13 @@
         <v>20</v>
       </c>
       <c r="E110" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="F110" t="s">
         <v>22</v>
       </c>
       <c r="G110" t="s">
-        <v>195</v>
+        <v>43</v>
       </c>
       <c r="H110" s="2">
         <v>6</v>
@@ -7279,16 +7285,16 @@
         <v>46301</v>
       </c>
       <c r="M110">
-        <v>630590</v>
+        <v>630717</v>
       </c>
       <c r="N110" t="s">
         <v>131</v>
       </c>
       <c r="O110">
-        <v>118.1</v>
+        <v>6.36</v>
       </c>
       <c r="P110" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="Q110" t="s">
         <v>28</v>
@@ -7299,28 +7305,28 @@
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>216</v>
+        <v>70</v>
       </c>
       <c r="B111" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="C111" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="D111" t="s">
         <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="F111" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G111" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="H111" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>183</v>
@@ -7332,22 +7338,22 @@
         <v>26</v>
       </c>
       <c r="L111" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="M111">
-        <v>630717</v>
+        <v>631043</v>
       </c>
       <c r="N111" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O111">
-        <v>6.36</v>
+        <v>14.23</v>
       </c>
       <c r="P111" t="s">
-        <v>251</v>
+        <v>28</v>
       </c>
       <c r="Q111" t="s">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="R111">
         <v>1</v>
@@ -7355,25 +7361,25 @@
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="B112" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="C112" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="D112" t="s">
         <v>20</v>
       </c>
       <c r="E112" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="F112" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G112" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="H112" s="2">
         <v>7</v>
@@ -7391,19 +7397,19 @@
         <v>46302</v>
       </c>
       <c r="M112">
-        <v>631043</v>
+        <v>631099</v>
       </c>
       <c r="N112" t="s">
         <v>44</v>
       </c>
       <c r="O112">
-        <v>14.23</v>
+        <v>0</v>
       </c>
       <c r="P112" t="s">
         <v>28</v>
       </c>
       <c r="Q112" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="R112">
         <v>1</v>
@@ -7411,7 +7417,7 @@
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B113" t="s">
         <v>219</v>
@@ -7423,7 +7429,7 @@
         <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F113" t="s">
         <v>22</v>
@@ -7447,19 +7453,19 @@
         <v>46302</v>
       </c>
       <c r="M113">
-        <v>631099</v>
+        <v>631115</v>
       </c>
       <c r="N113" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="P113" t="s">
         <v>28</v>
       </c>
       <c r="Q113" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="R113">
         <v>1</v>
@@ -7467,10 +7473,10 @@
     </row>
     <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B114" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C114" t="s">
         <v>193</v>
@@ -7479,16 +7485,16 @@
         <v>20</v>
       </c>
       <c r="E114" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F114" t="s">
         <v>22</v>
       </c>
       <c r="G114" t="s">
-        <v>43</v>
+        <v>195</v>
       </c>
       <c r="H114" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>183</v>
@@ -7500,16 +7506,16 @@
         <v>26</v>
       </c>
       <c r="L114" s="1">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="M114">
-        <v>631115</v>
+        <v>631302</v>
       </c>
       <c r="N114" t="s">
         <v>59</v>
       </c>
       <c r="O114">
-        <v>2.0499999999999998</v>
+        <v>3.34</v>
       </c>
       <c r="P114" t="s">
         <v>28</v>
@@ -7523,10 +7529,10 @@
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B115" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C115" t="s">
         <v>193</v>
@@ -7535,7 +7541,7 @@
         <v>20</v>
       </c>
       <c r="E115" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F115" t="s">
         <v>22</v>
@@ -7559,16 +7565,16 @@
         <v>46303</v>
       </c>
       <c r="M115">
-        <v>631302</v>
+        <v>635101</v>
       </c>
       <c r="N115" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="O115">
-        <v>3.34</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="P115" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q115" t="s">
         <v>28</v>
@@ -7579,28 +7585,28 @@
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>221</v>
+        <v>70</v>
       </c>
       <c r="B116" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="C116" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="D116" t="s">
         <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>225</v>
+        <v>146</v>
       </c>
       <c r="F116" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G116" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="H116" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>183</v>
@@ -7612,19 +7618,19 @@
         <v>26</v>
       </c>
       <c r="L116" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="M116">
-        <v>635101</v>
+        <v>631720</v>
       </c>
       <c r="N116" t="s">
         <v>131</v>
       </c>
       <c r="O116">
-        <v>4.1900000000000004</v>
+        <v>2.34</v>
       </c>
       <c r="P116" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q116" t="s">
         <v>28</v>
@@ -7635,10 +7641,10 @@
     </row>
     <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C117" t="s">
         <v>19</v>
@@ -7647,16 +7653,16 @@
         <v>20</v>
       </c>
       <c r="E117" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G117" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="H117" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>183</v>
@@ -7668,51 +7674,51 @@
         <v>26</v>
       </c>
       <c r="L117" s="1">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="M117">
-        <v>631720</v>
+        <v>632724</v>
       </c>
       <c r="N117" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O117">
-        <v>2.34</v>
+        <v>8.07</v>
       </c>
       <c r="P117" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q117" t="s">
-        <v>28</v>
-      </c>
-      <c r="R117">
-        <v>1</v>
+        <v>142</v>
+      </c>
+      <c r="R117" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="B118" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="C118" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="D118" t="s">
         <v>20</v>
       </c>
       <c r="E118" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="F118" t="s">
         <v>22</v>
       </c>
       <c r="G118" t="s">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="H118" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>183</v>
@@ -7724,25 +7730,25 @@
         <v>26</v>
       </c>
       <c r="L118" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="M118">
-        <v>632724</v>
+        <v>630814</v>
       </c>
       <c r="N118" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O118">
-        <v>8.07</v>
+        <v>7.53</v>
       </c>
       <c r="P118" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q118" t="s">
-        <v>142</v>
-      </c>
-      <c r="R118" t="e">
-        <v>#N/A</v>
+        <v>28</v>
+      </c>
+      <c r="R118">
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -7753,13 +7759,13 @@
         <v>226</v>
       </c>
       <c r="C119" t="s">
-        <v>193</v>
+        <v>49</v>
       </c>
       <c r="D119" t="s">
         <v>20</v>
       </c>
       <c r="E119" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="F119" t="s">
         <v>22</v>
@@ -7783,13 +7789,13 @@
         <v>46309</v>
       </c>
       <c r="M119">
-        <v>630814</v>
+        <v>627337</v>
       </c>
       <c r="N119" t="s">
         <v>131</v>
       </c>
       <c r="O119">
-        <v>7.53</v>
+        <v>80.19</v>
       </c>
       <c r="P119" t="s">
         <v>35</v>
@@ -7803,25 +7809,25 @@
     </row>
     <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>191</v>
+        <v>70</v>
       </c>
       <c r="B120" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="C120" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D120" t="s">
         <v>20</v>
       </c>
       <c r="E120" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="F120" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G120" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="H120" s="2">
         <v>14</v>
@@ -7839,16 +7845,16 @@
         <v>46309</v>
       </c>
       <c r="M120">
-        <v>627337</v>
+        <v>634211</v>
       </c>
       <c r="N120" t="s">
         <v>131</v>
       </c>
       <c r="O120">
-        <v>80.19</v>
+        <v>3.01</v>
       </c>
       <c r="P120" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q120" t="s">
         <v>28</v>
@@ -7862,7 +7868,7 @@
         <v>70</v>
       </c>
       <c r="B121" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C121" t="s">
         <v>19</v>
@@ -7877,7 +7883,7 @@
         <v>90</v>
       </c>
       <c r="G121" t="s">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="H121" s="2">
         <v>14</v>
@@ -7895,13 +7901,13 @@
         <v>46309</v>
       </c>
       <c r="M121">
-        <v>634211</v>
+        <v>634159</v>
       </c>
       <c r="N121" t="s">
         <v>131</v>
       </c>
       <c r="O121">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="P121" t="s">
         <v>55</v>
@@ -7915,28 +7921,28 @@
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="B122" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="C122" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="D122" t="s">
         <v>20</v>
       </c>
       <c r="E122" t="s">
-        <v>146</v>
+        <v>222</v>
       </c>
       <c r="F122" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G122" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="H122" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>183</v>
@@ -7948,30 +7954,30 @@
         <v>26</v>
       </c>
       <c r="L122" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="M122">
-        <v>634159</v>
+        <v>637667</v>
       </c>
       <c r="N122" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O122">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P122" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Q122" t="s">
-        <v>28</v>
-      </c>
-      <c r="R122">
-        <v>1</v>
+        <v>242</v>
+      </c>
+      <c r="R122" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="B123" t="s">
         <v>228</v>
@@ -7983,7 +7989,7 @@
         <v>20</v>
       </c>
       <c r="E123" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="F123" t="s">
         <v>22</v>
@@ -7992,7 +7998,7 @@
         <v>195</v>
       </c>
       <c r="H123" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>183</v>
@@ -8004,33 +8010,33 @@
         <v>26</v>
       </c>
       <c r="L123" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="M123">
-        <v>637667</v>
+        <v>635112</v>
       </c>
       <c r="N123" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>76.19</v>
       </c>
       <c r="P123" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="Q123" t="s">
-        <v>243</v>
-      </c>
-      <c r="R123" t="e">
-        <v>#N/A</v>
+        <v>28</v>
+      </c>
+      <c r="R123">
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="B124" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C124" t="s">
         <v>193</v>
@@ -8039,7 +8045,7 @@
         <v>20</v>
       </c>
       <c r="E124" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="F124" t="s">
         <v>22</v>
@@ -8048,7 +8054,7 @@
         <v>195</v>
       </c>
       <c r="H124" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>183</v>
@@ -8060,19 +8066,19 @@
         <v>26</v>
       </c>
       <c r="L124" s="1">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="M124">
-        <v>635112</v>
+        <v>637473</v>
       </c>
       <c r="N124" t="s">
         <v>131</v>
       </c>
       <c r="O124">
-        <v>76.19</v>
+        <v>85.98</v>
       </c>
       <c r="P124" t="s">
-        <v>206</v>
+        <v>35</v>
       </c>
       <c r="Q124" t="s">
         <v>28</v>
@@ -8083,10 +8089,10 @@
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B125" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C125" t="s">
         <v>193</v>
@@ -8095,13 +8101,13 @@
         <v>20</v>
       </c>
       <c r="E125" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="F125" t="s">
         <v>22</v>
       </c>
       <c r="G125" t="s">
-        <v>195</v>
+        <v>32</v>
       </c>
       <c r="H125" s="2">
         <v>20</v>
@@ -8119,13 +8125,13 @@
         <v>46315</v>
       </c>
       <c r="M125">
-        <v>637473</v>
+        <v>637657</v>
       </c>
       <c r="N125" t="s">
         <v>131</v>
       </c>
       <c r="O125">
-        <v>85.98</v>
+        <v>3.61</v>
       </c>
       <c r="P125" t="s">
         <v>35</v>
@@ -8139,7 +8145,7 @@
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B126" t="s">
         <v>235</v>
@@ -8151,13 +8157,13 @@
         <v>20</v>
       </c>
       <c r="E126" t="s">
-        <v>225</v>
+        <v>31</v>
       </c>
       <c r="F126" t="s">
         <v>22</v>
       </c>
       <c r="G126" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="H126" s="2">
         <v>20</v>
@@ -8175,13 +8181,13 @@
         <v>46315</v>
       </c>
       <c r="M126">
-        <v>637657</v>
+        <v>637739</v>
       </c>
       <c r="N126" t="s">
         <v>131</v>
       </c>
       <c r="O126">
-        <v>3.61</v>
+        <v>10.29</v>
       </c>
       <c r="P126" t="s">
         <v>35</v>
@@ -8195,28 +8201,28 @@
     </row>
     <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>221</v>
+        <v>70</v>
       </c>
       <c r="B127" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C127" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="D127" t="s">
         <v>20</v>
       </c>
       <c r="E127" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="F127" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G127" t="s">
-        <v>237</v>
+        <v>91</v>
       </c>
       <c r="H127" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>183</v>
@@ -8228,19 +8234,19 @@
         <v>26</v>
       </c>
       <c r="L127" s="1">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="M127">
-        <v>637739</v>
+        <v>637939</v>
       </c>
       <c r="N127" t="s">
         <v>131</v>
       </c>
       <c r="O127">
-        <v>10.29</v>
+        <v>43.16</v>
       </c>
       <c r="P127" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="Q127" t="s">
         <v>28</v>
@@ -8287,13 +8293,13 @@
         <v>46316</v>
       </c>
       <c r="M128">
-        <v>637939</v>
+        <v>638118</v>
       </c>
       <c r="N128" t="s">
         <v>131</v>
       </c>
       <c r="O128">
-        <v>43.16</v>
+        <v>43.4</v>
       </c>
       <c r="P128" t="s">
         <v>27</v>
@@ -8343,13 +8349,13 @@
         <v>46316</v>
       </c>
       <c r="M129">
-        <v>638118</v>
+        <v>637919</v>
       </c>
       <c r="N129" t="s">
         <v>131</v>
       </c>
       <c r="O129">
-        <v>43.4</v>
+        <v>4.38</v>
       </c>
       <c r="P129" t="s">
         <v>27</v>
@@ -8363,25 +8369,25 @@
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="B130" t="s">
         <v>240</v>
       </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="D130" t="s">
         <v>20</v>
       </c>
       <c r="E130" t="s">
-        <v>146</v>
+        <v>224</v>
       </c>
       <c r="F130" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G130" t="s">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="H130" s="2">
         <v>21</v>
@@ -8399,16 +8405,16 @@
         <v>46316</v>
       </c>
       <c r="M130">
-        <v>637919</v>
+        <v>641470</v>
       </c>
       <c r="N130" t="s">
         <v>131</v>
       </c>
       <c r="O130">
-        <v>4.38</v>
+        <v>12.34</v>
       </c>
       <c r="P130" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q130" t="s">
         <v>28</v>
@@ -8419,28 +8425,28 @@
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="B131" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C131" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="D131" t="s">
         <v>20</v>
       </c>
       <c r="E131" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="F131" t="s">
         <v>22</v>
       </c>
       <c r="G131" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H131" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>183</v>
@@ -8452,19 +8458,19 @@
         <v>26</v>
       </c>
       <c r="L131" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="M131">
-        <v>641470</v>
+        <v>587871</v>
       </c>
       <c r="N131" t="s">
         <v>131</v>
       </c>
       <c r="O131">
-        <v>12.34</v>
+        <v>35.64</v>
       </c>
       <c r="P131" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q131" t="s">
         <v>28</v>
@@ -8475,25 +8481,25 @@
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>191</v>
+        <v>70</v>
       </c>
       <c r="B132" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C132" t="s">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="D132" t="s">
         <v>20</v>
       </c>
       <c r="E132" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="F132" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G132" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H132" s="2">
         <v>22</v>
@@ -8511,16 +8517,16 @@
         <v>46317</v>
       </c>
       <c r="M132">
-        <v>587871</v>
+        <v>638510</v>
       </c>
       <c r="N132" t="s">
         <v>131</v>
       </c>
       <c r="O132">
-        <v>35.64</v>
+        <v>2.71</v>
       </c>
       <c r="P132" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="Q132" t="s">
         <v>28</v>
@@ -8531,25 +8537,25 @@
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="B133" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C133" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="D133" t="s">
         <v>20</v>
       </c>
       <c r="E133" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="F133" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G133" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="H133" s="2">
         <v>22</v>
@@ -8567,13 +8573,13 @@
         <v>46317</v>
       </c>
       <c r="M133">
-        <v>638510</v>
+        <v>638503</v>
       </c>
       <c r="N133" t="s">
         <v>131</v>
       </c>
       <c r="O133">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P133" t="s">
         <v>27</v>
@@ -8587,28 +8593,28 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>221</v>
+        <v>70</v>
       </c>
       <c r="B134" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C134" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="D134" t="s">
         <v>20</v>
       </c>
       <c r="E134" t="s">
-        <v>31</v>
+        <v>146</v>
       </c>
       <c r="F134" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G134" t="s">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="H134" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>183</v>
@@ -8620,16 +8626,16 @@
         <v>26</v>
       </c>
       <c r="L134" s="1">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="M134">
-        <v>638503</v>
+        <v>639513</v>
       </c>
       <c r="N134" t="s">
         <v>131</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P134" t="s">
         <v>27</v>
@@ -8646,7 +8652,7 @@
         <v>70</v>
       </c>
       <c r="B135" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C135" t="s">
         <v>19</v>
@@ -8679,13 +8685,13 @@
         <v>46318</v>
       </c>
       <c r="M135">
-        <v>639513</v>
+        <v>639446</v>
       </c>
       <c r="N135" t="s">
         <v>131</v>
       </c>
       <c r="O135">
-        <v>3.99</v>
+        <v>3.31</v>
       </c>
       <c r="P135" t="s">
         <v>27</v>
@@ -8699,28 +8705,28 @@
     </row>
     <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>70</v>
+        <v>191</v>
       </c>
       <c r="B136" t="s">
+        <v>252</v>
+      </c>
+      <c r="C136" t="s">
+        <v>193</v>
+      </c>
+      <c r="D136" t="s">
+        <v>20</v>
+      </c>
+      <c r="E136" t="s">
+        <v>205</v>
+      </c>
+      <c r="F136" t="s">
+        <v>22</v>
+      </c>
+      <c r="G136" t="s">
         <v>253</v>
       </c>
-      <c r="C136" t="s">
-        <v>19</v>
-      </c>
-      <c r="D136" t="s">
-        <v>20</v>
-      </c>
-      <c r="E136" t="s">
-        <v>146</v>
-      </c>
-      <c r="F136" t="s">
-        <v>90</v>
-      </c>
-      <c r="G136" t="s">
-        <v>104</v>
-      </c>
       <c r="H136" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>183</v>
@@ -8732,22 +8738,22 @@
         <v>26</v>
       </c>
       <c r="L136" s="1">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="M136">
-        <v>639446</v>
+        <v>640237</v>
       </c>
       <c r="N136" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="O136">
-        <v>3.31</v>
+        <v>3.78</v>
       </c>
       <c r="P136" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q136" t="s">
-        <v>28</v>
+        <v>254</v>
       </c>
       <c r="R136">
         <v>1</v>
@@ -8758,7 +8764,7 @@
         <v>191</v>
       </c>
       <c r="B137" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C137" t="s">
         <v>193</v>
@@ -8767,16 +8773,16 @@
         <v>20</v>
       </c>
       <c r="E137" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F137" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G137" t="s">
-        <v>255</v>
+        <v>91</v>
       </c>
       <c r="H137" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>183</v>
@@ -8788,22 +8794,22 @@
         <v>26</v>
       </c>
       <c r="L137" s="1">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="M137">
-        <v>640237</v>
+        <v>640462</v>
       </c>
       <c r="N137" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="O137">
-        <v>3.78</v>
+        <v>2.5</v>
       </c>
       <c r="P137" t="s">
-        <v>28</v>
+        <v>265</v>
       </c>
       <c r="Q137" t="s">
-        <v>256</v>
+        <v>28</v>
       </c>
       <c r="R137">
         <v>1</v>
@@ -8811,10 +8817,10 @@
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="B138" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C138" t="s">
         <v>193</v>
@@ -8823,13 +8829,13 @@
         <v>20</v>
       </c>
       <c r="E138" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="F138" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="G138" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="H138" s="2">
         <v>27</v>
@@ -8847,13 +8853,13 @@
         <v>46322</v>
       </c>
       <c r="M138">
-        <v>640462</v>
+        <v>641061</v>
       </c>
       <c r="N138" t="s">
         <v>131</v>
       </c>
       <c r="O138">
-        <v>2.5</v>
+        <v>5.34</v>
       </c>
       <c r="P138" t="s">
         <v>35</v>
@@ -8867,10 +8873,10 @@
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B139" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C139" t="s">
         <v>193</v>
@@ -8879,7 +8885,7 @@
         <v>20</v>
       </c>
       <c r="E139" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="F139" t="s">
         <v>22</v>
@@ -8902,17 +8908,17 @@
       <c r="L139" s="1">
         <v>46322</v>
       </c>
-      <c r="M139">
-        <v>641061</v>
+      <c r="M139" t="s">
+        <v>153</v>
       </c>
       <c r="N139" t="s">
-        <v>131</v>
-      </c>
-      <c r="O139">
-        <v>5.34</v>
+        <v>153</v>
+      </c>
+      <c r="O139" t="s">
+        <v>153</v>
       </c>
       <c r="P139" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="Q139" t="s">
         <v>28</v>
@@ -8923,28 +8929,28 @@
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>216</v>
+        <v>70</v>
       </c>
       <c r="B140" t="s">
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="D140" t="s">
         <v>20</v>
       </c>
       <c r="E140" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="F140" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G140" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="H140" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>183</v>
@@ -8956,19 +8962,19 @@
         <v>26</v>
       </c>
       <c r="L140" s="1">
-        <v>46322</v>
-      </c>
-      <c r="M140" t="s">
-        <v>153</v>
+        <v>46323</v>
+      </c>
+      <c r="M140">
+        <v>641279</v>
       </c>
       <c r="N140" t="s">
-        <v>153</v>
-      </c>
-      <c r="O140" t="s">
-        <v>153</v>
+        <v>131</v>
+      </c>
+      <c r="O140">
+        <v>3.34</v>
       </c>
       <c r="P140" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q140" t="s">
         <v>28</v>
@@ -8982,7 +8988,7 @@
         <v>70</v>
       </c>
       <c r="B141" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C141" t="s">
         <v>19</v>
@@ -8997,7 +9003,7 @@
         <v>90</v>
       </c>
       <c r="G141" t="s">
-        <v>104</v>
+        <v>247</v>
       </c>
       <c r="H141" s="2">
         <v>28</v>
@@ -9015,13 +9021,13 @@
         <v>46323</v>
       </c>
       <c r="M141">
-        <v>641279</v>
+        <v>641267</v>
       </c>
       <c r="N141" t="s">
         <v>131</v>
       </c>
       <c r="O141">
-        <v>3.34</v>
+        <v>9.19</v>
       </c>
       <c r="P141" t="s">
         <v>27</v>
@@ -9038,7 +9044,7 @@
         <v>70</v>
       </c>
       <c r="B142" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C142" t="s">
         <v>19</v>
@@ -9053,10 +9059,10 @@
         <v>90</v>
       </c>
       <c r="G142" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="H142" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>183</v>
@@ -9068,16 +9074,16 @@
         <v>26</v>
       </c>
       <c r="L142" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="M142">
-        <v>641267</v>
+        <v>641780</v>
       </c>
       <c r="N142" t="s">
         <v>131</v>
       </c>
       <c r="O142">
-        <v>9.19</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="P142" t="s">
         <v>27</v>
@@ -9085,31 +9091,31 @@
       <c r="Q142" t="s">
         <v>28</v>
       </c>
-      <c r="R142">
-        <v>1</v>
+      <c r="R142" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="B143" t="s">
+        <v>262</v>
+      </c>
+      <c r="C143" t="s">
+        <v>193</v>
+      </c>
+      <c r="D143" t="s">
+        <v>20</v>
+      </c>
+      <c r="E143" t="s">
+        <v>203</v>
+      </c>
+      <c r="F143" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143" t="s">
         <v>263</v>
-      </c>
-      <c r="C143" t="s">
-        <v>19</v>
-      </c>
-      <c r="D143" t="s">
-        <v>20</v>
-      </c>
-      <c r="E143" t="s">
-        <v>146</v>
-      </c>
-      <c r="F143" t="s">
-        <v>90</v>
-      </c>
-      <c r="G143" t="s">
-        <v>91</v>
       </c>
       <c r="H143" s="2">
         <v>29</v>
@@ -9127,48 +9133,48 @@
         <v>46324</v>
       </c>
       <c r="M143">
-        <v>641780</v>
+        <v>641950</v>
       </c>
       <c r="N143" t="s">
         <v>131</v>
       </c>
       <c r="O143">
-        <v>4.9000000000000004</v>
+        <v>0</v>
       </c>
       <c r="P143" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="Q143" t="s">
         <v>28</v>
       </c>
-      <c r="R143" t="e">
-        <v>#N/A</v>
+      <c r="R143">
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>216</v>
+        <v>70</v>
       </c>
       <c r="B144" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C144" t="s">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="D144" t="s">
         <v>20</v>
       </c>
       <c r="E144" t="s">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="F144" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="G144" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="H144" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>183</v>
@@ -9180,24 +9186,80 @@
         <v>26</v>
       </c>
       <c r="L144" s="1">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="M144">
-        <v>641950</v>
+        <v>641841</v>
       </c>
       <c r="N144" t="s">
         <v>131</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="P144" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="Q144" t="s">
         <v>28</v>
       </c>
       <c r="R144" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>70</v>
+      </c>
+      <c r="B145" t="s">
+        <v>267</v>
+      </c>
+      <c r="C145" t="s">
+        <v>19</v>
+      </c>
+      <c r="D145" t="s">
+        <v>20</v>
+      </c>
+      <c r="E145" t="s">
+        <v>146</v>
+      </c>
+      <c r="F145" t="s">
+        <v>90</v>
+      </c>
+      <c r="G145" t="s">
+        <v>247</v>
+      </c>
+      <c r="H145" s="2">
+        <v>30</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L145" s="1">
+        <v>46325</v>
+      </c>
+      <c r="M145">
+        <v>642724</v>
+      </c>
+      <c r="N145" t="s">
+        <v>131</v>
+      </c>
+      <c r="O145">
+        <v>3.21</v>
+      </c>
+      <c r="P145" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>28</v>
+      </c>
+      <c r="R145" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -10384,7 +10446,7 @@
         <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -10398,7 +10460,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -10412,7 +10474,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -10426,7 +10488,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -10440,7 +10502,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -10454,7 +10516,7 @@
         <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -10468,7 +10530,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -10482,7 +10544,7 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -10496,7 +10558,7 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -10510,7 +10572,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -10524,7 +10586,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -10538,7 +10600,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -10552,7 +10614,7 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -10560,13 +10622,13 @@
         <v>46296</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C14">
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -10574,13 +10636,13 @@
         <v>46296</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -10590,26 +10652,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -10870,26 +10912,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10906,4 +10949,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="312" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7ED296-5F35-46ED-A88F-B8FB63EA2383}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61F25435-DB69-456F-95E9-28E9BB14ECFE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="269">
   <si>
     <t>Usuário</t>
   </si>
@@ -839,13 +839,16 @@
     <t>SLA EXPIRADO</t>
   </si>
   <si>
-    <t>AJUSTE DE DOCUMENTAÇÃO</t>
-  </si>
-  <si>
     <t>FELIPE DA CUNHA SILVA</t>
   </si>
   <si>
     <t>ROMILDO DE ALMEIDA MOREIRA</t>
+  </si>
+  <si>
+    <t>FRANCISCO DANIELIO DE SOUZA</t>
+  </si>
+  <si>
+    <t>MARIA PEREIRA DE AMORIM DIAS</t>
   </si>
 </sst>
 </file>
@@ -1171,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R145"/>
+  <dimension ref="A1:R147"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -8016,13 +8019,13 @@
         <v>635112</v>
       </c>
       <c r="N123" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="O123">
         <v>76.19</v>
       </c>
       <c r="P123" t="s">
-        <v>206</v>
+        <v>28</v>
       </c>
       <c r="Q123" t="s">
         <v>28</v>
@@ -8078,7 +8081,7 @@
         <v>85.98</v>
       </c>
       <c r="P124" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q124" t="s">
         <v>28</v>
@@ -8582,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="P133" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q133" t="s">
         <v>28</v>
@@ -8803,10 +8806,10 @@
         <v>131</v>
       </c>
       <c r="O137">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P137" t="s">
-        <v>265</v>
+        <v>206</v>
       </c>
       <c r="Q137" t="s">
         <v>28</v>
@@ -8908,17 +8911,17 @@
       <c r="L139" s="1">
         <v>46322</v>
       </c>
-      <c r="M139" t="s">
-        <v>153</v>
+      <c r="M139">
+        <v>642731</v>
       </c>
       <c r="N139" t="s">
-        <v>153</v>
-      </c>
-      <c r="O139" t="s">
-        <v>153</v>
+        <v>131</v>
+      </c>
+      <c r="O139">
+        <v>29.33</v>
       </c>
       <c r="P139" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q139" t="s">
         <v>28</v>
@@ -9091,8 +9094,8 @@
       <c r="Q142" t="s">
         <v>28</v>
       </c>
-      <c r="R142" t="e">
-        <v>#N/A</v>
+      <c r="R142">
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:18" x14ac:dyDescent="0.25">
@@ -9156,7 +9159,7 @@
         <v>70</v>
       </c>
       <c r="B144" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C144" t="s">
         <v>19</v>
@@ -9203,8 +9206,8 @@
       <c r="Q144" t="s">
         <v>28</v>
       </c>
-      <c r="R144" t="e">
-        <v>#N/A</v>
+      <c r="R144">
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
@@ -9212,7 +9215,7 @@
         <v>70</v>
       </c>
       <c r="B145" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C145" t="s">
         <v>19</v>
@@ -9259,8 +9262,120 @@
       <c r="Q145" t="s">
         <v>28</v>
       </c>
-      <c r="R145" t="e">
-        <v>#N/A</v>
+      <c r="R145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>70</v>
+      </c>
+      <c r="B146" t="s">
+        <v>267</v>
+      </c>
+      <c r="C146" t="s">
+        <v>19</v>
+      </c>
+      <c r="D146" t="s">
+        <v>20</v>
+      </c>
+      <c r="E146" t="s">
+        <v>146</v>
+      </c>
+      <c r="F146" t="s">
+        <v>90</v>
+      </c>
+      <c r="G146" t="s">
+        <v>247</v>
+      </c>
+      <c r="H146" s="2">
+        <v>30</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L146" s="1">
+        <v>46325</v>
+      </c>
+      <c r="M146">
+        <v>642729</v>
+      </c>
+      <c r="N146" t="s">
+        <v>131</v>
+      </c>
+      <c r="O146">
+        <v>2.16</v>
+      </c>
+      <c r="P146" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>28</v>
+      </c>
+      <c r="R146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>70</v>
+      </c>
+      <c r="B147" t="s">
+        <v>268</v>
+      </c>
+      <c r="C147" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" t="s">
+        <v>20</v>
+      </c>
+      <c r="E147" t="s">
+        <v>146</v>
+      </c>
+      <c r="F147" t="s">
+        <v>90</v>
+      </c>
+      <c r="G147" t="s">
+        <v>247</v>
+      </c>
+      <c r="H147" s="2">
+        <v>30</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L147" s="1">
+        <v>46325</v>
+      </c>
+      <c r="M147">
+        <v>642735</v>
+      </c>
+      <c r="N147" t="s">
+        <v>131</v>
+      </c>
+      <c r="O147">
+        <v>2.11</v>
+      </c>
+      <c r="P147" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>28</v>
+      </c>
+      <c r="R147">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10652,6 +10767,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100419CAAB7BFEB5348884DC19A205C8B20" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="e8ef5911af915d28c7292ae157e2efd8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cefda5ab-fc9a-44ce-8da7-9655a4827298" xmlns:ns3="56aee56a-c72d-444c-b43d-3bc54f84985f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="511f4552cf11e197cd7177e190d492e7" ns2:_="" ns3:_="">
     <xsd:import namespace="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
@@ -10912,15 +11036,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10933,6 +11048,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF4860A-53D2-4527-8C6D-F1046CB80CC8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10951,14 +11074,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>

--- a/Base SDR Rua.xlsx
+++ b/Base SDR Rua.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energisa.sharepoint.com/sites/Dados_Alsol/Documentos Partilhados/COMERCIAL/COMERCIAL - ATUAL/GESTÃO SDR/Acompanhamento SDR/HTMLS Pablo/Materiais IA - Vai para o HTML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61F25435-DB69-456F-95E9-28E9BB14ECFE}"/>
+  <xr:revisionPtr revIDLastSave="322" documentId="13_ncr:1_{B58457A8-479C-46E5-89F0-901B80D41E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF423E29-6CFD-4A1A-AA92-0E6CE4C2E884}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6825,10 +6825,10 @@
         <v>91</v>
       </c>
       <c r="H102" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>25</v>
@@ -6837,7 +6837,7 @@
         <v>26</v>
       </c>
       <c r="L102" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="M102">
         <v>627870</v>
@@ -10767,12 +10767,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11037,20 +11039,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="56aee56a-c72d-444c-b43d-3bc54f84985f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cefda5ab-fc9a-44ce-8da7-9655a4827298">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
+    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11075,12 +11078,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5878A5-BB64-4B23-97F1-D9AADF889EA0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888B570D-AE5F-455B-8EF0-A1A1B2887A9F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56aee56a-c72d-444c-b43d-3bc54f84985f"/>
-    <ds:schemaRef ds:uri="cefda5ab-fc9a-44ce-8da7-9655a4827298"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>